--- a/data/CAP_Semana_12.xlsx
+++ b/data/CAP_Semana_12.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Relatório_Felipe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Relatório_Felipe\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4786722-23AB-4FFB-93ED-E66DE65181EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70285413-8C69-4042-85E1-4B506EA30FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2130" windowWidth="20640" windowHeight="11040" xr2:uid="{8D2EDE68-77A0-48FE-A03B-A2F0182CE2F6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="192">
   <si>
     <t>id</t>
   </si>
@@ -602,6 +602,21 @@
   </si>
   <si>
     <t>GRATIFICAÇÃO</t>
+  </si>
+  <si>
+    <t>TB EXPRESS - MICHAEL F DAMASCENO</t>
+  </si>
+  <si>
+    <t>DESPESA ADMINIST</t>
+  </si>
+  <si>
+    <t>CHAVE PIX CNPJ: 20395841000152 MICHAEL F. DAMASCENO</t>
+  </si>
+  <si>
+    <t>SABESP - BRUNO BALAGUER</t>
+  </si>
+  <si>
+    <t>82660000012 7 42300097091 7 11027649744 0 00002995373 4</t>
   </si>
 </sst>
 </file>
@@ -1301,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05925770-A8EB-4BF6-A793-5E873493123B}">
-  <dimension ref="A1:AX137"/>
+  <dimension ref="A1:AX139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -4997,27 +5012,27 @@
       <c r="AW48" s="35"/>
       <c r="AX48" s="35"/>
     </row>
-    <row r="49" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="26"/>
       <c r="B49" s="27">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="C49" s="27">
         <v>46097</v>
       </c>
       <c r="D49" s="28"/>
       <c r="E49" s="29" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="F49" s="28"/>
       <c r="G49" s="29" t="s">
         <v>52</v>
       </c>
       <c r="H49" s="29" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="I49" s="31">
-        <v>281</v>
+        <v>1445</v>
       </c>
       <c r="J49" s="29" t="b">
         <v>1</v>
@@ -5034,12 +5049,10 @@
       <c r="N49" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O49" s="29">
-        <v>8971143886</v>
-      </c>
-      <c r="P49" s="32" t="s">
-        <v>90</v>
-      </c>
+      <c r="O49" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="P49" s="33"/>
       <c r="Q49" s="33"/>
       <c r="R49" s="34"/>
       <c r="S49" s="34"/>
@@ -5078,33 +5091,33 @@
     <row r="50" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="26"/>
       <c r="B50" s="27">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="C50" s="27">
         <v>46097</v>
       </c>
       <c r="D50" s="28"/>
       <c r="E50" s="29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F50" s="28"/>
       <c r="G50" s="29" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="I50" s="31">
-        <v>50000</v>
+        <v>281</v>
       </c>
       <c r="J50" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K50" s="29" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="L50" s="29" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M50" s="29" t="s">
         <v>22</v>
@@ -5112,11 +5125,13 @@
       <c r="N50" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O50" s="28"/>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="O50" s="29">
+        <v>8971143886</v>
+      </c>
+      <c r="P50" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q50" s="33"/>
       <c r="R50" s="34"/>
       <c r="S50" s="34"/>
       <c r="T50" s="34"/>
@@ -5151,7 +5166,7 @@
       <c r="AW50" s="35"/>
       <c r="AX50" s="35"/>
     </row>
-    <row r="51" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="26"/>
       <c r="B51" s="27">
         <v>46079</v>
@@ -5161,26 +5176,26 @@
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="29" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F51" s="28"/>
       <c r="G51" s="29" t="s">
         <v>33</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="I51" s="31">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="J51" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K51" s="29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L51" s="29" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M51" s="29" t="s">
         <v>22</v>
@@ -5190,7 +5205,9 @@
       </c>
       <c r="O51" s="28"/>
       <c r="P51" s="33"/>
-      <c r="Q51" s="33"/>
+      <c r="Q51" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R51" s="34"/>
       <c r="S51" s="34"/>
       <c r="T51" s="34"/>
@@ -5226,167 +5243,161 @@
       <c r="AX51" s="35"/>
     </row>
     <row r="52" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="38"/>
-      <c r="N52" s="38"/>
-      <c r="O52" s="38"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="40"/>
-      <c r="S52" s="40"/>
-      <c r="T52" s="40"/>
-      <c r="U52" s="40"/>
-      <c r="V52" s="40"/>
-      <c r="W52" s="40"/>
-      <c r="X52" s="40"/>
-      <c r="Y52" s="40"/>
-      <c r="Z52" s="41"/>
-      <c r="AA52" s="41"/>
-      <c r="AB52" s="41"/>
-      <c r="AC52" s="41"/>
-      <c r="AD52" s="41"/>
-      <c r="AE52" s="41"/>
-      <c r="AF52" s="41"/>
-      <c r="AG52" s="41"/>
-      <c r="AH52" s="41"/>
-      <c r="AI52" s="41"/>
-      <c r="AJ52" s="41"/>
-      <c r="AK52" s="41"/>
-      <c r="AL52" s="41"/>
-      <c r="AM52" s="41"/>
-      <c r="AN52" s="41"/>
-      <c r="AO52" s="41"/>
-      <c r="AP52" s="41"/>
-      <c r="AQ52" s="41"/>
-      <c r="AR52" s="41"/>
-      <c r="AS52" s="41"/>
-      <c r="AT52" s="41"/>
-      <c r="AU52" s="41"/>
-      <c r="AV52" s="41"/>
-      <c r="AW52" s="41"/>
-      <c r="AX52" s="41"/>
-    </row>
-    <row r="53" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
-      <c r="B53" s="20">
+      <c r="A52" s="26"/>
+      <c r="B52" s="27">
         <v>46079</v>
       </c>
-      <c r="C53" s="20">
-        <v>46098</v>
-      </c>
-      <c r="D53" s="21"/>
-      <c r="E53" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="F53" s="21"/>
-      <c r="G53" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="I53" s="24">
-        <v>357721.76</v>
-      </c>
-      <c r="J53" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="L53" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N53" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O53" s="21"/>
-      <c r="P53" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q53" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="R53" s="17"/>
-      <c r="S53" s="17"/>
-      <c r="T53" s="17"/>
-      <c r="U53" s="17"/>
-      <c r="V53" s="17"/>
-      <c r="W53" s="17"/>
-      <c r="X53" s="17"/>
-      <c r="Y53" s="17"/>
-      <c r="Z53" s="18"/>
-      <c r="AA53" s="18"/>
-      <c r="AB53" s="18"/>
-      <c r="AC53" s="18"/>
-      <c r="AD53" s="18"/>
-      <c r="AE53" s="18"/>
-      <c r="AF53" s="18"/>
-      <c r="AG53" s="18"/>
-      <c r="AH53" s="18"/>
-      <c r="AI53" s="18"/>
-      <c r="AJ53" s="18"/>
-      <c r="AK53" s="18"/>
-      <c r="AL53" s="18"/>
-      <c r="AM53" s="18"/>
-      <c r="AN53" s="18"/>
-      <c r="AO53" s="18"/>
-      <c r="AP53" s="18"/>
-      <c r="AQ53" s="18"/>
-      <c r="AR53" s="18"/>
-      <c r="AS53" s="18"/>
-      <c r="AT53" s="18"/>
-      <c r="AU53" s="18"/>
-      <c r="AV53" s="18"/>
-      <c r="AW53" s="18"/>
-      <c r="AX53" s="18"/>
-    </row>
-    <row r="54" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="27">
+        <v>46097</v>
+      </c>
+      <c r="D52" s="28"/>
+      <c r="E52" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" s="28"/>
+      <c r="G52" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I52" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J52" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L52" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M52" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N52" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O52" s="28"/>
+      <c r="P52" s="33"/>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="34"/>
+      <c r="S52" s="34"/>
+      <c r="T52" s="34"/>
+      <c r="U52" s="34"/>
+      <c r="V52" s="34"/>
+      <c r="W52" s="34"/>
+      <c r="X52" s="34"/>
+      <c r="Y52" s="34"/>
+      <c r="Z52" s="35"/>
+      <c r="AA52" s="35"/>
+      <c r="AB52" s="35"/>
+      <c r="AC52" s="35"/>
+      <c r="AD52" s="35"/>
+      <c r="AE52" s="35"/>
+      <c r="AF52" s="35"/>
+      <c r="AG52" s="35"/>
+      <c r="AH52" s="35"/>
+      <c r="AI52" s="35"/>
+      <c r="AJ52" s="35"/>
+      <c r="AK52" s="35"/>
+      <c r="AL52" s="35"/>
+      <c r="AM52" s="35"/>
+      <c r="AN52" s="35"/>
+      <c r="AO52" s="35"/>
+      <c r="AP52" s="35"/>
+      <c r="AQ52" s="35"/>
+      <c r="AR52" s="35"/>
+      <c r="AS52" s="35"/>
+      <c r="AT52" s="35"/>
+      <c r="AU52" s="35"/>
+      <c r="AV52" s="35"/>
+      <c r="AW52" s="35"/>
+      <c r="AX52" s="35"/>
+    </row>
+    <row r="53" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="37"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="38"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="39"/>
+      <c r="Q53" s="39"/>
+      <c r="R53" s="40"/>
+      <c r="S53" s="40"/>
+      <c r="T53" s="40"/>
+      <c r="U53" s="40"/>
+      <c r="V53" s="40"/>
+      <c r="W53" s="40"/>
+      <c r="X53" s="40"/>
+      <c r="Y53" s="40"/>
+      <c r="Z53" s="41"/>
+      <c r="AA53" s="41"/>
+      <c r="AB53" s="41"/>
+      <c r="AC53" s="41"/>
+      <c r="AD53" s="41"/>
+      <c r="AE53" s="41"/>
+      <c r="AF53" s="41"/>
+      <c r="AG53" s="41"/>
+      <c r="AH53" s="41"/>
+      <c r="AI53" s="41"/>
+      <c r="AJ53" s="41"/>
+      <c r="AK53" s="41"/>
+      <c r="AL53" s="41"/>
+      <c r="AM53" s="41"/>
+      <c r="AN53" s="41"/>
+      <c r="AO53" s="41"/>
+      <c r="AP53" s="41"/>
+      <c r="AQ53" s="41"/>
+      <c r="AR53" s="41"/>
+      <c r="AS53" s="41"/>
+      <c r="AT53" s="41"/>
+      <c r="AU53" s="41"/>
+      <c r="AV53" s="41"/>
+      <c r="AW53" s="41"/>
+      <c r="AX53" s="41"/>
+    </row>
+    <row r="54" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19"/>
       <c r="B54" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C54" s="20">
         <v>46098</v>
       </c>
       <c r="D54" s="21"/>
       <c r="E54" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="F54" s="23">
-        <v>9748</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F54" s="21"/>
       <c r="G54" s="22" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="I54" s="24">
-        <v>1700</v>
+        <v>357721.76</v>
       </c>
       <c r="J54" s="22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="22" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="L54" s="22" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M54" s="22" t="s">
         <v>22</v>
@@ -5395,8 +5406,12 @@
         <v>23</v>
       </c>
       <c r="O54" s="21"/>
-      <c r="P54" s="25"/>
-      <c r="Q54" s="25"/>
+      <c r="P54" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q54" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="17"/>
       <c r="S54" s="17"/>
       <c r="T54" s="17"/>
@@ -5434,26 +5449,26 @@
     <row r="55" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19"/>
       <c r="B55" s="20">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C55" s="20">
         <v>46098</v>
       </c>
       <c r="D55" s="21"/>
       <c r="E55" s="22" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="F55" s="23">
-        <v>538</v>
+        <v>9748</v>
       </c>
       <c r="G55" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I55" s="24">
-        <v>1905</v>
+        <v>1700</v>
       </c>
       <c r="J55" s="22" t="b">
         <v>1</v>
@@ -5462,7 +5477,7 @@
         <v>20</v>
       </c>
       <c r="L55" s="22" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M55" s="22" t="s">
         <v>22</v>
@@ -5510,26 +5525,26 @@
     <row r="56" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19"/>
       <c r="B56" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C56" s="20">
         <v>46098</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="22" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F56" s="23">
-        <v>268673</v>
+        <v>538</v>
       </c>
       <c r="G56" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I56" s="24">
-        <v>10752.15</v>
+        <v>1905</v>
       </c>
       <c r="J56" s="22" t="b">
         <v>1</v>
@@ -5593,19 +5608,19 @@
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F57" s="23">
-        <v>7913</v>
+        <v>268673</v>
       </c>
       <c r="G57" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I57" s="24">
-        <v>7892.43</v>
+        <v>10752.15</v>
       </c>
       <c r="J57" s="22" t="b">
         <v>1</v>
@@ -5669,19 +5684,19 @@
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F58" s="23">
-        <v>361471</v>
+        <v>7913</v>
       </c>
       <c r="G58" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="I58" s="24">
-        <v>4750</v>
+        <v>7892.43</v>
       </c>
       <c r="J58" s="22" t="b">
         <v>1</v>
@@ -5735,111 +5750,109 @@
       <c r="AW58" s="18"/>
       <c r="AX58" s="18"/>
     </row>
-    <row r="59" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="26"/>
-      <c r="B59" s="27">
-        <v>46078</v>
-      </c>
-      <c r="C59" s="27">
+    <row r="59" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="19"/>
+      <c r="B59" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C59" s="20">
         <v>46098</v>
       </c>
-      <c r="D59" s="28"/>
-      <c r="E59" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="28"/>
-      <c r="G59" s="29" t="s">
+      <c r="D59" s="21"/>
+      <c r="E59" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F59" s="23">
+        <v>361471</v>
+      </c>
+      <c r="G59" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H59" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I59" s="31">
-        <v>3000</v>
-      </c>
-      <c r="J59" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K59" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M59" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N59" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O59" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P59" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q59" s="33"/>
-      <c r="R59" s="34"/>
-      <c r="S59" s="34"/>
-      <c r="T59" s="34"/>
-      <c r="U59" s="34"/>
-      <c r="V59" s="34"/>
-      <c r="W59" s="34"/>
-      <c r="X59" s="34"/>
-      <c r="Y59" s="34"/>
-      <c r="Z59" s="35"/>
-      <c r="AA59" s="35"/>
-      <c r="AB59" s="35"/>
-      <c r="AC59" s="35"/>
-      <c r="AD59" s="35"/>
-      <c r="AE59" s="35"/>
-      <c r="AF59" s="35"/>
-      <c r="AG59" s="35"/>
-      <c r="AH59" s="35"/>
-      <c r="AI59" s="35"/>
-      <c r="AJ59" s="35"/>
-      <c r="AK59" s="35"/>
-      <c r="AL59" s="35"/>
-      <c r="AM59" s="35"/>
-      <c r="AN59" s="35"/>
-      <c r="AO59" s="35"/>
-      <c r="AP59" s="35"/>
-      <c r="AQ59" s="35"/>
-      <c r="AR59" s="35"/>
-      <c r="AS59" s="35"/>
-      <c r="AT59" s="35"/>
-      <c r="AU59" s="35"/>
-      <c r="AV59" s="35"/>
-      <c r="AW59" s="35"/>
-      <c r="AX59" s="35"/>
-    </row>
-    <row r="60" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H59" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="I59" s="24">
+        <v>4750</v>
+      </c>
+      <c r="J59" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L59" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N59" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O59" s="21"/>
+      <c r="P59" s="25"/>
+      <c r="Q59" s="25"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="17"/>
+      <c r="V59" s="17"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="17"/>
+      <c r="Z59" s="18"/>
+      <c r="AA59" s="18"/>
+      <c r="AB59" s="18"/>
+      <c r="AC59" s="18"/>
+      <c r="AD59" s="18"/>
+      <c r="AE59" s="18"/>
+      <c r="AF59" s="18"/>
+      <c r="AG59" s="18"/>
+      <c r="AH59" s="18"/>
+      <c r="AI59" s="18"/>
+      <c r="AJ59" s="18"/>
+      <c r="AK59" s="18"/>
+      <c r="AL59" s="18"/>
+      <c r="AM59" s="18"/>
+      <c r="AN59" s="18"/>
+      <c r="AO59" s="18"/>
+      <c r="AP59" s="18"/>
+      <c r="AQ59" s="18"/>
+      <c r="AR59" s="18"/>
+      <c r="AS59" s="18"/>
+      <c r="AT59" s="18"/>
+      <c r="AU59" s="18"/>
+      <c r="AV59" s="18"/>
+      <c r="AW59" s="18"/>
+      <c r="AX59" s="18"/>
+    </row>
+    <row r="60" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="26"/>
       <c r="B60" s="27">
-        <v>46091</v>
+        <v>46078</v>
       </c>
       <c r="C60" s="27">
         <v>46098</v>
       </c>
       <c r="D60" s="28"/>
       <c r="E60" s="29" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="F60" s="28"/>
       <c r="G60" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H60" s="29" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="I60" s="31">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="J60" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K60" s="29" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L60" s="29" t="s">
         <v>27</v>
@@ -5850,11 +5863,13 @@
       <c r="N60" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O60" s="28"/>
-      <c r="P60" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q60" s="28"/>
+      <c r="O60" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="P60" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q60" s="33"/>
       <c r="R60" s="34"/>
       <c r="S60" s="34"/>
       <c r="T60" s="34"/>
@@ -5889,29 +5904,27 @@
       <c r="AW60" s="35"/>
       <c r="AX60" s="35"/>
     </row>
-    <row r="61" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="26"/>
       <c r="B61" s="27">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C61" s="27">
         <v>46098</v>
       </c>
       <c r="D61" s="28"/>
       <c r="E61" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="F61" s="30">
-        <v>6173</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="F61" s="28"/>
       <c r="G61" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H61" s="29" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="I61" s="31">
-        <v>1099.17</v>
+        <v>3800</v>
       </c>
       <c r="J61" s="29" t="b">
         <v>1</v>
@@ -5929,7 +5942,9 @@
         <v>28</v>
       </c>
       <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
+      <c r="P61" s="42" t="s">
+        <v>106</v>
+      </c>
       <c r="Q61" s="28"/>
       <c r="R61" s="34"/>
       <c r="S61" s="34"/>
@@ -5977,8 +5992,8 @@
       <c r="E62" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F62" s="30" t="s">
-        <v>108</v>
+      <c r="F62" s="30">
+        <v>6173</v>
       </c>
       <c r="G62" s="29" t="s">
         <v>18</v>
@@ -5987,7 +6002,7 @@
         <v>80</v>
       </c>
       <c r="I62" s="31">
-        <v>8458.83</v>
+        <v>1099.17</v>
       </c>
       <c r="J62" s="29" t="b">
         <v>1</v>
@@ -6053,8 +6068,8 @@
       <c r="E63" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F63" s="30">
-        <v>6172</v>
+      <c r="F63" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="G63" s="29" t="s">
         <v>18</v>
@@ -6063,7 +6078,7 @@
         <v>80</v>
       </c>
       <c r="I63" s="31">
-        <v>1494.4</v>
+        <v>8458.83</v>
       </c>
       <c r="J63" s="29" t="b">
         <v>1</v>
@@ -6129,8 +6144,8 @@
       <c r="E64" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F64" s="30" t="s">
-        <v>109</v>
+      <c r="F64" s="30">
+        <v>6172</v>
       </c>
       <c r="G64" s="29" t="s">
         <v>18</v>
@@ -6139,7 +6154,7 @@
         <v>80</v>
       </c>
       <c r="I64" s="31">
-        <v>11500.4</v>
+        <v>1494.4</v>
       </c>
       <c r="J64" s="29" t="b">
         <v>1</v>
@@ -6205,8 +6220,8 @@
       <c r="E65" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F65" s="30">
-        <v>6175</v>
+      <c r="F65" s="30" t="s">
+        <v>109</v>
       </c>
       <c r="G65" s="29" t="s">
         <v>18</v>
@@ -6215,13 +6230,13 @@
         <v>80</v>
       </c>
       <c r="I65" s="31">
-        <v>1055.76</v>
+        <v>11500.4</v>
       </c>
       <c r="J65" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K65" s="29" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="L65" s="29" t="s">
         <v>27</v>
@@ -6281,8 +6296,8 @@
       <c r="E66" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F66" s="30" t="s">
-        <v>111</v>
+      <c r="F66" s="30">
+        <v>6175</v>
       </c>
       <c r="G66" s="29" t="s">
         <v>18</v>
@@ -6291,7 +6306,7 @@
         <v>80</v>
       </c>
       <c r="I66" s="31">
-        <v>8124.74</v>
+        <v>1055.76</v>
       </c>
       <c r="J66" s="29" t="b">
         <v>1</v>
@@ -6348,7 +6363,7 @@
     <row r="67" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="26"/>
       <c r="B67" s="27">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C67" s="27">
         <v>46098</v>
@@ -6357,8 +6372,8 @@
       <c r="E67" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F67" s="30">
-        <v>6174</v>
+      <c r="F67" s="30" t="s">
+        <v>111</v>
       </c>
       <c r="G67" s="29" t="s">
         <v>18</v>
@@ -6367,7 +6382,7 @@
         <v>80</v>
       </c>
       <c r="I67" s="31">
-        <v>2946.3</v>
+        <v>8124.74</v>
       </c>
       <c r="J67" s="29" t="b">
         <v>1</v>
@@ -6433,8 +6448,8 @@
       <c r="E68" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="30" t="s">
-        <v>112</v>
+      <c r="F68" s="30">
+        <v>6174</v>
       </c>
       <c r="G68" s="29" t="s">
         <v>18</v>
@@ -6443,7 +6458,7 @@
         <v>80</v>
       </c>
       <c r="I68" s="31">
-        <v>22973.7</v>
+        <v>2946.3</v>
       </c>
       <c r="J68" s="29" t="b">
         <v>1</v>
@@ -6497,33 +6512,35 @@
       <c r="AW68" s="35"/>
       <c r="AX68" s="35"/>
     </row>
-    <row r="69" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="26"/>
       <c r="B69" s="27">
-        <v>46092</v>
+        <v>46084</v>
       </c>
       <c r="C69" s="27">
         <v>46098</v>
       </c>
       <c r="D69" s="28"/>
       <c r="E69" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="F69" s="28"/>
+        <v>107</v>
+      </c>
+      <c r="F69" s="30" t="s">
+        <v>112</v>
+      </c>
       <c r="G69" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H69" s="29" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="I69" s="31">
-        <v>17607.77</v>
+        <v>22973.7</v>
       </c>
       <c r="J69" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K69" s="29" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="L69" s="29" t="s">
         <v>27</v>
@@ -6535,9 +6552,7 @@
         <v>28</v>
       </c>
       <c r="O69" s="28"/>
-      <c r="P69" s="42" t="s">
-        <v>83</v>
-      </c>
+      <c r="P69" s="28"/>
       <c r="Q69" s="28"/>
       <c r="R69" s="34"/>
       <c r="S69" s="34"/>
@@ -6576,30 +6591,30 @@
     <row r="70" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="26"/>
       <c r="B70" s="27">
-        <v>46079</v>
+        <v>46092</v>
       </c>
       <c r="C70" s="27">
         <v>46098</v>
       </c>
       <c r="D70" s="28"/>
       <c r="E70" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F70" s="28"/>
       <c r="G70" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H70" s="29" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I70" s="31">
-        <v>34692</v>
+        <v>17607.77</v>
       </c>
       <c r="J70" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K70" s="29" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="L70" s="29" t="s">
         <v>27</v>
@@ -6612,7 +6627,7 @@
       </c>
       <c r="O70" s="28"/>
       <c r="P70" s="42" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="Q70" s="28"/>
       <c r="R70" s="34"/>
@@ -6669,7 +6684,7 @@
         <v>25</v>
       </c>
       <c r="I71" s="31">
-        <v>33600</v>
+        <v>34692</v>
       </c>
       <c r="J71" s="29" t="b">
         <v>1</v>
@@ -6688,7 +6703,7 @@
       </c>
       <c r="O71" s="28"/>
       <c r="P71" s="42" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Q71" s="28"/>
       <c r="R71" s="34"/>
@@ -6725,7 +6740,7 @@
       <c r="AW71" s="35"/>
       <c r="AX71" s="35"/>
     </row>
-    <row r="72" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="26"/>
       <c r="B72" s="27">
         <v>46079</v>
@@ -6735,17 +6750,17 @@
       </c>
       <c r="D72" s="28"/>
       <c r="E72" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F72" s="28"/>
       <c r="G72" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H72" s="29" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="I72" s="31">
-        <v>19602</v>
+        <v>33600</v>
       </c>
       <c r="J72" s="29" t="b">
         <v>1</v>
@@ -6763,10 +6778,10 @@
         <v>28</v>
       </c>
       <c r="O72" s="28"/>
-      <c r="P72" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q72" s="33"/>
+      <c r="P72" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q72" s="28"/>
       <c r="R72" s="34"/>
       <c r="S72" s="34"/>
       <c r="T72" s="34"/>
@@ -6804,7 +6819,7 @@
     <row r="73" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="26"/>
       <c r="B73" s="27">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C73" s="27">
         <v>46098</v>
@@ -6821,7 +6836,7 @@
         <v>80</v>
       </c>
       <c r="I73" s="31">
-        <v>4003.16</v>
+        <v>19602</v>
       </c>
       <c r="J73" s="29" t="b">
         <v>1</v>
@@ -6840,7 +6855,7 @@
       </c>
       <c r="O73" s="28"/>
       <c r="P73" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q73" s="33"/>
       <c r="R73" s="34"/>
@@ -6897,7 +6912,7 @@
         <v>80</v>
       </c>
       <c r="I74" s="31">
-        <v>5166.72</v>
+        <v>4003.16</v>
       </c>
       <c r="J74" s="29" t="b">
         <v>1</v>
@@ -6916,7 +6931,7 @@
       </c>
       <c r="O74" s="28"/>
       <c r="P74" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q74" s="33"/>
       <c r="R74" s="34"/>
@@ -6953,33 +6968,33 @@
       <c r="AW74" s="35"/>
       <c r="AX74" s="35"/>
     </row>
-    <row r="75" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="26"/>
       <c r="B75" s="27">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C75" s="27">
         <v>46098</v>
       </c>
       <c r="D75" s="28"/>
       <c r="E75" s="29" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="F75" s="28"/>
       <c r="G75" s="29" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H75" s="29" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I75" s="31">
-        <v>20000</v>
+        <v>5166.72</v>
       </c>
       <c r="J75" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K75" s="29" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="L75" s="29" t="s">
         <v>27</v>
@@ -6991,7 +7006,9 @@
         <v>28</v>
       </c>
       <c r="O75" s="28"/>
-      <c r="P75" s="33"/>
+      <c r="P75" s="9" t="s">
+        <v>118</v>
+      </c>
       <c r="Q75" s="33"/>
       <c r="R75" s="34"/>
       <c r="S75" s="34"/>
@@ -7028,132 +7045,130 @@
       <c r="AX75" s="35"/>
     </row>
     <row r="76" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
-      <c r="B76" s="38"/>
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
-      <c r="L76" s="38"/>
-      <c r="M76" s="38"/>
-      <c r="N76" s="38"/>
-      <c r="O76" s="38"/>
-      <c r="P76" s="39"/>
-      <c r="Q76" s="39"/>
-      <c r="R76" s="40"/>
-      <c r="S76" s="40"/>
-      <c r="T76" s="40"/>
-      <c r="U76" s="40"/>
-      <c r="V76" s="40"/>
-      <c r="W76" s="40"/>
-      <c r="X76" s="40"/>
-      <c r="Y76" s="40"/>
-      <c r="Z76" s="41"/>
-      <c r="AA76" s="41"/>
-      <c r="AB76" s="41"/>
-      <c r="AC76" s="41"/>
-      <c r="AD76" s="41"/>
-      <c r="AE76" s="41"/>
-      <c r="AF76" s="41"/>
-      <c r="AG76" s="41"/>
-      <c r="AH76" s="41"/>
-      <c r="AI76" s="41"/>
-      <c r="AJ76" s="41"/>
-      <c r="AK76" s="41"/>
-      <c r="AL76" s="41"/>
-      <c r="AM76" s="41"/>
-      <c r="AN76" s="41"/>
-      <c r="AO76" s="41"/>
-      <c r="AP76" s="41"/>
-      <c r="AQ76" s="41"/>
-      <c r="AR76" s="41"/>
-      <c r="AS76" s="41"/>
-      <c r="AT76" s="41"/>
-      <c r="AU76" s="41"/>
-      <c r="AV76" s="41"/>
-      <c r="AW76" s="41"/>
-      <c r="AX76" s="41"/>
+      <c r="A76" s="26"/>
+      <c r="B76" s="27">
+        <v>46079</v>
+      </c>
+      <c r="C76" s="27">
+        <v>46098</v>
+      </c>
+      <c r="D76" s="28"/>
+      <c r="E76" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F76" s="28"/>
+      <c r="G76" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H76" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I76" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J76" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K76" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L76" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M76" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N76" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O76" s="28"/>
+      <c r="P76" s="33"/>
+      <c r="Q76" s="33"/>
+      <c r="R76" s="34"/>
+      <c r="S76" s="34"/>
+      <c r="T76" s="34"/>
+      <c r="U76" s="34"/>
+      <c r="V76" s="34"/>
+      <c r="W76" s="34"/>
+      <c r="X76" s="34"/>
+      <c r="Y76" s="34"/>
+      <c r="Z76" s="35"/>
+      <c r="AA76" s="35"/>
+      <c r="AB76" s="35"/>
+      <c r="AC76" s="35"/>
+      <c r="AD76" s="35"/>
+      <c r="AE76" s="35"/>
+      <c r="AF76" s="35"/>
+      <c r="AG76" s="35"/>
+      <c r="AH76" s="35"/>
+      <c r="AI76" s="35"/>
+      <c r="AJ76" s="35"/>
+      <c r="AK76" s="35"/>
+      <c r="AL76" s="35"/>
+      <c r="AM76" s="35"/>
+      <c r="AN76" s="35"/>
+      <c r="AO76" s="35"/>
+      <c r="AP76" s="35"/>
+      <c r="AQ76" s="35"/>
+      <c r="AR76" s="35"/>
+      <c r="AS76" s="35"/>
+      <c r="AT76" s="35"/>
+      <c r="AU76" s="35"/>
+      <c r="AV76" s="35"/>
+      <c r="AW76" s="35"/>
+      <c r="AX76" s="35"/>
     </row>
     <row r="77" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="19"/>
-      <c r="B77" s="20">
-        <v>46079</v>
-      </c>
-      <c r="C77" s="20">
-        <v>46099</v>
-      </c>
-      <c r="D77" s="21"/>
-      <c r="E77" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="F77" s="23">
-        <v>388534</v>
-      </c>
-      <c r="G77" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H77" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="I77" s="24">
-        <v>24497.55</v>
-      </c>
-      <c r="J77" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K77" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L77" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N77" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O77" s="21"/>
-      <c r="P77" s="25"/>
-      <c r="Q77" s="25"/>
-      <c r="R77" s="17"/>
-      <c r="S77" s="17"/>
-      <c r="T77" s="17"/>
-      <c r="U77" s="17"/>
-      <c r="V77" s="17"/>
-      <c r="W77" s="17"/>
-      <c r="X77" s="17"/>
-      <c r="Y77" s="17"/>
-      <c r="Z77" s="18"/>
-      <c r="AA77" s="18"/>
-      <c r="AB77" s="18"/>
-      <c r="AC77" s="18"/>
-      <c r="AD77" s="18"/>
-      <c r="AE77" s="18"/>
-      <c r="AF77" s="18"/>
-      <c r="AG77" s="18"/>
-      <c r="AH77" s="18"/>
-      <c r="AI77" s="18"/>
-      <c r="AJ77" s="18"/>
-      <c r="AK77" s="18"/>
-      <c r="AL77" s="18"/>
-      <c r="AM77" s="18"/>
-      <c r="AN77" s="18"/>
-      <c r="AO77" s="18"/>
-      <c r="AP77" s="18"/>
-      <c r="AQ77" s="18"/>
-      <c r="AR77" s="18"/>
-      <c r="AS77" s="18"/>
-      <c r="AT77" s="18"/>
-      <c r="AU77" s="18"/>
-      <c r="AV77" s="18"/>
-      <c r="AW77" s="18"/>
-      <c r="AX77" s="18"/>
+      <c r="A77" s="37"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="38"/>
+      <c r="K77" s="38"/>
+      <c r="L77" s="38"/>
+      <c r="M77" s="38"/>
+      <c r="N77" s="38"/>
+      <c r="O77" s="38"/>
+      <c r="P77" s="39"/>
+      <c r="Q77" s="39"/>
+      <c r="R77" s="40"/>
+      <c r="S77" s="40"/>
+      <c r="T77" s="40"/>
+      <c r="U77" s="40"/>
+      <c r="V77" s="40"/>
+      <c r="W77" s="40"/>
+      <c r="X77" s="40"/>
+      <c r="Y77" s="40"/>
+      <c r="Z77" s="41"/>
+      <c r="AA77" s="41"/>
+      <c r="AB77" s="41"/>
+      <c r="AC77" s="41"/>
+      <c r="AD77" s="41"/>
+      <c r="AE77" s="41"/>
+      <c r="AF77" s="41"/>
+      <c r="AG77" s="41"/>
+      <c r="AH77" s="41"/>
+      <c r="AI77" s="41"/>
+      <c r="AJ77" s="41"/>
+      <c r="AK77" s="41"/>
+      <c r="AL77" s="41"/>
+      <c r="AM77" s="41"/>
+      <c r="AN77" s="41"/>
+      <c r="AO77" s="41"/>
+      <c r="AP77" s="41"/>
+      <c r="AQ77" s="41"/>
+      <c r="AR77" s="41"/>
+      <c r="AS77" s="41"/>
+      <c r="AT77" s="41"/>
+      <c r="AU77" s="41"/>
+      <c r="AV77" s="41"/>
+      <c r="AW77" s="41"/>
+      <c r="AX77" s="41"/>
     </row>
     <row r="78" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19"/>
@@ -7165,10 +7180,10 @@
       </c>
       <c r="D78" s="21"/>
       <c r="E78" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F78" s="23">
-        <v>60375</v>
+        <v>388534</v>
       </c>
       <c r="G78" s="22" t="s">
         <v>18</v>
@@ -7177,7 +7192,7 @@
         <v>25</v>
       </c>
       <c r="I78" s="24">
-        <v>855</v>
+        <v>24497.55</v>
       </c>
       <c r="J78" s="22" t="b">
         <v>1</v>
@@ -7241,19 +7256,19 @@
       </c>
       <c r="D79" s="21"/>
       <c r="E79" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F79" s="23">
-        <v>28133</v>
+        <v>60375</v>
       </c>
       <c r="G79" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="I79" s="24">
-        <v>477.75</v>
+        <v>855</v>
       </c>
       <c r="J79" s="22" t="b">
         <v>1</v>
@@ -7317,19 +7332,19 @@
       </c>
       <c r="D80" s="21"/>
       <c r="E80" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F80" s="23">
-        <v>17703</v>
+        <v>28133</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H80" s="22" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I80" s="24">
-        <v>721.7</v>
+        <v>477.75</v>
       </c>
       <c r="J80" s="22" t="b">
         <v>1</v>
@@ -7386,26 +7401,26 @@
     <row r="81" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="19"/>
       <c r="B81" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C81" s="20">
         <v>46099</v>
       </c>
       <c r="D81" s="21"/>
       <c r="E81" s="22" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="F81" s="23">
-        <v>30520</v>
+        <v>17703</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I81" s="24">
-        <v>4214.67</v>
+        <v>721.7</v>
       </c>
       <c r="J81" s="22" t="b">
         <v>1</v>
@@ -7459,113 +7474,109 @@
       <c r="AW81" s="18"/>
       <c r="AX81" s="18"/>
     </row>
-    <row r="82" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="26"/>
-      <c r="B82" s="27">
-        <v>46079</v>
-      </c>
-      <c r="C82" s="27">
+    <row r="82" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="19"/>
+      <c r="B82" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C82" s="20">
         <v>46099</v>
       </c>
-      <c r="D82" s="28"/>
-      <c r="E82" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="F82" s="28"/>
-      <c r="G82" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="H82" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="I82" s="31">
-        <v>48000</v>
-      </c>
-      <c r="J82" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K82" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="L82" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M82" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N82" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O82" s="28"/>
-      <c r="P82" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q82" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R82" s="34"/>
-      <c r="S82" s="34"/>
-      <c r="T82" s="34"/>
-      <c r="U82" s="34"/>
-      <c r="V82" s="34"/>
-      <c r="W82" s="34"/>
-      <c r="X82" s="34"/>
-      <c r="Y82" s="34"/>
-      <c r="Z82" s="35"/>
-      <c r="AA82" s="35"/>
-      <c r="AB82" s="35"/>
-      <c r="AC82" s="35"/>
-      <c r="AD82" s="35"/>
-      <c r="AE82" s="35"/>
-      <c r="AF82" s="35"/>
-      <c r="AG82" s="35"/>
-      <c r="AH82" s="35"/>
-      <c r="AI82" s="35"/>
-      <c r="AJ82" s="35"/>
-      <c r="AK82" s="35"/>
-      <c r="AL82" s="35"/>
-      <c r="AM82" s="35"/>
-      <c r="AN82" s="35"/>
-      <c r="AO82" s="35"/>
-      <c r="AP82" s="35"/>
-      <c r="AQ82" s="35"/>
-      <c r="AR82" s="35"/>
-      <c r="AS82" s="35"/>
-      <c r="AT82" s="35"/>
-      <c r="AU82" s="35"/>
-      <c r="AV82" s="35"/>
-      <c r="AW82" s="35"/>
-      <c r="AX82" s="35"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F82" s="23">
+        <v>30520</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" s="24">
+        <v>4214.67</v>
+      </c>
+      <c r="J82" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K82" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L82" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N82" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O82" s="21"/>
+      <c r="P82" s="25"/>
+      <c r="Q82" s="25"/>
+      <c r="R82" s="17"/>
+      <c r="S82" s="17"/>
+      <c r="T82" s="17"/>
+      <c r="U82" s="17"/>
+      <c r="V82" s="17"/>
+      <c r="W82" s="17"/>
+      <c r="X82" s="17"/>
+      <c r="Y82" s="17"/>
+      <c r="Z82" s="18"/>
+      <c r="AA82" s="18"/>
+      <c r="AB82" s="18"/>
+      <c r="AC82" s="18"/>
+      <c r="AD82" s="18"/>
+      <c r="AE82" s="18"/>
+      <c r="AF82" s="18"/>
+      <c r="AG82" s="18"/>
+      <c r="AH82" s="18"/>
+      <c r="AI82" s="18"/>
+      <c r="AJ82" s="18"/>
+      <c r="AK82" s="18"/>
+      <c r="AL82" s="18"/>
+      <c r="AM82" s="18"/>
+      <c r="AN82" s="18"/>
+      <c r="AO82" s="18"/>
+      <c r="AP82" s="18"/>
+      <c r="AQ82" s="18"/>
+      <c r="AR82" s="18"/>
+      <c r="AS82" s="18"/>
+      <c r="AT82" s="18"/>
+      <c r="AU82" s="18"/>
+      <c r="AV82" s="18"/>
+      <c r="AW82" s="18"/>
+      <c r="AX82" s="18"/>
     </row>
     <row r="83" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="26"/>
       <c r="B83" s="27">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C83" s="27">
         <v>46099</v>
       </c>
       <c r="D83" s="28"/>
       <c r="E83" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F83" s="30">
-        <v>239234</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="F83" s="28"/>
       <c r="G83" s="29" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H83" s="29" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="I83" s="31">
-        <v>1993.24</v>
+        <v>48000</v>
       </c>
       <c r="J83" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K83" s="29" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="L83" s="29" t="s">
         <v>27</v>
@@ -7578,9 +7589,11 @@
       </c>
       <c r="O83" s="28"/>
       <c r="P83" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q83" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="Q83" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R83" s="34"/>
       <c r="S83" s="34"/>
       <c r="T83" s="34"/>
@@ -7628,7 +7641,7 @@
         <v>17</v>
       </c>
       <c r="F84" s="30">
-        <v>239250</v>
+        <v>239234</v>
       </c>
       <c r="G84" s="29" t="s">
         <v>18</v>
@@ -7637,7 +7650,7 @@
         <v>19</v>
       </c>
       <c r="I84" s="31">
-        <v>2714.34</v>
+        <v>1993.24</v>
       </c>
       <c r="J84" s="29" t="b">
         <v>1</v>
@@ -7703,10 +7716,10 @@
       </c>
       <c r="D85" s="28"/>
       <c r="E85" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F85" s="30" t="s">
-        <v>128</v>
+        <v>17</v>
+      </c>
+      <c r="F85" s="30">
+        <v>239250</v>
       </c>
       <c r="G85" s="29" t="s">
         <v>18</v>
@@ -7715,7 +7728,7 @@
         <v>19</v>
       </c>
       <c r="I85" s="31">
-        <v>41034</v>
+        <v>2714.34</v>
       </c>
       <c r="J85" s="29" t="b">
         <v>1</v>
@@ -7781,9 +7794,11 @@
       </c>
       <c r="D86" s="28"/>
       <c r="E86" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="F86" s="28"/>
+        <v>30</v>
+      </c>
+      <c r="F86" s="30" t="s">
+        <v>128</v>
+      </c>
       <c r="G86" s="29" t="s">
         <v>18</v>
       </c>
@@ -7791,7 +7806,7 @@
         <v>19</v>
       </c>
       <c r="I86" s="31">
-        <v>640</v>
+        <v>41034</v>
       </c>
       <c r="J86" s="29" t="b">
         <v>1</v>
@@ -7810,17 +7825,17 @@
       </c>
       <c r="O86" s="28"/>
       <c r="P86" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q86" s="33"/>
-      <c r="R86" s="35"/>
-      <c r="S86" s="35"/>
-      <c r="T86" s="35"/>
-      <c r="U86" s="35"/>
-      <c r="V86" s="35"/>
-      <c r="W86" s="35"/>
-      <c r="X86" s="35"/>
-      <c r="Y86" s="35"/>
+      <c r="R86" s="34"/>
+      <c r="S86" s="34"/>
+      <c r="T86" s="34"/>
+      <c r="U86" s="34"/>
+      <c r="V86" s="34"/>
+      <c r="W86" s="34"/>
+      <c r="X86" s="34"/>
+      <c r="Y86" s="34"/>
       <c r="Z86" s="35"/>
       <c r="AA86" s="35"/>
       <c r="AB86" s="35"/>
@@ -7857,7 +7872,7 @@
       </c>
       <c r="D87" s="28"/>
       <c r="E87" s="29" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="F87" s="28"/>
       <c r="G87" s="29" t="s">
@@ -7867,7 +7882,7 @@
         <v>19</v>
       </c>
       <c r="I87" s="31">
-        <v>13145.01</v>
+        <v>640</v>
       </c>
       <c r="J87" s="29" t="b">
         <v>1</v>
@@ -7923,33 +7938,33 @@
       <c r="AW87" s="35"/>
       <c r="AX87" s="35"/>
     </row>
-    <row r="88" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="26"/>
       <c r="B88" s="27">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C88" s="27">
         <v>46099</v>
       </c>
       <c r="D88" s="28"/>
       <c r="E88" s="29" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F88" s="28"/>
       <c r="G88" s="29" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H88" s="29" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="I88" s="31">
-        <v>5000</v>
+        <v>13145.01</v>
       </c>
       <c r="J88" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K88" s="29" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="L88" s="29" t="s">
         <v>27</v>
@@ -7960,10 +7975,10 @@
       <c r="N88" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O88" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="P88" s="33"/>
+      <c r="O88" s="28"/>
+      <c r="P88" s="32" t="s">
+        <v>130</v>
+      </c>
       <c r="Q88" s="33"/>
       <c r="R88" s="35"/>
       <c r="S88" s="35"/>
@@ -7999,7 +8014,7 @@
       <c r="AW88" s="35"/>
       <c r="AX88" s="35"/>
     </row>
-    <row r="89" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="26"/>
       <c r="B89" s="27">
         <v>46079</v>
@@ -8009,23 +8024,23 @@
       </c>
       <c r="D89" s="28"/>
       <c r="E89" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F89" s="28"/>
       <c r="G89" s="29" t="s">
         <v>36</v>
       </c>
       <c r="H89" s="29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I89" s="31">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="J89" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K89" s="29" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="L89" s="29" t="s">
         <v>27</v>
@@ -8037,20 +8052,18 @@
         <v>28</v>
       </c>
       <c r="O89" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="P89" s="32" t="s">
-        <v>135</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="P89" s="33"/>
       <c r="Q89" s="33"/>
-      <c r="R89" s="34"/>
-      <c r="S89" s="34"/>
-      <c r="T89" s="34"/>
-      <c r="U89" s="34"/>
-      <c r="V89" s="34"/>
-      <c r="W89" s="34"/>
-      <c r="X89" s="34"/>
-      <c r="Y89" s="34"/>
+      <c r="R89" s="35"/>
+      <c r="S89" s="35"/>
+      <c r="T89" s="35"/>
+      <c r="U89" s="35"/>
+      <c r="V89" s="35"/>
+      <c r="W89" s="35"/>
+      <c r="X89" s="35"/>
+      <c r="Y89" s="35"/>
       <c r="Z89" s="35"/>
       <c r="AA89" s="35"/>
       <c r="AB89" s="35"/>
@@ -8087,7 +8100,7 @@
       </c>
       <c r="D90" s="28"/>
       <c r="E90" s="29" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F90" s="28"/>
       <c r="G90" s="29" t="s">
@@ -8115,14 +8128,12 @@
         <v>28</v>
       </c>
       <c r="O90" s="29" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P90" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="Q90" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q90" s="33"/>
       <c r="R90" s="34"/>
       <c r="S90" s="34"/>
       <c r="T90" s="34"/>
@@ -8157,7 +8168,7 @@
       <c r="AW90" s="35"/>
       <c r="AX90" s="35"/>
     </row>
-    <row r="91" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="26"/>
       <c r="B91" s="27">
         <v>46079</v>
@@ -8167,7 +8178,7 @@
       </c>
       <c r="D91" s="28"/>
       <c r="E91" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F91" s="28"/>
       <c r="G91" s="29" t="s">
@@ -8195,7 +8206,7 @@
         <v>28</v>
       </c>
       <c r="O91" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="P91" s="32" t="s">
         <v>135</v>
@@ -8237,7 +8248,7 @@
       <c r="AW91" s="35"/>
       <c r="AX91" s="35"/>
     </row>
-    <row r="92" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="26"/>
       <c r="B92" s="27">
         <v>46079</v>
@@ -8247,7 +8258,7 @@
       </c>
       <c r="D92" s="28"/>
       <c r="E92" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F92" s="28"/>
       <c r="G92" s="29" t="s">
@@ -8275,7 +8286,7 @@
         <v>28</v>
       </c>
       <c r="O92" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="P92" s="32" t="s">
         <v>135</v>
@@ -8320,14 +8331,14 @@
     <row r="93" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="26"/>
       <c r="B93" s="27">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="C93" s="27">
         <v>46099</v>
       </c>
       <c r="D93" s="28"/>
       <c r="E93" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F93" s="28"/>
       <c r="G93" s="29" t="s">
@@ -8337,7 +8348,7 @@
         <v>49</v>
       </c>
       <c r="I93" s="31">
-        <v>340.9</v>
+        <v>500</v>
       </c>
       <c r="J93" s="29" t="b">
         <v>1</v>
@@ -8355,12 +8366,14 @@
         <v>28</v>
       </c>
       <c r="O93" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P93" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="Q93" s="33"/>
+      <c r="Q93" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R93" s="34"/>
       <c r="S93" s="34"/>
       <c r="T93" s="34"/>
@@ -8398,30 +8411,30 @@
     <row r="94" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="26"/>
       <c r="B94" s="27">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C94" s="27">
         <v>46099</v>
       </c>
       <c r="D94" s="28"/>
       <c r="E94" s="29" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="F94" s="28"/>
       <c r="G94" s="29" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H94" s="29" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="I94" s="31">
-        <v>14454</v>
+        <v>340.9</v>
       </c>
       <c r="J94" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K94" s="29" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L94" s="29" t="s">
         <v>27</v>
@@ -8432,9 +8445,11 @@
       <c r="N94" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O94" s="28"/>
-      <c r="P94" s="9" t="s">
-        <v>144</v>
+      <c r="O94" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="P94" s="32" t="s">
+        <v>135</v>
       </c>
       <c r="Q94" s="33"/>
       <c r="R94" s="34"/>
@@ -8471,7 +8486,7 @@
       <c r="AW94" s="35"/>
       <c r="AX94" s="35"/>
     </row>
-    <row r="95" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="26"/>
       <c r="B95" s="27">
         <v>46079</v>
@@ -8481,23 +8496,23 @@
       </c>
       <c r="D95" s="28"/>
       <c r="E95" s="29" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="F95" s="28"/>
       <c r="G95" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H95" s="29" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="I95" s="31">
-        <v>7500</v>
+        <v>14454</v>
       </c>
       <c r="J95" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K95" s="29" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L95" s="29" t="s">
         <v>27</v>
@@ -8508,11 +8523,9 @@
       <c r="N95" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O95" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P95" s="32" t="s">
-        <v>145</v>
+      <c r="O95" s="28"/>
+      <c r="P95" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="Q95" s="33"/>
       <c r="R95" s="34"/>
@@ -8549,7 +8562,7 @@
       <c r="AW95" s="35"/>
       <c r="AX95" s="35"/>
     </row>
-    <row r="96" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="26"/>
       <c r="B96" s="27">
         <v>46079</v>
@@ -8559,23 +8572,23 @@
       </c>
       <c r="D96" s="28"/>
       <c r="E96" s="29" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F96" s="28"/>
       <c r="G96" s="29" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H96" s="29" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I96" s="31">
-        <v>20000</v>
+        <v>7500</v>
       </c>
       <c r="J96" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K96" s="29" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="L96" s="29" t="s">
         <v>27</v>
@@ -8586,8 +8599,12 @@
       <c r="N96" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O96" s="28"/>
-      <c r="P96" s="33"/>
+      <c r="O96" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="P96" s="32" t="s">
+        <v>145</v>
+      </c>
       <c r="Q96" s="33"/>
       <c r="R96" s="34"/>
       <c r="S96" s="34"/>
@@ -8624,136 +8641,132 @@
       <c r="AX96" s="35"/>
     </row>
     <row r="97" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="37"/>
-      <c r="B97" s="38"/>
-      <c r="C97" s="38"/>
-      <c r="D97" s="38"/>
-      <c r="E97" s="38"/>
-      <c r="F97" s="38"/>
-      <c r="G97" s="38"/>
-      <c r="H97" s="38"/>
-      <c r="I97" s="39"/>
-      <c r="J97" s="38"/>
-      <c r="K97" s="38"/>
-      <c r="L97" s="38"/>
-      <c r="M97" s="38"/>
-      <c r="N97" s="38"/>
-      <c r="O97" s="38"/>
-      <c r="P97" s="39"/>
-      <c r="Q97" s="39"/>
-      <c r="R97" s="40"/>
-      <c r="S97" s="40"/>
-      <c r="T97" s="40"/>
-      <c r="U97" s="40"/>
-      <c r="V97" s="40"/>
-      <c r="W97" s="40"/>
-      <c r="X97" s="40"/>
-      <c r="Y97" s="40"/>
-      <c r="Z97" s="41"/>
-      <c r="AA97" s="41"/>
-      <c r="AB97" s="41"/>
-      <c r="AC97" s="41"/>
-      <c r="AD97" s="41"/>
-      <c r="AE97" s="41"/>
-      <c r="AF97" s="41"/>
-      <c r="AG97" s="41"/>
-      <c r="AH97" s="41"/>
-      <c r="AI97" s="41"/>
-      <c r="AJ97" s="41"/>
-      <c r="AK97" s="41"/>
-      <c r="AL97" s="41"/>
-      <c r="AM97" s="41"/>
-      <c r="AN97" s="41"/>
-      <c r="AO97" s="41"/>
-      <c r="AP97" s="41"/>
-      <c r="AQ97" s="41"/>
-      <c r="AR97" s="41"/>
-      <c r="AS97" s="41"/>
-      <c r="AT97" s="41"/>
-      <c r="AU97" s="41"/>
-      <c r="AV97" s="41"/>
-      <c r="AW97" s="41"/>
-      <c r="AX97" s="41"/>
-    </row>
-    <row r="98" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="19"/>
-      <c r="B98" s="20">
+      <c r="A97" s="26"/>
+      <c r="B97" s="27">
         <v>46079</v>
       </c>
-      <c r="C98" s="20">
-        <v>46100</v>
-      </c>
-      <c r="D98" s="21"/>
-      <c r="E98" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="F98" s="21"/>
-      <c r="G98" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="H98" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="I98" s="24">
-        <v>41201.949999999997</v>
-      </c>
-      <c r="J98" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K98" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="L98" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N98" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O98" s="21"/>
-      <c r="P98" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q98" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="R98" s="17"/>
-      <c r="S98" s="17"/>
-      <c r="T98" s="17"/>
-      <c r="U98" s="17"/>
-      <c r="V98" s="17"/>
-      <c r="W98" s="17"/>
-      <c r="X98" s="17"/>
-      <c r="Y98" s="17"/>
-      <c r="Z98" s="18"/>
-      <c r="AA98" s="18"/>
-      <c r="AB98" s="18"/>
-      <c r="AC98" s="18"/>
-      <c r="AD98" s="18"/>
-      <c r="AE98" s="18"/>
-      <c r="AF98" s="18"/>
-      <c r="AG98" s="18"/>
-      <c r="AH98" s="18"/>
-      <c r="AI98" s="18"/>
-      <c r="AJ98" s="18"/>
-      <c r="AK98" s="18"/>
-      <c r="AL98" s="18"/>
-      <c r="AM98" s="18"/>
-      <c r="AN98" s="18"/>
-      <c r="AO98" s="18"/>
-      <c r="AP98" s="18"/>
-      <c r="AQ98" s="18"/>
-      <c r="AR98" s="18"/>
-      <c r="AS98" s="18"/>
-      <c r="AT98" s="18"/>
-      <c r="AU98" s="18"/>
-      <c r="AV98" s="18"/>
-      <c r="AW98" s="18"/>
-      <c r="AX98" s="18"/>
-    </row>
-    <row r="99" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C97" s="27">
+        <v>46099</v>
+      </c>
+      <c r="D97" s="28"/>
+      <c r="E97" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F97" s="28"/>
+      <c r="G97" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H97" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I97" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J97" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K97" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L97" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M97" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N97" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O97" s="28"/>
+      <c r="P97" s="33"/>
+      <c r="Q97" s="33"/>
+      <c r="R97" s="34"/>
+      <c r="S97" s="34"/>
+      <c r="T97" s="34"/>
+      <c r="U97" s="34"/>
+      <c r="V97" s="34"/>
+      <c r="W97" s="34"/>
+      <c r="X97" s="34"/>
+      <c r="Y97" s="34"/>
+      <c r="Z97" s="35"/>
+      <c r="AA97" s="35"/>
+      <c r="AB97" s="35"/>
+      <c r="AC97" s="35"/>
+      <c r="AD97" s="35"/>
+      <c r="AE97" s="35"/>
+      <c r="AF97" s="35"/>
+      <c r="AG97" s="35"/>
+      <c r="AH97" s="35"/>
+      <c r="AI97" s="35"/>
+      <c r="AJ97" s="35"/>
+      <c r="AK97" s="35"/>
+      <c r="AL97" s="35"/>
+      <c r="AM97" s="35"/>
+      <c r="AN97" s="35"/>
+      <c r="AO97" s="35"/>
+      <c r="AP97" s="35"/>
+      <c r="AQ97" s="35"/>
+      <c r="AR97" s="35"/>
+      <c r="AS97" s="35"/>
+      <c r="AT97" s="35"/>
+      <c r="AU97" s="35"/>
+      <c r="AV97" s="35"/>
+      <c r="AW97" s="35"/>
+      <c r="AX97" s="35"/>
+    </row>
+    <row r="98" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="37"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="38"/>
+      <c r="G98" s="38"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="39"/>
+      <c r="J98" s="38"/>
+      <c r="K98" s="38"/>
+      <c r="L98" s="38"/>
+      <c r="M98" s="38"/>
+      <c r="N98" s="38"/>
+      <c r="O98" s="38"/>
+      <c r="P98" s="39"/>
+      <c r="Q98" s="39"/>
+      <c r="R98" s="40"/>
+      <c r="S98" s="40"/>
+      <c r="T98" s="40"/>
+      <c r="U98" s="40"/>
+      <c r="V98" s="40"/>
+      <c r="W98" s="40"/>
+      <c r="X98" s="40"/>
+      <c r="Y98" s="40"/>
+      <c r="Z98" s="41"/>
+      <c r="AA98" s="41"/>
+      <c r="AB98" s="41"/>
+      <c r="AC98" s="41"/>
+      <c r="AD98" s="41"/>
+      <c r="AE98" s="41"/>
+      <c r="AF98" s="41"/>
+      <c r="AG98" s="41"/>
+      <c r="AH98" s="41"/>
+      <c r="AI98" s="41"/>
+      <c r="AJ98" s="41"/>
+      <c r="AK98" s="41"/>
+      <c r="AL98" s="41"/>
+      <c r="AM98" s="41"/>
+      <c r="AN98" s="41"/>
+      <c r="AO98" s="41"/>
+      <c r="AP98" s="41"/>
+      <c r="AQ98" s="41"/>
+      <c r="AR98" s="41"/>
+      <c r="AS98" s="41"/>
+      <c r="AT98" s="41"/>
+      <c r="AU98" s="41"/>
+      <c r="AV98" s="41"/>
+      <c r="AW98" s="41"/>
+      <c r="AX98" s="41"/>
+    </row>
+    <row r="99" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="19"/>
       <c r="B99" s="20">
         <v>46079</v>
@@ -8763,25 +8776,23 @@
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="F99" s="23" t="s">
-        <v>151</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F99" s="21"/>
       <c r="G99" s="22" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H99" s="22" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I99" s="24">
-        <v>163.96</v>
+        <v>41201.949999999997</v>
       </c>
       <c r="J99" s="22" t="b">
         <v>1</v>
       </c>
       <c r="K99" s="22" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="L99" s="22" t="s">
         <v>21</v>
@@ -8793,8 +8804,12 @@
         <v>23</v>
       </c>
       <c r="O99" s="21"/>
-      <c r="P99" s="25"/>
-      <c r="Q99" s="25"/>
+      <c r="P99" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q99" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="R99" s="17"/>
       <c r="S99" s="17"/>
       <c r="T99" s="17"/>
@@ -8839,19 +8854,19 @@
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F100" s="23">
-        <v>453494</v>
+        <v>150</v>
+      </c>
+      <c r="F100" s="23" t="s">
+        <v>151</v>
       </c>
       <c r="G100" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="I100" s="24">
-        <v>10079.950000000001</v>
+        <v>163.96</v>
       </c>
       <c r="J100" s="22" t="b">
         <v>1</v>
@@ -8915,19 +8930,19 @@
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="22" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="F101" s="23">
-        <v>264272</v>
+        <v>453494</v>
       </c>
       <c r="G101" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="I101" s="24">
-        <v>3452.46</v>
+        <v>10079.950000000001</v>
       </c>
       <c r="J101" s="22" t="b">
         <v>1</v>
@@ -8991,19 +9006,19 @@
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="22" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="F102" s="23">
-        <v>268025</v>
+        <v>264272</v>
       </c>
       <c r="G102" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H102" s="22" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I102" s="24">
-        <v>17864.88</v>
+        <v>3452.46</v>
       </c>
       <c r="J102" s="22" t="b">
         <v>1</v>
@@ -9060,17 +9075,17 @@
     <row r="103" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="19"/>
       <c r="B103" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C103" s="20">
         <v>46100</v>
       </c>
       <c r="D103" s="21"/>
       <c r="E103" s="22" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="F103" s="23">
-        <v>924426</v>
+        <v>268025</v>
       </c>
       <c r="G103" s="22" t="s">
         <v>18</v>
@@ -9079,7 +9094,7 @@
         <v>25</v>
       </c>
       <c r="I103" s="24">
-        <v>7298.44</v>
+        <v>17864.88</v>
       </c>
       <c r="J103" s="22" t="b">
         <v>1</v>
@@ -9143,19 +9158,19 @@
       </c>
       <c r="D104" s="21"/>
       <c r="E104" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F104" s="23">
-        <v>2295</v>
+        <v>924426</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I104" s="24">
-        <v>909.15</v>
+        <v>7298.44</v>
       </c>
       <c r="J104" s="22" t="b">
         <v>1</v>
@@ -9219,19 +9234,19 @@
       </c>
       <c r="D105" s="21"/>
       <c r="E105" s="22" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="F105" s="23">
-        <v>9755</v>
+        <v>2295</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I105" s="24">
-        <v>1700</v>
+        <v>909.15</v>
       </c>
       <c r="J105" s="22" t="b">
         <v>1</v>
@@ -9240,7 +9255,7 @@
         <v>20</v>
       </c>
       <c r="L105" s="22" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M105" s="22" t="s">
         <v>22</v>
@@ -9286,90 +9301,92 @@
       <c r="AX105" s="18"/>
     </row>
     <row r="106" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="26"/>
-      <c r="B106" s="27">
-        <v>46079</v>
-      </c>
-      <c r="C106" s="27">
+      <c r="A106" s="19"/>
+      <c r="B106" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C106" s="20">
         <v>46100</v>
       </c>
-      <c r="D106" s="28"/>
-      <c r="E106" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="F106" s="28"/>
-      <c r="G106" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="H106" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="I106" s="31">
-        <v>540</v>
-      </c>
-      <c r="J106" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K106" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="L106" s="29" t="s">
+      <c r="D106" s="21"/>
+      <c r="E106" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="F106" s="23">
+        <v>9755</v>
+      </c>
+      <c r="G106" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H106" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I106" s="24">
+        <v>1700</v>
+      </c>
+      <c r="J106" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K106" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L106" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="M106" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N106" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O106" s="28"/>
-      <c r="P106" s="33"/>
-      <c r="Q106" s="33"/>
-      <c r="R106" s="34"/>
-      <c r="S106" s="34"/>
-      <c r="T106" s="34"/>
-      <c r="U106" s="34"/>
-      <c r="V106" s="34"/>
-      <c r="W106" s="34"/>
-      <c r="X106" s="34"/>
-      <c r="Y106" s="34"/>
-      <c r="Z106" s="35"/>
-      <c r="AA106" s="35"/>
-      <c r="AB106" s="35"/>
-      <c r="AC106" s="35"/>
-      <c r="AD106" s="35"/>
-      <c r="AE106" s="35"/>
-      <c r="AF106" s="35"/>
-      <c r="AG106" s="35"/>
-      <c r="AH106" s="35"/>
-      <c r="AI106" s="35"/>
-      <c r="AJ106" s="35"/>
-      <c r="AK106" s="35"/>
-      <c r="AL106" s="35"/>
-      <c r="AM106" s="35"/>
-      <c r="AN106" s="35"/>
-      <c r="AO106" s="35"/>
-      <c r="AP106" s="35"/>
-      <c r="AQ106" s="35"/>
-      <c r="AR106" s="35"/>
-      <c r="AS106" s="35"/>
-      <c r="AT106" s="35"/>
-      <c r="AU106" s="35"/>
-      <c r="AV106" s="35"/>
-      <c r="AW106" s="35"/>
-      <c r="AX106" s="35"/>
-    </row>
-    <row r="107" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M106" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N106" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O106" s="21"/>
+      <c r="P106" s="25"/>
+      <c r="Q106" s="25"/>
+      <c r="R106" s="17"/>
+      <c r="S106" s="17"/>
+      <c r="T106" s="17"/>
+      <c r="U106" s="17"/>
+      <c r="V106" s="17"/>
+      <c r="W106" s="17"/>
+      <c r="X106" s="17"/>
+      <c r="Y106" s="17"/>
+      <c r="Z106" s="18"/>
+      <c r="AA106" s="18"/>
+      <c r="AB106" s="18"/>
+      <c r="AC106" s="18"/>
+      <c r="AD106" s="18"/>
+      <c r="AE106" s="18"/>
+      <c r="AF106" s="18"/>
+      <c r="AG106" s="18"/>
+      <c r="AH106" s="18"/>
+      <c r="AI106" s="18"/>
+      <c r="AJ106" s="18"/>
+      <c r="AK106" s="18"/>
+      <c r="AL106" s="18"/>
+      <c r="AM106" s="18"/>
+      <c r="AN106" s="18"/>
+      <c r="AO106" s="18"/>
+      <c r="AP106" s="18"/>
+      <c r="AQ106" s="18"/>
+      <c r="AR106" s="18"/>
+      <c r="AS106" s="18"/>
+      <c r="AT106" s="18"/>
+      <c r="AU106" s="18"/>
+      <c r="AV106" s="18"/>
+      <c r="AW106" s="18"/>
+      <c r="AX106" s="18"/>
+    </row>
+    <row r="107" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="26"/>
       <c r="B107" s="27">
-        <v>46091</v>
+        <v>46079</v>
       </c>
       <c r="C107" s="27">
         <v>46100</v>
       </c>
       <c r="D107" s="28"/>
       <c r="E107" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F107" s="28"/>
       <c r="G107" s="29" t="s">
@@ -9379,13 +9396,13 @@
         <v>157</v>
       </c>
       <c r="I107" s="31">
-        <v>448.55</v>
+        <v>540</v>
       </c>
       <c r="J107" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K107" s="29" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="L107" s="29" t="s">
         <v>27</v>
@@ -9396,9 +9413,7 @@
       <c r="N107" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O107" s="29" t="s">
-        <v>160</v>
-      </c>
+      <c r="O107" s="28"/>
       <c r="P107" s="33"/>
       <c r="Q107" s="33"/>
       <c r="R107" s="34"/>
@@ -9435,33 +9450,33 @@
       <c r="AW107" s="35"/>
       <c r="AX107" s="35"/>
     </row>
-    <row r="108" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="26"/>
       <c r="B108" s="27">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="C108" s="27">
         <v>46100</v>
       </c>
       <c r="D108" s="28"/>
       <c r="E108" s="29" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="F108" s="28"/>
       <c r="G108" s="29" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H108" s="29" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="I108" s="31">
-        <v>9975</v>
+        <v>448.55</v>
       </c>
       <c r="J108" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K108" s="29" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="L108" s="29" t="s">
         <v>27</v>
@@ -9473,11 +9488,9 @@
         <v>28</v>
       </c>
       <c r="O108" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P108" s="32" t="s">
-        <v>161</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="P108" s="33"/>
       <c r="Q108" s="33"/>
       <c r="R108" s="34"/>
       <c r="S108" s="34"/>
@@ -9516,7 +9529,7 @@
     <row r="109" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="26"/>
       <c r="B109" s="27">
-        <v>46059</v>
+        <v>46084</v>
       </c>
       <c r="C109" s="27">
         <v>46100</v>
@@ -9533,7 +9546,7 @@
         <v>19</v>
       </c>
       <c r="I109" s="31">
-        <v>10000</v>
+        <v>9975</v>
       </c>
       <c r="J109" s="29" t="b">
         <v>1</v>
@@ -9554,7 +9567,7 @@
         <v>76</v>
       </c>
       <c r="P109" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q109" s="33"/>
       <c r="R109" s="34"/>
@@ -9591,33 +9604,33 @@
       <c r="AW109" s="35"/>
       <c r="AX109" s="35"/>
     </row>
-    <row r="110" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="26"/>
       <c r="B110" s="27">
-        <v>46079</v>
+        <v>46059</v>
       </c>
       <c r="C110" s="27">
         <v>46100</v>
       </c>
       <c r="D110" s="28"/>
       <c r="E110" s="29" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F110" s="28"/>
       <c r="G110" s="29" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H110" s="29" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I110" s="31">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="J110" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K110" s="29" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="L110" s="29" t="s">
         <v>27</v>
@@ -9628,17 +9641,21 @@
       <c r="N110" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O110" s="28"/>
-      <c r="P110" s="33"/>
+      <c r="O110" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="P110" s="32" t="s">
+        <v>162</v>
+      </c>
       <c r="Q110" s="33"/>
-      <c r="R110" s="35"/>
-      <c r="S110" s="35"/>
-      <c r="T110" s="35"/>
-      <c r="U110" s="35"/>
-      <c r="V110" s="35"/>
-      <c r="W110" s="35"/>
-      <c r="X110" s="35"/>
-      <c r="Y110" s="35"/>
+      <c r="R110" s="34"/>
+      <c r="S110" s="34"/>
+      <c r="T110" s="34"/>
+      <c r="U110" s="34"/>
+      <c r="V110" s="34"/>
+      <c r="W110" s="34"/>
+      <c r="X110" s="34"/>
+      <c r="Y110" s="34"/>
       <c r="Z110" s="35"/>
       <c r="AA110" s="35"/>
       <c r="AB110" s="35"/>
@@ -9666,134 +9683,132 @@
       <c r="AX110" s="35"/>
     </row>
     <row r="111" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="37"/>
-      <c r="B111" s="38"/>
-      <c r="C111" s="38"/>
-      <c r="D111" s="38"/>
-      <c r="E111" s="38"/>
-      <c r="F111" s="38"/>
-      <c r="G111" s="38"/>
-      <c r="H111" s="38"/>
-      <c r="I111" s="39"/>
-      <c r="J111" s="38"/>
-      <c r="K111" s="38"/>
-      <c r="L111" s="38"/>
-      <c r="M111" s="38"/>
-      <c r="N111" s="38"/>
-      <c r="O111" s="38"/>
-      <c r="P111" s="39"/>
-      <c r="Q111" s="39"/>
-      <c r="R111" s="41"/>
-      <c r="S111" s="41"/>
-      <c r="T111" s="41"/>
-      <c r="U111" s="41"/>
-      <c r="V111" s="41"/>
-      <c r="W111" s="41"/>
-      <c r="X111" s="41"/>
-      <c r="Y111" s="41"/>
-      <c r="Z111" s="41"/>
-      <c r="AA111" s="41"/>
-      <c r="AB111" s="41"/>
-      <c r="AC111" s="41"/>
-      <c r="AD111" s="41"/>
-      <c r="AE111" s="41"/>
-      <c r="AF111" s="41"/>
-      <c r="AG111" s="41"/>
-      <c r="AH111" s="41"/>
-      <c r="AI111" s="41"/>
-      <c r="AJ111" s="41"/>
-      <c r="AK111" s="41"/>
-      <c r="AL111" s="41"/>
-      <c r="AM111" s="41"/>
-      <c r="AN111" s="41"/>
-      <c r="AO111" s="41"/>
-      <c r="AP111" s="41"/>
-      <c r="AQ111" s="41"/>
-      <c r="AR111" s="41"/>
-      <c r="AS111" s="41"/>
-      <c r="AT111" s="41"/>
-      <c r="AU111" s="41"/>
-      <c r="AV111" s="41"/>
-      <c r="AW111" s="41"/>
-      <c r="AX111" s="41"/>
-    </row>
-    <row r="112" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="26"/>
-      <c r="B112" s="27">
+      <c r="A111" s="26"/>
+      <c r="B111" s="27">
         <v>46079</v>
       </c>
-      <c r="C112" s="27">
-        <v>46101</v>
-      </c>
-      <c r="D112" s="28"/>
-      <c r="E112" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="F112" s="28"/>
-      <c r="G112" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="H112" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="I112" s="31">
-        <v>110000</v>
-      </c>
-      <c r="J112" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K112" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="L112" s="29" t="s">
+      <c r="C111" s="27">
+        <v>46100</v>
+      </c>
+      <c r="D111" s="28"/>
+      <c r="E111" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F111" s="28"/>
+      <c r="G111" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H111" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I111" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J111" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K111" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L111" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="M112" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N112" s="29" t="s">
+      <c r="M111" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N111" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O112" s="28"/>
-      <c r="P112" s="33"/>
-      <c r="Q112" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R112" s="35"/>
-      <c r="S112" s="35"/>
-      <c r="T112" s="35"/>
-      <c r="U112" s="35"/>
-      <c r="V112" s="35"/>
-      <c r="W112" s="35"/>
-      <c r="X112" s="35"/>
-      <c r="Y112" s="35"/>
-      <c r="Z112" s="35"/>
-      <c r="AA112" s="35"/>
-      <c r="AB112" s="35"/>
-      <c r="AC112" s="35"/>
-      <c r="AD112" s="35"/>
-      <c r="AE112" s="35"/>
-      <c r="AF112" s="35"/>
-      <c r="AG112" s="35"/>
-      <c r="AH112" s="35"/>
-      <c r="AI112" s="35"/>
-      <c r="AJ112" s="35"/>
-      <c r="AK112" s="35"/>
-      <c r="AL112" s="35"/>
-      <c r="AM112" s="35"/>
-      <c r="AN112" s="35"/>
-      <c r="AO112" s="35"/>
-      <c r="AP112" s="35"/>
-      <c r="AQ112" s="35"/>
-      <c r="AR112" s="35"/>
-      <c r="AS112" s="35"/>
-      <c r="AT112" s="35"/>
-      <c r="AU112" s="35"/>
-      <c r="AV112" s="35"/>
-      <c r="AW112" s="35"/>
-      <c r="AX112" s="35"/>
-    </row>
-    <row r="113" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O111" s="28"/>
+      <c r="P111" s="33"/>
+      <c r="Q111" s="33"/>
+      <c r="R111" s="35"/>
+      <c r="S111" s="35"/>
+      <c r="T111" s="35"/>
+      <c r="U111" s="35"/>
+      <c r="V111" s="35"/>
+      <c r="W111" s="35"/>
+      <c r="X111" s="35"/>
+      <c r="Y111" s="35"/>
+      <c r="Z111" s="35"/>
+      <c r="AA111" s="35"/>
+      <c r="AB111" s="35"/>
+      <c r="AC111" s="35"/>
+      <c r="AD111" s="35"/>
+      <c r="AE111" s="35"/>
+      <c r="AF111" s="35"/>
+      <c r="AG111" s="35"/>
+      <c r="AH111" s="35"/>
+      <c r="AI111" s="35"/>
+      <c r="AJ111" s="35"/>
+      <c r="AK111" s="35"/>
+      <c r="AL111" s="35"/>
+      <c r="AM111" s="35"/>
+      <c r="AN111" s="35"/>
+      <c r="AO111" s="35"/>
+      <c r="AP111" s="35"/>
+      <c r="AQ111" s="35"/>
+      <c r="AR111" s="35"/>
+      <c r="AS111" s="35"/>
+      <c r="AT111" s="35"/>
+      <c r="AU111" s="35"/>
+      <c r="AV111" s="35"/>
+      <c r="AW111" s="35"/>
+      <c r="AX111" s="35"/>
+    </row>
+    <row r="112" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="37"/>
+      <c r="B112" s="38"/>
+      <c r="C112" s="38"/>
+      <c r="D112" s="38"/>
+      <c r="E112" s="38"/>
+      <c r="F112" s="38"/>
+      <c r="G112" s="38"/>
+      <c r="H112" s="38"/>
+      <c r="I112" s="39"/>
+      <c r="J112" s="38"/>
+      <c r="K112" s="38"/>
+      <c r="L112" s="38"/>
+      <c r="M112" s="38"/>
+      <c r="N112" s="38"/>
+      <c r="O112" s="38"/>
+      <c r="P112" s="39"/>
+      <c r="Q112" s="39"/>
+      <c r="R112" s="41"/>
+      <c r="S112" s="41"/>
+      <c r="T112" s="41"/>
+      <c r="U112" s="41"/>
+      <c r="V112" s="41"/>
+      <c r="W112" s="41"/>
+      <c r="X112" s="41"/>
+      <c r="Y112" s="41"/>
+      <c r="Z112" s="41"/>
+      <c r="AA112" s="41"/>
+      <c r="AB112" s="41"/>
+      <c r="AC112" s="41"/>
+      <c r="AD112" s="41"/>
+      <c r="AE112" s="41"/>
+      <c r="AF112" s="41"/>
+      <c r="AG112" s="41"/>
+      <c r="AH112" s="41"/>
+      <c r="AI112" s="41"/>
+      <c r="AJ112" s="41"/>
+      <c r="AK112" s="41"/>
+      <c r="AL112" s="41"/>
+      <c r="AM112" s="41"/>
+      <c r="AN112" s="41"/>
+      <c r="AO112" s="41"/>
+      <c r="AP112" s="41"/>
+      <c r="AQ112" s="41"/>
+      <c r="AR112" s="41"/>
+      <c r="AS112" s="41"/>
+      <c r="AT112" s="41"/>
+      <c r="AU112" s="41"/>
+      <c r="AV112" s="41"/>
+      <c r="AW112" s="41"/>
+      <c r="AX112" s="41"/>
+    </row>
+    <row r="113" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="26"/>
       <c r="B113" s="27">
         <v>46079</v>
@@ -9803,23 +9818,23 @@
       </c>
       <c r="D113" s="28"/>
       <c r="E113" s="29" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="F113" s="28"/>
       <c r="G113" s="29" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="H113" s="29" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="I113" s="31">
-        <v>7851.77</v>
+        <v>110000</v>
       </c>
       <c r="J113" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K113" s="29" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="L113" s="29" t="s">
         <v>27</v>
@@ -9831,18 +9846,18 @@
         <v>28</v>
       </c>
       <c r="O113" s="28"/>
-      <c r="P113" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q113" s="28"/>
-      <c r="R113" s="34"/>
-      <c r="S113" s="34"/>
-      <c r="T113" s="34"/>
-      <c r="U113" s="34"/>
-      <c r="V113" s="34"/>
-      <c r="W113" s="34"/>
-      <c r="X113" s="34"/>
-      <c r="Y113" s="34"/>
+      <c r="P113" s="33"/>
+      <c r="Q113" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R113" s="35"/>
+      <c r="S113" s="35"/>
+      <c r="T113" s="35"/>
+      <c r="U113" s="35"/>
+      <c r="V113" s="35"/>
+      <c r="W113" s="35"/>
+      <c r="X113" s="35"/>
+      <c r="Y113" s="35"/>
       <c r="Z113" s="35"/>
       <c r="AA113" s="35"/>
       <c r="AB113" s="35"/>
@@ -9869,27 +9884,27 @@
       <c r="AW113" s="35"/>
       <c r="AX113" s="35"/>
     </row>
-    <row r="114" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:50" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="26"/>
       <c r="B114" s="27">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C114" s="27">
         <v>46101</v>
       </c>
       <c r="D114" s="28"/>
       <c r="E114" s="29" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="F114" s="28"/>
       <c r="G114" s="29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H114" s="29" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="I114" s="31">
-        <v>700</v>
+        <v>1242.3</v>
       </c>
       <c r="J114" s="29" t="b">
         <v>1</v>
@@ -9906,13 +9921,11 @@
       <c r="N114" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O114" s="28"/>
-      <c r="P114" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q114" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="O114" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="P114" s="28"/>
+      <c r="Q114" s="28"/>
       <c r="R114" s="34"/>
       <c r="S114" s="34"/>
       <c r="T114" s="34"/>
@@ -9947,7 +9960,7 @@
       <c r="AW114" s="35"/>
       <c r="AX114" s="35"/>
     </row>
-    <row r="115" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="26"/>
       <c r="B115" s="27">
         <v>46079</v>
@@ -9957,23 +9970,23 @@
       </c>
       <c r="D115" s="28"/>
       <c r="E115" s="29" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F115" s="28"/>
       <c r="G115" s="29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H115" s="29" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I115" s="31">
-        <v>5000</v>
+        <v>7851.77</v>
       </c>
       <c r="J115" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K115" s="29" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="L115" s="29" t="s">
         <v>27</v>
@@ -9984,13 +9997,11 @@
       <c r="N115" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O115" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="P115" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q115" s="33"/>
+      <c r="O115" s="28"/>
+      <c r="P115" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q115" s="28"/>
       <c r="R115" s="34"/>
       <c r="S115" s="34"/>
       <c r="T115" s="34"/>
@@ -10035,7 +10046,7 @@
       </c>
       <c r="D116" s="28"/>
       <c r="E116" s="29" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F116" s="28"/>
       <c r="G116" s="29" t="s">
@@ -10045,7 +10056,7 @@
         <v>49</v>
       </c>
       <c r="I116" s="31">
-        <v>10000</v>
+        <v>700</v>
       </c>
       <c r="J116" s="29" t="b">
         <v>1</v>
@@ -10063,7 +10074,9 @@
         <v>28</v>
       </c>
       <c r="O116" s="28"/>
-      <c r="P116" s="33"/>
+      <c r="P116" s="32" t="s">
+        <v>166</v>
+      </c>
       <c r="Q116" s="32" t="s">
         <v>39</v>
       </c>
@@ -10111,23 +10124,23 @@
       </c>
       <c r="D117" s="28"/>
       <c r="E117" s="29" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="F117" s="28"/>
       <c r="G117" s="29" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="H117" s="29" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I117" s="31">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="J117" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K117" s="29" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L117" s="29" t="s">
         <v>27</v>
@@ -10138,13 +10151,13 @@
       <c r="N117" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O117" s="28"/>
+      <c r="O117" s="29" t="s">
+        <v>168</v>
+      </c>
       <c r="P117" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q117" s="32" t="s">
-        <v>39</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="Q117" s="33"/>
       <c r="R117" s="34"/>
       <c r="S117" s="34"/>
       <c r="T117" s="34"/>
@@ -10180,158 +10193,160 @@
       <c r="AX117" s="35"/>
     </row>
     <row r="118" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="19"/>
-      <c r="B118" s="20">
+      <c r="A118" s="26"/>
+      <c r="B118" s="27">
         <v>46079</v>
       </c>
-      <c r="C118" s="20">
+      <c r="C118" s="27">
         <v>46101</v>
       </c>
-      <c r="D118" s="21"/>
-      <c r="E118" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="F118" s="21"/>
-      <c r="G118" s="22" t="s">
+      <c r="D118" s="28"/>
+      <c r="E118" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F118" s="28"/>
+      <c r="G118" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H118" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="I118" s="24">
-        <v>96500</v>
-      </c>
-      <c r="J118" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K118" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="L118" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M118" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N118" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O118" s="21"/>
-      <c r="P118" s="25"/>
-      <c r="Q118" s="36" t="s">
+      <c r="H118" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I118" s="31">
+        <v>10000</v>
+      </c>
+      <c r="J118" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K118" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L118" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M118" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N118" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O118" s="28"/>
+      <c r="P118" s="33"/>
+      <c r="Q118" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R118" s="17"/>
-      <c r="S118" s="17"/>
-      <c r="T118" s="17"/>
-      <c r="U118" s="17"/>
-      <c r="V118" s="17"/>
-      <c r="W118" s="17"/>
-      <c r="X118" s="17"/>
-      <c r="Y118" s="17"/>
-      <c r="Z118" s="18"/>
-      <c r="AA118" s="18"/>
-      <c r="AB118" s="18"/>
-      <c r="AC118" s="18"/>
-      <c r="AD118" s="18"/>
-      <c r="AE118" s="18"/>
-      <c r="AF118" s="18"/>
-      <c r="AG118" s="18"/>
-      <c r="AH118" s="18"/>
-      <c r="AI118" s="18"/>
-      <c r="AJ118" s="18"/>
-      <c r="AK118" s="18"/>
-      <c r="AL118" s="18"/>
-      <c r="AM118" s="18"/>
-      <c r="AN118" s="18"/>
-      <c r="AO118" s="18"/>
-      <c r="AP118" s="18"/>
-      <c r="AQ118" s="18"/>
-      <c r="AR118" s="18"/>
-      <c r="AS118" s="18"/>
-      <c r="AT118" s="18"/>
-      <c r="AU118" s="18"/>
-      <c r="AV118" s="18"/>
-      <c r="AW118" s="18"/>
-      <c r="AX118" s="18"/>
-    </row>
-    <row r="119" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="19"/>
-      <c r="B119" s="20">
+      <c r="R118" s="34"/>
+      <c r="S118" s="34"/>
+      <c r="T118" s="34"/>
+      <c r="U118" s="34"/>
+      <c r="V118" s="34"/>
+      <c r="W118" s="34"/>
+      <c r="X118" s="34"/>
+      <c r="Y118" s="34"/>
+      <c r="Z118" s="35"/>
+      <c r="AA118" s="35"/>
+      <c r="AB118" s="35"/>
+      <c r="AC118" s="35"/>
+      <c r="AD118" s="35"/>
+      <c r="AE118" s="35"/>
+      <c r="AF118" s="35"/>
+      <c r="AG118" s="35"/>
+      <c r="AH118" s="35"/>
+      <c r="AI118" s="35"/>
+      <c r="AJ118" s="35"/>
+      <c r="AK118" s="35"/>
+      <c r="AL118" s="35"/>
+      <c r="AM118" s="35"/>
+      <c r="AN118" s="35"/>
+      <c r="AO118" s="35"/>
+      <c r="AP118" s="35"/>
+      <c r="AQ118" s="35"/>
+      <c r="AR118" s="35"/>
+      <c r="AS118" s="35"/>
+      <c r="AT118" s="35"/>
+      <c r="AU118" s="35"/>
+      <c r="AV118" s="35"/>
+      <c r="AW118" s="35"/>
+      <c r="AX118" s="35"/>
+    </row>
+    <row r="119" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="26"/>
+      <c r="B119" s="27">
         <v>46079</v>
       </c>
-      <c r="C119" s="20">
+      <c r="C119" s="27">
         <v>46101</v>
       </c>
-      <c r="D119" s="21"/>
-      <c r="E119" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F119" s="23">
-        <v>239304</v>
-      </c>
-      <c r="G119" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H119" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I119" s="24">
-        <v>50348.42</v>
-      </c>
-      <c r="J119" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K119" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L119" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M119" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N119" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O119" s="21"/>
-      <c r="P119" s="25"/>
-      <c r="Q119" s="25"/>
-      <c r="R119" s="17"/>
-      <c r="S119" s="17"/>
-      <c r="T119" s="17"/>
-      <c r="U119" s="17"/>
-      <c r="V119" s="17"/>
-      <c r="W119" s="17"/>
-      <c r="X119" s="17"/>
-      <c r="Y119" s="17"/>
-      <c r="Z119" s="18"/>
-      <c r="AA119" s="18"/>
-      <c r="AB119" s="18"/>
-      <c r="AC119" s="18"/>
-      <c r="AD119" s="18"/>
-      <c r="AE119" s="18"/>
-      <c r="AF119" s="18"/>
-      <c r="AG119" s="18"/>
-      <c r="AH119" s="18"/>
-      <c r="AI119" s="18"/>
-      <c r="AJ119" s="18"/>
-      <c r="AK119" s="18"/>
-      <c r="AL119" s="18"/>
-      <c r="AM119" s="18"/>
-      <c r="AN119" s="18"/>
-      <c r="AO119" s="18"/>
-      <c r="AP119" s="18"/>
-      <c r="AQ119" s="18"/>
-      <c r="AR119" s="18"/>
-      <c r="AS119" s="18"/>
-      <c r="AT119" s="18"/>
-      <c r="AU119" s="18"/>
-      <c r="AV119" s="18"/>
-      <c r="AW119" s="18"/>
-      <c r="AX119" s="18"/>
-    </row>
-    <row r="120" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D119" s="28"/>
+      <c r="E119" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="F119" s="28"/>
+      <c r="G119" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H119" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="I119" s="31">
+        <v>25000</v>
+      </c>
+      <c r="J119" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K119" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L119" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M119" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N119" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O119" s="28"/>
+      <c r="P119" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q119" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R119" s="34"/>
+      <c r="S119" s="34"/>
+      <c r="T119" s="34"/>
+      <c r="U119" s="34"/>
+      <c r="V119" s="34"/>
+      <c r="W119" s="34"/>
+      <c r="X119" s="34"/>
+      <c r="Y119" s="34"/>
+      <c r="Z119" s="35"/>
+      <c r="AA119" s="35"/>
+      <c r="AB119" s="35"/>
+      <c r="AC119" s="35"/>
+      <c r="AD119" s="35"/>
+      <c r="AE119" s="35"/>
+      <c r="AF119" s="35"/>
+      <c r="AG119" s="35"/>
+      <c r="AH119" s="35"/>
+      <c r="AI119" s="35"/>
+      <c r="AJ119" s="35"/>
+      <c r="AK119" s="35"/>
+      <c r="AL119" s="35"/>
+      <c r="AM119" s="35"/>
+      <c r="AN119" s="35"/>
+      <c r="AO119" s="35"/>
+      <c r="AP119" s="35"/>
+      <c r="AQ119" s="35"/>
+      <c r="AR119" s="35"/>
+      <c r="AS119" s="35"/>
+      <c r="AT119" s="35"/>
+      <c r="AU119" s="35"/>
+      <c r="AV119" s="35"/>
+      <c r="AW119" s="35"/>
+      <c r="AX119" s="35"/>
+    </row>
+    <row r="120" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="19"/>
       <c r="B120" s="20">
         <v>46079</v>
@@ -10341,25 +10356,23 @@
       </c>
       <c r="D120" s="21"/>
       <c r="E120" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F120" s="23">
-        <v>239298</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="F120" s="21"/>
       <c r="G120" s="22" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H120" s="22" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I120" s="24">
-        <v>68272.17</v>
+        <v>96500</v>
       </c>
       <c r="J120" s="22" t="b">
         <v>1</v>
       </c>
       <c r="K120" s="22" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L120" s="22" t="s">
         <v>21</v>
@@ -10372,7 +10385,9 @@
       </c>
       <c r="O120" s="21"/>
       <c r="P120" s="25"/>
-      <c r="Q120" s="25"/>
+      <c r="Q120" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="R120" s="17"/>
       <c r="S120" s="17"/>
       <c r="T120" s="17"/>
@@ -10420,7 +10435,7 @@
         <v>17</v>
       </c>
       <c r="F121" s="23">
-        <v>239302</v>
+        <v>239304</v>
       </c>
       <c r="G121" s="22" t="s">
         <v>18</v>
@@ -10429,7 +10444,7 @@
         <v>19</v>
       </c>
       <c r="I121" s="24">
-        <v>33965.33</v>
+        <v>50348.42</v>
       </c>
       <c r="J121" s="22" t="b">
         <v>1</v>
@@ -10496,7 +10511,7 @@
         <v>17</v>
       </c>
       <c r="F122" s="23">
-        <v>239277</v>
+        <v>239298</v>
       </c>
       <c r="G122" s="22" t="s">
         <v>18</v>
@@ -10505,7 +10520,7 @@
         <v>19</v>
       </c>
       <c r="I122" s="24">
-        <v>59591.360000000001</v>
+        <v>68272.17</v>
       </c>
       <c r="J122" s="22" t="b">
         <v>1</v>
@@ -10569,10 +10584,10 @@
       </c>
       <c r="D123" s="21"/>
       <c r="E123" s="22" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="F123" s="23">
-        <v>455202</v>
+        <v>239302</v>
       </c>
       <c r="G123" s="22" t="s">
         <v>18</v>
@@ -10581,7 +10596,7 @@
         <v>19</v>
       </c>
       <c r="I123" s="24">
-        <v>8400</v>
+        <v>33965.33</v>
       </c>
       <c r="J123" s="22" t="b">
         <v>1</v>
@@ -10645,19 +10660,19 @@
       </c>
       <c r="D124" s="21"/>
       <c r="E124" s="22" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="F124" s="23">
-        <v>132239</v>
+        <v>239277</v>
       </c>
       <c r="G124" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H124" s="22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I124" s="24">
-        <v>4556</v>
+        <v>59591.360000000001</v>
       </c>
       <c r="J124" s="22" t="b">
         <v>1</v>
@@ -10721,19 +10736,19 @@
       </c>
       <c r="D125" s="21"/>
       <c r="E125" s="22" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="F125" s="23">
-        <v>264292</v>
+        <v>455202</v>
       </c>
       <c r="G125" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H125" s="22" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="I125" s="24">
-        <v>208.77</v>
+        <v>8400</v>
       </c>
       <c r="J125" s="22" t="b">
         <v>1</v>
@@ -10790,17 +10805,17 @@
     <row r="126" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="19"/>
       <c r="B126" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C126" s="20">
         <v>46101</v>
       </c>
       <c r="D126" s="21"/>
       <c r="E126" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F126" s="23">
-        <v>10550</v>
+        <v>132239</v>
       </c>
       <c r="G126" s="22" t="s">
         <v>18</v>
@@ -10809,7 +10824,7 @@
         <v>25</v>
       </c>
       <c r="I126" s="24">
-        <v>15396</v>
+        <v>4556</v>
       </c>
       <c r="J126" s="22" t="b">
         <v>1</v>
@@ -10866,26 +10881,26 @@
     <row r="127" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="19"/>
       <c r="B127" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C127" s="20">
         <v>46101</v>
       </c>
       <c r="D127" s="21"/>
       <c r="E127" s="22" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="F127" s="23">
-        <v>8060</v>
+        <v>264292</v>
       </c>
       <c r="G127" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="I127" s="24">
-        <v>53488.32</v>
+        <v>208.77</v>
       </c>
       <c r="J127" s="22" t="b">
         <v>1</v>
@@ -10949,10 +10964,10 @@
       </c>
       <c r="D128" s="21"/>
       <c r="E128" s="22" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="F128" s="23">
-        <v>123589</v>
+        <v>10550</v>
       </c>
       <c r="G128" s="22" t="s">
         <v>18</v>
@@ -10961,7 +10976,7 @@
         <v>25</v>
       </c>
       <c r="I128" s="24">
-        <v>26875.16</v>
+        <v>15396</v>
       </c>
       <c r="J128" s="22" t="b">
         <v>1</v>
@@ -11025,19 +11040,19 @@
       </c>
       <c r="D129" s="21"/>
       <c r="E129" s="22" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="F129" s="23">
-        <v>123587</v>
+        <v>8060</v>
       </c>
       <c r="G129" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H129" s="22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I129" s="24">
-        <v>26875.16</v>
+        <v>53488.32</v>
       </c>
       <c r="J129" s="22" t="b">
         <v>1</v>
@@ -11091,189 +11106,187 @@
       <c r="AW129" s="18"/>
       <c r="AX129" s="18"/>
     </row>
-    <row r="130" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="26"/>
-      <c r="B130" s="27">
+    <row r="130" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="19"/>
+      <c r="B130" s="20">
         <v>46093</v>
       </c>
-      <c r="C130" s="27">
+      <c r="C130" s="20">
         <v>46101</v>
       </c>
-      <c r="D130" s="28"/>
-      <c r="E130" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F130" s="30">
-        <v>239278</v>
-      </c>
-      <c r="G130" s="29" t="s">
+      <c r="D130" s="21"/>
+      <c r="E130" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F130" s="23">
+        <v>123589</v>
+      </c>
+      <c r="G130" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H130" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I130" s="31">
-        <v>1784.35</v>
-      </c>
-      <c r="J130" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K130" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L130" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M130" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N130" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O130" s="28"/>
-      <c r="P130" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q130" s="33"/>
-      <c r="R130" s="34"/>
-      <c r="S130" s="34"/>
-      <c r="T130" s="34"/>
-      <c r="U130" s="34"/>
-      <c r="V130" s="34"/>
-      <c r="W130" s="34"/>
-      <c r="X130" s="34"/>
-      <c r="Y130" s="34"/>
-      <c r="Z130" s="35"/>
-      <c r="AA130" s="35"/>
-      <c r="AB130" s="35"/>
-      <c r="AC130" s="35"/>
-      <c r="AD130" s="35"/>
-      <c r="AE130" s="35"/>
-      <c r="AF130" s="35"/>
-      <c r="AG130" s="35"/>
-      <c r="AH130" s="35"/>
-      <c r="AI130" s="35"/>
-      <c r="AJ130" s="35"/>
-      <c r="AK130" s="35"/>
-      <c r="AL130" s="35"/>
-      <c r="AM130" s="35"/>
-      <c r="AN130" s="35"/>
-      <c r="AO130" s="35"/>
-      <c r="AP130" s="35"/>
-      <c r="AQ130" s="35"/>
-      <c r="AR130" s="35"/>
-      <c r="AS130" s="35"/>
-      <c r="AT130" s="35"/>
-      <c r="AU130" s="35"/>
-      <c r="AV130" s="35"/>
-      <c r="AW130" s="35"/>
-      <c r="AX130" s="35"/>
-    </row>
-    <row r="131" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="26"/>
-      <c r="B131" s="27">
+      <c r="H130" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I130" s="24">
+        <v>26875.16</v>
+      </c>
+      <c r="J130" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K130" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L130" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M130" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N130" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O130" s="21"/>
+      <c r="P130" s="25"/>
+      <c r="Q130" s="25"/>
+      <c r="R130" s="17"/>
+      <c r="S130" s="17"/>
+      <c r="T130" s="17"/>
+      <c r="U130" s="17"/>
+      <c r="V130" s="17"/>
+      <c r="W130" s="17"/>
+      <c r="X130" s="17"/>
+      <c r="Y130" s="17"/>
+      <c r="Z130" s="18"/>
+      <c r="AA130" s="18"/>
+      <c r="AB130" s="18"/>
+      <c r="AC130" s="18"/>
+      <c r="AD130" s="18"/>
+      <c r="AE130" s="18"/>
+      <c r="AF130" s="18"/>
+      <c r="AG130" s="18"/>
+      <c r="AH130" s="18"/>
+      <c r="AI130" s="18"/>
+      <c r="AJ130" s="18"/>
+      <c r="AK130" s="18"/>
+      <c r="AL130" s="18"/>
+      <c r="AM130" s="18"/>
+      <c r="AN130" s="18"/>
+      <c r="AO130" s="18"/>
+      <c r="AP130" s="18"/>
+      <c r="AQ130" s="18"/>
+      <c r="AR130" s="18"/>
+      <c r="AS130" s="18"/>
+      <c r="AT130" s="18"/>
+      <c r="AU130" s="18"/>
+      <c r="AV130" s="18"/>
+      <c r="AW130" s="18"/>
+      <c r="AX130" s="18"/>
+    </row>
+    <row r="131" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="19"/>
+      <c r="B131" s="20">
         <v>46093</v>
       </c>
-      <c r="C131" s="27">
+      <c r="C131" s="20">
         <v>46101</v>
       </c>
-      <c r="D131" s="28"/>
-      <c r="E131" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F131" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="G131" s="29" t="s">
+      <c r="D131" s="21"/>
+      <c r="E131" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F131" s="23">
+        <v>123587</v>
+      </c>
+      <c r="G131" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H131" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I131" s="31">
-        <v>15549.89</v>
-      </c>
-      <c r="J131" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K131" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L131" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M131" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N131" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O131" s="28"/>
-      <c r="P131" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q131" s="33"/>
-      <c r="R131" s="34"/>
-      <c r="S131" s="34"/>
-      <c r="T131" s="34"/>
-      <c r="U131" s="34"/>
-      <c r="V131" s="34"/>
-      <c r="W131" s="34"/>
-      <c r="X131" s="34"/>
-      <c r="Y131" s="34"/>
-      <c r="Z131" s="35"/>
-      <c r="AA131" s="35"/>
-      <c r="AB131" s="35"/>
-      <c r="AC131" s="35"/>
-      <c r="AD131" s="35"/>
-      <c r="AE131" s="35"/>
-      <c r="AF131" s="35"/>
-      <c r="AG131" s="35"/>
-      <c r="AH131" s="35"/>
-      <c r="AI131" s="35"/>
-      <c r="AJ131" s="35"/>
-      <c r="AK131" s="35"/>
-      <c r="AL131" s="35"/>
-      <c r="AM131" s="35"/>
-      <c r="AN131" s="35"/>
-      <c r="AO131" s="35"/>
-      <c r="AP131" s="35"/>
-      <c r="AQ131" s="35"/>
-      <c r="AR131" s="35"/>
-      <c r="AS131" s="35"/>
-      <c r="AT131" s="35"/>
-      <c r="AU131" s="35"/>
-      <c r="AV131" s="35"/>
-      <c r="AW131" s="35"/>
-      <c r="AX131" s="35"/>
+      <c r="H131" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I131" s="24">
+        <v>26875.16</v>
+      </c>
+      <c r="J131" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K131" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L131" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M131" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N131" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O131" s="21"/>
+      <c r="P131" s="25"/>
+      <c r="Q131" s="25"/>
+      <c r="R131" s="17"/>
+      <c r="S131" s="17"/>
+      <c r="T131" s="17"/>
+      <c r="U131" s="17"/>
+      <c r="V131" s="17"/>
+      <c r="W131" s="17"/>
+      <c r="X131" s="17"/>
+      <c r="Y131" s="17"/>
+      <c r="Z131" s="18"/>
+      <c r="AA131" s="18"/>
+      <c r="AB131" s="18"/>
+      <c r="AC131" s="18"/>
+      <c r="AD131" s="18"/>
+      <c r="AE131" s="18"/>
+      <c r="AF131" s="18"/>
+      <c r="AG131" s="18"/>
+      <c r="AH131" s="18"/>
+      <c r="AI131" s="18"/>
+      <c r="AJ131" s="18"/>
+      <c r="AK131" s="18"/>
+      <c r="AL131" s="18"/>
+      <c r="AM131" s="18"/>
+      <c r="AN131" s="18"/>
+      <c r="AO131" s="18"/>
+      <c r="AP131" s="18"/>
+      <c r="AQ131" s="18"/>
+      <c r="AR131" s="18"/>
+      <c r="AS131" s="18"/>
+      <c r="AT131" s="18"/>
+      <c r="AU131" s="18"/>
+      <c r="AV131" s="18"/>
+      <c r="AW131" s="18"/>
+      <c r="AX131" s="18"/>
     </row>
     <row r="132" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="26"/>
       <c r="B132" s="27">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C132" s="27">
         <v>46101</v>
       </c>
       <c r="D132" s="28"/>
       <c r="E132" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="F132" s="28"/>
+        <v>17</v>
+      </c>
+      <c r="F132" s="30">
+        <v>239278</v>
+      </c>
       <c r="G132" s="29" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H132" s="29" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="I132" s="31">
-        <v>5000</v>
+        <v>1784.35</v>
       </c>
       <c r="J132" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K132" s="29" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L132" s="29" t="s">
         <v>27</v>
@@ -11285,10 +11298,10 @@
         <v>28</v>
       </c>
       <c r="O132" s="28"/>
-      <c r="P132" s="33"/>
-      <c r="Q132" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="P132" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q132" s="33"/>
       <c r="R132" s="34"/>
       <c r="S132" s="34"/>
       <c r="T132" s="34"/>
@@ -11326,30 +11339,32 @@
     <row r="133" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="26"/>
       <c r="B133" s="27">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C133" s="27">
         <v>46101</v>
       </c>
       <c r="D133" s="28"/>
       <c r="E133" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F133" s="28"/>
+        <v>30</v>
+      </c>
+      <c r="F133" s="30" t="s">
+        <v>176</v>
+      </c>
       <c r="G133" s="29" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H133" s="29" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="I133" s="31">
-        <v>8000</v>
+        <v>15549.89</v>
       </c>
       <c r="J133" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K133" s="29" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L133" s="29" t="s">
         <v>27</v>
@@ -11362,11 +11377,9 @@
       </c>
       <c r="O133" s="28"/>
       <c r="P133" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q133" s="32" t="s">
-        <v>39</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Q133" s="33"/>
       <c r="R133" s="34"/>
       <c r="S133" s="34"/>
       <c r="T133" s="34"/>
@@ -11401,33 +11414,33 @@
       <c r="AW133" s="35"/>
       <c r="AX133" s="35"/>
     </row>
-    <row r="134" spans="1:50" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="26"/>
       <c r="B134" s="27">
-        <v>46092</v>
+        <v>46079</v>
       </c>
       <c r="C134" s="27">
         <v>46101</v>
       </c>
       <c r="D134" s="28"/>
       <c r="E134" s="29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F134" s="28"/>
       <c r="G134" s="29" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="H134" s="29" t="s">
-        <v>180</v>
+        <v>49</v>
       </c>
       <c r="I134" s="31">
-        <v>146.75</v>
+        <v>5000</v>
       </c>
       <c r="J134" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K134" s="29" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="L134" s="29" t="s">
         <v>27</v>
@@ -11438,11 +11451,11 @@
       <c r="N134" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O134" s="29" t="s">
-        <v>181</v>
-      </c>
+      <c r="O134" s="28"/>
       <c r="P134" s="33"/>
-      <c r="Q134" s="33"/>
+      <c r="Q134" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R134" s="34"/>
       <c r="S134" s="34"/>
       <c r="T134" s="34"/>
@@ -11480,30 +11493,30 @@
     <row r="135" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="26"/>
       <c r="B135" s="27">
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="C135" s="27">
         <v>46101</v>
       </c>
       <c r="D135" s="28"/>
       <c r="E135" s="29" t="s">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="F135" s="28"/>
       <c r="G135" s="29" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H135" s="29" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="I135" s="31">
-        <v>22800</v>
+        <v>8000</v>
       </c>
       <c r="J135" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K135" s="29" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L135" s="29" t="s">
         <v>27</v>
@@ -11514,13 +11527,13 @@
       <c r="N135" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O135" s="29" t="s">
-        <v>94</v>
-      </c>
+      <c r="O135" s="28"/>
       <c r="P135" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q135" s="33"/>
+        <v>178</v>
+      </c>
+      <c r="Q135" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R135" s="34"/>
       <c r="S135" s="34"/>
       <c r="T135" s="34"/>
@@ -11555,33 +11568,33 @@
       <c r="AW135" s="35"/>
       <c r="AX135" s="35"/>
     </row>
-    <row r="136" spans="1:50" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:50" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="26"/>
       <c r="B136" s="27">
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="C136" s="27">
         <v>46101</v>
       </c>
       <c r="D136" s="28"/>
       <c r="E136" s="29" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F136" s="28"/>
       <c r="G136" s="29" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H136" s="29" t="s">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="I136" s="31">
-        <v>88344</v>
+        <v>146.75</v>
       </c>
       <c r="J136" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K136" s="29" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L136" s="29" t="s">
         <v>27</v>
@@ -11593,11 +11606,9 @@
         <v>28</v>
       </c>
       <c r="O136" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="P136" s="32" t="s">
-        <v>175</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="P136" s="33"/>
       <c r="Q136" s="33"/>
       <c r="R136" s="34"/>
       <c r="S136" s="34"/>
@@ -11633,33 +11644,33 @@
       <c r="AW136" s="35"/>
       <c r="AX136" s="35"/>
     </row>
-    <row r="137" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="26"/>
       <c r="B137" s="27">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C137" s="27">
         <v>46101</v>
       </c>
       <c r="D137" s="28"/>
       <c r="E137" s="29" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="F137" s="28"/>
       <c r="G137" s="29" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H137" s="29" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I137" s="31">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="J137" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K137" s="29" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="L137" s="29" t="s">
         <v>27</v>
@@ -11670,8 +11681,12 @@
       <c r="N137" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O137" s="28"/>
-      <c r="P137" s="33"/>
+      <c r="O137" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="P137" s="32" t="s">
+        <v>183</v>
+      </c>
       <c r="Q137" s="33"/>
       <c r="R137" s="34"/>
       <c r="S137" s="34"/>
@@ -11707,6 +11722,158 @@
       <c r="AW137" s="35"/>
       <c r="AX137" s="35"/>
     </row>
+    <row r="138" spans="1:50" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="26"/>
+      <c r="B138" s="27">
+        <v>46071</v>
+      </c>
+      <c r="C138" s="27">
+        <v>46101</v>
+      </c>
+      <c r="D138" s="28"/>
+      <c r="E138" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F138" s="28"/>
+      <c r="G138" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H138" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I138" s="31">
+        <v>88344</v>
+      </c>
+      <c r="J138" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K138" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L138" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M138" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N138" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O138" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="P138" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q138" s="33"/>
+      <c r="R138" s="34"/>
+      <c r="S138" s="34"/>
+      <c r="T138" s="34"/>
+      <c r="U138" s="34"/>
+      <c r="V138" s="34"/>
+      <c r="W138" s="34"/>
+      <c r="X138" s="34"/>
+      <c r="Y138" s="34"/>
+      <c r="Z138" s="35"/>
+      <c r="AA138" s="35"/>
+      <c r="AB138" s="35"/>
+      <c r="AC138" s="35"/>
+      <c r="AD138" s="35"/>
+      <c r="AE138" s="35"/>
+      <c r="AF138" s="35"/>
+      <c r="AG138" s="35"/>
+      <c r="AH138" s="35"/>
+      <c r="AI138" s="35"/>
+      <c r="AJ138" s="35"/>
+      <c r="AK138" s="35"/>
+      <c r="AL138" s="35"/>
+      <c r="AM138" s="35"/>
+      <c r="AN138" s="35"/>
+      <c r="AO138" s="35"/>
+      <c r="AP138" s="35"/>
+      <c r="AQ138" s="35"/>
+      <c r="AR138" s="35"/>
+      <c r="AS138" s="35"/>
+      <c r="AT138" s="35"/>
+      <c r="AU138" s="35"/>
+      <c r="AV138" s="35"/>
+      <c r="AW138" s="35"/>
+      <c r="AX138" s="35"/>
+    </row>
+    <row r="139" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="26"/>
+      <c r="B139" s="27">
+        <v>46079</v>
+      </c>
+      <c r="C139" s="27">
+        <v>46101</v>
+      </c>
+      <c r="D139" s="28"/>
+      <c r="E139" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F139" s="28"/>
+      <c r="G139" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H139" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I139" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J139" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K139" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L139" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M139" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N139" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O139" s="28"/>
+      <c r="P139" s="33"/>
+      <c r="Q139" s="33"/>
+      <c r="R139" s="34"/>
+      <c r="S139" s="34"/>
+      <c r="T139" s="34"/>
+      <c r="U139" s="34"/>
+      <c r="V139" s="34"/>
+      <c r="W139" s="34"/>
+      <c r="X139" s="34"/>
+      <c r="Y139" s="34"/>
+      <c r="Z139" s="35"/>
+      <c r="AA139" s="35"/>
+      <c r="AB139" s="35"/>
+      <c r="AC139" s="35"/>
+      <c r="AD139" s="35"/>
+      <c r="AE139" s="35"/>
+      <c r="AF139" s="35"/>
+      <c r="AG139" s="35"/>
+      <c r="AH139" s="35"/>
+      <c r="AI139" s="35"/>
+      <c r="AJ139" s="35"/>
+      <c r="AK139" s="35"/>
+      <c r="AL139" s="35"/>
+      <c r="AM139" s="35"/>
+      <c r="AN139" s="35"/>
+      <c r="AO139" s="35"/>
+      <c r="AP139" s="35"/>
+      <c r="AQ139" s="35"/>
+      <c r="AR139" s="35"/>
+      <c r="AS139" s="35"/>
+      <c r="AT139" s="35"/>
+      <c r="AU139" s="35"/>
+      <c r="AV139" s="35"/>
+      <c r="AW139" s="35"/>
+      <c r="AX139" s="35"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/CAP_Semana_12.xlsx
+++ b/data/CAP_Semana_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Relatório_Felipe\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70285413-8C69-4042-85E1-4B506EA30FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE5CB57-40E8-420E-B54C-81A7C7BCF4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2130" windowWidth="20640" windowHeight="11040" xr2:uid="{8D2EDE68-77A0-48FE-A03B-A2F0182CE2F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D2EDE68-77A0-48FE-A03B-A2F0182CE2F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="198">
   <si>
     <t>id</t>
   </si>
@@ -617,6 +617,24 @@
   </si>
   <si>
     <t>82660000012 7 42300097091 7 11027649744 0 00002995373 4</t>
+  </si>
+  <si>
+    <t>REEMBOLSO LUCIANA BALAGUER</t>
+  </si>
+  <si>
+    <t>167.786.868-63</t>
+  </si>
+  <si>
+    <t>Referente ao aparelho ar Condicionado sala Tortuga’s</t>
+  </si>
+  <si>
+    <t>CHEGOU EM 13-03-2026 - GIRUS MÓVEIS</t>
+  </si>
+  <si>
+    <t>SABESP - AL GLÓRIA 902</t>
+  </si>
+  <si>
+    <t>SABESP - AL GLÓRIA 903</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05925770-A8EB-4BF6-A793-5E873493123B}">
-  <dimension ref="A1:AX139"/>
+  <dimension ref="A1:AX143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1886,17 +1904,17 @@
       <c r="AW7" s="35"/>
       <c r="AX7" s="35"/>
     </row>
-    <row r="8" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
       <c r="B8" s="27">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="C8" s="27">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="D8" s="28"/>
       <c r="E8" s="29" t="s">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="F8" s="28"/>
       <c r="G8" s="29" t="s">
@@ -1906,13 +1924,13 @@
         <v>33</v>
       </c>
       <c r="I8" s="31">
-        <v>1536.3</v>
+        <v>5319.51</v>
       </c>
       <c r="J8" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="L8" s="29" t="s">
         <v>27</v>
@@ -1923,8 +1941,12 @@
       <c r="N8" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="28"/>
-      <c r="P8" s="33"/>
+      <c r="O8" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>194</v>
+      </c>
       <c r="Q8" s="33"/>
       <c r="R8" s="34"/>
       <c r="S8" s="34"/>
@@ -1960,83 +1982,81 @@
       <c r="AW8" s="35"/>
       <c r="AX8" s="35"/>
     </row>
-    <row r="9" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20">
+    <row r="9" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27">
         <v>46079</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="27">
         <v>46096</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="24">
-        <v>91850</v>
-      </c>
-      <c r="J9" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="21"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="18"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="18"/>
-      <c r="AD9" s="18"/>
-      <c r="AE9" s="18"/>
-      <c r="AF9" s="18"/>
-      <c r="AG9" s="18"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="18"/>
-      <c r="AJ9" s="18"/>
-      <c r="AK9" s="18"/>
-      <c r="AL9" s="18"/>
-      <c r="AM9" s="18"/>
-      <c r="AN9" s="18"/>
-      <c r="AO9" s="18"/>
-      <c r="AP9" s="18"/>
-      <c r="AQ9" s="18"/>
-      <c r="AR9" s="18"/>
-      <c r="AS9" s="18"/>
-      <c r="AT9" s="18"/>
-      <c r="AU9" s="18"/>
-      <c r="AV9" s="18"/>
-      <c r="AW9" s="18"/>
-      <c r="AX9" s="18"/>
-    </row>
-    <row r="10" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="28"/>
+      <c r="E9" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="31">
+        <v>1536.3</v>
+      </c>
+      <c r="J9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" s="28"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="34"/>
+      <c r="V9" s="34"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="34"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="35"/>
+      <c r="AC9" s="35"/>
+      <c r="AD9" s="35"/>
+      <c r="AE9" s="35"/>
+      <c r="AF9" s="35"/>
+      <c r="AG9" s="35"/>
+      <c r="AH9" s="35"/>
+      <c r="AI9" s="35"/>
+      <c r="AJ9" s="35"/>
+      <c r="AK9" s="35"/>
+      <c r="AL9" s="35"/>
+      <c r="AM9" s="35"/>
+      <c r="AN9" s="35"/>
+      <c r="AO9" s="35"/>
+      <c r="AP9" s="35"/>
+      <c r="AQ9" s="35"/>
+      <c r="AR9" s="35"/>
+      <c r="AS9" s="35"/>
+      <c r="AT9" s="35"/>
+      <c r="AU9" s="35"/>
+      <c r="AV9" s="35"/>
+      <c r="AW9" s="35"/>
+      <c r="AX9" s="35"/>
+    </row>
+    <row r="10" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
       <c r="B10" s="20">
         <v>46079</v>
@@ -2046,25 +2066,23 @@
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="23">
-        <v>239230</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="22" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I10" s="24">
-        <v>54012.14</v>
+        <v>91850</v>
       </c>
       <c r="J10" s="22" t="b">
         <v>1</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="L10" s="22" t="s">
         <v>21</v>
@@ -2077,7 +2095,9 @@
       </c>
       <c r="O10" s="21"/>
       <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
       <c r="T10" s="17"/>
@@ -2125,7 +2145,7 @@
         <v>17</v>
       </c>
       <c r="F11" s="23">
-        <v>239251</v>
+        <v>239230</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>18</v>
@@ -2134,7 +2154,7 @@
         <v>19</v>
       </c>
       <c r="I11" s="24">
-        <v>38256.19</v>
+        <v>54012.14</v>
       </c>
       <c r="J11" s="22" t="b">
         <v>1</v>
@@ -2201,7 +2221,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="23">
-        <v>239233</v>
+        <v>239251</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>18</v>
@@ -2210,7 +2230,7 @@
         <v>19</v>
       </c>
       <c r="I12" s="24">
-        <v>51600.43</v>
+        <v>38256.19</v>
       </c>
       <c r="J12" s="22" t="b">
         <v>1</v>
@@ -2274,10 +2294,10 @@
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="22" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F13" s="23">
-        <v>403</v>
+        <v>239233</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>18</v>
@@ -2286,7 +2306,7 @@
         <v>19</v>
       </c>
       <c r="I13" s="24">
-        <v>16632</v>
+        <v>51600.43</v>
       </c>
       <c r="J13" s="22" t="b">
         <v>1</v>
@@ -2340,83 +2360,81 @@
       <c r="AW13" s="18"/>
       <c r="AX13" s="18"/>
     </row>
-    <row r="14" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
-        <v>46093</v>
-      </c>
-      <c r="C14" s="27">
+    <row r="14" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="19"/>
+      <c r="B14" s="20">
+        <v>46079</v>
+      </c>
+      <c r="C14" s="20">
         <v>46096</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="30">
-        <v>239190</v>
-      </c>
-      <c r="G14" s="29" t="s">
+      <c r="D14" s="21"/>
+      <c r="E14" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="23">
+        <v>403</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="29" t="s">
+      <c r="H14" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="31">
-        <v>3763.46</v>
-      </c>
-      <c r="J14" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="28"/>
-      <c r="P14" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="34"/>
-      <c r="X14" s="34"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="35"/>
-      <c r="AC14" s="35"/>
-      <c r="AD14" s="35"/>
-      <c r="AE14" s="35"/>
-      <c r="AF14" s="35"/>
-      <c r="AG14" s="35"/>
-      <c r="AH14" s="35"/>
-      <c r="AI14" s="35"/>
-      <c r="AJ14" s="35"/>
-      <c r="AK14" s="35"/>
-      <c r="AL14" s="35"/>
-      <c r="AM14" s="35"/>
-      <c r="AN14" s="35"/>
-      <c r="AO14" s="35"/>
-      <c r="AP14" s="35"/>
-      <c r="AQ14" s="35"/>
-      <c r="AR14" s="35"/>
-      <c r="AS14" s="35"/>
-      <c r="AT14" s="35"/>
-      <c r="AU14" s="35"/>
-      <c r="AV14" s="35"/>
-      <c r="AW14" s="35"/>
-      <c r="AX14" s="35"/>
+      <c r="I14" s="24">
+        <v>16632</v>
+      </c>
+      <c r="J14" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="21"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="18"/>
+      <c r="AA14" s="18"/>
+      <c r="AB14" s="18"/>
+      <c r="AC14" s="18"/>
+      <c r="AD14" s="18"/>
+      <c r="AE14" s="18"/>
+      <c r="AF14" s="18"/>
+      <c r="AG14" s="18"/>
+      <c r="AH14" s="18"/>
+      <c r="AI14" s="18"/>
+      <c r="AJ14" s="18"/>
+      <c r="AK14" s="18"/>
+      <c r="AL14" s="18"/>
+      <c r="AM14" s="18"/>
+      <c r="AN14" s="18"/>
+      <c r="AO14" s="18"/>
+      <c r="AP14" s="18"/>
+      <c r="AQ14" s="18"/>
+      <c r="AR14" s="18"/>
+      <c r="AS14" s="18"/>
+      <c r="AT14" s="18"/>
+      <c r="AU14" s="18"/>
+      <c r="AV14" s="18"/>
+      <c r="AW14" s="18"/>
+      <c r="AX14" s="18"/>
     </row>
     <row r="15" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
@@ -2431,7 +2449,7 @@
         <v>17</v>
       </c>
       <c r="F15" s="30">
-        <v>239181</v>
+        <v>239190</v>
       </c>
       <c r="G15" s="29" t="s">
         <v>18</v>
@@ -2440,7 +2458,7 @@
         <v>19</v>
       </c>
       <c r="I15" s="31">
-        <v>2666.43</v>
+        <v>3763.46</v>
       </c>
       <c r="J15" s="29" t="b">
         <v>1</v>
@@ -2506,10 +2524,10 @@
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>42</v>
+        <v>17</v>
+      </c>
+      <c r="F16" s="30">
+        <v>239181</v>
       </c>
       <c r="G16" s="29" t="s">
         <v>18</v>
@@ -2518,7 +2536,7 @@
         <v>19</v>
       </c>
       <c r="I16" s="31">
-        <v>56055.03</v>
+        <v>2666.43</v>
       </c>
       <c r="J16" s="29" t="b">
         <v>1</v>
@@ -2577,30 +2595,32 @@
     <row r="17" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="26"/>
       <c r="B17" s="27">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C17" s="27">
         <v>46096</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="28"/>
+        <v>30</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>42</v>
+      </c>
       <c r="G17" s="29" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I17" s="31">
-        <v>1949.26</v>
+        <v>56055.03</v>
       </c>
       <c r="J17" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K17" s="29" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L17" s="29" t="s">
         <v>27</v>
@@ -2613,11 +2633,9 @@
       </c>
       <c r="O17" s="28"/>
       <c r="P17" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q17" s="32" t="s">
-        <v>39</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q17" s="33"/>
       <c r="R17" s="34"/>
       <c r="S17" s="34"/>
       <c r="T17" s="34"/>
@@ -2655,30 +2673,30 @@
     <row r="18" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
       <c r="B18" s="27">
-        <v>46091</v>
+        <v>46079</v>
       </c>
       <c r="C18" s="27">
         <v>46096</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" s="29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I18" s="31">
-        <v>5000</v>
+        <v>1949.26</v>
       </c>
       <c r="J18" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="L18" s="29" t="s">
         <v>27</v>
@@ -2691,9 +2709,11 @@
       </c>
       <c r="O18" s="28"/>
       <c r="P18" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q18" s="33"/>
+        <v>44</v>
+      </c>
+      <c r="Q18" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R18" s="34"/>
       <c r="S18" s="34"/>
       <c r="T18" s="34"/>
@@ -2731,30 +2751,30 @@
     <row r="19" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="26"/>
       <c r="B19" s="27">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="C19" s="27">
         <v>46096</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="29" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" s="29" t="s">
         <v>36</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I19" s="31">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="J19" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K19" s="29" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L19" s="29" t="s">
         <v>27</v>
@@ -2766,10 +2786,10 @@
         <v>28</v>
       </c>
       <c r="O19" s="28"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="P19" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" s="33"/>
       <c r="R19" s="34"/>
       <c r="S19" s="34"/>
       <c r="T19" s="34"/>
@@ -2814,7 +2834,7 @@
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" s="29" t="s">
@@ -2881,306 +2901,308 @@
       <c r="AX20" s="35"/>
     </row>
     <row r="21" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>46079</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="27">
         <v>46096</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22" t="s">
+      <c r="D21" s="28"/>
+      <c r="E21" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" s="31">
+        <v>2000</v>
+      </c>
+      <c r="J21" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="L21" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" s="28"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34"/>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="34"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="35"/>
+      <c r="AD21" s="35"/>
+      <c r="AE21" s="35"/>
+      <c r="AF21" s="35"/>
+      <c r="AG21" s="35"/>
+      <c r="AH21" s="35"/>
+      <c r="AI21" s="35"/>
+      <c r="AJ21" s="35"/>
+      <c r="AK21" s="35"/>
+      <c r="AL21" s="35"/>
+      <c r="AM21" s="35"/>
+      <c r="AN21" s="35"/>
+      <c r="AO21" s="35"/>
+      <c r="AP21" s="35"/>
+      <c r="AQ21" s="35"/>
+      <c r="AR21" s="35"/>
+      <c r="AS21" s="35"/>
+      <c r="AT21" s="35"/>
+      <c r="AU21" s="35"/>
+      <c r="AV21" s="35"/>
+      <c r="AW21" s="35"/>
+      <c r="AX21" s="35"/>
+    </row>
+    <row r="22" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="19"/>
+      <c r="B22" s="20">
+        <v>46079</v>
+      </c>
+      <c r="C22" s="20">
+        <v>46096</v>
+      </c>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="22" t="s">
+      <c r="F22" s="21"/>
+      <c r="G22" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H22" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I22" s="24">
         <v>10959.65</v>
       </c>
-      <c r="J21" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="22" t="s">
+      <c r="J22" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="L21" s="22" t="s">
+      <c r="L22" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N21" s="22" t="s">
+      <c r="M22" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="O21" s="21"/>
-      <c r="P21" s="36" t="s">
+      <c r="O22" s="21"/>
+      <c r="P22" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="Q21" s="36" t="s">
+      <c r="Q22" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="18"/>
-      <c r="AC21" s="18"/>
-      <c r="AD21" s="18"/>
-      <c r="AE21" s="18"/>
-      <c r="AF21" s="18"/>
-      <c r="AG21" s="18"/>
-      <c r="AH21" s="18"/>
-      <c r="AI21" s="18"/>
-      <c r="AJ21" s="18"/>
-      <c r="AK21" s="18"/>
-      <c r="AL21" s="18"/>
-      <c r="AM21" s="18"/>
-      <c r="AN21" s="18"/>
-      <c r="AO21" s="18"/>
-      <c r="AP21" s="18"/>
-      <c r="AQ21" s="18"/>
-      <c r="AR21" s="18"/>
-      <c r="AS21" s="18"/>
-      <c r="AT21" s="18"/>
-      <c r="AU21" s="18"/>
-      <c r="AV21" s="18"/>
-      <c r="AW21" s="18"/>
-      <c r="AX21" s="18"/>
-    </row>
-    <row r="22" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="18"/>
+      <c r="AA22" s="18"/>
+      <c r="AB22" s="18"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="18"/>
+      <c r="AE22" s="18"/>
+      <c r="AF22" s="18"/>
+      <c r="AG22" s="18"/>
+      <c r="AH22" s="18"/>
+      <c r="AI22" s="18"/>
+      <c r="AJ22" s="18"/>
+      <c r="AK22" s="18"/>
+      <c r="AL22" s="18"/>
+      <c r="AM22" s="18"/>
+      <c r="AN22" s="18"/>
+      <c r="AO22" s="18"/>
+      <c r="AP22" s="18"/>
+      <c r="AQ22" s="18"/>
+      <c r="AR22" s="18"/>
+      <c r="AS22" s="18"/>
+      <c r="AT22" s="18"/>
+      <c r="AU22" s="18"/>
+      <c r="AV22" s="18"/>
+      <c r="AW22" s="18"/>
+      <c r="AX22" s="18"/>
+    </row>
+    <row r="23" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
         <v>46079</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C23" s="27">
         <v>46096</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29" t="s">
+      <c r="D23" s="28"/>
+      <c r="E23" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="28"/>
-      <c r="G22" s="29" t="s">
+      <c r="F23" s="28"/>
+      <c r="G23" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="29" t="s">
+      <c r="H23" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I23" s="31">
         <v>112029.24</v>
       </c>
-      <c r="J22" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="29" t="s">
+      <c r="J23" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="L22" s="29" t="s">
+      <c r="L23" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="M22" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="29" t="s">
+      <c r="M23" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O22" s="28"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="35"/>
-      <c r="AC22" s="35"/>
-      <c r="AD22" s="35"/>
-      <c r="AE22" s="35"/>
-      <c r="AF22" s="35"/>
-      <c r="AG22" s="35"/>
-      <c r="AH22" s="35"/>
-      <c r="AI22" s="35"/>
-      <c r="AJ22" s="35"/>
-      <c r="AK22" s="35"/>
-      <c r="AL22" s="35"/>
-      <c r="AM22" s="35"/>
-      <c r="AN22" s="35"/>
-      <c r="AO22" s="35"/>
-      <c r="AP22" s="35"/>
-      <c r="AQ22" s="35"/>
-      <c r="AR22" s="35"/>
-      <c r="AS22" s="35"/>
-      <c r="AT22" s="35"/>
-      <c r="AU22" s="35"/>
-      <c r="AV22" s="35"/>
-      <c r="AW22" s="35"/>
-      <c r="AX22" s="35"/>
-    </row>
-    <row r="23" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="20">
+      <c r="O23" s="28"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="35"/>
+      <c r="AD23" s="35"/>
+      <c r="AE23" s="35"/>
+      <c r="AF23" s="35"/>
+      <c r="AG23" s="35"/>
+      <c r="AH23" s="35"/>
+      <c r="AI23" s="35"/>
+      <c r="AJ23" s="35"/>
+      <c r="AK23" s="35"/>
+      <c r="AL23" s="35"/>
+      <c r="AM23" s="35"/>
+      <c r="AN23" s="35"/>
+      <c r="AO23" s="35"/>
+      <c r="AP23" s="35"/>
+      <c r="AQ23" s="35"/>
+      <c r="AR23" s="35"/>
+      <c r="AS23" s="35"/>
+      <c r="AT23" s="35"/>
+      <c r="AU23" s="35"/>
+      <c r="AV23" s="35"/>
+      <c r="AW23" s="35"/>
+      <c r="AX23" s="35"/>
+    </row>
+    <row r="24" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20">
         <v>46079</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C24" s="20">
         <v>46096</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="22" t="s">
+      <c r="D24" s="21"/>
+      <c r="E24" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="22" t="s">
+      <c r="F24" s="21"/>
+      <c r="G24" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H24" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I24" s="24">
         <v>38156.089999999997</v>
       </c>
-      <c r="J23" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="22" t="s">
+      <c r="J24" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="L23" s="22" t="s">
+      <c r="L24" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N23" s="22" t="s">
+      <c r="M24" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="O23" s="21"/>
-      <c r="P23" s="36" t="s">
+      <c r="O24" s="21"/>
+      <c r="P24" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="18"/>
-      <c r="AA23" s="18"/>
-      <c r="AB23" s="18"/>
-      <c r="AC23" s="18"/>
-      <c r="AD23" s="18"/>
-      <c r="AE23" s="18"/>
-      <c r="AF23" s="18"/>
-      <c r="AG23" s="18"/>
-      <c r="AH23" s="18"/>
-      <c r="AI23" s="18"/>
-      <c r="AJ23" s="18"/>
-      <c r="AK23" s="18"/>
-      <c r="AL23" s="18"/>
-      <c r="AM23" s="18"/>
-      <c r="AN23" s="18"/>
-      <c r="AO23" s="18"/>
-      <c r="AP23" s="18"/>
-      <c r="AQ23" s="18"/>
-      <c r="AR23" s="18"/>
-      <c r="AS23" s="18"/>
-      <c r="AT23" s="18"/>
-      <c r="AU23" s="18"/>
-      <c r="AV23" s="18"/>
-      <c r="AW23" s="18"/>
-      <c r="AX23" s="18"/>
-    </row>
-    <row r="24" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
-        <v>46079</v>
-      </c>
-      <c r="C24" s="27">
-        <v>46096</v>
-      </c>
-      <c r="D24" s="28"/>
-      <c r="E24" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="31">
-        <v>4467.6499999999996</v>
-      </c>
-      <c r="J24" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M24" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N24" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O24" s="28"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="34"/>
-      <c r="W24" s="34"/>
-      <c r="X24" s="34"/>
-      <c r="Y24" s="34"/>
-      <c r="Z24" s="35"/>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="35"/>
-      <c r="AC24" s="35"/>
-      <c r="AD24" s="35"/>
-      <c r="AE24" s="35"/>
-      <c r="AF24" s="35"/>
-      <c r="AG24" s="35"/>
-      <c r="AH24" s="35"/>
-      <c r="AI24" s="35"/>
-      <c r="AJ24" s="35"/>
-      <c r="AK24" s="35"/>
-      <c r="AL24" s="35"/>
-      <c r="AM24" s="35"/>
-      <c r="AN24" s="35"/>
-      <c r="AO24" s="35"/>
-      <c r="AP24" s="35"/>
-      <c r="AQ24" s="35"/>
-      <c r="AR24" s="35"/>
-      <c r="AS24" s="35"/>
-      <c r="AT24" s="35"/>
-      <c r="AU24" s="35"/>
-      <c r="AV24" s="35"/>
-      <c r="AW24" s="35"/>
-      <c r="AX24" s="35"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="18"/>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="18"/>
+      <c r="AE24" s="18"/>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="18"/>
+      <c r="AH24" s="18"/>
+      <c r="AI24" s="18"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="18"/>
+      <c r="AL24" s="18"/>
+      <c r="AM24" s="18"/>
+      <c r="AN24" s="18"/>
+      <c r="AO24" s="18"/>
+      <c r="AP24" s="18"/>
+      <c r="AQ24" s="18"/>
+      <c r="AR24" s="18"/>
+      <c r="AS24" s="18"/>
+      <c r="AT24" s="18"/>
+      <c r="AU24" s="18"/>
+      <c r="AV24" s="18"/>
+      <c r="AW24" s="18"/>
+      <c r="AX24" s="18"/>
     </row>
     <row r="25" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="26"/>
@@ -3192,7 +3214,7 @@
       </c>
       <c r="D25" s="28"/>
       <c r="E25" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F25" s="28"/>
       <c r="G25" s="29" t="s">
@@ -3202,7 +3224,7 @@
         <v>33</v>
       </c>
       <c r="I25" s="31">
-        <v>8113.24</v>
+        <v>4467.6499999999996</v>
       </c>
       <c r="J25" s="29" t="b">
         <v>1</v>
@@ -3257,78 +3279,78 @@
       <c r="AX25" s="35"/>
     </row>
     <row r="26" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="20">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <v>46079</v>
       </c>
-      <c r="C26" s="20">
-        <v>46097</v>
-      </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="21"/>
-      <c r="G26" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="I26" s="24">
-        <v>34171.46</v>
-      </c>
-      <c r="J26" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="L26" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O26" s="21"/>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="18"/>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="18"/>
-      <c r="AG26" s="18"/>
-      <c r="AH26" s="18"/>
-      <c r="AI26" s="18"/>
-      <c r="AJ26" s="18"/>
-      <c r="AK26" s="18"/>
-      <c r="AL26" s="18"/>
-      <c r="AM26" s="18"/>
-      <c r="AN26" s="18"/>
-      <c r="AO26" s="18"/>
-      <c r="AP26" s="18"/>
-      <c r="AQ26" s="18"/>
-      <c r="AR26" s="18"/>
-      <c r="AS26" s="18"/>
-      <c r="AT26" s="18"/>
-      <c r="AU26" s="18"/>
-      <c r="AV26" s="18"/>
-      <c r="AW26" s="18"/>
-      <c r="AX26" s="18"/>
+      <c r="C26" s="27">
+        <v>46096</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="28"/>
+      <c r="G26" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="31">
+        <v>8113.24</v>
+      </c>
+      <c r="J26" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O26" s="28"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="34"/>
+      <c r="V26" s="34"/>
+      <c r="W26" s="34"/>
+      <c r="X26" s="34"/>
+      <c r="Y26" s="34"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="35"/>
+      <c r="AC26" s="35"/>
+      <c r="AD26" s="35"/>
+      <c r="AE26" s="35"/>
+      <c r="AF26" s="35"/>
+      <c r="AG26" s="35"/>
+      <c r="AH26" s="35"/>
+      <c r="AI26" s="35"/>
+      <c r="AJ26" s="35"/>
+      <c r="AK26" s="35"/>
+      <c r="AL26" s="35"/>
+      <c r="AM26" s="35"/>
+      <c r="AN26" s="35"/>
+      <c r="AO26" s="35"/>
+      <c r="AP26" s="35"/>
+      <c r="AQ26" s="35"/>
+      <c r="AR26" s="35"/>
+      <c r="AS26" s="35"/>
+      <c r="AT26" s="35"/>
+      <c r="AU26" s="35"/>
+      <c r="AV26" s="35"/>
+      <c r="AW26" s="35"/>
+      <c r="AX26" s="35"/>
     </row>
     <row r="27" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19"/>
@@ -3340,25 +3362,23 @@
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="23">
-        <v>450699</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="F27" s="21"/>
       <c r="G27" s="22" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="I27" s="24">
-        <v>16411.240000000002</v>
+        <v>34171.46</v>
       </c>
       <c r="J27" s="22" t="b">
         <v>1</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="L27" s="22" t="s">
         <v>21</v>
@@ -3416,19 +3436,19 @@
       </c>
       <c r="D28" s="21"/>
       <c r="E28" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F28" s="23">
-        <v>57825</v>
+        <v>450699</v>
       </c>
       <c r="G28" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I28" s="24">
-        <v>16470.32</v>
+        <v>16411.240000000002</v>
       </c>
       <c r="J28" s="22" t="b">
         <v>1</v>
@@ -3495,7 +3515,7 @@
         <v>67</v>
       </c>
       <c r="F29" s="23">
-        <v>57999</v>
+        <v>57825</v>
       </c>
       <c r="G29" s="22" t="s">
         <v>18</v>
@@ -3504,7 +3524,7 @@
         <v>25</v>
       </c>
       <c r="I29" s="24">
-        <v>10881.82</v>
+        <v>16470.32</v>
       </c>
       <c r="J29" s="22" t="b">
         <v>1</v>
@@ -3568,19 +3588,19 @@
       </c>
       <c r="D30" s="21"/>
       <c r="E30" s="22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F30" s="23">
-        <v>454961</v>
+        <v>57999</v>
       </c>
       <c r="G30" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I30" s="24">
-        <v>12600</v>
+        <v>10881.82</v>
       </c>
       <c r="J30" s="22" t="b">
         <v>1</v>
@@ -3644,10 +3664,10 @@
       </c>
       <c r="D31" s="21"/>
       <c r="E31" s="22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F31" s="23">
-        <v>536</v>
+        <v>454961</v>
       </c>
       <c r="G31" s="22" t="s">
         <v>18</v>
@@ -3656,7 +3676,7 @@
         <v>19</v>
       </c>
       <c r="I31" s="24">
-        <v>4637.5</v>
+        <v>12600</v>
       </c>
       <c r="J31" s="22" t="b">
         <v>1</v>
@@ -3713,26 +3733,26 @@
     <row r="32" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19"/>
       <c r="B32" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C32" s="20">
         <v>46097</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F32" s="23">
-        <v>30505</v>
+        <v>536</v>
       </c>
       <c r="G32" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I32" s="24">
-        <v>2676.24</v>
+        <v>4637.5</v>
       </c>
       <c r="J32" s="22" t="b">
         <v>1</v>
@@ -3796,19 +3816,19 @@
       </c>
       <c r="D33" s="21"/>
       <c r="E33" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33" s="23">
-        <v>1852</v>
+        <v>30505</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I33" s="24">
-        <v>5848</v>
+        <v>2676.24</v>
       </c>
       <c r="J33" s="22" t="b">
         <v>1</v>
@@ -3872,19 +3892,19 @@
       </c>
       <c r="D34" s="21"/>
       <c r="E34" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F34" s="23">
-        <v>123358</v>
+        <v>1852</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I34" s="24">
-        <v>31001.439999999999</v>
+        <v>5848</v>
       </c>
       <c r="J34" s="22" t="b">
         <v>1</v>
@@ -3951,7 +3971,7 @@
         <v>72</v>
       </c>
       <c r="F35" s="23">
-        <v>123356</v>
+        <v>123358</v>
       </c>
       <c r="G35" s="22" t="s">
         <v>18</v>
@@ -4014,109 +4034,109 @@
       <c r="AW35" s="18"/>
       <c r="AX35" s="18"/>
     </row>
-    <row r="36" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="26"/>
-      <c r="B36" s="27">
-        <v>46079</v>
-      </c>
-      <c r="C36" s="27">
+    <row r="36" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="19"/>
+      <c r="B36" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C36" s="20">
         <v>46097</v>
       </c>
-      <c r="D36" s="28"/>
-      <c r="E36" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="I36" s="31">
-        <v>35000</v>
-      </c>
-      <c r="J36" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="L36" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M36" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N36" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O36" s="28"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="34"/>
-      <c r="W36" s="34"/>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="35"/>
-      <c r="AA36" s="35"/>
-      <c r="AB36" s="35"/>
-      <c r="AC36" s="35"/>
-      <c r="AD36" s="35"/>
-      <c r="AE36" s="35"/>
-      <c r="AF36" s="35"/>
-      <c r="AG36" s="35"/>
-      <c r="AH36" s="35"/>
-      <c r="AI36" s="35"/>
-      <c r="AJ36" s="35"/>
-      <c r="AK36" s="35"/>
-      <c r="AL36" s="35"/>
-      <c r="AM36" s="35"/>
-      <c r="AN36" s="35"/>
-      <c r="AO36" s="35"/>
-      <c r="AP36" s="35"/>
-      <c r="AQ36" s="35"/>
-      <c r="AR36" s="35"/>
-      <c r="AS36" s="35"/>
-      <c r="AT36" s="35"/>
-      <c r="AU36" s="35"/>
-      <c r="AV36" s="35"/>
-      <c r="AW36" s="35"/>
-      <c r="AX36" s="35"/>
-    </row>
-    <row r="37" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="21"/>
+      <c r="E36" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="23">
+        <v>123356</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" s="24">
+        <v>31001.439999999999</v>
+      </c>
+      <c r="J36" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="21"/>
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
+      <c r="Z36" s="18"/>
+      <c r="AA36" s="18"/>
+      <c r="AB36" s="18"/>
+      <c r="AC36" s="18"/>
+      <c r="AD36" s="18"/>
+      <c r="AE36" s="18"/>
+      <c r="AF36" s="18"/>
+      <c r="AG36" s="18"/>
+      <c r="AH36" s="18"/>
+      <c r="AI36" s="18"/>
+      <c r="AJ36" s="18"/>
+      <c r="AK36" s="18"/>
+      <c r="AL36" s="18"/>
+      <c r="AM36" s="18"/>
+      <c r="AN36" s="18"/>
+      <c r="AO36" s="18"/>
+      <c r="AP36" s="18"/>
+      <c r="AQ36" s="18"/>
+      <c r="AR36" s="18"/>
+      <c r="AS36" s="18"/>
+      <c r="AT36" s="18"/>
+      <c r="AU36" s="18"/>
+      <c r="AV36" s="18"/>
+      <c r="AW36" s="18"/>
+      <c r="AX36" s="18"/>
+    </row>
+    <row r="37" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="26"/>
       <c r="B37" s="27">
-        <v>46056</v>
+        <v>46079</v>
       </c>
       <c r="C37" s="27">
         <v>46097</v>
       </c>
       <c r="D37" s="28"/>
       <c r="E37" s="29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F37" s="28"/>
       <c r="G37" s="29" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I37" s="31">
-        <v>14050</v>
+        <v>35000</v>
       </c>
       <c r="J37" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K37" s="29" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="L37" s="29" t="s">
         <v>27</v>
@@ -4127,13 +4147,11 @@
       <c r="N37" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O37" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P37" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q37" s="33"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R37" s="34"/>
       <c r="S37" s="34"/>
       <c r="T37" s="34"/>
@@ -4171,7 +4189,7 @@
     <row r="38" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="26"/>
       <c r="B38" s="27">
-        <v>46077</v>
+        <v>46056</v>
       </c>
       <c r="C38" s="27">
         <v>46097</v>
@@ -4188,7 +4206,7 @@
         <v>19</v>
       </c>
       <c r="I38" s="31">
-        <v>3075</v>
+        <v>14050</v>
       </c>
       <c r="J38" s="29" t="b">
         <v>1</v>
@@ -4209,7 +4227,7 @@
         <v>76</v>
       </c>
       <c r="P38" s="32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q38" s="33"/>
       <c r="R38" s="34"/>
@@ -4246,33 +4264,33 @@
       <c r="AW38" s="35"/>
       <c r="AX38" s="35"/>
     </row>
-    <row r="39" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="26"/>
       <c r="B39" s="27">
-        <v>46086</v>
+        <v>46077</v>
       </c>
       <c r="C39" s="27">
         <v>46097</v>
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="29" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F39" s="28"/>
       <c r="G39" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H39" s="29" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="I39" s="31">
-        <v>3807</v>
+        <v>3075</v>
       </c>
       <c r="J39" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K39" s="29" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="L39" s="29" t="s">
         <v>27</v>
@@ -4283,9 +4301,11 @@
       <c r="N39" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O39" s="28"/>
-      <c r="P39" s="32">
-        <v>41</v>
+      <c r="O39" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="P39" s="32" t="s">
+        <v>78</v>
       </c>
       <c r="Q39" s="33"/>
       <c r="R39" s="34"/>
@@ -4342,7 +4362,7 @@
         <v>80</v>
       </c>
       <c r="I40" s="31">
-        <v>5710.5</v>
+        <v>3807</v>
       </c>
       <c r="J40" s="29" t="b">
         <v>1</v>
@@ -4361,7 +4381,7 @@
       </c>
       <c r="O40" s="28"/>
       <c r="P40" s="32">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q40" s="33"/>
       <c r="R40" s="34"/>
@@ -4401,18 +4421,16 @@
     <row r="41" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26"/>
       <c r="B41" s="27">
-        <v>46091</v>
+        <v>46086</v>
       </c>
       <c r="C41" s="27">
         <v>46097</v>
       </c>
       <c r="D41" s="28"/>
       <c r="E41" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="F41" s="30">
-        <v>3319</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F41" s="28"/>
       <c r="G41" s="29" t="s">
         <v>18</v>
       </c>
@@ -4420,13 +4438,13 @@
         <v>80</v>
       </c>
       <c r="I41" s="31">
-        <v>1983.75</v>
+        <v>5710.5</v>
       </c>
       <c r="J41" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K41" s="29" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="L41" s="29" t="s">
         <v>27</v>
@@ -4438,8 +4456,8 @@
         <v>28</v>
       </c>
       <c r="O41" s="28"/>
-      <c r="P41" s="32" t="s">
-        <v>83</v>
+      <c r="P41" s="32">
+        <v>45</v>
       </c>
       <c r="Q41" s="33"/>
       <c r="R41" s="34"/>
@@ -4488,8 +4506,8 @@
       <c r="E42" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="F42" s="30" t="s">
-        <v>84</v>
+      <c r="F42" s="30">
+        <v>3319</v>
       </c>
       <c r="G42" s="29" t="s">
         <v>18</v>
@@ -4498,7 +4516,7 @@
         <v>80</v>
       </c>
       <c r="I42" s="31">
-        <v>9775</v>
+        <v>1983.75</v>
       </c>
       <c r="J42" s="29" t="b">
         <v>1</v>
@@ -4554,7 +4572,7 @@
       <c r="AW42" s="35"/>
       <c r="AX42" s="35"/>
     </row>
-    <row r="43" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26"/>
       <c r="B43" s="27">
         <v>46091</v>
@@ -4566,8 +4584,8 @@
       <c r="E43" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="30">
-        <v>3333</v>
+      <c r="F43" s="30" t="s">
+        <v>84</v>
       </c>
       <c r="G43" s="29" t="s">
         <v>18</v>
@@ -4576,7 +4594,7 @@
         <v>80</v>
       </c>
       <c r="I43" s="31">
-        <v>709.39</v>
+        <v>9775</v>
       </c>
       <c r="J43" s="29" t="b">
         <v>1</v>
@@ -4594,7 +4612,9 @@
         <v>28</v>
       </c>
       <c r="O43" s="28"/>
-      <c r="P43" s="33"/>
+      <c r="P43" s="32" t="s">
+        <v>83</v>
+      </c>
       <c r="Q43" s="33"/>
       <c r="R43" s="34"/>
       <c r="S43" s="34"/>
@@ -4642,8 +4662,8 @@
       <c r="E44" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="F44" s="30" t="s">
-        <v>85</v>
+      <c r="F44" s="30">
+        <v>3333</v>
       </c>
       <c r="G44" s="29" t="s">
         <v>18</v>
@@ -4652,7 +4672,7 @@
         <v>80</v>
       </c>
       <c r="I44" s="31">
-        <v>3495.54</v>
+        <v>709.39</v>
       </c>
       <c r="J44" s="29" t="b">
         <v>1</v>
@@ -4709,26 +4729,26 @@
     <row r="45" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="26"/>
       <c r="B45" s="27">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="C45" s="27">
         <v>46097</v>
       </c>
       <c r="D45" s="28"/>
       <c r="E45" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" s="30">
-        <v>123036</v>
+        <v>82</v>
+      </c>
+      <c r="F45" s="30" t="s">
+        <v>85</v>
       </c>
       <c r="G45" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H45" s="29" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="I45" s="31">
-        <v>27943.03</v>
+        <v>3495.54</v>
       </c>
       <c r="J45" s="29" t="b">
         <v>1</v>
@@ -4795,7 +4815,7 @@
         <v>86</v>
       </c>
       <c r="F46" s="30">
-        <v>123037</v>
+        <v>123036</v>
       </c>
       <c r="G46" s="29" t="s">
         <v>18</v>
@@ -4871,7 +4891,7 @@
         <v>86</v>
       </c>
       <c r="F47" s="30">
-        <v>123038</v>
+        <v>123037</v>
       </c>
       <c r="G47" s="29" t="s">
         <v>18</v>
@@ -4934,20 +4954,20 @@
       <c r="AW47" s="35"/>
       <c r="AX47" s="35"/>
     </row>
-    <row r="48" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="26"/>
       <c r="B48" s="27">
-        <v>46092</v>
+        <v>46079</v>
       </c>
       <c r="C48" s="27">
         <v>46097</v>
       </c>
       <c r="D48" s="28"/>
       <c r="E48" s="29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F48" s="30">
-        <v>358061</v>
+        <v>123038</v>
       </c>
       <c r="G48" s="29" t="s">
         <v>18</v>
@@ -4956,7 +4976,7 @@
         <v>25</v>
       </c>
       <c r="I48" s="31">
-        <v>96205.83</v>
+        <v>27943.03</v>
       </c>
       <c r="J48" s="29" t="b">
         <v>1</v>
@@ -4974,9 +4994,7 @@
         <v>28</v>
       </c>
       <c r="O48" s="28"/>
-      <c r="P48" s="32" t="s">
-        <v>88</v>
-      </c>
+      <c r="P48" s="33"/>
       <c r="Q48" s="33"/>
       <c r="R48" s="34"/>
       <c r="S48" s="34"/>
@@ -5012,27 +5030,29 @@
       <c r="AW48" s="35"/>
       <c r="AX48" s="35"/>
     </row>
-    <row r="49" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="26"/>
       <c r="B49" s="27">
-        <v>46093</v>
+        <v>46092</v>
       </c>
       <c r="C49" s="27">
         <v>46097</v>
       </c>
       <c r="D49" s="28"/>
       <c r="E49" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="F49" s="28"/>
+        <v>87</v>
+      </c>
+      <c r="F49" s="30">
+        <v>358061</v>
+      </c>
       <c r="G49" s="29" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H49" s="29" t="s">
-        <v>188</v>
+        <v>25</v>
       </c>
       <c r="I49" s="31">
-        <v>1445</v>
+        <v>96205.83</v>
       </c>
       <c r="J49" s="29" t="b">
         <v>1</v>
@@ -5049,10 +5069,10 @@
       <c r="N49" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O49" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="P49" s="33"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="32" t="s">
+        <v>88</v>
+      </c>
       <c r="Q49" s="33"/>
       <c r="R49" s="34"/>
       <c r="S49" s="34"/>
@@ -5088,27 +5108,27 @@
       <c r="AW49" s="35"/>
       <c r="AX49" s="35"/>
     </row>
-    <row r="50" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="26"/>
       <c r="B50" s="27">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="C50" s="27">
         <v>46097</v>
       </c>
       <c r="D50" s="28"/>
       <c r="E50" s="29" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="F50" s="28"/>
       <c r="G50" s="29" t="s">
         <v>52</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="I50" s="31">
-        <v>281</v>
+        <v>1445</v>
       </c>
       <c r="J50" s="29" t="b">
         <v>1</v>
@@ -5125,12 +5145,10 @@
       <c r="N50" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O50" s="29">
-        <v>8971143886</v>
-      </c>
-      <c r="P50" s="32" t="s">
-        <v>90</v>
-      </c>
+      <c r="O50" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="P50" s="33"/>
       <c r="Q50" s="33"/>
       <c r="R50" s="34"/>
       <c r="S50" s="34"/>
@@ -5169,33 +5187,33 @@
     <row r="51" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="26"/>
       <c r="B51" s="27">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="C51" s="27">
         <v>46097</v>
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F51" s="28"/>
       <c r="G51" s="29" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="I51" s="31">
-        <v>50000</v>
+        <v>281</v>
       </c>
       <c r="J51" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K51" s="29" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="L51" s="29" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M51" s="29" t="s">
         <v>22</v>
@@ -5203,11 +5221,13 @@
       <c r="N51" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O51" s="28"/>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="O51" s="29">
+        <v>8971143886</v>
+      </c>
+      <c r="P51" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q51" s="33"/>
       <c r="R51" s="34"/>
       <c r="S51" s="34"/>
       <c r="T51" s="34"/>
@@ -5242,7 +5262,7 @@
       <c r="AW51" s="35"/>
       <c r="AX51" s="35"/>
     </row>
-    <row r="52" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="26"/>
       <c r="B52" s="27">
         <v>46079</v>
@@ -5252,26 +5272,26 @@
       </c>
       <c r="D52" s="28"/>
       <c r="E52" s="29" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F52" s="28"/>
       <c r="G52" s="29" t="s">
         <v>33</v>
       </c>
       <c r="H52" s="29" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="I52" s="31">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="J52" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K52" s="29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L52" s="29" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M52" s="29" t="s">
         <v>22</v>
@@ -5281,7 +5301,9 @@
       </c>
       <c r="O52" s="28"/>
       <c r="P52" s="33"/>
-      <c r="Q52" s="33"/>
+      <c r="Q52" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R52" s="34"/>
       <c r="S52" s="34"/>
       <c r="T52" s="34"/>
@@ -5317,167 +5339,161 @@
       <c r="AX52" s="35"/>
     </row>
     <row r="53" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="38"/>
-      <c r="N53" s="38"/>
-      <c r="O53" s="38"/>
-      <c r="P53" s="39"/>
-      <c r="Q53" s="39"/>
-      <c r="R53" s="40"/>
-      <c r="S53" s="40"/>
-      <c r="T53" s="40"/>
-      <c r="U53" s="40"/>
-      <c r="V53" s="40"/>
-      <c r="W53" s="40"/>
-      <c r="X53" s="40"/>
-      <c r="Y53" s="40"/>
-      <c r="Z53" s="41"/>
-      <c r="AA53" s="41"/>
-      <c r="AB53" s="41"/>
-      <c r="AC53" s="41"/>
-      <c r="AD53" s="41"/>
-      <c r="AE53" s="41"/>
-      <c r="AF53" s="41"/>
-      <c r="AG53" s="41"/>
-      <c r="AH53" s="41"/>
-      <c r="AI53" s="41"/>
-      <c r="AJ53" s="41"/>
-      <c r="AK53" s="41"/>
-      <c r="AL53" s="41"/>
-      <c r="AM53" s="41"/>
-      <c r="AN53" s="41"/>
-      <c r="AO53" s="41"/>
-      <c r="AP53" s="41"/>
-      <c r="AQ53" s="41"/>
-      <c r="AR53" s="41"/>
-      <c r="AS53" s="41"/>
-      <c r="AT53" s="41"/>
-      <c r="AU53" s="41"/>
-      <c r="AV53" s="41"/>
-      <c r="AW53" s="41"/>
-      <c r="AX53" s="41"/>
-    </row>
-    <row r="54" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="19"/>
-      <c r="B54" s="20">
+      <c r="A53" s="26"/>
+      <c r="B53" s="27">
         <v>46079</v>
       </c>
-      <c r="C54" s="20">
-        <v>46098</v>
-      </c>
-      <c r="D54" s="21"/>
-      <c r="E54" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="F54" s="21"/>
-      <c r="G54" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="I54" s="24">
-        <v>357721.76</v>
-      </c>
-      <c r="J54" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="L54" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M54" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N54" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O54" s="21"/>
-      <c r="P54" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q54" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="17"/>
-      <c r="V54" s="17"/>
-      <c r="W54" s="17"/>
-      <c r="X54" s="17"/>
-      <c r="Y54" s="17"/>
-      <c r="Z54" s="18"/>
-      <c r="AA54" s="18"/>
-      <c r="AB54" s="18"/>
-      <c r="AC54" s="18"/>
-      <c r="AD54" s="18"/>
-      <c r="AE54" s="18"/>
-      <c r="AF54" s="18"/>
-      <c r="AG54" s="18"/>
-      <c r="AH54" s="18"/>
-      <c r="AI54" s="18"/>
-      <c r="AJ54" s="18"/>
-      <c r="AK54" s="18"/>
-      <c r="AL54" s="18"/>
-      <c r="AM54" s="18"/>
-      <c r="AN54" s="18"/>
-      <c r="AO54" s="18"/>
-      <c r="AP54" s="18"/>
-      <c r="AQ54" s="18"/>
-      <c r="AR54" s="18"/>
-      <c r="AS54" s="18"/>
-      <c r="AT54" s="18"/>
-      <c r="AU54" s="18"/>
-      <c r="AV54" s="18"/>
-      <c r="AW54" s="18"/>
-      <c r="AX54" s="18"/>
-    </row>
-    <row r="55" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="27">
+        <v>46097</v>
+      </c>
+      <c r="D53" s="28"/>
+      <c r="E53" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="28"/>
+      <c r="G53" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I53" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J53" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L53" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M53" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N53" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O53" s="28"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="33"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="34"/>
+      <c r="T53" s="34"/>
+      <c r="U53" s="34"/>
+      <c r="V53" s="34"/>
+      <c r="W53" s="34"/>
+      <c r="X53" s="34"/>
+      <c r="Y53" s="34"/>
+      <c r="Z53" s="35"/>
+      <c r="AA53" s="35"/>
+      <c r="AB53" s="35"/>
+      <c r="AC53" s="35"/>
+      <c r="AD53" s="35"/>
+      <c r="AE53" s="35"/>
+      <c r="AF53" s="35"/>
+      <c r="AG53" s="35"/>
+      <c r="AH53" s="35"/>
+      <c r="AI53" s="35"/>
+      <c r="AJ53" s="35"/>
+      <c r="AK53" s="35"/>
+      <c r="AL53" s="35"/>
+      <c r="AM53" s="35"/>
+      <c r="AN53" s="35"/>
+      <c r="AO53" s="35"/>
+      <c r="AP53" s="35"/>
+      <c r="AQ53" s="35"/>
+      <c r="AR53" s="35"/>
+      <c r="AS53" s="35"/>
+      <c r="AT53" s="35"/>
+      <c r="AU53" s="35"/>
+      <c r="AV53" s="35"/>
+      <c r="AW53" s="35"/>
+      <c r="AX53" s="35"/>
+    </row>
+    <row r="54" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="37"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="39"/>
+      <c r="Q54" s="39"/>
+      <c r="R54" s="40"/>
+      <c r="S54" s="40"/>
+      <c r="T54" s="40"/>
+      <c r="U54" s="40"/>
+      <c r="V54" s="40"/>
+      <c r="W54" s="40"/>
+      <c r="X54" s="40"/>
+      <c r="Y54" s="40"/>
+      <c r="Z54" s="41"/>
+      <c r="AA54" s="41"/>
+      <c r="AB54" s="41"/>
+      <c r="AC54" s="41"/>
+      <c r="AD54" s="41"/>
+      <c r="AE54" s="41"/>
+      <c r="AF54" s="41"/>
+      <c r="AG54" s="41"/>
+      <c r="AH54" s="41"/>
+      <c r="AI54" s="41"/>
+      <c r="AJ54" s="41"/>
+      <c r="AK54" s="41"/>
+      <c r="AL54" s="41"/>
+      <c r="AM54" s="41"/>
+      <c r="AN54" s="41"/>
+      <c r="AO54" s="41"/>
+      <c r="AP54" s="41"/>
+      <c r="AQ54" s="41"/>
+      <c r="AR54" s="41"/>
+      <c r="AS54" s="41"/>
+      <c r="AT54" s="41"/>
+      <c r="AU54" s="41"/>
+      <c r="AV54" s="41"/>
+      <c r="AW54" s="41"/>
+      <c r="AX54" s="41"/>
+    </row>
+    <row r="55" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19"/>
       <c r="B55" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C55" s="20">
         <v>46098</v>
       </c>
       <c r="D55" s="21"/>
       <c r="E55" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="F55" s="23">
-        <v>9748</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F55" s="21"/>
       <c r="G55" s="22" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="I55" s="24">
-        <v>1700</v>
+        <v>357721.76</v>
       </c>
       <c r="J55" s="22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="22" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="L55" s="22" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M55" s="22" t="s">
         <v>22</v>
@@ -5486,8 +5502,12 @@
         <v>23</v>
       </c>
       <c r="O55" s="21"/>
-      <c r="P55" s="25"/>
-      <c r="Q55" s="25"/>
+      <c r="P55" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q55" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="R55" s="17"/>
       <c r="S55" s="17"/>
       <c r="T55" s="17"/>
@@ -5525,26 +5545,26 @@
     <row r="56" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19"/>
       <c r="B56" s="20">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C56" s="20">
         <v>46098</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="22" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="F56" s="23">
-        <v>538</v>
+        <v>9748</v>
       </c>
       <c r="G56" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I56" s="24">
-        <v>1905</v>
+        <v>1700</v>
       </c>
       <c r="J56" s="22" t="b">
         <v>1</v>
@@ -5553,7 +5573,7 @@
         <v>20</v>
       </c>
       <c r="L56" s="22" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M56" s="22" t="s">
         <v>22</v>
@@ -5601,26 +5621,26 @@
     <row r="57" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19"/>
       <c r="B57" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C57" s="20">
         <v>46098</v>
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="22" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F57" s="23">
-        <v>268673</v>
+        <v>538</v>
       </c>
       <c r="G57" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I57" s="24">
-        <v>10752.15</v>
+        <v>1905</v>
       </c>
       <c r="J57" s="22" t="b">
         <v>1</v>
@@ -5684,19 +5704,19 @@
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F58" s="23">
-        <v>7913</v>
+        <v>268673</v>
       </c>
       <c r="G58" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I58" s="24">
-        <v>7892.43</v>
+        <v>10752.15</v>
       </c>
       <c r="J58" s="22" t="b">
         <v>1</v>
@@ -5760,19 +5780,19 @@
       </c>
       <c r="D59" s="21"/>
       <c r="E59" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F59" s="23">
-        <v>361471</v>
+        <v>7913</v>
       </c>
       <c r="G59" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="I59" s="24">
-        <v>4750</v>
+        <v>7892.43</v>
       </c>
       <c r="J59" s="22" t="b">
         <v>1</v>
@@ -5826,111 +5846,109 @@
       <c r="AW59" s="18"/>
       <c r="AX59" s="18"/>
     </row>
-    <row r="60" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="26"/>
-      <c r="B60" s="27">
-        <v>46078</v>
-      </c>
-      <c r="C60" s="27">
+    <row r="60" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="19"/>
+      <c r="B60" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C60" s="20">
         <v>46098</v>
       </c>
-      <c r="D60" s="28"/>
-      <c r="E60" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="F60" s="28"/>
-      <c r="G60" s="29" t="s">
+      <c r="D60" s="21"/>
+      <c r="E60" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F60" s="23">
+        <v>361471</v>
+      </c>
+      <c r="G60" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I60" s="31">
-        <v>3000</v>
-      </c>
-      <c r="J60" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K60" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L60" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M60" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N60" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O60" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P60" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q60" s="33"/>
-      <c r="R60" s="34"/>
-      <c r="S60" s="34"/>
-      <c r="T60" s="34"/>
-      <c r="U60" s="34"/>
-      <c r="V60" s="34"/>
-      <c r="W60" s="34"/>
-      <c r="X60" s="34"/>
-      <c r="Y60" s="34"/>
-      <c r="Z60" s="35"/>
-      <c r="AA60" s="35"/>
-      <c r="AB60" s="35"/>
-      <c r="AC60" s="35"/>
-      <c r="AD60" s="35"/>
-      <c r="AE60" s="35"/>
-      <c r="AF60" s="35"/>
-      <c r="AG60" s="35"/>
-      <c r="AH60" s="35"/>
-      <c r="AI60" s="35"/>
-      <c r="AJ60" s="35"/>
-      <c r="AK60" s="35"/>
-      <c r="AL60" s="35"/>
-      <c r="AM60" s="35"/>
-      <c r="AN60" s="35"/>
-      <c r="AO60" s="35"/>
-      <c r="AP60" s="35"/>
-      <c r="AQ60" s="35"/>
-      <c r="AR60" s="35"/>
-      <c r="AS60" s="35"/>
-      <c r="AT60" s="35"/>
-      <c r="AU60" s="35"/>
-      <c r="AV60" s="35"/>
-      <c r="AW60" s="35"/>
-      <c r="AX60" s="35"/>
-    </row>
-    <row r="61" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H60" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="I60" s="24">
+        <v>4750</v>
+      </c>
+      <c r="J60" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K60" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N60" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O60" s="21"/>
+      <c r="P60" s="25"/>
+      <c r="Q60" s="25"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="17"/>
+      <c r="V60" s="17"/>
+      <c r="W60" s="17"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="17"/>
+      <c r="Z60" s="18"/>
+      <c r="AA60" s="18"/>
+      <c r="AB60" s="18"/>
+      <c r="AC60" s="18"/>
+      <c r="AD60" s="18"/>
+      <c r="AE60" s="18"/>
+      <c r="AF60" s="18"/>
+      <c r="AG60" s="18"/>
+      <c r="AH60" s="18"/>
+      <c r="AI60" s="18"/>
+      <c r="AJ60" s="18"/>
+      <c r="AK60" s="18"/>
+      <c r="AL60" s="18"/>
+      <c r="AM60" s="18"/>
+      <c r="AN60" s="18"/>
+      <c r="AO60" s="18"/>
+      <c r="AP60" s="18"/>
+      <c r="AQ60" s="18"/>
+      <c r="AR60" s="18"/>
+      <c r="AS60" s="18"/>
+      <c r="AT60" s="18"/>
+      <c r="AU60" s="18"/>
+      <c r="AV60" s="18"/>
+      <c r="AW60" s="18"/>
+      <c r="AX60" s="18"/>
+    </row>
+    <row r="61" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="26"/>
       <c r="B61" s="27">
-        <v>46091</v>
+        <v>46078</v>
       </c>
       <c r="C61" s="27">
         <v>46098</v>
       </c>
       <c r="D61" s="28"/>
       <c r="E61" s="29" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="F61" s="28"/>
       <c r="G61" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H61" s="29" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="I61" s="31">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="J61" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K61" s="29" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L61" s="29" t="s">
         <v>27</v>
@@ -5941,11 +5959,13 @@
       <c r="N61" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O61" s="28"/>
-      <c r="P61" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q61" s="28"/>
+      <c r="O61" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="P61" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q61" s="33"/>
       <c r="R61" s="34"/>
       <c r="S61" s="34"/>
       <c r="T61" s="34"/>
@@ -5980,29 +6000,27 @@
       <c r="AW61" s="35"/>
       <c r="AX61" s="35"/>
     </row>
-    <row r="62" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="26"/>
       <c r="B62" s="27">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C62" s="27">
         <v>46098</v>
       </c>
       <c r="D62" s="28"/>
       <c r="E62" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="F62" s="30">
-        <v>6173</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="F62" s="28"/>
       <c r="G62" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H62" s="29" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="I62" s="31">
-        <v>1099.17</v>
+        <v>3800</v>
       </c>
       <c r="J62" s="29" t="b">
         <v>1</v>
@@ -6020,7 +6038,9 @@
         <v>28</v>
       </c>
       <c r="O62" s="28"/>
-      <c r="P62" s="28"/>
+      <c r="P62" s="42" t="s">
+        <v>106</v>
+      </c>
       <c r="Q62" s="28"/>
       <c r="R62" s="34"/>
       <c r="S62" s="34"/>
@@ -6068,8 +6088,8 @@
       <c r="E63" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F63" s="30" t="s">
-        <v>108</v>
+      <c r="F63" s="30">
+        <v>6173</v>
       </c>
       <c r="G63" s="29" t="s">
         <v>18</v>
@@ -6078,7 +6098,7 @@
         <v>80</v>
       </c>
       <c r="I63" s="31">
-        <v>8458.83</v>
+        <v>1099.17</v>
       </c>
       <c r="J63" s="29" t="b">
         <v>1</v>
@@ -6144,8 +6164,8 @@
       <c r="E64" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F64" s="30">
-        <v>6172</v>
+      <c r="F64" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="G64" s="29" t="s">
         <v>18</v>
@@ -6154,7 +6174,7 @@
         <v>80</v>
       </c>
       <c r="I64" s="31">
-        <v>1494.4</v>
+        <v>8458.83</v>
       </c>
       <c r="J64" s="29" t="b">
         <v>1</v>
@@ -6220,8 +6240,8 @@
       <c r="E65" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F65" s="30" t="s">
-        <v>109</v>
+      <c r="F65" s="30">
+        <v>6172</v>
       </c>
       <c r="G65" s="29" t="s">
         <v>18</v>
@@ -6230,7 +6250,7 @@
         <v>80</v>
       </c>
       <c r="I65" s="31">
-        <v>11500.4</v>
+        <v>1494.4</v>
       </c>
       <c r="J65" s="29" t="b">
         <v>1</v>
@@ -6296,8 +6316,8 @@
       <c r="E66" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F66" s="30">
-        <v>6175</v>
+      <c r="F66" s="30" t="s">
+        <v>109</v>
       </c>
       <c r="G66" s="29" t="s">
         <v>18</v>
@@ -6306,13 +6326,13 @@
         <v>80</v>
       </c>
       <c r="I66" s="31">
-        <v>1055.76</v>
+        <v>11500.4</v>
       </c>
       <c r="J66" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K66" s="29" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="L66" s="29" t="s">
         <v>27</v>
@@ -6372,8 +6392,8 @@
       <c r="E67" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F67" s="30" t="s">
-        <v>111</v>
+      <c r="F67" s="30">
+        <v>6175</v>
       </c>
       <c r="G67" s="29" t="s">
         <v>18</v>
@@ -6382,7 +6402,7 @@
         <v>80</v>
       </c>
       <c r="I67" s="31">
-        <v>8124.74</v>
+        <v>1055.76</v>
       </c>
       <c r="J67" s="29" t="b">
         <v>1</v>
@@ -6439,7 +6459,7 @@
     <row r="68" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="26"/>
       <c r="B68" s="27">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C68" s="27">
         <v>46098</v>
@@ -6448,8 +6468,8 @@
       <c r="E68" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="30">
-        <v>6174</v>
+      <c r="F68" s="30" t="s">
+        <v>111</v>
       </c>
       <c r="G68" s="29" t="s">
         <v>18</v>
@@ -6458,7 +6478,7 @@
         <v>80</v>
       </c>
       <c r="I68" s="31">
-        <v>2946.3</v>
+        <v>8124.74</v>
       </c>
       <c r="J68" s="29" t="b">
         <v>1</v>
@@ -6524,8 +6544,8 @@
       <c r="E69" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="F69" s="30" t="s">
-        <v>112</v>
+      <c r="F69" s="30">
+        <v>6174</v>
       </c>
       <c r="G69" s="29" t="s">
         <v>18</v>
@@ -6534,7 +6554,7 @@
         <v>80</v>
       </c>
       <c r="I69" s="31">
-        <v>22973.7</v>
+        <v>2946.3</v>
       </c>
       <c r="J69" s="29" t="b">
         <v>1</v>
@@ -6588,33 +6608,35 @@
       <c r="AW69" s="35"/>
       <c r="AX69" s="35"/>
     </row>
-    <row r="70" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="26"/>
       <c r="B70" s="27">
-        <v>46092</v>
+        <v>46084</v>
       </c>
       <c r="C70" s="27">
         <v>46098</v>
       </c>
       <c r="D70" s="28"/>
       <c r="E70" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="F70" s="28"/>
+        <v>107</v>
+      </c>
+      <c r="F70" s="30" t="s">
+        <v>112</v>
+      </c>
       <c r="G70" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H70" s="29" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="I70" s="31">
-        <v>17607.77</v>
+        <v>22973.7</v>
       </c>
       <c r="J70" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K70" s="29" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="L70" s="29" t="s">
         <v>27</v>
@@ -6626,9 +6648,7 @@
         <v>28</v>
       </c>
       <c r="O70" s="28"/>
-      <c r="P70" s="42" t="s">
-        <v>83</v>
-      </c>
+      <c r="P70" s="28"/>
       <c r="Q70" s="28"/>
       <c r="R70" s="34"/>
       <c r="S70" s="34"/>
@@ -6667,30 +6687,30 @@
     <row r="71" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="26"/>
       <c r="B71" s="27">
-        <v>46079</v>
+        <v>46092</v>
       </c>
       <c r="C71" s="27">
         <v>46098</v>
       </c>
       <c r="D71" s="28"/>
       <c r="E71" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F71" s="28"/>
       <c r="G71" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="29" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I71" s="31">
-        <v>34692</v>
+        <v>17607.77</v>
       </c>
       <c r="J71" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K71" s="29" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="L71" s="29" t="s">
         <v>27</v>
@@ -6703,7 +6723,7 @@
       </c>
       <c r="O71" s="28"/>
       <c r="P71" s="42" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="Q71" s="28"/>
       <c r="R71" s="34"/>
@@ -6760,7 +6780,7 @@
         <v>25</v>
       </c>
       <c r="I72" s="31">
-        <v>33600</v>
+        <v>34692</v>
       </c>
       <c r="J72" s="29" t="b">
         <v>1</v>
@@ -6779,7 +6799,7 @@
       </c>
       <c r="O72" s="28"/>
       <c r="P72" s="42" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Q72" s="28"/>
       <c r="R72" s="34"/>
@@ -6816,7 +6836,7 @@
       <c r="AW72" s="35"/>
       <c r="AX72" s="35"/>
     </row>
-    <row r="73" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="26"/>
       <c r="B73" s="27">
         <v>46079</v>
@@ -6826,17 +6846,17 @@
       </c>
       <c r="D73" s="28"/>
       <c r="E73" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F73" s="28"/>
       <c r="G73" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H73" s="29" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="I73" s="31">
-        <v>19602</v>
+        <v>33600</v>
       </c>
       <c r="J73" s="29" t="b">
         <v>1</v>
@@ -6854,10 +6874,10 @@
         <v>28</v>
       </c>
       <c r="O73" s="28"/>
-      <c r="P73" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q73" s="33"/>
+      <c r="P73" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q73" s="28"/>
       <c r="R73" s="34"/>
       <c r="S73" s="34"/>
       <c r="T73" s="34"/>
@@ -6895,7 +6915,7 @@
     <row r="74" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="26"/>
       <c r="B74" s="27">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C74" s="27">
         <v>46098</v>
@@ -6912,7 +6932,7 @@
         <v>80</v>
       </c>
       <c r="I74" s="31">
-        <v>4003.16</v>
+        <v>19602</v>
       </c>
       <c r="J74" s="29" t="b">
         <v>1</v>
@@ -6931,7 +6951,7 @@
       </c>
       <c r="O74" s="28"/>
       <c r="P74" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q74" s="33"/>
       <c r="R74" s="34"/>
@@ -6988,7 +7008,7 @@
         <v>80</v>
       </c>
       <c r="I75" s="31">
-        <v>5166.72</v>
+        <v>4003.16</v>
       </c>
       <c r="J75" s="29" t="b">
         <v>1</v>
@@ -7007,7 +7027,7 @@
       </c>
       <c r="O75" s="28"/>
       <c r="P75" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q75" s="33"/>
       <c r="R75" s="34"/>
@@ -7044,33 +7064,33 @@
       <c r="AW75" s="35"/>
       <c r="AX75" s="35"/>
     </row>
-    <row r="76" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="26"/>
       <c r="B76" s="27">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C76" s="27">
         <v>46098</v>
       </c>
       <c r="D76" s="28"/>
       <c r="E76" s="29" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="F76" s="28"/>
       <c r="G76" s="29" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H76" s="29" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I76" s="31">
-        <v>20000</v>
+        <v>5166.72</v>
       </c>
       <c r="J76" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K76" s="29" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="L76" s="29" t="s">
         <v>27</v>
@@ -7082,7 +7102,9 @@
         <v>28</v>
       </c>
       <c r="O76" s="28"/>
-      <c r="P76" s="33"/>
+      <c r="P76" s="9" t="s">
+        <v>118</v>
+      </c>
       <c r="Q76" s="33"/>
       <c r="R76" s="34"/>
       <c r="S76" s="34"/>
@@ -7119,132 +7141,130 @@
       <c r="AX76" s="35"/>
     </row>
     <row r="77" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="38"/>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="38"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="39"/>
-      <c r="J77" s="38"/>
-      <c r="K77" s="38"/>
-      <c r="L77" s="38"/>
-      <c r="M77" s="38"/>
-      <c r="N77" s="38"/>
-      <c r="O77" s="38"/>
-      <c r="P77" s="39"/>
-      <c r="Q77" s="39"/>
-      <c r="R77" s="40"/>
-      <c r="S77" s="40"/>
-      <c r="T77" s="40"/>
-      <c r="U77" s="40"/>
-      <c r="V77" s="40"/>
-      <c r="W77" s="40"/>
-      <c r="X77" s="40"/>
-      <c r="Y77" s="40"/>
-      <c r="Z77" s="41"/>
-      <c r="AA77" s="41"/>
-      <c r="AB77" s="41"/>
-      <c r="AC77" s="41"/>
-      <c r="AD77" s="41"/>
-      <c r="AE77" s="41"/>
-      <c r="AF77" s="41"/>
-      <c r="AG77" s="41"/>
-      <c r="AH77" s="41"/>
-      <c r="AI77" s="41"/>
-      <c r="AJ77" s="41"/>
-      <c r="AK77" s="41"/>
-      <c r="AL77" s="41"/>
-      <c r="AM77" s="41"/>
-      <c r="AN77" s="41"/>
-      <c r="AO77" s="41"/>
-      <c r="AP77" s="41"/>
-      <c r="AQ77" s="41"/>
-      <c r="AR77" s="41"/>
-      <c r="AS77" s="41"/>
-      <c r="AT77" s="41"/>
-      <c r="AU77" s="41"/>
-      <c r="AV77" s="41"/>
-      <c r="AW77" s="41"/>
-      <c r="AX77" s="41"/>
+      <c r="A77" s="26"/>
+      <c r="B77" s="27">
+        <v>46079</v>
+      </c>
+      <c r="C77" s="27">
+        <v>46098</v>
+      </c>
+      <c r="D77" s="28"/>
+      <c r="E77" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F77" s="28"/>
+      <c r="G77" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H77" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I77" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J77" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K77" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L77" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M77" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N77" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O77" s="28"/>
+      <c r="P77" s="33"/>
+      <c r="Q77" s="33"/>
+      <c r="R77" s="34"/>
+      <c r="S77" s="34"/>
+      <c r="T77" s="34"/>
+      <c r="U77" s="34"/>
+      <c r="V77" s="34"/>
+      <c r="W77" s="34"/>
+      <c r="X77" s="34"/>
+      <c r="Y77" s="34"/>
+      <c r="Z77" s="35"/>
+      <c r="AA77" s="35"/>
+      <c r="AB77" s="35"/>
+      <c r="AC77" s="35"/>
+      <c r="AD77" s="35"/>
+      <c r="AE77" s="35"/>
+      <c r="AF77" s="35"/>
+      <c r="AG77" s="35"/>
+      <c r="AH77" s="35"/>
+      <c r="AI77" s="35"/>
+      <c r="AJ77" s="35"/>
+      <c r="AK77" s="35"/>
+      <c r="AL77" s="35"/>
+      <c r="AM77" s="35"/>
+      <c r="AN77" s="35"/>
+      <c r="AO77" s="35"/>
+      <c r="AP77" s="35"/>
+      <c r="AQ77" s="35"/>
+      <c r="AR77" s="35"/>
+      <c r="AS77" s="35"/>
+      <c r="AT77" s="35"/>
+      <c r="AU77" s="35"/>
+      <c r="AV77" s="35"/>
+      <c r="AW77" s="35"/>
+      <c r="AX77" s="35"/>
     </row>
     <row r="78" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="19"/>
-      <c r="B78" s="20">
-        <v>46079</v>
-      </c>
-      <c r="C78" s="20">
-        <v>46099</v>
-      </c>
-      <c r="D78" s="21"/>
-      <c r="E78" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="F78" s="23">
-        <v>388534</v>
-      </c>
-      <c r="G78" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H78" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="I78" s="24">
-        <v>24497.55</v>
-      </c>
-      <c r="J78" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K78" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L78" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N78" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O78" s="21"/>
-      <c r="P78" s="25"/>
-      <c r="Q78" s="25"/>
-      <c r="R78" s="17"/>
-      <c r="S78" s="17"/>
-      <c r="T78" s="17"/>
-      <c r="U78" s="17"/>
-      <c r="V78" s="17"/>
-      <c r="W78" s="17"/>
-      <c r="X78" s="17"/>
-      <c r="Y78" s="17"/>
-      <c r="Z78" s="18"/>
-      <c r="AA78" s="18"/>
-      <c r="AB78" s="18"/>
-      <c r="AC78" s="18"/>
-      <c r="AD78" s="18"/>
-      <c r="AE78" s="18"/>
-      <c r="AF78" s="18"/>
-      <c r="AG78" s="18"/>
-      <c r="AH78" s="18"/>
-      <c r="AI78" s="18"/>
-      <c r="AJ78" s="18"/>
-      <c r="AK78" s="18"/>
-      <c r="AL78" s="18"/>
-      <c r="AM78" s="18"/>
-      <c r="AN78" s="18"/>
-      <c r="AO78" s="18"/>
-      <c r="AP78" s="18"/>
-      <c r="AQ78" s="18"/>
-      <c r="AR78" s="18"/>
-      <c r="AS78" s="18"/>
-      <c r="AT78" s="18"/>
-      <c r="AU78" s="18"/>
-      <c r="AV78" s="18"/>
-      <c r="AW78" s="18"/>
-      <c r="AX78" s="18"/>
+      <c r="A78" s="37"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="38"/>
+      <c r="I78" s="39"/>
+      <c r="J78" s="38"/>
+      <c r="K78" s="38"/>
+      <c r="L78" s="38"/>
+      <c r="M78" s="38"/>
+      <c r="N78" s="38"/>
+      <c r="O78" s="38"/>
+      <c r="P78" s="39"/>
+      <c r="Q78" s="39"/>
+      <c r="R78" s="40"/>
+      <c r="S78" s="40"/>
+      <c r="T78" s="40"/>
+      <c r="U78" s="40"/>
+      <c r="V78" s="40"/>
+      <c r="W78" s="40"/>
+      <c r="X78" s="40"/>
+      <c r="Y78" s="40"/>
+      <c r="Z78" s="41"/>
+      <c r="AA78" s="41"/>
+      <c r="AB78" s="41"/>
+      <c r="AC78" s="41"/>
+      <c r="AD78" s="41"/>
+      <c r="AE78" s="41"/>
+      <c r="AF78" s="41"/>
+      <c r="AG78" s="41"/>
+      <c r="AH78" s="41"/>
+      <c r="AI78" s="41"/>
+      <c r="AJ78" s="41"/>
+      <c r="AK78" s="41"/>
+      <c r="AL78" s="41"/>
+      <c r="AM78" s="41"/>
+      <c r="AN78" s="41"/>
+      <c r="AO78" s="41"/>
+      <c r="AP78" s="41"/>
+      <c r="AQ78" s="41"/>
+      <c r="AR78" s="41"/>
+      <c r="AS78" s="41"/>
+      <c r="AT78" s="41"/>
+      <c r="AU78" s="41"/>
+      <c r="AV78" s="41"/>
+      <c r="AW78" s="41"/>
+      <c r="AX78" s="41"/>
     </row>
     <row r="79" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="19"/>
@@ -7256,10 +7276,10 @@
       </c>
       <c r="D79" s="21"/>
       <c r="E79" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F79" s="23">
-        <v>60375</v>
+        <v>388534</v>
       </c>
       <c r="G79" s="22" t="s">
         <v>18</v>
@@ -7268,7 +7288,7 @@
         <v>25</v>
       </c>
       <c r="I79" s="24">
-        <v>855</v>
+        <v>24497.55</v>
       </c>
       <c r="J79" s="22" t="b">
         <v>1</v>
@@ -7332,19 +7352,19 @@
       </c>
       <c r="D80" s="21"/>
       <c r="E80" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F80" s="23">
-        <v>28133</v>
+        <v>60375</v>
       </c>
       <c r="G80" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H80" s="22" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="I80" s="24">
-        <v>477.75</v>
+        <v>855</v>
       </c>
       <c r="J80" s="22" t="b">
         <v>1</v>
@@ -7408,19 +7428,19 @@
       </c>
       <c r="D81" s="21"/>
       <c r="E81" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F81" s="23">
-        <v>17703</v>
+        <v>28133</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I81" s="24">
-        <v>721.7</v>
+        <v>477.75</v>
       </c>
       <c r="J81" s="22" t="b">
         <v>1</v>
@@ -7477,26 +7497,26 @@
     <row r="82" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19"/>
       <c r="B82" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C82" s="20">
         <v>46099</v>
       </c>
       <c r="D82" s="21"/>
       <c r="E82" s="22" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="F82" s="23">
-        <v>30520</v>
+        <v>17703</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I82" s="24">
-        <v>4214.67</v>
+        <v>721.7</v>
       </c>
       <c r="J82" s="22" t="b">
         <v>1</v>
@@ -7550,113 +7570,109 @@
       <c r="AW82" s="18"/>
       <c r="AX82" s="18"/>
     </row>
-    <row r="83" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="26"/>
-      <c r="B83" s="27">
-        <v>46079</v>
-      </c>
-      <c r="C83" s="27">
+    <row r="83" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="19"/>
+      <c r="B83" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C83" s="20">
         <v>46099</v>
       </c>
-      <c r="D83" s="28"/>
-      <c r="E83" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="F83" s="28"/>
-      <c r="G83" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="H83" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="I83" s="31">
-        <v>48000</v>
-      </c>
-      <c r="J83" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K83" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="L83" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M83" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N83" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O83" s="28"/>
-      <c r="P83" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q83" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R83" s="34"/>
-      <c r="S83" s="34"/>
-      <c r="T83" s="34"/>
-      <c r="U83" s="34"/>
-      <c r="V83" s="34"/>
-      <c r="W83" s="34"/>
-      <c r="X83" s="34"/>
-      <c r="Y83" s="34"/>
-      <c r="Z83" s="35"/>
-      <c r="AA83" s="35"/>
-      <c r="AB83" s="35"/>
-      <c r="AC83" s="35"/>
-      <c r="AD83" s="35"/>
-      <c r="AE83" s="35"/>
-      <c r="AF83" s="35"/>
-      <c r="AG83" s="35"/>
-      <c r="AH83" s="35"/>
-      <c r="AI83" s="35"/>
-      <c r="AJ83" s="35"/>
-      <c r="AK83" s="35"/>
-      <c r="AL83" s="35"/>
-      <c r="AM83" s="35"/>
-      <c r="AN83" s="35"/>
-      <c r="AO83" s="35"/>
-      <c r="AP83" s="35"/>
-      <c r="AQ83" s="35"/>
-      <c r="AR83" s="35"/>
-      <c r="AS83" s="35"/>
-      <c r="AT83" s="35"/>
-      <c r="AU83" s="35"/>
-      <c r="AV83" s="35"/>
-      <c r="AW83" s="35"/>
-      <c r="AX83" s="35"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F83" s="23">
+        <v>30520</v>
+      </c>
+      <c r="G83" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83" s="24">
+        <v>4214.67</v>
+      </c>
+      <c r="J83" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K83" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L83" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M83" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N83" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O83" s="21"/>
+      <c r="P83" s="25"/>
+      <c r="Q83" s="25"/>
+      <c r="R83" s="17"/>
+      <c r="S83" s="17"/>
+      <c r="T83" s="17"/>
+      <c r="U83" s="17"/>
+      <c r="V83" s="17"/>
+      <c r="W83" s="17"/>
+      <c r="X83" s="17"/>
+      <c r="Y83" s="17"/>
+      <c r="Z83" s="18"/>
+      <c r="AA83" s="18"/>
+      <c r="AB83" s="18"/>
+      <c r="AC83" s="18"/>
+      <c r="AD83" s="18"/>
+      <c r="AE83" s="18"/>
+      <c r="AF83" s="18"/>
+      <c r="AG83" s="18"/>
+      <c r="AH83" s="18"/>
+      <c r="AI83" s="18"/>
+      <c r="AJ83" s="18"/>
+      <c r="AK83" s="18"/>
+      <c r="AL83" s="18"/>
+      <c r="AM83" s="18"/>
+      <c r="AN83" s="18"/>
+      <c r="AO83" s="18"/>
+      <c r="AP83" s="18"/>
+      <c r="AQ83" s="18"/>
+      <c r="AR83" s="18"/>
+      <c r="AS83" s="18"/>
+      <c r="AT83" s="18"/>
+      <c r="AU83" s="18"/>
+      <c r="AV83" s="18"/>
+      <c r="AW83" s="18"/>
+      <c r="AX83" s="18"/>
     </row>
     <row r="84" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26"/>
       <c r="B84" s="27">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C84" s="27">
         <v>46099</v>
       </c>
       <c r="D84" s="28"/>
       <c r="E84" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F84" s="30">
-        <v>239234</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="F84" s="28"/>
       <c r="G84" s="29" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H84" s="29" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="I84" s="31">
-        <v>1993.24</v>
+        <v>48000</v>
       </c>
       <c r="J84" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K84" s="29" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="L84" s="29" t="s">
         <v>27</v>
@@ -7669,9 +7685,11 @@
       </c>
       <c r="O84" s="28"/>
       <c r="P84" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q84" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="Q84" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R84" s="34"/>
       <c r="S84" s="34"/>
       <c r="T84" s="34"/>
@@ -7719,7 +7737,7 @@
         <v>17</v>
       </c>
       <c r="F85" s="30">
-        <v>239250</v>
+        <v>239234</v>
       </c>
       <c r="G85" s="29" t="s">
         <v>18</v>
@@ -7728,7 +7746,7 @@
         <v>19</v>
       </c>
       <c r="I85" s="31">
-        <v>2714.34</v>
+        <v>1993.24</v>
       </c>
       <c r="J85" s="29" t="b">
         <v>1</v>
@@ -7794,10 +7812,10 @@
       </c>
       <c r="D86" s="28"/>
       <c r="E86" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F86" s="30" t="s">
-        <v>128</v>
+        <v>17</v>
+      </c>
+      <c r="F86" s="30">
+        <v>239250</v>
       </c>
       <c r="G86" s="29" t="s">
         <v>18</v>
@@ -7806,7 +7824,7 @@
         <v>19</v>
       </c>
       <c r="I86" s="31">
-        <v>41034</v>
+        <v>2714.34</v>
       </c>
       <c r="J86" s="29" t="b">
         <v>1</v>
@@ -7872,9 +7890,11 @@
       </c>
       <c r="D87" s="28"/>
       <c r="E87" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="F87" s="28"/>
+        <v>30</v>
+      </c>
+      <c r="F87" s="30" t="s">
+        <v>128</v>
+      </c>
       <c r="G87" s="29" t="s">
         <v>18</v>
       </c>
@@ -7882,7 +7902,7 @@
         <v>19</v>
       </c>
       <c r="I87" s="31">
-        <v>640</v>
+        <v>41034</v>
       </c>
       <c r="J87" s="29" t="b">
         <v>1</v>
@@ -7901,17 +7921,17 @@
       </c>
       <c r="O87" s="28"/>
       <c r="P87" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q87" s="33"/>
-      <c r="R87" s="35"/>
-      <c r="S87" s="35"/>
-      <c r="T87" s="35"/>
-      <c r="U87" s="35"/>
-      <c r="V87" s="35"/>
-      <c r="W87" s="35"/>
-      <c r="X87" s="35"/>
-      <c r="Y87" s="35"/>
+      <c r="R87" s="34"/>
+      <c r="S87" s="34"/>
+      <c r="T87" s="34"/>
+      <c r="U87" s="34"/>
+      <c r="V87" s="34"/>
+      <c r="W87" s="34"/>
+      <c r="X87" s="34"/>
+      <c r="Y87" s="34"/>
       <c r="Z87" s="35"/>
       <c r="AA87" s="35"/>
       <c r="AB87" s="35"/>
@@ -7948,7 +7968,7 @@
       </c>
       <c r="D88" s="28"/>
       <c r="E88" s="29" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="F88" s="28"/>
       <c r="G88" s="29" t="s">
@@ -7958,7 +7978,7 @@
         <v>19</v>
       </c>
       <c r="I88" s="31">
-        <v>13145.01</v>
+        <v>640</v>
       </c>
       <c r="J88" s="29" t="b">
         <v>1</v>
@@ -8014,33 +8034,33 @@
       <c r="AW88" s="35"/>
       <c r="AX88" s="35"/>
     </row>
-    <row r="89" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="26"/>
       <c r="B89" s="27">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C89" s="27">
         <v>46099</v>
       </c>
       <c r="D89" s="28"/>
       <c r="E89" s="29" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F89" s="28"/>
       <c r="G89" s="29" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H89" s="29" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="I89" s="31">
-        <v>5000</v>
+        <v>13145.01</v>
       </c>
       <c r="J89" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K89" s="29" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="L89" s="29" t="s">
         <v>27</v>
@@ -8051,10 +8071,10 @@
       <c r="N89" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O89" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="P89" s="33"/>
+      <c r="O89" s="28"/>
+      <c r="P89" s="32" t="s">
+        <v>130</v>
+      </c>
       <c r="Q89" s="33"/>
       <c r="R89" s="35"/>
       <c r="S89" s="35"/>
@@ -8090,7 +8110,7 @@
       <c r="AW89" s="35"/>
       <c r="AX89" s="35"/>
     </row>
-    <row r="90" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="26"/>
       <c r="B90" s="27">
         <v>46079</v>
@@ -8100,23 +8120,23 @@
       </c>
       <c r="D90" s="28"/>
       <c r="E90" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F90" s="28"/>
       <c r="G90" s="29" t="s">
         <v>36</v>
       </c>
       <c r="H90" s="29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I90" s="31">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="J90" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K90" s="29" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="L90" s="29" t="s">
         <v>27</v>
@@ -8128,20 +8148,18 @@
         <v>28</v>
       </c>
       <c r="O90" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="P90" s="32" t="s">
-        <v>135</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="P90" s="33"/>
       <c r="Q90" s="33"/>
-      <c r="R90" s="34"/>
-      <c r="S90" s="34"/>
-      <c r="T90" s="34"/>
-      <c r="U90" s="34"/>
-      <c r="V90" s="34"/>
-      <c r="W90" s="34"/>
-      <c r="X90" s="34"/>
-      <c r="Y90" s="34"/>
+      <c r="R90" s="35"/>
+      <c r="S90" s="35"/>
+      <c r="T90" s="35"/>
+      <c r="U90" s="35"/>
+      <c r="V90" s="35"/>
+      <c r="W90" s="35"/>
+      <c r="X90" s="35"/>
+      <c r="Y90" s="35"/>
       <c r="Z90" s="35"/>
       <c r="AA90" s="35"/>
       <c r="AB90" s="35"/>
@@ -8178,7 +8196,7 @@
       </c>
       <c r="D91" s="28"/>
       <c r="E91" s="29" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F91" s="28"/>
       <c r="G91" s="29" t="s">
@@ -8206,14 +8224,12 @@
         <v>28</v>
       </c>
       <c r="O91" s="29" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P91" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="Q91" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q91" s="33"/>
       <c r="R91" s="34"/>
       <c r="S91" s="34"/>
       <c r="T91" s="34"/>
@@ -8248,7 +8264,7 @@
       <c r="AW91" s="35"/>
       <c r="AX91" s="35"/>
     </row>
-    <row r="92" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="26"/>
       <c r="B92" s="27">
         <v>46079</v>
@@ -8258,7 +8274,7 @@
       </c>
       <c r="D92" s="28"/>
       <c r="E92" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F92" s="28"/>
       <c r="G92" s="29" t="s">
@@ -8286,7 +8302,7 @@
         <v>28</v>
       </c>
       <c r="O92" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="P92" s="32" t="s">
         <v>135</v>
@@ -8328,7 +8344,7 @@
       <c r="AW92" s="35"/>
       <c r="AX92" s="35"/>
     </row>
-    <row r="93" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="26"/>
       <c r="B93" s="27">
         <v>46079</v>
@@ -8338,7 +8354,7 @@
       </c>
       <c r="D93" s="28"/>
       <c r="E93" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F93" s="28"/>
       <c r="G93" s="29" t="s">
@@ -8366,7 +8382,7 @@
         <v>28</v>
       </c>
       <c r="O93" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="P93" s="32" t="s">
         <v>135</v>
@@ -8411,14 +8427,14 @@
     <row r="94" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="26"/>
       <c r="B94" s="27">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="C94" s="27">
         <v>46099</v>
       </c>
       <c r="D94" s="28"/>
       <c r="E94" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F94" s="28"/>
       <c r="G94" s="29" t="s">
@@ -8428,7 +8444,7 @@
         <v>49</v>
       </c>
       <c r="I94" s="31">
-        <v>340.9</v>
+        <v>500</v>
       </c>
       <c r="J94" s="29" t="b">
         <v>1</v>
@@ -8446,12 +8462,14 @@
         <v>28</v>
       </c>
       <c r="O94" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P94" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="Q94" s="33"/>
+      <c r="Q94" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R94" s="34"/>
       <c r="S94" s="34"/>
       <c r="T94" s="34"/>
@@ -8489,30 +8507,30 @@
     <row r="95" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="26"/>
       <c r="B95" s="27">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C95" s="27">
         <v>46099</v>
       </c>
       <c r="D95" s="28"/>
       <c r="E95" s="29" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="F95" s="28"/>
       <c r="G95" s="29" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H95" s="29" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="I95" s="31">
-        <v>14454</v>
+        <v>340.9</v>
       </c>
       <c r="J95" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K95" s="29" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L95" s="29" t="s">
         <v>27</v>
@@ -8523,9 +8541,11 @@
       <c r="N95" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O95" s="28"/>
-      <c r="P95" s="9" t="s">
-        <v>144</v>
+      <c r="O95" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="P95" s="32" t="s">
+        <v>135</v>
       </c>
       <c r="Q95" s="33"/>
       <c r="R95" s="34"/>
@@ -8562,7 +8582,7 @@
       <c r="AW95" s="35"/>
       <c r="AX95" s="35"/>
     </row>
-    <row r="96" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="26"/>
       <c r="B96" s="27">
         <v>46079</v>
@@ -8572,23 +8592,23 @@
       </c>
       <c r="D96" s="28"/>
       <c r="E96" s="29" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="F96" s="28"/>
       <c r="G96" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H96" s="29" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="I96" s="31">
-        <v>7500</v>
+        <v>14454</v>
       </c>
       <c r="J96" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K96" s="29" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L96" s="29" t="s">
         <v>27</v>
@@ -8599,11 +8619,9 @@
       <c r="N96" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O96" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P96" s="32" t="s">
-        <v>145</v>
+      <c r="O96" s="28"/>
+      <c r="P96" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="Q96" s="33"/>
       <c r="R96" s="34"/>
@@ -8640,7 +8658,7 @@
       <c r="AW96" s="35"/>
       <c r="AX96" s="35"/>
     </row>
-    <row r="97" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="26"/>
       <c r="B97" s="27">
         <v>46079</v>
@@ -8650,23 +8668,23 @@
       </c>
       <c r="D97" s="28"/>
       <c r="E97" s="29" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F97" s="28"/>
       <c r="G97" s="29" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H97" s="29" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I97" s="31">
-        <v>20000</v>
+        <v>7500</v>
       </c>
       <c r="J97" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K97" s="29" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="L97" s="29" t="s">
         <v>27</v>
@@ -8677,8 +8695,12 @@
       <c r="N97" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O97" s="28"/>
-      <c r="P97" s="33"/>
+      <c r="O97" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="P97" s="32" t="s">
+        <v>145</v>
+      </c>
       <c r="Q97" s="33"/>
       <c r="R97" s="34"/>
       <c r="S97" s="34"/>
@@ -8715,136 +8737,132 @@
       <c r="AX97" s="35"/>
     </row>
     <row r="98" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="37"/>
-      <c r="B98" s="38"/>
-      <c r="C98" s="38"/>
-      <c r="D98" s="38"/>
-      <c r="E98" s="38"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="38"/>
-      <c r="H98" s="38"/>
-      <c r="I98" s="39"/>
-      <c r="J98" s="38"/>
-      <c r="K98" s="38"/>
-      <c r="L98" s="38"/>
-      <c r="M98" s="38"/>
-      <c r="N98" s="38"/>
-      <c r="O98" s="38"/>
-      <c r="P98" s="39"/>
-      <c r="Q98" s="39"/>
-      <c r="R98" s="40"/>
-      <c r="S98" s="40"/>
-      <c r="T98" s="40"/>
-      <c r="U98" s="40"/>
-      <c r="V98" s="40"/>
-      <c r="W98" s="40"/>
-      <c r="X98" s="40"/>
-      <c r="Y98" s="40"/>
-      <c r="Z98" s="41"/>
-      <c r="AA98" s="41"/>
-      <c r="AB98" s="41"/>
-      <c r="AC98" s="41"/>
-      <c r="AD98" s="41"/>
-      <c r="AE98" s="41"/>
-      <c r="AF98" s="41"/>
-      <c r="AG98" s="41"/>
-      <c r="AH98" s="41"/>
-      <c r="AI98" s="41"/>
-      <c r="AJ98" s="41"/>
-      <c r="AK98" s="41"/>
-      <c r="AL98" s="41"/>
-      <c r="AM98" s="41"/>
-      <c r="AN98" s="41"/>
-      <c r="AO98" s="41"/>
-      <c r="AP98" s="41"/>
-      <c r="AQ98" s="41"/>
-      <c r="AR98" s="41"/>
-      <c r="AS98" s="41"/>
-      <c r="AT98" s="41"/>
-      <c r="AU98" s="41"/>
-      <c r="AV98" s="41"/>
-      <c r="AW98" s="41"/>
-      <c r="AX98" s="41"/>
-    </row>
-    <row r="99" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="19"/>
-      <c r="B99" s="20">
+      <c r="A98" s="26"/>
+      <c r="B98" s="27">
         <v>46079</v>
       </c>
-      <c r="C99" s="20">
-        <v>46100</v>
-      </c>
-      <c r="D99" s="21"/>
-      <c r="E99" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="F99" s="21"/>
-      <c r="G99" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="H99" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="I99" s="24">
-        <v>41201.949999999997</v>
-      </c>
-      <c r="J99" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K99" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="L99" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N99" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O99" s="21"/>
-      <c r="P99" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q99" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="R99" s="17"/>
-      <c r="S99" s="17"/>
-      <c r="T99" s="17"/>
-      <c r="U99" s="17"/>
-      <c r="V99" s="17"/>
-      <c r="W99" s="17"/>
-      <c r="X99" s="17"/>
-      <c r="Y99" s="17"/>
-      <c r="Z99" s="18"/>
-      <c r="AA99" s="18"/>
-      <c r="AB99" s="18"/>
-      <c r="AC99" s="18"/>
-      <c r="AD99" s="18"/>
-      <c r="AE99" s="18"/>
-      <c r="AF99" s="18"/>
-      <c r="AG99" s="18"/>
-      <c r="AH99" s="18"/>
-      <c r="AI99" s="18"/>
-      <c r="AJ99" s="18"/>
-      <c r="AK99" s="18"/>
-      <c r="AL99" s="18"/>
-      <c r="AM99" s="18"/>
-      <c r="AN99" s="18"/>
-      <c r="AO99" s="18"/>
-      <c r="AP99" s="18"/>
-      <c r="AQ99" s="18"/>
-      <c r="AR99" s="18"/>
-      <c r="AS99" s="18"/>
-      <c r="AT99" s="18"/>
-      <c r="AU99" s="18"/>
-      <c r="AV99" s="18"/>
-      <c r="AW99" s="18"/>
-      <c r="AX99" s="18"/>
-    </row>
-    <row r="100" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="27">
+        <v>46099</v>
+      </c>
+      <c r="D98" s="28"/>
+      <c r="E98" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F98" s="28"/>
+      <c r="G98" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H98" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I98" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J98" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K98" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L98" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M98" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N98" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O98" s="28"/>
+      <c r="P98" s="33"/>
+      <c r="Q98" s="33"/>
+      <c r="R98" s="34"/>
+      <c r="S98" s="34"/>
+      <c r="T98" s="34"/>
+      <c r="U98" s="34"/>
+      <c r="V98" s="34"/>
+      <c r="W98" s="34"/>
+      <c r="X98" s="34"/>
+      <c r="Y98" s="34"/>
+      <c r="Z98" s="35"/>
+      <c r="AA98" s="35"/>
+      <c r="AB98" s="35"/>
+      <c r="AC98" s="35"/>
+      <c r="AD98" s="35"/>
+      <c r="AE98" s="35"/>
+      <c r="AF98" s="35"/>
+      <c r="AG98" s="35"/>
+      <c r="AH98" s="35"/>
+      <c r="AI98" s="35"/>
+      <c r="AJ98" s="35"/>
+      <c r="AK98" s="35"/>
+      <c r="AL98" s="35"/>
+      <c r="AM98" s="35"/>
+      <c r="AN98" s="35"/>
+      <c r="AO98" s="35"/>
+      <c r="AP98" s="35"/>
+      <c r="AQ98" s="35"/>
+      <c r="AR98" s="35"/>
+      <c r="AS98" s="35"/>
+      <c r="AT98" s="35"/>
+      <c r="AU98" s="35"/>
+      <c r="AV98" s="35"/>
+      <c r="AW98" s="35"/>
+      <c r="AX98" s="35"/>
+    </row>
+    <row r="99" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="37"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38"/>
+      <c r="G99" s="38"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="39"/>
+      <c r="J99" s="38"/>
+      <c r="K99" s="38"/>
+      <c r="L99" s="38"/>
+      <c r="M99" s="38"/>
+      <c r="N99" s="38"/>
+      <c r="O99" s="38"/>
+      <c r="P99" s="39"/>
+      <c r="Q99" s="39"/>
+      <c r="R99" s="40"/>
+      <c r="S99" s="40"/>
+      <c r="T99" s="40"/>
+      <c r="U99" s="40"/>
+      <c r="V99" s="40"/>
+      <c r="W99" s="40"/>
+      <c r="X99" s="40"/>
+      <c r="Y99" s="40"/>
+      <c r="Z99" s="41"/>
+      <c r="AA99" s="41"/>
+      <c r="AB99" s="41"/>
+      <c r="AC99" s="41"/>
+      <c r="AD99" s="41"/>
+      <c r="AE99" s="41"/>
+      <c r="AF99" s="41"/>
+      <c r="AG99" s="41"/>
+      <c r="AH99" s="41"/>
+      <c r="AI99" s="41"/>
+      <c r="AJ99" s="41"/>
+      <c r="AK99" s="41"/>
+      <c r="AL99" s="41"/>
+      <c r="AM99" s="41"/>
+      <c r="AN99" s="41"/>
+      <c r="AO99" s="41"/>
+      <c r="AP99" s="41"/>
+      <c r="AQ99" s="41"/>
+      <c r="AR99" s="41"/>
+      <c r="AS99" s="41"/>
+      <c r="AT99" s="41"/>
+      <c r="AU99" s="41"/>
+      <c r="AV99" s="41"/>
+      <c r="AW99" s="41"/>
+      <c r="AX99" s="41"/>
+    </row>
+    <row r="100" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="19"/>
       <c r="B100" s="20">
         <v>46079</v>
@@ -8854,25 +8872,23 @@
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="F100" s="23" t="s">
-        <v>151</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F100" s="21"/>
       <c r="G100" s="22" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I100" s="24">
-        <v>163.96</v>
+        <v>41201.949999999997</v>
       </c>
       <c r="J100" s="22" t="b">
         <v>1</v>
       </c>
       <c r="K100" s="22" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="L100" s="22" t="s">
         <v>21</v>
@@ -8884,8 +8900,12 @@
         <v>23</v>
       </c>
       <c r="O100" s="21"/>
-      <c r="P100" s="25"/>
-      <c r="Q100" s="25"/>
+      <c r="P100" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q100" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="R100" s="17"/>
       <c r="S100" s="17"/>
       <c r="T100" s="17"/>
@@ -8930,19 +8950,19 @@
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F101" s="23">
-        <v>453494</v>
+        <v>150</v>
+      </c>
+      <c r="F101" s="23" t="s">
+        <v>151</v>
       </c>
       <c r="G101" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="I101" s="24">
-        <v>10079.950000000001</v>
+        <v>163.96</v>
       </c>
       <c r="J101" s="22" t="b">
         <v>1</v>
@@ -9006,19 +9026,19 @@
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="22" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="F102" s="23">
-        <v>264272</v>
+        <v>453494</v>
       </c>
       <c r="G102" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H102" s="22" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="I102" s="24">
-        <v>3452.46</v>
+        <v>10079.950000000001</v>
       </c>
       <c r="J102" s="22" t="b">
         <v>1</v>
@@ -9082,19 +9102,19 @@
       </c>
       <c r="D103" s="21"/>
       <c r="E103" s="22" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="F103" s="23">
-        <v>268025</v>
+        <v>264272</v>
       </c>
       <c r="G103" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H103" s="22" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I103" s="24">
-        <v>17864.88</v>
+        <v>3452.46</v>
       </c>
       <c r="J103" s="22" t="b">
         <v>1</v>
@@ -9151,17 +9171,17 @@
     <row r="104" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="19"/>
       <c r="B104" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C104" s="20">
         <v>46100</v>
       </c>
       <c r="D104" s="21"/>
       <c r="E104" s="22" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="F104" s="23">
-        <v>924426</v>
+        <v>268025</v>
       </c>
       <c r="G104" s="22" t="s">
         <v>18</v>
@@ -9170,7 +9190,7 @@
         <v>25</v>
       </c>
       <c r="I104" s="24">
-        <v>7298.44</v>
+        <v>17864.88</v>
       </c>
       <c r="J104" s="22" t="b">
         <v>1</v>
@@ -9234,19 +9254,19 @@
       </c>
       <c r="D105" s="21"/>
       <c r="E105" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F105" s="23">
-        <v>2295</v>
+        <v>924426</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I105" s="24">
-        <v>909.15</v>
+        <v>7298.44</v>
       </c>
       <c r="J105" s="22" t="b">
         <v>1</v>
@@ -9310,19 +9330,19 @@
       </c>
       <c r="D106" s="21"/>
       <c r="E106" s="22" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="F106" s="23">
-        <v>9755</v>
+        <v>2295</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I106" s="24">
-        <v>1700</v>
+        <v>909.15</v>
       </c>
       <c r="J106" s="22" t="b">
         <v>1</v>
@@ -9331,7 +9351,7 @@
         <v>20</v>
       </c>
       <c r="L106" s="22" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M106" s="22" t="s">
         <v>22</v>
@@ -9377,106 +9397,110 @@
       <c r="AX106" s="18"/>
     </row>
     <row r="107" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="26"/>
-      <c r="B107" s="27">
-        <v>46079</v>
-      </c>
-      <c r="C107" s="27">
+      <c r="A107" s="19"/>
+      <c r="B107" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C107" s="20">
         <v>46100</v>
       </c>
-      <c r="D107" s="28"/>
-      <c r="E107" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="F107" s="28"/>
-      <c r="G107" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="H107" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="I107" s="31">
-        <v>540</v>
-      </c>
-      <c r="J107" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K107" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="L107" s="29" t="s">
+      <c r="D107" s="21"/>
+      <c r="E107" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="F107" s="23">
+        <v>9755</v>
+      </c>
+      <c r="G107" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H107" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I107" s="24">
+        <v>1700</v>
+      </c>
+      <c r="J107" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K107" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L107" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="M107" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N107" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O107" s="28"/>
-      <c r="P107" s="33"/>
-      <c r="Q107" s="33"/>
-      <c r="R107" s="34"/>
-      <c r="S107" s="34"/>
-      <c r="T107" s="34"/>
-      <c r="U107" s="34"/>
-      <c r="V107" s="34"/>
-      <c r="W107" s="34"/>
-      <c r="X107" s="34"/>
-      <c r="Y107" s="34"/>
-      <c r="Z107" s="35"/>
-      <c r="AA107" s="35"/>
-      <c r="AB107" s="35"/>
-      <c r="AC107" s="35"/>
-      <c r="AD107" s="35"/>
-      <c r="AE107" s="35"/>
-      <c r="AF107" s="35"/>
-      <c r="AG107" s="35"/>
-      <c r="AH107" s="35"/>
-      <c r="AI107" s="35"/>
-      <c r="AJ107" s="35"/>
-      <c r="AK107" s="35"/>
-      <c r="AL107" s="35"/>
-      <c r="AM107" s="35"/>
-      <c r="AN107" s="35"/>
-      <c r="AO107" s="35"/>
-      <c r="AP107" s="35"/>
-      <c r="AQ107" s="35"/>
-      <c r="AR107" s="35"/>
-      <c r="AS107" s="35"/>
-      <c r="AT107" s="35"/>
-      <c r="AU107" s="35"/>
-      <c r="AV107" s="35"/>
-      <c r="AW107" s="35"/>
-      <c r="AX107" s="35"/>
-    </row>
-    <row r="108" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M107" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N107" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O107" s="21"/>
+      <c r="P107" s="25"/>
+      <c r="Q107" s="25"/>
+      <c r="R107" s="17"/>
+      <c r="S107" s="17"/>
+      <c r="T107" s="17"/>
+      <c r="U107" s="17"/>
+      <c r="V107" s="17"/>
+      <c r="W107" s="17"/>
+      <c r="X107" s="17"/>
+      <c r="Y107" s="17"/>
+      <c r="Z107" s="18"/>
+      <c r="AA107" s="18"/>
+      <c r="AB107" s="18"/>
+      <c r="AC107" s="18"/>
+      <c r="AD107" s="18"/>
+      <c r="AE107" s="18"/>
+      <c r="AF107" s="18"/>
+      <c r="AG107" s="18"/>
+      <c r="AH107" s="18"/>
+      <c r="AI107" s="18"/>
+      <c r="AJ107" s="18"/>
+      <c r="AK107" s="18"/>
+      <c r="AL107" s="18"/>
+      <c r="AM107" s="18"/>
+      <c r="AN107" s="18"/>
+      <c r="AO107" s="18"/>
+      <c r="AP107" s="18"/>
+      <c r="AQ107" s="18"/>
+      <c r="AR107" s="18"/>
+      <c r="AS107" s="18"/>
+      <c r="AT107" s="18"/>
+      <c r="AU107" s="18"/>
+      <c r="AV107" s="18"/>
+      <c r="AW107" s="18"/>
+      <c r="AX107" s="18"/>
+    </row>
+    <row r="108" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="26"/>
       <c r="B108" s="27">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C108" s="27">
         <v>46100</v>
       </c>
       <c r="D108" s="28"/>
       <c r="E108" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="F108" s="28"/>
+        <v>87</v>
+      </c>
+      <c r="F108" s="30">
+        <v>3185</v>
+      </c>
       <c r="G108" s="29" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H108" s="29" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="I108" s="31">
-        <v>448.55</v>
+        <v>96166.44</v>
       </c>
       <c r="J108" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K108" s="29" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="L108" s="29" t="s">
         <v>27</v>
@@ -9487,10 +9511,10 @@
       <c r="N108" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O108" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="P108" s="33"/>
+      <c r="O108" s="28"/>
+      <c r="P108" s="32" t="s">
+        <v>195</v>
+      </c>
       <c r="Q108" s="33"/>
       <c r="R108" s="34"/>
       <c r="S108" s="34"/>
@@ -9526,33 +9550,33 @@
       <c r="AW108" s="35"/>
       <c r="AX108" s="35"/>
     </row>
-    <row r="109" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="26"/>
       <c r="B109" s="27">
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="C109" s="27">
         <v>46100</v>
       </c>
       <c r="D109" s="28"/>
       <c r="E109" s="29" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="F109" s="28"/>
       <c r="G109" s="29" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H109" s="29" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="I109" s="31">
-        <v>9975</v>
+        <v>540</v>
       </c>
       <c r="J109" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K109" s="29" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L109" s="29" t="s">
         <v>27</v>
@@ -9563,12 +9587,8 @@
       <c r="N109" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O109" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P109" s="32" t="s">
-        <v>161</v>
-      </c>
+      <c r="O109" s="28"/>
+      <c r="P109" s="33"/>
       <c r="Q109" s="33"/>
       <c r="R109" s="34"/>
       <c r="S109" s="34"/>
@@ -9604,33 +9624,33 @@
       <c r="AW109" s="35"/>
       <c r="AX109" s="35"/>
     </row>
-    <row r="110" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:50" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="26"/>
       <c r="B110" s="27">
-        <v>46059</v>
+        <v>46091</v>
       </c>
       <c r="C110" s="27">
         <v>46100</v>
       </c>
       <c r="D110" s="28"/>
       <c r="E110" s="29" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="F110" s="28"/>
       <c r="G110" s="29" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H110" s="29" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="I110" s="31">
-        <v>10000</v>
+        <v>448.55</v>
       </c>
       <c r="J110" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K110" s="29" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="L110" s="29" t="s">
         <v>27</v>
@@ -9642,11 +9662,9 @@
         <v>28</v>
       </c>
       <c r="O110" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P110" s="32" t="s">
-        <v>162</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="P110" s="33"/>
       <c r="Q110" s="33"/>
       <c r="R110" s="34"/>
       <c r="S110" s="34"/>
@@ -9682,33 +9700,33 @@
       <c r="AW110" s="35"/>
       <c r="AX110" s="35"/>
     </row>
-    <row r="111" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="26"/>
       <c r="B111" s="27">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C111" s="27">
         <v>46100</v>
       </c>
       <c r="D111" s="28"/>
       <c r="E111" s="29" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F111" s="28"/>
       <c r="G111" s="29" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H111" s="29" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I111" s="31">
-        <v>20000</v>
+        <v>9975</v>
       </c>
       <c r="J111" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K111" s="29" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="L111" s="29" t="s">
         <v>27</v>
@@ -9719,17 +9737,21 @@
       <c r="N111" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O111" s="28"/>
-      <c r="P111" s="33"/>
+      <c r="O111" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="P111" s="32" t="s">
+        <v>161</v>
+      </c>
       <c r="Q111" s="33"/>
-      <c r="R111" s="35"/>
-      <c r="S111" s="35"/>
-      <c r="T111" s="35"/>
-      <c r="U111" s="35"/>
-      <c r="V111" s="35"/>
-      <c r="W111" s="35"/>
-      <c r="X111" s="35"/>
-      <c r="Y111" s="35"/>
+      <c r="R111" s="34"/>
+      <c r="S111" s="34"/>
+      <c r="T111" s="34"/>
+      <c r="U111" s="34"/>
+      <c r="V111" s="34"/>
+      <c r="W111" s="34"/>
+      <c r="X111" s="34"/>
+      <c r="Y111" s="34"/>
       <c r="Z111" s="35"/>
       <c r="AA111" s="35"/>
       <c r="AB111" s="35"/>
@@ -9756,85 +9778,111 @@
       <c r="AW111" s="35"/>
       <c r="AX111" s="35"/>
     </row>
-    <row r="112" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="37"/>
-      <c r="B112" s="38"/>
-      <c r="C112" s="38"/>
-      <c r="D112" s="38"/>
-      <c r="E112" s="38"/>
-      <c r="F112" s="38"/>
-      <c r="G112" s="38"/>
-      <c r="H112" s="38"/>
-      <c r="I112" s="39"/>
-      <c r="J112" s="38"/>
-      <c r="K112" s="38"/>
-      <c r="L112" s="38"/>
-      <c r="M112" s="38"/>
-      <c r="N112" s="38"/>
-      <c r="O112" s="38"/>
-      <c r="P112" s="39"/>
-      <c r="Q112" s="39"/>
-      <c r="R112" s="41"/>
-      <c r="S112" s="41"/>
-      <c r="T112" s="41"/>
-      <c r="U112" s="41"/>
-      <c r="V112" s="41"/>
-      <c r="W112" s="41"/>
-      <c r="X112" s="41"/>
-      <c r="Y112" s="41"/>
-      <c r="Z112" s="41"/>
-      <c r="AA112" s="41"/>
-      <c r="AB112" s="41"/>
-      <c r="AC112" s="41"/>
-      <c r="AD112" s="41"/>
-      <c r="AE112" s="41"/>
-      <c r="AF112" s="41"/>
-      <c r="AG112" s="41"/>
-      <c r="AH112" s="41"/>
-      <c r="AI112" s="41"/>
-      <c r="AJ112" s="41"/>
-      <c r="AK112" s="41"/>
-      <c r="AL112" s="41"/>
-      <c r="AM112" s="41"/>
-      <c r="AN112" s="41"/>
-      <c r="AO112" s="41"/>
-      <c r="AP112" s="41"/>
-      <c r="AQ112" s="41"/>
-      <c r="AR112" s="41"/>
-      <c r="AS112" s="41"/>
-      <c r="AT112" s="41"/>
-      <c r="AU112" s="41"/>
-      <c r="AV112" s="41"/>
-      <c r="AW112" s="41"/>
-      <c r="AX112" s="41"/>
-    </row>
-    <row r="113" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="26"/>
+      <c r="B112" s="27">
+        <v>46059</v>
+      </c>
+      <c r="C112" s="27">
+        <v>46100</v>
+      </c>
+      <c r="D112" s="28"/>
+      <c r="E112" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="F112" s="28"/>
+      <c r="G112" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H112" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I112" s="31">
+        <v>10000</v>
+      </c>
+      <c r="J112" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K112" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L112" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M112" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N112" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O112" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="P112" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q112" s="33"/>
+      <c r="R112" s="34"/>
+      <c r="S112" s="34"/>
+      <c r="T112" s="34"/>
+      <c r="U112" s="34"/>
+      <c r="V112" s="34"/>
+      <c r="W112" s="34"/>
+      <c r="X112" s="34"/>
+      <c r="Y112" s="34"/>
+      <c r="Z112" s="35"/>
+      <c r="AA112" s="35"/>
+      <c r="AB112" s="35"/>
+      <c r="AC112" s="35"/>
+      <c r="AD112" s="35"/>
+      <c r="AE112" s="35"/>
+      <c r="AF112" s="35"/>
+      <c r="AG112" s="35"/>
+      <c r="AH112" s="35"/>
+      <c r="AI112" s="35"/>
+      <c r="AJ112" s="35"/>
+      <c r="AK112" s="35"/>
+      <c r="AL112" s="35"/>
+      <c r="AM112" s="35"/>
+      <c r="AN112" s="35"/>
+      <c r="AO112" s="35"/>
+      <c r="AP112" s="35"/>
+      <c r="AQ112" s="35"/>
+      <c r="AR112" s="35"/>
+      <c r="AS112" s="35"/>
+      <c r="AT112" s="35"/>
+      <c r="AU112" s="35"/>
+      <c r="AV112" s="35"/>
+      <c r="AW112" s="35"/>
+      <c r="AX112" s="35"/>
+    </row>
+    <row r="113" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="26"/>
       <c r="B113" s="27">
         <v>46079</v>
       </c>
       <c r="C113" s="27">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="D113" s="28"/>
       <c r="E113" s="29" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="F113" s="28"/>
       <c r="G113" s="29" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="H113" s="29" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="I113" s="31">
-        <v>110000</v>
+        <v>20000</v>
       </c>
       <c r="J113" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K113" s="29" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="L113" s="29" t="s">
         <v>27</v>
@@ -9847,9 +9895,7 @@
       </c>
       <c r="O113" s="28"/>
       <c r="P113" s="33"/>
-      <c r="Q113" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q113" s="33"/>
       <c r="R113" s="35"/>
       <c r="S113" s="35"/>
       <c r="T113" s="35"/>
@@ -9884,83 +9930,59 @@
       <c r="AW113" s="35"/>
       <c r="AX113" s="35"/>
     </row>
-    <row r="114" spans="1:50" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="26"/>
-      <c r="B114" s="27">
-        <v>46093</v>
-      </c>
-      <c r="C114" s="27">
-        <v>46101</v>
-      </c>
-      <c r="D114" s="28"/>
-      <c r="E114" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="F114" s="28"/>
-      <c r="G114" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="H114" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="I114" s="31">
-        <v>1242.3</v>
-      </c>
-      <c r="J114" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K114" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="L114" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M114" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N114" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O114" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="P114" s="28"/>
-      <c r="Q114" s="28"/>
-      <c r="R114" s="34"/>
-      <c r="S114" s="34"/>
-      <c r="T114" s="34"/>
-      <c r="U114" s="34"/>
-      <c r="V114" s="34"/>
-      <c r="W114" s="34"/>
-      <c r="X114" s="34"/>
-      <c r="Y114" s="34"/>
-      <c r="Z114" s="35"/>
-      <c r="AA114" s="35"/>
-      <c r="AB114" s="35"/>
-      <c r="AC114" s="35"/>
-      <c r="AD114" s="35"/>
-      <c r="AE114" s="35"/>
-      <c r="AF114" s="35"/>
-      <c r="AG114" s="35"/>
-      <c r="AH114" s="35"/>
-      <c r="AI114" s="35"/>
-      <c r="AJ114" s="35"/>
-      <c r="AK114" s="35"/>
-      <c r="AL114" s="35"/>
-      <c r="AM114" s="35"/>
-      <c r="AN114" s="35"/>
-      <c r="AO114" s="35"/>
-      <c r="AP114" s="35"/>
-      <c r="AQ114" s="35"/>
-      <c r="AR114" s="35"/>
-      <c r="AS114" s="35"/>
-      <c r="AT114" s="35"/>
-      <c r="AU114" s="35"/>
-      <c r="AV114" s="35"/>
-      <c r="AW114" s="35"/>
-      <c r="AX114" s="35"/>
-    </row>
-    <row r="115" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="37"/>
+      <c r="B114" s="38"/>
+      <c r="C114" s="38"/>
+      <c r="D114" s="38"/>
+      <c r="E114" s="38"/>
+      <c r="F114" s="38"/>
+      <c r="G114" s="38"/>
+      <c r="H114" s="38"/>
+      <c r="I114" s="39"/>
+      <c r="J114" s="38"/>
+      <c r="K114" s="38"/>
+      <c r="L114" s="38"/>
+      <c r="M114" s="38"/>
+      <c r="N114" s="38"/>
+      <c r="O114" s="38"/>
+      <c r="P114" s="39"/>
+      <c r="Q114" s="39"/>
+      <c r="R114" s="41"/>
+      <c r="S114" s="41"/>
+      <c r="T114" s="41"/>
+      <c r="U114" s="41"/>
+      <c r="V114" s="41"/>
+      <c r="W114" s="41"/>
+      <c r="X114" s="41"/>
+      <c r="Y114" s="41"/>
+      <c r="Z114" s="41"/>
+      <c r="AA114" s="41"/>
+      <c r="AB114" s="41"/>
+      <c r="AC114" s="41"/>
+      <c r="AD114" s="41"/>
+      <c r="AE114" s="41"/>
+      <c r="AF114" s="41"/>
+      <c r="AG114" s="41"/>
+      <c r="AH114" s="41"/>
+      <c r="AI114" s="41"/>
+      <c r="AJ114" s="41"/>
+      <c r="AK114" s="41"/>
+      <c r="AL114" s="41"/>
+      <c r="AM114" s="41"/>
+      <c r="AN114" s="41"/>
+      <c r="AO114" s="41"/>
+      <c r="AP114" s="41"/>
+      <c r="AQ114" s="41"/>
+      <c r="AR114" s="41"/>
+      <c r="AS114" s="41"/>
+      <c r="AT114" s="41"/>
+      <c r="AU114" s="41"/>
+      <c r="AV114" s="41"/>
+      <c r="AW114" s="41"/>
+      <c r="AX114" s="41"/>
+    </row>
+    <row r="115" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="26"/>
       <c r="B115" s="27">
         <v>46079</v>
@@ -9970,23 +9992,23 @@
       </c>
       <c r="D115" s="28"/>
       <c r="E115" s="29" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="F115" s="28"/>
       <c r="G115" s="29" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="H115" s="29" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="I115" s="31">
-        <v>7851.77</v>
+        <v>110000</v>
       </c>
       <c r="J115" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K115" s="29" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="L115" s="29" t="s">
         <v>27</v>
@@ -9998,18 +10020,18 @@
         <v>28</v>
       </c>
       <c r="O115" s="28"/>
-      <c r="P115" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q115" s="28"/>
-      <c r="R115" s="34"/>
-      <c r="S115" s="34"/>
-      <c r="T115" s="34"/>
-      <c r="U115" s="34"/>
-      <c r="V115" s="34"/>
-      <c r="W115" s="34"/>
-      <c r="X115" s="34"/>
-      <c r="Y115" s="34"/>
+      <c r="P115" s="33"/>
+      <c r="Q115" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R115" s="35"/>
+      <c r="S115" s="35"/>
+      <c r="T115" s="35"/>
+      <c r="U115" s="35"/>
+      <c r="V115" s="35"/>
+      <c r="W115" s="35"/>
+      <c r="X115" s="35"/>
+      <c r="Y115" s="35"/>
       <c r="Z115" s="35"/>
       <c r="AA115" s="35"/>
       <c r="AB115" s="35"/>
@@ -10036,27 +10058,27 @@
       <c r="AW115" s="35"/>
       <c r="AX115" s="35"/>
     </row>
-    <row r="116" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:50" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="26"/>
       <c r="B116" s="27">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C116" s="27">
         <v>46101</v>
       </c>
       <c r="D116" s="28"/>
       <c r="E116" s="29" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="F116" s="28"/>
       <c r="G116" s="29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H116" s="29" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="I116" s="31">
-        <v>700</v>
+        <v>1242.3</v>
       </c>
       <c r="J116" s="29" t="b">
         <v>1</v>
@@ -10073,13 +10095,11 @@
       <c r="N116" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O116" s="28"/>
-      <c r="P116" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q116" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="O116" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="P116" s="28"/>
+      <c r="Q116" s="28"/>
       <c r="R116" s="34"/>
       <c r="S116" s="34"/>
       <c r="T116" s="34"/>
@@ -10114,33 +10134,33 @@
       <c r="AW116" s="35"/>
       <c r="AX116" s="35"/>
     </row>
-    <row r="117" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="26"/>
       <c r="B117" s="27">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="C117" s="27">
         <v>46101</v>
       </c>
       <c r="D117" s="28"/>
       <c r="E117" s="29" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="F117" s="28"/>
       <c r="G117" s="29" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H117" s="29" t="s">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="I117" s="31">
-        <v>5000</v>
+        <v>84.24</v>
       </c>
       <c r="J117" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K117" s="29" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="L117" s="29" t="s">
         <v>27</v>
@@ -10151,13 +10171,9 @@
       <c r="N117" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O117" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="P117" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q117" s="33"/>
+      <c r="O117" s="28"/>
+      <c r="P117" s="28"/>
+      <c r="Q117" s="28"/>
       <c r="R117" s="34"/>
       <c r="S117" s="34"/>
       <c r="T117" s="34"/>
@@ -10192,27 +10208,27 @@
       <c r="AW117" s="35"/>
       <c r="AX117" s="35"/>
     </row>
-    <row r="118" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="26"/>
       <c r="B118" s="27">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="C118" s="27">
         <v>46101</v>
       </c>
       <c r="D118" s="28"/>
       <c r="E118" s="29" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="F118" s="28"/>
       <c r="G118" s="29" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H118" s="29" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="I118" s="31">
-        <v>10000</v>
+        <v>688.88</v>
       </c>
       <c r="J118" s="29" t="b">
         <v>1</v>
@@ -10230,10 +10246,8 @@
         <v>28</v>
       </c>
       <c r="O118" s="28"/>
-      <c r="P118" s="33"/>
-      <c r="Q118" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="P118" s="28"/>
+      <c r="Q118" s="28"/>
       <c r="R118" s="34"/>
       <c r="S118" s="34"/>
       <c r="T118" s="34"/>
@@ -10268,7 +10282,7 @@
       <c r="AW118" s="35"/>
       <c r="AX118" s="35"/>
     </row>
-    <row r="119" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="26"/>
       <c r="B119" s="27">
         <v>46079</v>
@@ -10278,17 +10292,17 @@
       </c>
       <c r="D119" s="28"/>
       <c r="E119" s="29" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="F119" s="28"/>
       <c r="G119" s="29" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="H119" s="29" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="I119" s="31">
-        <v>25000</v>
+        <v>7851.77</v>
       </c>
       <c r="J119" s="29" t="b">
         <v>1</v>
@@ -10306,12 +10320,10 @@
         <v>28</v>
       </c>
       <c r="O119" s="28"/>
-      <c r="P119" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q119" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="P119" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q119" s="28"/>
       <c r="R119" s="34"/>
       <c r="S119" s="34"/>
       <c r="T119" s="34"/>
@@ -10347,310 +10359,316 @@
       <c r="AX119" s="35"/>
     </row>
     <row r="120" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="19"/>
-      <c r="B120" s="20">
+      <c r="A120" s="26"/>
+      <c r="B120" s="27">
         <v>46079</v>
       </c>
-      <c r="C120" s="20">
+      <c r="C120" s="27">
         <v>46101</v>
       </c>
-      <c r="D120" s="21"/>
-      <c r="E120" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="F120" s="21"/>
-      <c r="G120" s="22" t="s">
+      <c r="D120" s="28"/>
+      <c r="E120" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F120" s="28"/>
+      <c r="G120" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H120" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="I120" s="24">
-        <v>96500</v>
-      </c>
-      <c r="J120" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K120" s="22" t="s">
+      <c r="H120" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I120" s="31">
+        <v>700</v>
+      </c>
+      <c r="J120" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K120" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L120" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M120" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N120" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O120" s="28"/>
+      <c r="P120" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q120" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R120" s="34"/>
+      <c r="S120" s="34"/>
+      <c r="T120" s="34"/>
+      <c r="U120" s="34"/>
+      <c r="V120" s="34"/>
+      <c r="W120" s="34"/>
+      <c r="X120" s="34"/>
+      <c r="Y120" s="34"/>
+      <c r="Z120" s="35"/>
+      <c r="AA120" s="35"/>
+      <c r="AB120" s="35"/>
+      <c r="AC120" s="35"/>
+      <c r="AD120" s="35"/>
+      <c r="AE120" s="35"/>
+      <c r="AF120" s="35"/>
+      <c r="AG120" s="35"/>
+      <c r="AH120" s="35"/>
+      <c r="AI120" s="35"/>
+      <c r="AJ120" s="35"/>
+      <c r="AK120" s="35"/>
+      <c r="AL120" s="35"/>
+      <c r="AM120" s="35"/>
+      <c r="AN120" s="35"/>
+      <c r="AO120" s="35"/>
+      <c r="AP120" s="35"/>
+      <c r="AQ120" s="35"/>
+      <c r="AR120" s="35"/>
+      <c r="AS120" s="35"/>
+      <c r="AT120" s="35"/>
+      <c r="AU120" s="35"/>
+      <c r="AV120" s="35"/>
+      <c r="AW120" s="35"/>
+      <c r="AX120" s="35"/>
+    </row>
+    <row r="121" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="26"/>
+      <c r="B121" s="27">
+        <v>46079</v>
+      </c>
+      <c r="C121" s="27">
+        <v>46101</v>
+      </c>
+      <c r="D121" s="28"/>
+      <c r="E121" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F121" s="28"/>
+      <c r="G121" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="H121" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="I121" s="31">
+        <v>5000</v>
+      </c>
+      <c r="J121" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K121" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="L120" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M120" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N120" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O120" s="21"/>
-      <c r="P120" s="25"/>
-      <c r="Q120" s="36" t="s">
+      <c r="L121" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M121" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N121" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O121" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="P121" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q121" s="33"/>
+      <c r="R121" s="34"/>
+      <c r="S121" s="34"/>
+      <c r="T121" s="34"/>
+      <c r="U121" s="34"/>
+      <c r="V121" s="34"/>
+      <c r="W121" s="34"/>
+      <c r="X121" s="34"/>
+      <c r="Y121" s="34"/>
+      <c r="Z121" s="35"/>
+      <c r="AA121" s="35"/>
+      <c r="AB121" s="35"/>
+      <c r="AC121" s="35"/>
+      <c r="AD121" s="35"/>
+      <c r="AE121" s="35"/>
+      <c r="AF121" s="35"/>
+      <c r="AG121" s="35"/>
+      <c r="AH121" s="35"/>
+      <c r="AI121" s="35"/>
+      <c r="AJ121" s="35"/>
+      <c r="AK121" s="35"/>
+      <c r="AL121" s="35"/>
+      <c r="AM121" s="35"/>
+      <c r="AN121" s="35"/>
+      <c r="AO121" s="35"/>
+      <c r="AP121" s="35"/>
+      <c r="AQ121" s="35"/>
+      <c r="AR121" s="35"/>
+      <c r="AS121" s="35"/>
+      <c r="AT121" s="35"/>
+      <c r="AU121" s="35"/>
+      <c r="AV121" s="35"/>
+      <c r="AW121" s="35"/>
+      <c r="AX121" s="35"/>
+    </row>
+    <row r="122" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="26"/>
+      <c r="B122" s="27">
+        <v>46079</v>
+      </c>
+      <c r="C122" s="27">
+        <v>46101</v>
+      </c>
+      <c r="D122" s="28"/>
+      <c r="E122" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F122" s="28"/>
+      <c r="G122" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="H122" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I122" s="31">
+        <v>10000</v>
+      </c>
+      <c r="J122" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K122" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L122" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M122" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N122" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O122" s="28"/>
+      <c r="P122" s="33"/>
+      <c r="Q122" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R120" s="17"/>
-      <c r="S120" s="17"/>
-      <c r="T120" s="17"/>
-      <c r="U120" s="17"/>
-      <c r="V120" s="17"/>
-      <c r="W120" s="17"/>
-      <c r="X120" s="17"/>
-      <c r="Y120" s="17"/>
-      <c r="Z120" s="18"/>
-      <c r="AA120" s="18"/>
-      <c r="AB120" s="18"/>
-      <c r="AC120" s="18"/>
-      <c r="AD120" s="18"/>
-      <c r="AE120" s="18"/>
-      <c r="AF120" s="18"/>
-      <c r="AG120" s="18"/>
-      <c r="AH120" s="18"/>
-      <c r="AI120" s="18"/>
-      <c r="AJ120" s="18"/>
-      <c r="AK120" s="18"/>
-      <c r="AL120" s="18"/>
-      <c r="AM120" s="18"/>
-      <c r="AN120" s="18"/>
-      <c r="AO120" s="18"/>
-      <c r="AP120" s="18"/>
-      <c r="AQ120" s="18"/>
-      <c r="AR120" s="18"/>
-      <c r="AS120" s="18"/>
-      <c r="AT120" s="18"/>
-      <c r="AU120" s="18"/>
-      <c r="AV120" s="18"/>
-      <c r="AW120" s="18"/>
-      <c r="AX120" s="18"/>
-    </row>
-    <row r="121" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="19"/>
-      <c r="B121" s="20">
+      <c r="R122" s="34"/>
+      <c r="S122" s="34"/>
+      <c r="T122" s="34"/>
+      <c r="U122" s="34"/>
+      <c r="V122" s="34"/>
+      <c r="W122" s="34"/>
+      <c r="X122" s="34"/>
+      <c r="Y122" s="34"/>
+      <c r="Z122" s="35"/>
+      <c r="AA122" s="35"/>
+      <c r="AB122" s="35"/>
+      <c r="AC122" s="35"/>
+      <c r="AD122" s="35"/>
+      <c r="AE122" s="35"/>
+      <c r="AF122" s="35"/>
+      <c r="AG122" s="35"/>
+      <c r="AH122" s="35"/>
+      <c r="AI122" s="35"/>
+      <c r="AJ122" s="35"/>
+      <c r="AK122" s="35"/>
+      <c r="AL122" s="35"/>
+      <c r="AM122" s="35"/>
+      <c r="AN122" s="35"/>
+      <c r="AO122" s="35"/>
+      <c r="AP122" s="35"/>
+      <c r="AQ122" s="35"/>
+      <c r="AR122" s="35"/>
+      <c r="AS122" s="35"/>
+      <c r="AT122" s="35"/>
+      <c r="AU122" s="35"/>
+      <c r="AV122" s="35"/>
+      <c r="AW122" s="35"/>
+      <c r="AX122" s="35"/>
+    </row>
+    <row r="123" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="26"/>
+      <c r="B123" s="27">
         <v>46079</v>
       </c>
-      <c r="C121" s="20">
+      <c r="C123" s="27">
         <v>46101</v>
       </c>
-      <c r="D121" s="21"/>
-      <c r="E121" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F121" s="23">
-        <v>239304</v>
-      </c>
-      <c r="G121" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H121" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I121" s="24">
-        <v>50348.42</v>
-      </c>
-      <c r="J121" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K121" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L121" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M121" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N121" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O121" s="21"/>
-      <c r="P121" s="25"/>
-      <c r="Q121" s="25"/>
-      <c r="R121" s="17"/>
-      <c r="S121" s="17"/>
-      <c r="T121" s="17"/>
-      <c r="U121" s="17"/>
-      <c r="V121" s="17"/>
-      <c r="W121" s="17"/>
-      <c r="X121" s="17"/>
-      <c r="Y121" s="17"/>
-      <c r="Z121" s="18"/>
-      <c r="AA121" s="18"/>
-      <c r="AB121" s="18"/>
-      <c r="AC121" s="18"/>
-      <c r="AD121" s="18"/>
-      <c r="AE121" s="18"/>
-      <c r="AF121" s="18"/>
-      <c r="AG121" s="18"/>
-      <c r="AH121" s="18"/>
-      <c r="AI121" s="18"/>
-      <c r="AJ121" s="18"/>
-      <c r="AK121" s="18"/>
-      <c r="AL121" s="18"/>
-      <c r="AM121" s="18"/>
-      <c r="AN121" s="18"/>
-      <c r="AO121" s="18"/>
-      <c r="AP121" s="18"/>
-      <c r="AQ121" s="18"/>
-      <c r="AR121" s="18"/>
-      <c r="AS121" s="18"/>
-      <c r="AT121" s="18"/>
-      <c r="AU121" s="18"/>
-      <c r="AV121" s="18"/>
-      <c r="AW121" s="18"/>
-      <c r="AX121" s="18"/>
-    </row>
-    <row r="122" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="19"/>
-      <c r="B122" s="20">
-        <v>46079</v>
-      </c>
-      <c r="C122" s="20">
-        <v>46101</v>
-      </c>
-      <c r="D122" s="21"/>
-      <c r="E122" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F122" s="23">
-        <v>239298</v>
-      </c>
-      <c r="G122" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H122" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I122" s="24">
-        <v>68272.17</v>
-      </c>
-      <c r="J122" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K122" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L122" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M122" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N122" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O122" s="21"/>
-      <c r="P122" s="25"/>
-      <c r="Q122" s="25"/>
-      <c r="R122" s="17"/>
-      <c r="S122" s="17"/>
-      <c r="T122" s="17"/>
-      <c r="U122" s="17"/>
-      <c r="V122" s="17"/>
-      <c r="W122" s="17"/>
-      <c r="X122" s="17"/>
-      <c r="Y122" s="17"/>
-      <c r="Z122" s="18"/>
-      <c r="AA122" s="18"/>
-      <c r="AB122" s="18"/>
-      <c r="AC122" s="18"/>
-      <c r="AD122" s="18"/>
-      <c r="AE122" s="18"/>
-      <c r="AF122" s="18"/>
-      <c r="AG122" s="18"/>
-      <c r="AH122" s="18"/>
-      <c r="AI122" s="18"/>
-      <c r="AJ122" s="18"/>
-      <c r="AK122" s="18"/>
-      <c r="AL122" s="18"/>
-      <c r="AM122" s="18"/>
-      <c r="AN122" s="18"/>
-      <c r="AO122" s="18"/>
-      <c r="AP122" s="18"/>
-      <c r="AQ122" s="18"/>
-      <c r="AR122" s="18"/>
-      <c r="AS122" s="18"/>
-      <c r="AT122" s="18"/>
-      <c r="AU122" s="18"/>
-      <c r="AV122" s="18"/>
-      <c r="AW122" s="18"/>
-      <c r="AX122" s="18"/>
-    </row>
-    <row r="123" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="19"/>
-      <c r="B123" s="20">
-        <v>46079</v>
-      </c>
-      <c r="C123" s="20">
-        <v>46101</v>
-      </c>
-      <c r="D123" s="21"/>
-      <c r="E123" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F123" s="23">
-        <v>239302</v>
-      </c>
-      <c r="G123" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H123" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I123" s="24">
-        <v>33965.33</v>
-      </c>
-      <c r="J123" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K123" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L123" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M123" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N123" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O123" s="21"/>
-      <c r="P123" s="25"/>
-      <c r="Q123" s="25"/>
-      <c r="R123" s="17"/>
-      <c r="S123" s="17"/>
-      <c r="T123" s="17"/>
-      <c r="U123" s="17"/>
-      <c r="V123" s="17"/>
-      <c r="W123" s="17"/>
-      <c r="X123" s="17"/>
-      <c r="Y123" s="17"/>
-      <c r="Z123" s="18"/>
-      <c r="AA123" s="18"/>
-      <c r="AB123" s="18"/>
-      <c r="AC123" s="18"/>
-      <c r="AD123" s="18"/>
-      <c r="AE123" s="18"/>
-      <c r="AF123" s="18"/>
-      <c r="AG123" s="18"/>
-      <c r="AH123" s="18"/>
-      <c r="AI123" s="18"/>
-      <c r="AJ123" s="18"/>
-      <c r="AK123" s="18"/>
-      <c r="AL123" s="18"/>
-      <c r="AM123" s="18"/>
-      <c r="AN123" s="18"/>
-      <c r="AO123" s="18"/>
-      <c r="AP123" s="18"/>
-      <c r="AQ123" s="18"/>
-      <c r="AR123" s="18"/>
-      <c r="AS123" s="18"/>
-      <c r="AT123" s="18"/>
-      <c r="AU123" s="18"/>
-      <c r="AV123" s="18"/>
-      <c r="AW123" s="18"/>
-      <c r="AX123" s="18"/>
-    </row>
-    <row r="124" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D123" s="28"/>
+      <c r="E123" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="F123" s="28"/>
+      <c r="G123" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H123" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="I123" s="31">
+        <v>25000</v>
+      </c>
+      <c r="J123" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K123" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L123" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M123" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N123" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O123" s="28"/>
+      <c r="P123" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q123" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="R123" s="34"/>
+      <c r="S123" s="34"/>
+      <c r="T123" s="34"/>
+      <c r="U123" s="34"/>
+      <c r="V123" s="34"/>
+      <c r="W123" s="34"/>
+      <c r="X123" s="34"/>
+      <c r="Y123" s="34"/>
+      <c r="Z123" s="35"/>
+      <c r="AA123" s="35"/>
+      <c r="AB123" s="35"/>
+      <c r="AC123" s="35"/>
+      <c r="AD123" s="35"/>
+      <c r="AE123" s="35"/>
+      <c r="AF123" s="35"/>
+      <c r="AG123" s="35"/>
+      <c r="AH123" s="35"/>
+      <c r="AI123" s="35"/>
+      <c r="AJ123" s="35"/>
+      <c r="AK123" s="35"/>
+      <c r="AL123" s="35"/>
+      <c r="AM123" s="35"/>
+      <c r="AN123" s="35"/>
+      <c r="AO123" s="35"/>
+      <c r="AP123" s="35"/>
+      <c r="AQ123" s="35"/>
+      <c r="AR123" s="35"/>
+      <c r="AS123" s="35"/>
+      <c r="AT123" s="35"/>
+      <c r="AU123" s="35"/>
+      <c r="AV123" s="35"/>
+      <c r="AW123" s="35"/>
+      <c r="AX123" s="35"/>
+    </row>
+    <row r="124" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="19"/>
       <c r="B124" s="20">
         <v>46079</v>
@@ -10660,25 +10678,23 @@
       </c>
       <c r="D124" s="21"/>
       <c r="E124" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F124" s="23">
-        <v>239277</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="F124" s="21"/>
       <c r="G124" s="22" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H124" s="22" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I124" s="24">
-        <v>59591.360000000001</v>
+        <v>96500</v>
       </c>
       <c r="J124" s="22" t="b">
         <v>1</v>
       </c>
       <c r="K124" s="22" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L124" s="22" t="s">
         <v>21</v>
@@ -10691,7 +10707,9 @@
       </c>
       <c r="O124" s="21"/>
       <c r="P124" s="25"/>
-      <c r="Q124" s="25"/>
+      <c r="Q124" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="R124" s="17"/>
       <c r="S124" s="17"/>
       <c r="T124" s="17"/>
@@ -10736,10 +10754,10 @@
       </c>
       <c r="D125" s="21"/>
       <c r="E125" s="22" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="F125" s="23">
-        <v>455202</v>
+        <v>239304</v>
       </c>
       <c r="G125" s="22" t="s">
         <v>18</v>
@@ -10748,7 +10766,7 @@
         <v>19</v>
       </c>
       <c r="I125" s="24">
-        <v>8400</v>
+        <v>50348.42</v>
       </c>
       <c r="J125" s="22" t="b">
         <v>1</v>
@@ -10812,19 +10830,19 @@
       </c>
       <c r="D126" s="21"/>
       <c r="E126" s="22" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="F126" s="23">
-        <v>132239</v>
+        <v>239298</v>
       </c>
       <c r="G126" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H126" s="22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I126" s="24">
-        <v>4556</v>
+        <v>68272.17</v>
       </c>
       <c r="J126" s="22" t="b">
         <v>1</v>
@@ -10888,19 +10906,19 @@
       </c>
       <c r="D127" s="21"/>
       <c r="E127" s="22" t="s">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c r="F127" s="23">
-        <v>264292</v>
+        <v>239302</v>
       </c>
       <c r="G127" s="22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="I127" s="24">
-        <v>208.77</v>
+        <v>33965.33</v>
       </c>
       <c r="J127" s="22" t="b">
         <v>1</v>
@@ -10957,26 +10975,26 @@
     <row r="128" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="19"/>
       <c r="B128" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C128" s="20">
         <v>46101</v>
       </c>
       <c r="D128" s="21"/>
       <c r="E128" s="22" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="F128" s="23">
-        <v>10550</v>
+        <v>239277</v>
       </c>
       <c r="G128" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H128" s="22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I128" s="24">
-        <v>15396</v>
+        <v>59591.360000000001</v>
       </c>
       <c r="J128" s="22" t="b">
         <v>1</v>
@@ -11033,17 +11051,17 @@
     <row r="129" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="19"/>
       <c r="B129" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C129" s="20">
         <v>46101</v>
       </c>
       <c r="D129" s="21"/>
       <c r="E129" s="22" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="F129" s="23">
-        <v>8060</v>
+        <v>455202</v>
       </c>
       <c r="G129" s="22" t="s">
         <v>18</v>
@@ -11052,7 +11070,7 @@
         <v>19</v>
       </c>
       <c r="I129" s="24">
-        <v>53488.32</v>
+        <v>8400</v>
       </c>
       <c r="J129" s="22" t="b">
         <v>1</v>
@@ -11109,17 +11127,17 @@
     <row r="130" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="19"/>
       <c r="B130" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C130" s="20">
         <v>46101</v>
       </c>
       <c r="D130" s="21"/>
       <c r="E130" s="22" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="F130" s="23">
-        <v>123589</v>
+        <v>132239</v>
       </c>
       <c r="G130" s="22" t="s">
         <v>18</v>
@@ -11128,7 +11146,7 @@
         <v>25</v>
       </c>
       <c r="I130" s="24">
-        <v>26875.16</v>
+        <v>4556</v>
       </c>
       <c r="J130" s="22" t="b">
         <v>1</v>
@@ -11185,26 +11203,26 @@
     <row r="131" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="19"/>
       <c r="B131" s="20">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C131" s="20">
         <v>46101</v>
       </c>
       <c r="D131" s="21"/>
       <c r="E131" s="22" t="s">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="F131" s="23">
-        <v>123587</v>
+        <v>264292</v>
       </c>
       <c r="G131" s="22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H131" s="22" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I131" s="24">
-        <v>26875.16</v>
+        <v>208.77</v>
       </c>
       <c r="J131" s="22" t="b">
         <v>1</v>
@@ -11258,343 +11276,339 @@
       <c r="AW131" s="18"/>
       <c r="AX131" s="18"/>
     </row>
-    <row r="132" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="26"/>
-      <c r="B132" s="27">
+    <row r="132" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="19"/>
+      <c r="B132" s="20">
         <v>46093</v>
       </c>
-      <c r="C132" s="27">
+      <c r="C132" s="20">
         <v>46101</v>
       </c>
-      <c r="D132" s="28"/>
-      <c r="E132" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F132" s="30">
-        <v>239278</v>
-      </c>
-      <c r="G132" s="29" t="s">
+      <c r="D132" s="21"/>
+      <c r="E132" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="F132" s="23">
+        <v>10550</v>
+      </c>
+      <c r="G132" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H132" s="29" t="s">
+      <c r="H132" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I132" s="24">
+        <v>15396</v>
+      </c>
+      <c r="J132" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K132" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L132" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M132" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N132" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O132" s="21"/>
+      <c r="P132" s="25"/>
+      <c r="Q132" s="25"/>
+      <c r="R132" s="17"/>
+      <c r="S132" s="17"/>
+      <c r="T132" s="17"/>
+      <c r="U132" s="17"/>
+      <c r="V132" s="17"/>
+      <c r="W132" s="17"/>
+      <c r="X132" s="17"/>
+      <c r="Y132" s="17"/>
+      <c r="Z132" s="18"/>
+      <c r="AA132" s="18"/>
+      <c r="AB132" s="18"/>
+      <c r="AC132" s="18"/>
+      <c r="AD132" s="18"/>
+      <c r="AE132" s="18"/>
+      <c r="AF132" s="18"/>
+      <c r="AG132" s="18"/>
+      <c r="AH132" s="18"/>
+      <c r="AI132" s="18"/>
+      <c r="AJ132" s="18"/>
+      <c r="AK132" s="18"/>
+      <c r="AL132" s="18"/>
+      <c r="AM132" s="18"/>
+      <c r="AN132" s="18"/>
+      <c r="AO132" s="18"/>
+      <c r="AP132" s="18"/>
+      <c r="AQ132" s="18"/>
+      <c r="AR132" s="18"/>
+      <c r="AS132" s="18"/>
+      <c r="AT132" s="18"/>
+      <c r="AU132" s="18"/>
+      <c r="AV132" s="18"/>
+      <c r="AW132" s="18"/>
+      <c r="AX132" s="18"/>
+    </row>
+    <row r="133" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="19"/>
+      <c r="B133" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C133" s="20">
+        <v>46101</v>
+      </c>
+      <c r="D133" s="21"/>
+      <c r="E133" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F133" s="23">
+        <v>8060</v>
+      </c>
+      <c r="G133" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H133" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I132" s="31">
-        <v>1784.35</v>
-      </c>
-      <c r="J132" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K132" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L132" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M132" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N132" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O132" s="28"/>
-      <c r="P132" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q132" s="33"/>
-      <c r="R132" s="34"/>
-      <c r="S132" s="34"/>
-      <c r="T132" s="34"/>
-      <c r="U132" s="34"/>
-      <c r="V132" s="34"/>
-      <c r="W132" s="34"/>
-      <c r="X132" s="34"/>
-      <c r="Y132" s="34"/>
-      <c r="Z132" s="35"/>
-      <c r="AA132" s="35"/>
-      <c r="AB132" s="35"/>
-      <c r="AC132" s="35"/>
-      <c r="AD132" s="35"/>
-      <c r="AE132" s="35"/>
-      <c r="AF132" s="35"/>
-      <c r="AG132" s="35"/>
-      <c r="AH132" s="35"/>
-      <c r="AI132" s="35"/>
-      <c r="AJ132" s="35"/>
-      <c r="AK132" s="35"/>
-      <c r="AL132" s="35"/>
-      <c r="AM132" s="35"/>
-      <c r="AN132" s="35"/>
-      <c r="AO132" s="35"/>
-      <c r="AP132" s="35"/>
-      <c r="AQ132" s="35"/>
-      <c r="AR132" s="35"/>
-      <c r="AS132" s="35"/>
-      <c r="AT132" s="35"/>
-      <c r="AU132" s="35"/>
-      <c r="AV132" s="35"/>
-      <c r="AW132" s="35"/>
-      <c r="AX132" s="35"/>
-    </row>
-    <row r="133" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="26"/>
-      <c r="B133" s="27">
+      <c r="I133" s="24">
+        <v>53488.32</v>
+      </c>
+      <c r="J133" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K133" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L133" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M133" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N133" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O133" s="21"/>
+      <c r="P133" s="25"/>
+      <c r="Q133" s="25"/>
+      <c r="R133" s="17"/>
+      <c r="S133" s="17"/>
+      <c r="T133" s="17"/>
+      <c r="U133" s="17"/>
+      <c r="V133" s="17"/>
+      <c r="W133" s="17"/>
+      <c r="X133" s="17"/>
+      <c r="Y133" s="17"/>
+      <c r="Z133" s="18"/>
+      <c r="AA133" s="18"/>
+      <c r="AB133" s="18"/>
+      <c r="AC133" s="18"/>
+      <c r="AD133" s="18"/>
+      <c r="AE133" s="18"/>
+      <c r="AF133" s="18"/>
+      <c r="AG133" s="18"/>
+      <c r="AH133" s="18"/>
+      <c r="AI133" s="18"/>
+      <c r="AJ133" s="18"/>
+      <c r="AK133" s="18"/>
+      <c r="AL133" s="18"/>
+      <c r="AM133" s="18"/>
+      <c r="AN133" s="18"/>
+      <c r="AO133" s="18"/>
+      <c r="AP133" s="18"/>
+      <c r="AQ133" s="18"/>
+      <c r="AR133" s="18"/>
+      <c r="AS133" s="18"/>
+      <c r="AT133" s="18"/>
+      <c r="AU133" s="18"/>
+      <c r="AV133" s="18"/>
+      <c r="AW133" s="18"/>
+      <c r="AX133" s="18"/>
+    </row>
+    <row r="134" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="19"/>
+      <c r="B134" s="20">
         <v>46093</v>
       </c>
-      <c r="C133" s="27">
+      <c r="C134" s="20">
         <v>46101</v>
       </c>
-      <c r="D133" s="28"/>
-      <c r="E133" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F133" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="G133" s="29" t="s">
+      <c r="D134" s="21"/>
+      <c r="E134" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F134" s="23">
+        <v>123589</v>
+      </c>
+      <c r="G134" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H133" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I133" s="31">
-        <v>15549.89</v>
-      </c>
-      <c r="J133" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K133" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L133" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M133" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N133" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O133" s="28"/>
-      <c r="P133" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q133" s="33"/>
-      <c r="R133" s="34"/>
-      <c r="S133" s="34"/>
-      <c r="T133" s="34"/>
-      <c r="U133" s="34"/>
-      <c r="V133" s="34"/>
-      <c r="W133" s="34"/>
-      <c r="X133" s="34"/>
-      <c r="Y133" s="34"/>
-      <c r="Z133" s="35"/>
-      <c r="AA133" s="35"/>
-      <c r="AB133" s="35"/>
-      <c r="AC133" s="35"/>
-      <c r="AD133" s="35"/>
-      <c r="AE133" s="35"/>
-      <c r="AF133" s="35"/>
-      <c r="AG133" s="35"/>
-      <c r="AH133" s="35"/>
-      <c r="AI133" s="35"/>
-      <c r="AJ133" s="35"/>
-      <c r="AK133" s="35"/>
-      <c r="AL133" s="35"/>
-      <c r="AM133" s="35"/>
-      <c r="AN133" s="35"/>
-      <c r="AO133" s="35"/>
-      <c r="AP133" s="35"/>
-      <c r="AQ133" s="35"/>
-      <c r="AR133" s="35"/>
-      <c r="AS133" s="35"/>
-      <c r="AT133" s="35"/>
-      <c r="AU133" s="35"/>
-      <c r="AV133" s="35"/>
-      <c r="AW133" s="35"/>
-      <c r="AX133" s="35"/>
-    </row>
-    <row r="134" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="26"/>
-      <c r="B134" s="27">
-        <v>46079</v>
-      </c>
-      <c r="C134" s="27">
+      <c r="H134" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I134" s="24">
+        <v>26875.16</v>
+      </c>
+      <c r="J134" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K134" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L134" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M134" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N134" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O134" s="21"/>
+      <c r="P134" s="25"/>
+      <c r="Q134" s="25"/>
+      <c r="R134" s="17"/>
+      <c r="S134" s="17"/>
+      <c r="T134" s="17"/>
+      <c r="U134" s="17"/>
+      <c r="V134" s="17"/>
+      <c r="W134" s="17"/>
+      <c r="X134" s="17"/>
+      <c r="Y134" s="17"/>
+      <c r="Z134" s="18"/>
+      <c r="AA134" s="18"/>
+      <c r="AB134" s="18"/>
+      <c r="AC134" s="18"/>
+      <c r="AD134" s="18"/>
+      <c r="AE134" s="18"/>
+      <c r="AF134" s="18"/>
+      <c r="AG134" s="18"/>
+      <c r="AH134" s="18"/>
+      <c r="AI134" s="18"/>
+      <c r="AJ134" s="18"/>
+      <c r="AK134" s="18"/>
+      <c r="AL134" s="18"/>
+      <c r="AM134" s="18"/>
+      <c r="AN134" s="18"/>
+      <c r="AO134" s="18"/>
+      <c r="AP134" s="18"/>
+      <c r="AQ134" s="18"/>
+      <c r="AR134" s="18"/>
+      <c r="AS134" s="18"/>
+      <c r="AT134" s="18"/>
+      <c r="AU134" s="18"/>
+      <c r="AV134" s="18"/>
+      <c r="AW134" s="18"/>
+      <c r="AX134" s="18"/>
+    </row>
+    <row r="135" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="19"/>
+      <c r="B135" s="20">
+        <v>46093</v>
+      </c>
+      <c r="C135" s="20">
         <v>46101</v>
       </c>
-      <c r="D134" s="28"/>
-      <c r="E134" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="F134" s="28"/>
-      <c r="G134" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="H134" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="I134" s="31">
-        <v>5000</v>
-      </c>
-      <c r="J134" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K134" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="L134" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M134" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N134" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O134" s="28"/>
-      <c r="P134" s="33"/>
-      <c r="Q134" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R134" s="34"/>
-      <c r="S134" s="34"/>
-      <c r="T134" s="34"/>
-      <c r="U134" s="34"/>
-      <c r="V134" s="34"/>
-      <c r="W134" s="34"/>
-      <c r="X134" s="34"/>
-      <c r="Y134" s="34"/>
-      <c r="Z134" s="35"/>
-      <c r="AA134" s="35"/>
-      <c r="AB134" s="35"/>
-      <c r="AC134" s="35"/>
-      <c r="AD134" s="35"/>
-      <c r="AE134" s="35"/>
-      <c r="AF134" s="35"/>
-      <c r="AG134" s="35"/>
-      <c r="AH134" s="35"/>
-      <c r="AI134" s="35"/>
-      <c r="AJ134" s="35"/>
-      <c r="AK134" s="35"/>
-      <c r="AL134" s="35"/>
-      <c r="AM134" s="35"/>
-      <c r="AN134" s="35"/>
-      <c r="AO134" s="35"/>
-      <c r="AP134" s="35"/>
-      <c r="AQ134" s="35"/>
-      <c r="AR134" s="35"/>
-      <c r="AS134" s="35"/>
-      <c r="AT134" s="35"/>
-      <c r="AU134" s="35"/>
-      <c r="AV134" s="35"/>
-      <c r="AW134" s="35"/>
-      <c r="AX134" s="35"/>
-    </row>
-    <row r="135" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="26"/>
-      <c r="B135" s="27">
-        <v>46079</v>
-      </c>
-      <c r="C135" s="27">
-        <v>46101</v>
-      </c>
-      <c r="D135" s="28"/>
-      <c r="E135" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F135" s="28"/>
-      <c r="G135" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="H135" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="I135" s="31">
-        <v>8000</v>
-      </c>
-      <c r="J135" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K135" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="L135" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M135" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N135" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O135" s="28"/>
-      <c r="P135" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q135" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R135" s="34"/>
-      <c r="S135" s="34"/>
-      <c r="T135" s="34"/>
-      <c r="U135" s="34"/>
-      <c r="V135" s="34"/>
-      <c r="W135" s="34"/>
-      <c r="X135" s="34"/>
-      <c r="Y135" s="34"/>
-      <c r="Z135" s="35"/>
-      <c r="AA135" s="35"/>
-      <c r="AB135" s="35"/>
-      <c r="AC135" s="35"/>
-      <c r="AD135" s="35"/>
-      <c r="AE135" s="35"/>
-      <c r="AF135" s="35"/>
-      <c r="AG135" s="35"/>
-      <c r="AH135" s="35"/>
-      <c r="AI135" s="35"/>
-      <c r="AJ135" s="35"/>
-      <c r="AK135" s="35"/>
-      <c r="AL135" s="35"/>
-      <c r="AM135" s="35"/>
-      <c r="AN135" s="35"/>
-      <c r="AO135" s="35"/>
-      <c r="AP135" s="35"/>
-      <c r="AQ135" s="35"/>
-      <c r="AR135" s="35"/>
-      <c r="AS135" s="35"/>
-      <c r="AT135" s="35"/>
-      <c r="AU135" s="35"/>
-      <c r="AV135" s="35"/>
-      <c r="AW135" s="35"/>
-      <c r="AX135" s="35"/>
-    </row>
-    <row r="136" spans="1:50" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D135" s="21"/>
+      <c r="E135" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F135" s="23">
+        <v>123587</v>
+      </c>
+      <c r="G135" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H135" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I135" s="24">
+        <v>26875.16</v>
+      </c>
+      <c r="J135" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K135" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L135" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M135" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N135" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O135" s="21"/>
+      <c r="P135" s="25"/>
+      <c r="Q135" s="25"/>
+      <c r="R135" s="17"/>
+      <c r="S135" s="17"/>
+      <c r="T135" s="17"/>
+      <c r="U135" s="17"/>
+      <c r="V135" s="17"/>
+      <c r="W135" s="17"/>
+      <c r="X135" s="17"/>
+      <c r="Y135" s="17"/>
+      <c r="Z135" s="18"/>
+      <c r="AA135" s="18"/>
+      <c r="AB135" s="18"/>
+      <c r="AC135" s="18"/>
+      <c r="AD135" s="18"/>
+      <c r="AE135" s="18"/>
+      <c r="AF135" s="18"/>
+      <c r="AG135" s="18"/>
+      <c r="AH135" s="18"/>
+      <c r="AI135" s="18"/>
+      <c r="AJ135" s="18"/>
+      <c r="AK135" s="18"/>
+      <c r="AL135" s="18"/>
+      <c r="AM135" s="18"/>
+      <c r="AN135" s="18"/>
+      <c r="AO135" s="18"/>
+      <c r="AP135" s="18"/>
+      <c r="AQ135" s="18"/>
+      <c r="AR135" s="18"/>
+      <c r="AS135" s="18"/>
+      <c r="AT135" s="18"/>
+      <c r="AU135" s="18"/>
+      <c r="AV135" s="18"/>
+      <c r="AW135" s="18"/>
+      <c r="AX135" s="18"/>
+    </row>
+    <row r="136" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="26"/>
       <c r="B136" s="27">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C136" s="27">
         <v>46101</v>
       </c>
       <c r="D136" s="28"/>
       <c r="E136" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="F136" s="28"/>
+        <v>17</v>
+      </c>
+      <c r="F136" s="30">
+        <v>239278</v>
+      </c>
       <c r="G136" s="29" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H136" s="29" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="I136" s="31">
-        <v>146.75</v>
+        <v>1784.35</v>
       </c>
       <c r="J136" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K136" s="29" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L136" s="29" t="s">
         <v>27</v>
@@ -11605,10 +11619,10 @@
       <c r="N136" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O136" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="P136" s="33"/>
+      <c r="O136" s="28"/>
+      <c r="P136" s="32" t="s">
+        <v>175</v>
+      </c>
       <c r="Q136" s="33"/>
       <c r="R136" s="34"/>
       <c r="S136" s="34"/>
@@ -11647,16 +11661,18 @@
     <row r="137" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="26"/>
       <c r="B137" s="27">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="C137" s="27">
         <v>46101</v>
       </c>
       <c r="D137" s="28"/>
       <c r="E137" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="F137" s="28"/>
+        <v>30</v>
+      </c>
+      <c r="F137" s="30" t="s">
+        <v>176</v>
+      </c>
       <c r="G137" s="29" t="s">
         <v>18</v>
       </c>
@@ -11664,7 +11680,7 @@
         <v>19</v>
       </c>
       <c r="I137" s="31">
-        <v>22800</v>
+        <v>15549.89</v>
       </c>
       <c r="J137" s="29" t="b">
         <v>1</v>
@@ -11681,11 +11697,9 @@
       <c r="N137" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O137" s="29" t="s">
-        <v>94</v>
-      </c>
+      <c r="O137" s="28"/>
       <c r="P137" s="32" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="Q137" s="33"/>
       <c r="R137" s="34"/>
@@ -11722,33 +11736,33 @@
       <c r="AW137" s="35"/>
       <c r="AX137" s="35"/>
     </row>
-    <row r="138" spans="1:50" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="26"/>
       <c r="B138" s="27">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="C138" s="27">
         <v>46101</v>
       </c>
       <c r="D138" s="28"/>
       <c r="E138" s="29" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F138" s="28"/>
       <c r="G138" s="29" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H138" s="29" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="I138" s="31">
-        <v>88344</v>
+        <v>5000</v>
       </c>
       <c r="J138" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K138" s="29" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="L138" s="29" t="s">
         <v>27</v>
@@ -11759,13 +11773,11 @@
       <c r="N138" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="O138" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="P138" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q138" s="33"/>
+      <c r="O138" s="28"/>
+      <c r="P138" s="33"/>
+      <c r="Q138" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R138" s="34"/>
       <c r="S138" s="34"/>
       <c r="T138" s="34"/>
@@ -11800,7 +11812,7 @@
       <c r="AW138" s="35"/>
       <c r="AX138" s="35"/>
     </row>
-    <row r="139" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="26"/>
       <c r="B139" s="27">
         <v>46079</v>
@@ -11810,23 +11822,23 @@
       </c>
       <c r="D139" s="28"/>
       <c r="E139" s="29" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F139" s="28"/>
       <c r="G139" s="29" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H139" s="29" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="I139" s="31">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="J139" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K139" s="29" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="L139" s="29" t="s">
         <v>27</v>
@@ -11838,8 +11850,12 @@
         <v>28</v>
       </c>
       <c r="O139" s="28"/>
-      <c r="P139" s="33"/>
-      <c r="Q139" s="33"/>
+      <c r="P139" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q139" s="32" t="s">
+        <v>39</v>
+      </c>
       <c r="R139" s="34"/>
       <c r="S139" s="34"/>
       <c r="T139" s="34"/>
@@ -11874,6 +11890,312 @@
       <c r="AW139" s="35"/>
       <c r="AX139" s="35"/>
     </row>
+    <row r="140" spans="1:50" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="26"/>
+      <c r="B140" s="27">
+        <v>46092</v>
+      </c>
+      <c r="C140" s="27">
+        <v>46101</v>
+      </c>
+      <c r="D140" s="28"/>
+      <c r="E140" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="F140" s="28"/>
+      <c r="G140" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H140" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="I140" s="31">
+        <v>146.75</v>
+      </c>
+      <c r="J140" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K140" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="L140" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M140" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N140" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O140" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="P140" s="33"/>
+      <c r="Q140" s="33"/>
+      <c r="R140" s="34"/>
+      <c r="S140" s="34"/>
+      <c r="T140" s="34"/>
+      <c r="U140" s="34"/>
+      <c r="V140" s="34"/>
+      <c r="W140" s="34"/>
+      <c r="X140" s="34"/>
+      <c r="Y140" s="34"/>
+      <c r="Z140" s="35"/>
+      <c r="AA140" s="35"/>
+      <c r="AB140" s="35"/>
+      <c r="AC140" s="35"/>
+      <c r="AD140" s="35"/>
+      <c r="AE140" s="35"/>
+      <c r="AF140" s="35"/>
+      <c r="AG140" s="35"/>
+      <c r="AH140" s="35"/>
+      <c r="AI140" s="35"/>
+      <c r="AJ140" s="35"/>
+      <c r="AK140" s="35"/>
+      <c r="AL140" s="35"/>
+      <c r="AM140" s="35"/>
+      <c r="AN140" s="35"/>
+      <c r="AO140" s="35"/>
+      <c r="AP140" s="35"/>
+      <c r="AQ140" s="35"/>
+      <c r="AR140" s="35"/>
+      <c r="AS140" s="35"/>
+      <c r="AT140" s="35"/>
+      <c r="AU140" s="35"/>
+      <c r="AV140" s="35"/>
+      <c r="AW140" s="35"/>
+      <c r="AX140" s="35"/>
+    </row>
+    <row r="141" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="26"/>
+      <c r="B141" s="27">
+        <v>46084</v>
+      </c>
+      <c r="C141" s="27">
+        <v>46101</v>
+      </c>
+      <c r="D141" s="28"/>
+      <c r="E141" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="F141" s="28"/>
+      <c r="G141" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H141" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I141" s="31">
+        <v>22800</v>
+      </c>
+      <c r="J141" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K141" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L141" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M141" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N141" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O141" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="P141" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q141" s="33"/>
+      <c r="R141" s="34"/>
+      <c r="S141" s="34"/>
+      <c r="T141" s="34"/>
+      <c r="U141" s="34"/>
+      <c r="V141" s="34"/>
+      <c r="W141" s="34"/>
+      <c r="X141" s="34"/>
+      <c r="Y141" s="34"/>
+      <c r="Z141" s="35"/>
+      <c r="AA141" s="35"/>
+      <c r="AB141" s="35"/>
+      <c r="AC141" s="35"/>
+      <c r="AD141" s="35"/>
+      <c r="AE141" s="35"/>
+      <c r="AF141" s="35"/>
+      <c r="AG141" s="35"/>
+      <c r="AH141" s="35"/>
+      <c r="AI141" s="35"/>
+      <c r="AJ141" s="35"/>
+      <c r="AK141" s="35"/>
+      <c r="AL141" s="35"/>
+      <c r="AM141" s="35"/>
+      <c r="AN141" s="35"/>
+      <c r="AO141" s="35"/>
+      <c r="AP141" s="35"/>
+      <c r="AQ141" s="35"/>
+      <c r="AR141" s="35"/>
+      <c r="AS141" s="35"/>
+      <c r="AT141" s="35"/>
+      <c r="AU141" s="35"/>
+      <c r="AV141" s="35"/>
+      <c r="AW141" s="35"/>
+      <c r="AX141" s="35"/>
+    </row>
+    <row r="142" spans="1:50" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="26"/>
+      <c r="B142" s="27">
+        <v>46071</v>
+      </c>
+      <c r="C142" s="27">
+        <v>46101</v>
+      </c>
+      <c r="D142" s="28"/>
+      <c r="E142" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F142" s="28"/>
+      <c r="G142" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H142" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I142" s="31">
+        <v>88344</v>
+      </c>
+      <c r="J142" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K142" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L142" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M142" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N142" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O142" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="P142" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q142" s="33"/>
+      <c r="R142" s="34"/>
+      <c r="S142" s="34"/>
+      <c r="T142" s="34"/>
+      <c r="U142" s="34"/>
+      <c r="V142" s="34"/>
+      <c r="W142" s="34"/>
+      <c r="X142" s="34"/>
+      <c r="Y142" s="34"/>
+      <c r="Z142" s="35"/>
+      <c r="AA142" s="35"/>
+      <c r="AB142" s="35"/>
+      <c r="AC142" s="35"/>
+      <c r="AD142" s="35"/>
+      <c r="AE142" s="35"/>
+      <c r="AF142" s="35"/>
+      <c r="AG142" s="35"/>
+      <c r="AH142" s="35"/>
+      <c r="AI142" s="35"/>
+      <c r="AJ142" s="35"/>
+      <c r="AK142" s="35"/>
+      <c r="AL142" s="35"/>
+      <c r="AM142" s="35"/>
+      <c r="AN142" s="35"/>
+      <c r="AO142" s="35"/>
+      <c r="AP142" s="35"/>
+      <c r="AQ142" s="35"/>
+      <c r="AR142" s="35"/>
+      <c r="AS142" s="35"/>
+      <c r="AT142" s="35"/>
+      <c r="AU142" s="35"/>
+      <c r="AV142" s="35"/>
+      <c r="AW142" s="35"/>
+      <c r="AX142" s="35"/>
+    </row>
+    <row r="143" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="26"/>
+      <c r="B143" s="27">
+        <v>46079</v>
+      </c>
+      <c r="C143" s="27">
+        <v>46101</v>
+      </c>
+      <c r="D143" s="28"/>
+      <c r="E143" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F143" s="28"/>
+      <c r="G143" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H143" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I143" s="31">
+        <v>20000</v>
+      </c>
+      <c r="J143" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K143" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L143" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M143" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N143" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O143" s="28"/>
+      <c r="P143" s="33"/>
+      <c r="Q143" s="33"/>
+      <c r="R143" s="34"/>
+      <c r="S143" s="34"/>
+      <c r="T143" s="34"/>
+      <c r="U143" s="34"/>
+      <c r="V143" s="34"/>
+      <c r="W143" s="34"/>
+      <c r="X143" s="34"/>
+      <c r="Y143" s="34"/>
+      <c r="Z143" s="35"/>
+      <c r="AA143" s="35"/>
+      <c r="AB143" s="35"/>
+      <c r="AC143" s="35"/>
+      <c r="AD143" s="35"/>
+      <c r="AE143" s="35"/>
+      <c r="AF143" s="35"/>
+      <c r="AG143" s="35"/>
+      <c r="AH143" s="35"/>
+      <c r="AI143" s="35"/>
+      <c r="AJ143" s="35"/>
+      <c r="AK143" s="35"/>
+      <c r="AL143" s="35"/>
+      <c r="AM143" s="35"/>
+      <c r="AN143" s="35"/>
+      <c r="AO143" s="35"/>
+      <c r="AP143" s="35"/>
+      <c r="AQ143" s="35"/>
+      <c r="AR143" s="35"/>
+      <c r="AS143" s="35"/>
+      <c r="AT143" s="35"/>
+      <c r="AU143" s="35"/>
+      <c r="AV143" s="35"/>
+      <c r="AW143" s="35"/>
+      <c r="AX143" s="35"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/CAP_Semana_12.xlsx
+++ b/data/CAP_Semana_12.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Relatório_Felipe\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E73A842-A0DF-46AB-8063-F99DE46ACDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44837DD-9AF9-4FDE-92A6-6F769BB032CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2130" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{8D2EDE68-77A0-48FE-A03B-A2F0182CE2F6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3268" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="413">
   <si>
     <t>id</t>
   </si>
@@ -1186,9 +1186,6 @@
     <t>ref. a compra de itens diversos para Madeira e Girus</t>
   </si>
   <si>
-    <t>PART.4</t>
-  </si>
-  <si>
     <t>Mangueira para máquina</t>
   </si>
   <si>
@@ -1213,19 +1210,92 @@
     <t>Kyara Aisaylla Florecio Ferreira</t>
   </si>
   <si>
-    <t>11 94295.8185</t>
-  </si>
-  <si>
     <t>INDUSLOG - PF</t>
   </si>
   <si>
     <t>MAYCON DOUGLAS DOS SANTOS CARDOSO</t>
   </si>
   <si>
-    <t>11 96802.3478</t>
-  </si>
-  <si>
     <t>CHEGOU EM 16-03-2026 - GIRUS MÓVEIS</t>
+  </si>
+  <si>
+    <t>kianebraz@gmail.com</t>
+  </si>
+  <si>
+    <t>44.205.107/0001-41</t>
+  </si>
+  <si>
+    <t>CHEGOU EM 18-03-2026</t>
+  </si>
+  <si>
+    <t>DARE - VERTEX</t>
+  </si>
+  <si>
+    <t>140.132.488-67</t>
+  </si>
+  <si>
+    <t>Roberto Vitorino Tosi</t>
+  </si>
+  <si>
+    <t>Chave Pix (CPF): 131.470.538-57</t>
+  </si>
+  <si>
+    <t>referente aos serviços de manutenção de peças realizados pela Squalidus</t>
+  </si>
+  <si>
+    <t>ref. a compra de botas de segurança para Click e lampadas para Madeira</t>
+  </si>
+  <si>
+    <t>CHEGOU EM 20-02-2026</t>
+  </si>
+  <si>
+    <t>LUIZ - 11957888306</t>
+  </si>
+  <si>
+    <t>ref. a compra de um notebook para Click</t>
+  </si>
+  <si>
+    <t>ref.a compra de um balde de graxa para Girus</t>
+  </si>
+  <si>
+    <t>Marcos Ferrari</t>
+  </si>
+  <si>
+    <t>Pix: 11 98182-3622</t>
+  </si>
+  <si>
+    <t>Lixa Norton G 80 - Material para produção Girus
+Qtde: 10 unid</t>
+  </si>
+  <si>
+    <t>11 942958185</t>
+  </si>
+  <si>
+    <t>11 968023478</t>
+  </si>
+  <si>
+    <t>VALDIR MANOEL CARVALHO</t>
+  </si>
+  <si>
+    <t>PIX 017.574.788-17</t>
+  </si>
+  <si>
+    <t>ELZA YOCOI OGAWA ( SR. MARIO)</t>
+  </si>
+  <si>
+    <t>641.071.088-72 ITAU AG 0672 CC 28683-8</t>
+  </si>
+  <si>
+    <t>MARCUS WELBY R. DA SILVA</t>
+  </si>
+  <si>
+    <t>11-984307476</t>
+  </si>
+  <si>
+    <t>EDVAN APARECIDO SILVESTRE</t>
+  </si>
+  <si>
+    <t>511.482.028-11</t>
   </si>
 </sst>
 </file>
@@ -1486,7 +1556,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1707,47 +1777,17 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="3" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15160,7 +15200,7 @@
     <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="40.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -15170,7 +15210,7 @@
     <col min="16" max="16" width="139.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="24.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -28846,20 +28886,20 @@
       <c r="C174" s="67">
         <v>46096</v>
       </c>
-      <c r="D174" s="67">
+      <c r="D174" s="90">
         <v>46099</v>
       </c>
-      <c r="E174" s="68" t="s">
+      <c r="E174" s="91" t="s">
         <v>371</v>
       </c>
-      <c r="F174" s="69"/>
-      <c r="G174" s="68" t="s">
+      <c r="F174" s="92"/>
+      <c r="G174" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="H174" s="68" t="s">
+      <c r="H174" s="91" t="s">
         <v>186</v>
       </c>
-      <c r="I174" s="70">
+      <c r="I174" s="93">
         <v>6433.96</v>
       </c>
       <c r="J174" s="68" t="b">
@@ -28924,20 +28964,20 @@
       <c r="C175" s="67">
         <v>46096</v>
       </c>
-      <c r="D175" s="67">
+      <c r="D175" s="90">
         <v>46099</v>
       </c>
-      <c r="E175" s="68" t="s">
+      <c r="E175" s="91" t="s">
         <v>373</v>
       </c>
-      <c r="F175" s="69"/>
-      <c r="G175" s="68" t="s">
+      <c r="F175" s="92"/>
+      <c r="G175" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="H175" s="68" t="s">
+      <c r="H175" s="91" t="s">
         <v>186</v>
       </c>
-      <c r="I175" s="70">
+      <c r="I175" s="93">
         <v>16611.46</v>
       </c>
       <c r="J175" s="68" t="b">
@@ -29002,20 +29042,20 @@
       <c r="C176" s="67">
         <v>46096</v>
       </c>
-      <c r="D176" s="67">
+      <c r="D176" s="90">
         <v>46099</v>
       </c>
-      <c r="E176" s="68" t="s">
+      <c r="E176" s="91" t="s">
         <v>374</v>
       </c>
-      <c r="F176" s="69"/>
-      <c r="G176" s="68" t="s">
+      <c r="F176" s="92"/>
+      <c r="G176" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="H176" s="68" t="s">
+      <c r="H176" s="91" t="s">
         <v>186</v>
       </c>
-      <c r="I176" s="70">
+      <c r="I176" s="93">
         <v>2046.84</v>
       </c>
       <c r="J176" s="68" t="b">
@@ -29154,19 +29194,45 @@
     </row>
     <row r="178" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="66"/>
-      <c r="B178" s="69"/>
-      <c r="C178" s="69"/>
-      <c r="D178" s="69"/>
-      <c r="E178" s="69"/>
-      <c r="F178" s="69"/>
-      <c r="G178" s="69"/>
-      <c r="H178" s="69"/>
-      <c r="I178" s="71"/>
-      <c r="J178" s="69"/>
-      <c r="K178" s="69"/>
-      <c r="L178" s="69"/>
-      <c r="M178" s="69"/>
-      <c r="N178" s="69"/>
+      <c r="B178" s="67">
+        <v>46093</v>
+      </c>
+      <c r="C178" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D178" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E178" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="F178" s="75">
+        <v>2295</v>
+      </c>
+      <c r="G178" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H178" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I178" s="70">
+        <v>909.15</v>
+      </c>
+      <c r="J178" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K178" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L178" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M178" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N178" s="68" t="s">
+        <v>23</v>
+      </c>
       <c r="O178" s="69"/>
       <c r="P178" s="71"/>
       <c r="Q178" s="71"/>
@@ -29206,19 +29272,45 @@
     </row>
     <row r="179" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="66"/>
-      <c r="B179" s="69"/>
-      <c r="C179" s="69"/>
-      <c r="D179" s="69"/>
-      <c r="E179" s="69"/>
-      <c r="F179" s="69"/>
-      <c r="G179" s="69"/>
-      <c r="H179" s="69"/>
-      <c r="I179" s="71"/>
-      <c r="J179" s="69"/>
-      <c r="K179" s="69"/>
-      <c r="L179" s="69"/>
-      <c r="M179" s="69"/>
-      <c r="N179" s="69"/>
+      <c r="B179" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C179" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D179" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E179" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F179" s="75">
+        <v>264272</v>
+      </c>
+      <c r="G179" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H179" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I179" s="70">
+        <v>3452.46</v>
+      </c>
+      <c r="J179" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K179" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L179" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M179" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N179" s="68" t="s">
+        <v>23</v>
+      </c>
       <c r="O179" s="69"/>
       <c r="P179" s="71"/>
       <c r="Q179" s="71"/>
@@ -29258,19 +29350,45 @@
     </row>
     <row r="180" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="66"/>
-      <c r="B180" s="69"/>
-      <c r="C180" s="69"/>
-      <c r="D180" s="69"/>
-      <c r="E180" s="69"/>
-      <c r="F180" s="69"/>
-      <c r="G180" s="69"/>
-      <c r="H180" s="69"/>
-      <c r="I180" s="71"/>
-      <c r="J180" s="69"/>
-      <c r="K180" s="69"/>
-      <c r="L180" s="69"/>
-      <c r="M180" s="69"/>
-      <c r="N180" s="69"/>
+      <c r="B180" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C180" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D180" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E180" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="F180" s="75">
+        <v>268025</v>
+      </c>
+      <c r="G180" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H180" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="I180" s="70">
+        <v>17864.88</v>
+      </c>
+      <c r="J180" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K180" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L180" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M180" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N180" s="68" t="s">
+        <v>23</v>
+      </c>
       <c r="O180" s="69"/>
       <c r="P180" s="71"/>
       <c r="Q180" s="71"/>
@@ -29310,19 +29428,45 @@
     </row>
     <row r="181" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="66"/>
-      <c r="B181" s="69"/>
-      <c r="C181" s="69"/>
-      <c r="D181" s="69"/>
-      <c r="E181" s="69"/>
-      <c r="F181" s="69"/>
-      <c r="G181" s="69"/>
-      <c r="H181" s="69"/>
-      <c r="I181" s="71"/>
-      <c r="J181" s="69"/>
-      <c r="K181" s="69"/>
-      <c r="L181" s="69"/>
-      <c r="M181" s="69"/>
-      <c r="N181" s="69"/>
+      <c r="B181" s="67">
+        <v>46093</v>
+      </c>
+      <c r="C181" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D181" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E181" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F181" s="75">
+        <v>924426</v>
+      </c>
+      <c r="G181" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H181" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="I181" s="70">
+        <v>7298.44</v>
+      </c>
+      <c r="J181" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K181" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L181" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M181" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N181" s="68" t="s">
+        <v>23</v>
+      </c>
       <c r="O181" s="69"/>
       <c r="P181" s="71"/>
       <c r="Q181" s="71"/>
@@ -29362,19 +29506,45 @@
     </row>
     <row r="182" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="66"/>
-      <c r="B182" s="69"/>
-      <c r="C182" s="69"/>
-      <c r="D182" s="69"/>
-      <c r="E182" s="69"/>
-      <c r="F182" s="69"/>
-      <c r="G182" s="69"/>
-      <c r="H182" s="69"/>
-      <c r="I182" s="71"/>
-      <c r="J182" s="69"/>
-      <c r="K182" s="69"/>
-      <c r="L182" s="69"/>
-      <c r="M182" s="69"/>
-      <c r="N182" s="69"/>
+      <c r="B182" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C182" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D182" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E182" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F182" s="75">
+        <v>453494</v>
+      </c>
+      <c r="G182" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H182" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I182" s="70">
+        <v>10079.950000000001</v>
+      </c>
+      <c r="J182" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K182" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L182" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M182" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N182" s="68" t="s">
+        <v>23</v>
+      </c>
       <c r="O182" s="69"/>
       <c r="P182" s="71"/>
       <c r="Q182" s="71"/>
@@ -29412,32 +29582,60 @@
       <c r="AW182" s="65"/>
       <c r="AX182" s="65"/>
     </row>
-    <row r="183" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="66"/>
-      <c r="B183" s="69"/>
-      <c r="C183" s="69"/>
-      <c r="D183" s="69"/>
-      <c r="E183" s="69"/>
+      <c r="B183" s="67">
+        <v>46099</v>
+      </c>
+      <c r="C183" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D183" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E183" s="68" t="s">
+        <v>207</v>
+      </c>
       <c r="F183" s="69"/>
-      <c r="G183" s="69"/>
-      <c r="H183" s="69"/>
-      <c r="I183" s="71"/>
-      <c r="J183" s="69"/>
-      <c r="K183" s="69"/>
-      <c r="L183" s="69"/>
-      <c r="M183" s="69"/>
-      <c r="N183" s="69"/>
-      <c r="O183" s="69"/>
-      <c r="P183" s="71"/>
+      <c r="G183" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H183" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I183" s="70">
+        <v>405.34</v>
+      </c>
+      <c r="J183" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K183" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L183" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M183" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N183" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O183" s="68">
+        <v>11981370647</v>
+      </c>
+      <c r="P183" s="73" t="s">
+        <v>376</v>
+      </c>
       <c r="Q183" s="71"/>
-      <c r="R183" s="64"/>
-      <c r="S183" s="64"/>
-      <c r="T183" s="64"/>
-      <c r="U183" s="64"/>
-      <c r="V183" s="64"/>
-      <c r="W183" s="64"/>
-      <c r="X183" s="64"/>
-      <c r="Y183" s="64"/>
+      <c r="R183" s="65"/>
+      <c r="S183" s="65"/>
+      <c r="T183" s="65"/>
+      <c r="U183" s="65"/>
+      <c r="V183" s="65"/>
+      <c r="W183" s="65"/>
+      <c r="X183" s="65"/>
+      <c r="Y183" s="65"/>
       <c r="Z183" s="65"/>
       <c r="AA183" s="65"/>
       <c r="AB183" s="65"/>
@@ -29464,23 +29662,51 @@
       <c r="AW183" s="65"/>
       <c r="AX183" s="65"/>
     </row>
-    <row r="184" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="66"/>
-      <c r="B184" s="69"/>
-      <c r="C184" s="69"/>
-      <c r="D184" s="69"/>
-      <c r="E184" s="69"/>
+      <c r="B184" s="67">
+        <v>46076</v>
+      </c>
+      <c r="C184" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D184" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E184" s="68" t="s">
+        <v>377</v>
+      </c>
       <c r="F184" s="69"/>
-      <c r="G184" s="69"/>
-      <c r="H184" s="69"/>
-      <c r="I184" s="71"/>
-      <c r="J184" s="69"/>
-      <c r="K184" s="69"/>
-      <c r="L184" s="69"/>
-      <c r="M184" s="69"/>
-      <c r="N184" s="69"/>
-      <c r="O184" s="69"/>
-      <c r="P184" s="71"/>
+      <c r="G184" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="H184" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="I184" s="70">
+        <v>20000</v>
+      </c>
+      <c r="J184" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K184" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="L184" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M184" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N184" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O184" s="68" t="s">
+        <v>378</v>
+      </c>
+      <c r="P184" s="73" t="s">
+        <v>379</v>
+      </c>
       <c r="Q184" s="71"/>
       <c r="R184" s="64"/>
       <c r="S184" s="64"/>
@@ -29516,23 +29742,53 @@
       <c r="AW184" s="65"/>
       <c r="AX184" s="65"/>
     </row>
-    <row r="185" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="66"/>
-      <c r="B185" s="69"/>
-      <c r="C185" s="69"/>
-      <c r="D185" s="69"/>
-      <c r="E185" s="69"/>
-      <c r="F185" s="69"/>
-      <c r="G185" s="69"/>
-      <c r="H185" s="69"/>
-      <c r="I185" s="71"/>
-      <c r="J185" s="69"/>
-      <c r="K185" s="69"/>
-      <c r="L185" s="69"/>
-      <c r="M185" s="69"/>
-      <c r="N185" s="69"/>
-      <c r="O185" s="69"/>
-      <c r="P185" s="71"/>
+      <c r="B185" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C185" s="67">
+        <v>46094</v>
+      </c>
+      <c r="D185" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E185" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="F185" s="75">
+        <v>123007</v>
+      </c>
+      <c r="G185" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H185" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="I185" s="70">
+        <v>2455</v>
+      </c>
+      <c r="J185" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K185" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L185" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M185" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N185" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O185" s="68" t="s">
+        <v>387</v>
+      </c>
+      <c r="P185" s="73" t="s">
+        <v>205</v>
+      </c>
       <c r="Q185" s="71"/>
       <c r="R185" s="64"/>
       <c r="S185" s="64"/>
@@ -29568,23 +29824,53 @@
       <c r="AW185" s="65"/>
       <c r="AX185" s="65"/>
     </row>
-    <row r="186" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="66"/>
-      <c r="B186" s="69"/>
-      <c r="C186" s="69"/>
-      <c r="D186" s="69"/>
-      <c r="E186" s="69"/>
-      <c r="F186" s="69"/>
-      <c r="G186" s="69"/>
-      <c r="H186" s="69"/>
-      <c r="I186" s="71"/>
-      <c r="J186" s="69"/>
-      <c r="K186" s="69"/>
-      <c r="L186" s="69"/>
-      <c r="M186" s="69"/>
-      <c r="N186" s="69"/>
-      <c r="O186" s="69"/>
-      <c r="P186" s="71"/>
+      <c r="B186" s="67">
+        <v>46094</v>
+      </c>
+      <c r="C186" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D186" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E186" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="F186" s="75">
+        <v>3185</v>
+      </c>
+      <c r="G186" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H186" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="I186" s="70">
+        <v>96166.44</v>
+      </c>
+      <c r="J186" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K186" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L186" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M186" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N186" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O186" s="68">
+        <v>3.4191121278143298E+46</v>
+      </c>
+      <c r="P186" s="73" t="s">
+        <v>195</v>
+      </c>
       <c r="Q186" s="71"/>
       <c r="R186" s="64"/>
       <c r="S186" s="64"/>
@@ -29620,32 +29906,60 @@
       <c r="AW186" s="65"/>
       <c r="AX186" s="65"/>
     </row>
-    <row r="187" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="66"/>
-      <c r="B187" s="69"/>
-      <c r="C187" s="69"/>
-      <c r="D187" s="69"/>
-      <c r="E187" s="69"/>
+      <c r="B187" s="67">
+        <v>46094</v>
+      </c>
+      <c r="C187" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D187" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E187" s="68" t="s">
+        <v>129</v>
+      </c>
       <c r="F187" s="69"/>
-      <c r="G187" s="69"/>
-      <c r="H187" s="69"/>
-      <c r="I187" s="71"/>
-      <c r="J187" s="69"/>
-      <c r="K187" s="69"/>
-      <c r="L187" s="69"/>
-      <c r="M187" s="69"/>
-      <c r="N187" s="69"/>
-      <c r="O187" s="69"/>
-      <c r="P187" s="71"/>
+      <c r="G187" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H187" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I187" s="70">
+        <v>11650</v>
+      </c>
+      <c r="J187" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K187" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L187" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M187" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N187" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O187" s="68" t="s">
+        <v>388</v>
+      </c>
+      <c r="P187" s="73" t="s">
+        <v>210</v>
+      </c>
       <c r="Q187" s="71"/>
-      <c r="R187" s="64"/>
-      <c r="S187" s="64"/>
-      <c r="T187" s="64"/>
-      <c r="U187" s="64"/>
-      <c r="V187" s="64"/>
-      <c r="W187" s="64"/>
-      <c r="X187" s="64"/>
-      <c r="Y187" s="64"/>
+      <c r="R187" s="65"/>
+      <c r="S187" s="65"/>
+      <c r="T187" s="65"/>
+      <c r="U187" s="65"/>
+      <c r="V187" s="65"/>
+      <c r="W187" s="65"/>
+      <c r="X187" s="65"/>
+      <c r="Y187" s="65"/>
       <c r="Z187" s="65"/>
       <c r="AA187" s="65"/>
       <c r="AB187" s="65"/>
@@ -29672,23 +29986,51 @@
       <c r="AW187" s="65"/>
       <c r="AX187" s="65"/>
     </row>
-    <row r="188" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="66"/>
-      <c r="B188" s="69"/>
-      <c r="C188" s="69"/>
-      <c r="D188" s="69"/>
-      <c r="E188" s="69"/>
+      <c r="B188" s="67">
+        <v>46098</v>
+      </c>
+      <c r="C188" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D188" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E188" s="68" t="s">
+        <v>380</v>
+      </c>
       <c r="F188" s="69"/>
-      <c r="G188" s="69"/>
-      <c r="H188" s="69"/>
-      <c r="I188" s="71"/>
-      <c r="J188" s="69"/>
-      <c r="K188" s="69"/>
-      <c r="L188" s="69"/>
-      <c r="M188" s="69"/>
-      <c r="N188" s="69"/>
-      <c r="O188" s="69"/>
-      <c r="P188" s="71"/>
+      <c r="G188" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H188" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="I188" s="70">
+        <v>6500</v>
+      </c>
+      <c r="J188" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K188" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="L188" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M188" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N188" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O188" s="68" t="s">
+        <v>381</v>
+      </c>
+      <c r="P188" s="73" t="s">
+        <v>382</v>
+      </c>
       <c r="Q188" s="71"/>
       <c r="R188" s="64"/>
       <c r="S188" s="64"/>
@@ -29724,2128 +30066,2204 @@
       <c r="AW188" s="65"/>
       <c r="AX188" s="65"/>
     </row>
-    <row r="189" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="90"/>
-      <c r="B189" s="91">
+    <row r="189" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="66"/>
+      <c r="B189" s="67">
+        <v>46084</v>
+      </c>
+      <c r="C189" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D189" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E189" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="F189" s="69"/>
+      <c r="G189" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H189" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I189" s="70">
+        <v>9975</v>
+      </c>
+      <c r="J189" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K189" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L189" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M189" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N189" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O189" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="P189" s="73" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q189" s="71"/>
+      <c r="R189" s="64"/>
+      <c r="S189" s="64"/>
+      <c r="T189" s="64"/>
+      <c r="U189" s="64"/>
+      <c r="V189" s="64"/>
+      <c r="W189" s="64"/>
+      <c r="X189" s="64"/>
+      <c r="Y189" s="64"/>
+      <c r="Z189" s="65"/>
+      <c r="AA189" s="65"/>
+      <c r="AB189" s="65"/>
+      <c r="AC189" s="65"/>
+      <c r="AD189" s="65"/>
+      <c r="AE189" s="65"/>
+      <c r="AF189" s="65"/>
+      <c r="AG189" s="65"/>
+      <c r="AH189" s="65"/>
+      <c r="AI189" s="65"/>
+      <c r="AJ189" s="65"/>
+      <c r="AK189" s="65"/>
+      <c r="AL189" s="65"/>
+      <c r="AM189" s="65"/>
+      <c r="AN189" s="65"/>
+      <c r="AO189" s="65"/>
+      <c r="AP189" s="65"/>
+      <c r="AQ189" s="65"/>
+      <c r="AR189" s="65"/>
+      <c r="AS189" s="65"/>
+      <c r="AT189" s="65"/>
+      <c r="AU189" s="65"/>
+      <c r="AV189" s="65"/>
+      <c r="AW189" s="65"/>
+      <c r="AX189" s="65"/>
+    </row>
+    <row r="190" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="66"/>
+      <c r="B190" s="67">
+        <v>46059</v>
+      </c>
+      <c r="C190" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D190" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E190" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="F190" s="69"/>
+      <c r="G190" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H190" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I190" s="70">
+        <v>10000</v>
+      </c>
+      <c r="J190" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K190" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L190" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M190" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N190" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O190" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="P190" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q190" s="71"/>
+      <c r="R190" s="64"/>
+      <c r="S190" s="64"/>
+      <c r="T190" s="64"/>
+      <c r="U190" s="64"/>
+      <c r="V190" s="64"/>
+      <c r="W190" s="64"/>
+      <c r="X190" s="64"/>
+      <c r="Y190" s="64"/>
+      <c r="Z190" s="65"/>
+      <c r="AA190" s="65"/>
+      <c r="AB190" s="65"/>
+      <c r="AC190" s="65"/>
+      <c r="AD190" s="65"/>
+      <c r="AE190" s="65"/>
+      <c r="AF190" s="65"/>
+      <c r="AG190" s="65"/>
+      <c r="AH190" s="65"/>
+      <c r="AI190" s="65"/>
+      <c r="AJ190" s="65"/>
+      <c r="AK190" s="65"/>
+      <c r="AL190" s="65"/>
+      <c r="AM190" s="65"/>
+      <c r="AN190" s="65"/>
+      <c r="AO190" s="65"/>
+      <c r="AP190" s="65"/>
+      <c r="AQ190" s="65"/>
+      <c r="AR190" s="65"/>
+      <c r="AS190" s="65"/>
+      <c r="AT190" s="65"/>
+      <c r="AU190" s="65"/>
+      <c r="AV190" s="65"/>
+      <c r="AW190" s="65"/>
+      <c r="AX190" s="65"/>
+    </row>
+    <row r="191" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="66"/>
+      <c r="B191" s="67">
+        <v>46100</v>
+      </c>
+      <c r="C191" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D191" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E191" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="F191" s="69"/>
+      <c r="G191" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H191" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I191" s="70">
+        <v>5725</v>
+      </c>
+      <c r="J191" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K191" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L191" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M191" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N191" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O191" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="P191" s="73" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q191" s="71"/>
+      <c r="R191" s="64"/>
+      <c r="S191" s="64"/>
+      <c r="T191" s="64"/>
+      <c r="U191" s="64"/>
+      <c r="V191" s="64"/>
+      <c r="W191" s="64"/>
+      <c r="X191" s="64"/>
+      <c r="Y191" s="64"/>
+      <c r="Z191" s="65"/>
+      <c r="AA191" s="65"/>
+      <c r="AB191" s="65"/>
+      <c r="AC191" s="65"/>
+      <c r="AD191" s="65"/>
+      <c r="AE191" s="65"/>
+      <c r="AF191" s="65"/>
+      <c r="AG191" s="65"/>
+      <c r="AH191" s="65"/>
+      <c r="AI191" s="65"/>
+      <c r="AJ191" s="65"/>
+      <c r="AK191" s="65"/>
+      <c r="AL191" s="65"/>
+      <c r="AM191" s="65"/>
+      <c r="AN191" s="65"/>
+      <c r="AO191" s="65"/>
+      <c r="AP191" s="65"/>
+      <c r="AQ191" s="65"/>
+      <c r="AR191" s="65"/>
+      <c r="AS191" s="65"/>
+      <c r="AT191" s="65"/>
+      <c r="AU191" s="65"/>
+      <c r="AV191" s="65"/>
+      <c r="AW191" s="65"/>
+      <c r="AX191" s="65"/>
+    </row>
+    <row r="192" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="66"/>
+      <c r="B192" s="67">
         <v>46079</v>
       </c>
-      <c r="C189" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D189" s="92"/>
-      <c r="E189" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F189" s="94">
-        <v>123006</v>
-      </c>
-      <c r="G189" s="93" t="s">
+      <c r="C192" s="67">
+        <v>46098</v>
+      </c>
+      <c r="D192" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E192" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="F192" s="69"/>
+      <c r="G192" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H192" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="I192" s="70">
+        <v>156000</v>
+      </c>
+      <c r="J192" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K192" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="L192" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M192" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N192" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O192" s="69"/>
+      <c r="P192" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q192" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="R192" s="64"/>
+      <c r="S192" s="64"/>
+      <c r="T192" s="64"/>
+      <c r="U192" s="64"/>
+      <c r="V192" s="64"/>
+      <c r="W192" s="64"/>
+      <c r="X192" s="64"/>
+      <c r="Y192" s="64"/>
+      <c r="Z192" s="65"/>
+      <c r="AA192" s="65"/>
+      <c r="AB192" s="65"/>
+      <c r="AC192" s="65"/>
+      <c r="AD192" s="65"/>
+      <c r="AE192" s="65"/>
+      <c r="AF192" s="65"/>
+      <c r="AG192" s="65"/>
+      <c r="AH192" s="65"/>
+      <c r="AI192" s="65"/>
+      <c r="AJ192" s="65"/>
+      <c r="AK192" s="65"/>
+      <c r="AL192" s="65"/>
+      <c r="AM192" s="65"/>
+      <c r="AN192" s="65"/>
+      <c r="AO192" s="65"/>
+      <c r="AP192" s="65"/>
+      <c r="AQ192" s="65"/>
+      <c r="AR192" s="65"/>
+      <c r="AS192" s="65"/>
+      <c r="AT192" s="65"/>
+      <c r="AU192" s="65"/>
+      <c r="AV192" s="65"/>
+      <c r="AW192" s="65"/>
+      <c r="AX192" s="65"/>
+    </row>
+    <row r="193" spans="1:50" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="66"/>
+      <c r="B193" s="67">
+        <v>46100</v>
+      </c>
+      <c r="C193" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D193" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E193" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="F193" s="69"/>
+      <c r="G193" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="H189" s="93" t="s">
+      <c r="H193" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I193" s="70">
+        <v>17920</v>
+      </c>
+      <c r="J193" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K193" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="L193" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M193" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N193" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O193" s="68" t="s">
+        <v>366</v>
+      </c>
+      <c r="P193" s="71"/>
+      <c r="Q193" s="71"/>
+      <c r="R193" s="65"/>
+      <c r="S193" s="65"/>
+      <c r="T193" s="65"/>
+      <c r="U193" s="65"/>
+      <c r="V193" s="65"/>
+      <c r="W193" s="65"/>
+      <c r="X193" s="65"/>
+      <c r="Y193" s="65"/>
+      <c r="Z193" s="65"/>
+      <c r="AA193" s="65"/>
+      <c r="AB193" s="65"/>
+      <c r="AC193" s="65"/>
+      <c r="AD193" s="65"/>
+      <c r="AE193" s="65"/>
+      <c r="AF193" s="65"/>
+      <c r="AG193" s="65"/>
+      <c r="AH193" s="65"/>
+      <c r="AI193" s="65"/>
+      <c r="AJ193" s="65"/>
+      <c r="AK193" s="65"/>
+      <c r="AL193" s="65"/>
+      <c r="AM193" s="65"/>
+      <c r="AN193" s="65"/>
+      <c r="AO193" s="65"/>
+      <c r="AP193" s="65"/>
+      <c r="AQ193" s="65"/>
+      <c r="AR193" s="65"/>
+      <c r="AS193" s="65"/>
+      <c r="AT193" s="65"/>
+      <c r="AU193" s="65"/>
+      <c r="AV193" s="65"/>
+      <c r="AW193" s="65"/>
+      <c r="AX193" s="65"/>
+    </row>
+    <row r="194" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="66"/>
+      <c r="B194" s="67">
+        <v>46100</v>
+      </c>
+      <c r="C194" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D194" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E194" s="68" t="s">
+        <v>390</v>
+      </c>
+      <c r="F194" s="69"/>
+      <c r="G194" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="H194" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="I194" s="70">
+        <v>218.99</v>
+      </c>
+      <c r="J194" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K194" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="L194" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M194" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N194" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O194" s="68">
+        <v>8.5840000002718907E+47</v>
+      </c>
+      <c r="P194" s="71"/>
+      <c r="Q194" s="71"/>
+      <c r="R194" s="65"/>
+      <c r="S194" s="65"/>
+      <c r="T194" s="65"/>
+      <c r="U194" s="65"/>
+      <c r="V194" s="65"/>
+      <c r="W194" s="65"/>
+      <c r="X194" s="65"/>
+      <c r="Y194" s="65"/>
+      <c r="Z194" s="65"/>
+      <c r="AA194" s="65"/>
+      <c r="AB194" s="65"/>
+      <c r="AC194" s="65"/>
+      <c r="AD194" s="65"/>
+      <c r="AE194" s="65"/>
+      <c r="AF194" s="65"/>
+      <c r="AG194" s="65"/>
+      <c r="AH194" s="65"/>
+      <c r="AI194" s="65"/>
+      <c r="AJ194" s="65"/>
+      <c r="AK194" s="65"/>
+      <c r="AL194" s="65"/>
+      <c r="AM194" s="65"/>
+      <c r="AN194" s="65"/>
+      <c r="AO194" s="65"/>
+      <c r="AP194" s="65"/>
+      <c r="AQ194" s="65"/>
+      <c r="AR194" s="65"/>
+      <c r="AS194" s="65"/>
+      <c r="AT194" s="65"/>
+      <c r="AU194" s="65"/>
+      <c r="AV194" s="65"/>
+      <c r="AW194" s="65"/>
+      <c r="AX194" s="65"/>
+    </row>
+    <row r="195" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="66"/>
+      <c r="B195" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C195" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D195" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E195" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="F195" s="69"/>
+      <c r="G195" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H195" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="I195" s="70">
+        <v>540</v>
+      </c>
+      <c r="J195" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K195" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L195" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M195" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N195" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O195" s="68" t="s">
+        <v>391</v>
+      </c>
+      <c r="P195" s="71"/>
+      <c r="Q195" s="71"/>
+      <c r="R195" s="64"/>
+      <c r="S195" s="64"/>
+      <c r="T195" s="64"/>
+      <c r="U195" s="64"/>
+      <c r="V195" s="64"/>
+      <c r="W195" s="64"/>
+      <c r="X195" s="64"/>
+      <c r="Y195" s="64"/>
+      <c r="Z195" s="65"/>
+      <c r="AA195" s="65"/>
+      <c r="AB195" s="65"/>
+      <c r="AC195" s="65"/>
+      <c r="AD195" s="65"/>
+      <c r="AE195" s="65"/>
+      <c r="AF195" s="65"/>
+      <c r="AG195" s="65"/>
+      <c r="AH195" s="65"/>
+      <c r="AI195" s="65"/>
+      <c r="AJ195" s="65"/>
+      <c r="AK195" s="65"/>
+      <c r="AL195" s="65"/>
+      <c r="AM195" s="65"/>
+      <c r="AN195" s="65"/>
+      <c r="AO195" s="65"/>
+      <c r="AP195" s="65"/>
+      <c r="AQ195" s="65"/>
+      <c r="AR195" s="65"/>
+      <c r="AS195" s="65"/>
+      <c r="AT195" s="65"/>
+      <c r="AU195" s="65"/>
+      <c r="AV195" s="65"/>
+      <c r="AW195" s="65"/>
+      <c r="AX195" s="65"/>
+    </row>
+    <row r="196" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="69"/>
+      <c r="B196" s="67">
+        <v>46100</v>
+      </c>
+      <c r="C196" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D196" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E196" s="68" t="s">
+        <v>392</v>
+      </c>
+      <c r="F196" s="69"/>
+      <c r="G196" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H196" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I196" s="70">
+        <v>250</v>
+      </c>
+      <c r="J196" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K196" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="L196" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M196" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N196" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O196" s="68" t="s">
+        <v>393</v>
+      </c>
+      <c r="P196" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q196" s="89"/>
+      <c r="R196" s="64"/>
+      <c r="S196" s="64"/>
+      <c r="T196" s="64"/>
+      <c r="U196" s="64"/>
+      <c r="V196" s="64"/>
+      <c r="W196" s="64"/>
+      <c r="X196" s="64"/>
+      <c r="Y196" s="64"/>
+      <c r="Z196" s="65"/>
+      <c r="AA196" s="65"/>
+      <c r="AB196" s="65"/>
+      <c r="AC196" s="65"/>
+      <c r="AD196" s="65"/>
+      <c r="AE196" s="65"/>
+      <c r="AF196" s="65"/>
+      <c r="AG196" s="65"/>
+      <c r="AH196" s="65"/>
+      <c r="AI196" s="65"/>
+      <c r="AJ196" s="65"/>
+      <c r="AK196" s="65"/>
+      <c r="AL196" s="65"/>
+      <c r="AM196" s="65"/>
+      <c r="AN196" s="65"/>
+      <c r="AO196" s="65"/>
+      <c r="AP196" s="65"/>
+      <c r="AQ196" s="65"/>
+      <c r="AR196" s="65"/>
+      <c r="AS196" s="65"/>
+      <c r="AT196" s="65"/>
+      <c r="AU196" s="65"/>
+      <c r="AV196" s="65"/>
+      <c r="AW196" s="65"/>
+      <c r="AX196" s="65"/>
+    </row>
+    <row r="197" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="66"/>
+      <c r="B197" s="67">
+        <v>46091</v>
+      </c>
+      <c r="C197" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D197" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E197" s="68" t="s">
+        <v>158</v>
+      </c>
+      <c r="F197" s="69"/>
+      <c r="G197" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H197" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="I197" s="70">
+        <v>448.55</v>
+      </c>
+      <c r="J197" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K197" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="L197" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M197" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N197" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O197" s="68">
+        <v>3.4191097357934902E+46</v>
+      </c>
+      <c r="P197" s="71"/>
+      <c r="Q197" s="71"/>
+      <c r="R197" s="64"/>
+      <c r="S197" s="64"/>
+      <c r="T197" s="64"/>
+      <c r="U197" s="64"/>
+      <c r="V197" s="64"/>
+      <c r="W197" s="64"/>
+      <c r="X197" s="64"/>
+      <c r="Y197" s="64"/>
+      <c r="Z197" s="65"/>
+      <c r="AA197" s="65"/>
+      <c r="AB197" s="65"/>
+      <c r="AC197" s="65"/>
+      <c r="AD197" s="65"/>
+      <c r="AE197" s="65"/>
+      <c r="AF197" s="65"/>
+      <c r="AG197" s="65"/>
+      <c r="AH197" s="65"/>
+      <c r="AI197" s="65"/>
+      <c r="AJ197" s="65"/>
+      <c r="AK197" s="65"/>
+      <c r="AL197" s="65"/>
+      <c r="AM197" s="65"/>
+      <c r="AN197" s="65"/>
+      <c r="AO197" s="65"/>
+      <c r="AP197" s="65"/>
+      <c r="AQ197" s="65"/>
+      <c r="AR197" s="65"/>
+      <c r="AS197" s="65"/>
+      <c r="AT197" s="65"/>
+      <c r="AU197" s="65"/>
+      <c r="AV197" s="65"/>
+      <c r="AW197" s="65"/>
+      <c r="AX197" s="65"/>
+    </row>
+    <row r="198" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="66"/>
+      <c r="B198" s="67">
+        <v>46100</v>
+      </c>
+      <c r="C198" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D198" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E198" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="F198" s="69"/>
+      <c r="G198" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H198" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I198" s="70">
+        <v>366.06</v>
+      </c>
+      <c r="J198" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K198" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="L198" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M198" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N198" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O198" s="68">
+        <v>4.2297115040006398E+46</v>
+      </c>
+      <c r="P198" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q198" s="71"/>
+      <c r="R198" s="65"/>
+      <c r="S198" s="65"/>
+      <c r="T198" s="65"/>
+      <c r="U198" s="65"/>
+      <c r="V198" s="65"/>
+      <c r="W198" s="65"/>
+      <c r="X198" s="65"/>
+      <c r="Y198" s="65"/>
+      <c r="Z198" s="65"/>
+      <c r="AA198" s="65"/>
+      <c r="AB198" s="65"/>
+      <c r="AC198" s="65"/>
+      <c r="AD198" s="65"/>
+      <c r="AE198" s="65"/>
+      <c r="AF198" s="65"/>
+      <c r="AG198" s="65"/>
+      <c r="AH198" s="65"/>
+      <c r="AI198" s="65"/>
+      <c r="AJ198" s="65"/>
+      <c r="AK198" s="65"/>
+      <c r="AL198" s="65"/>
+      <c r="AM198" s="65"/>
+      <c r="AN198" s="65"/>
+      <c r="AO198" s="65"/>
+      <c r="AP198" s="65"/>
+      <c r="AQ198" s="65"/>
+      <c r="AR198" s="65"/>
+      <c r="AS198" s="65"/>
+      <c r="AT198" s="65"/>
+      <c r="AU198" s="65"/>
+      <c r="AV198" s="65"/>
+      <c r="AW198" s="65"/>
+      <c r="AX198" s="65"/>
+    </row>
+    <row r="199" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="66"/>
+      <c r="B199" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C199" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D199" s="67">
+        <v>46100</v>
+      </c>
+      <c r="E199" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="F199" s="69"/>
+      <c r="G199" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H199" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="I199" s="70">
+        <v>96500</v>
+      </c>
+      <c r="J199" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K199" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="L199" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M199" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N199" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O199" s="69"/>
+      <c r="P199" s="71"/>
+      <c r="Q199" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="R199" s="64"/>
+      <c r="S199" s="64"/>
+      <c r="T199" s="64"/>
+      <c r="U199" s="64"/>
+      <c r="V199" s="64"/>
+      <c r="W199" s="64"/>
+      <c r="X199" s="64"/>
+      <c r="Y199" s="64"/>
+      <c r="Z199" s="65"/>
+      <c r="AA199" s="65"/>
+      <c r="AB199" s="65"/>
+      <c r="AC199" s="65"/>
+      <c r="AD199" s="65"/>
+      <c r="AE199" s="65"/>
+      <c r="AF199" s="65"/>
+      <c r="AG199" s="65"/>
+      <c r="AH199" s="65"/>
+      <c r="AI199" s="65"/>
+      <c r="AJ199" s="65"/>
+      <c r="AK199" s="65"/>
+      <c r="AL199" s="65"/>
+      <c r="AM199" s="65"/>
+      <c r="AN199" s="65"/>
+      <c r="AO199" s="65"/>
+      <c r="AP199" s="65"/>
+      <c r="AQ199" s="65"/>
+      <c r="AR199" s="65"/>
+      <c r="AS199" s="65"/>
+      <c r="AT199" s="65"/>
+      <c r="AU199" s="65"/>
+      <c r="AV199" s="65"/>
+      <c r="AW199" s="65"/>
+      <c r="AX199" s="65"/>
+    </row>
+    <row r="200" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="66"/>
+      <c r="B200" s="67">
+        <v>46093</v>
+      </c>
+      <c r="C200" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D200" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E200" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="F200" s="75">
+        <v>9755</v>
+      </c>
+      <c r="G200" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H200" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="I189" s="95">
-        <v>164.95</v>
-      </c>
-      <c r="J189" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K189" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L189" s="93" t="s">
+      <c r="I200" s="70">
+        <v>1700</v>
+      </c>
+      <c r="J200" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K200" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L200" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="M189" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N189" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O189" s="92"/>
-      <c r="P189" s="96" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q189" s="97"/>
-      <c r="R189" s="98"/>
-      <c r="S189" s="98"/>
-      <c r="T189" s="98"/>
-      <c r="U189" s="98"/>
-      <c r="V189" s="98"/>
-      <c r="W189" s="98"/>
-      <c r="X189" s="98"/>
-      <c r="Y189" s="98"/>
-      <c r="Z189" s="99"/>
-      <c r="AA189" s="99"/>
-      <c r="AB189" s="99"/>
-      <c r="AC189" s="99"/>
-      <c r="AD189" s="99"/>
-      <c r="AE189" s="99"/>
-      <c r="AF189" s="99"/>
-      <c r="AG189" s="99"/>
-      <c r="AH189" s="99"/>
-      <c r="AI189" s="99"/>
-      <c r="AJ189" s="99"/>
-      <c r="AK189" s="99"/>
-      <c r="AL189" s="99"/>
-      <c r="AM189" s="99"/>
-      <c r="AN189" s="99"/>
-      <c r="AO189" s="99"/>
-      <c r="AP189" s="99"/>
-      <c r="AQ189" s="99"/>
-      <c r="AR189" s="99"/>
-      <c r="AS189" s="99"/>
-      <c r="AT189" s="99"/>
-      <c r="AU189" s="99"/>
-      <c r="AV189" s="99"/>
-      <c r="AW189" s="99"/>
-      <c r="AX189" s="99"/>
-    </row>
-    <row r="190" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="90"/>
-      <c r="B190" s="91">
+      <c r="M200" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N200" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O200" s="69"/>
+      <c r="P200" s="71"/>
+      <c r="Q200" s="71"/>
+      <c r="R200" s="64"/>
+      <c r="S200" s="64"/>
+      <c r="T200" s="64"/>
+      <c r="U200" s="64"/>
+      <c r="V200" s="64"/>
+      <c r="W200" s="64"/>
+      <c r="X200" s="64"/>
+      <c r="Y200" s="64"/>
+      <c r="Z200" s="65"/>
+      <c r="AA200" s="65"/>
+      <c r="AB200" s="65"/>
+      <c r="AC200" s="65"/>
+      <c r="AD200" s="65"/>
+      <c r="AE200" s="65"/>
+      <c r="AF200" s="65"/>
+      <c r="AG200" s="65"/>
+      <c r="AH200" s="65"/>
+      <c r="AI200" s="65"/>
+      <c r="AJ200" s="65"/>
+      <c r="AK200" s="65"/>
+      <c r="AL200" s="65"/>
+      <c r="AM200" s="65"/>
+      <c r="AN200" s="65"/>
+      <c r="AO200" s="65"/>
+      <c r="AP200" s="65"/>
+      <c r="AQ200" s="65"/>
+      <c r="AR200" s="65"/>
+      <c r="AS200" s="65"/>
+      <c r="AT200" s="65"/>
+      <c r="AU200" s="65"/>
+      <c r="AV200" s="65"/>
+      <c r="AW200" s="65"/>
+      <c r="AX200" s="65"/>
+    </row>
+    <row r="201" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="66"/>
+      <c r="B201" s="67">
         <v>46079</v>
       </c>
-      <c r="C190" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D190" s="92"/>
-      <c r="E190" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F190" s="94">
-        <v>123007</v>
-      </c>
-      <c r="G190" s="93" t="s">
+      <c r="C201" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D201" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E201" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="F201" s="75" t="s">
+        <v>151</v>
+      </c>
+      <c r="G201" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="H190" s="93" t="s">
+      <c r="H201" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="I201" s="70">
+        <v>163.96</v>
+      </c>
+      <c r="J201" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K201" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L201" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M201" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N201" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O201" s="69"/>
+      <c r="P201" s="71"/>
+      <c r="Q201" s="71"/>
+      <c r="R201" s="64"/>
+      <c r="S201" s="64"/>
+      <c r="T201" s="64"/>
+      <c r="U201" s="64"/>
+      <c r="V201" s="64"/>
+      <c r="W201" s="64"/>
+      <c r="X201" s="64"/>
+      <c r="Y201" s="64"/>
+      <c r="Z201" s="65"/>
+      <c r="AA201" s="65"/>
+      <c r="AB201" s="65"/>
+      <c r="AC201" s="65"/>
+      <c r="AD201" s="65"/>
+      <c r="AE201" s="65"/>
+      <c r="AF201" s="65"/>
+      <c r="AG201" s="65"/>
+      <c r="AH201" s="65"/>
+      <c r="AI201" s="65"/>
+      <c r="AJ201" s="65"/>
+      <c r="AK201" s="65"/>
+      <c r="AL201" s="65"/>
+      <c r="AM201" s="65"/>
+      <c r="AN201" s="65"/>
+      <c r="AO201" s="65"/>
+      <c r="AP201" s="65"/>
+      <c r="AQ201" s="65"/>
+      <c r="AR201" s="65"/>
+      <c r="AS201" s="65"/>
+      <c r="AT201" s="65"/>
+      <c r="AU201" s="65"/>
+      <c r="AV201" s="65"/>
+      <c r="AW201" s="65"/>
+      <c r="AX201" s="65"/>
+    </row>
+    <row r="202" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="66"/>
+      <c r="B202" s="67">
+        <v>46093</v>
+      </c>
+      <c r="C202" s="67">
+        <v>46099</v>
+      </c>
+      <c r="D202" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E202" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202" s="75">
+        <v>239234</v>
+      </c>
+      <c r="G202" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H202" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I202" s="70">
+        <v>1993.24</v>
+      </c>
+      <c r="J202" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K202" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L202" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M202" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N202" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O202" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="P202" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q202" s="71"/>
+      <c r="R202" s="64"/>
+      <c r="S202" s="64"/>
+      <c r="T202" s="64"/>
+      <c r="U202" s="64"/>
+      <c r="V202" s="64"/>
+      <c r="W202" s="64"/>
+      <c r="X202" s="64"/>
+      <c r="Y202" s="64"/>
+      <c r="Z202" s="65"/>
+      <c r="AA202" s="65"/>
+      <c r="AB202" s="65"/>
+      <c r="AC202" s="65"/>
+      <c r="AD202" s="65"/>
+      <c r="AE202" s="65"/>
+      <c r="AF202" s="65"/>
+      <c r="AG202" s="65"/>
+      <c r="AH202" s="65"/>
+      <c r="AI202" s="65"/>
+      <c r="AJ202" s="65"/>
+      <c r="AK202" s="65"/>
+      <c r="AL202" s="65"/>
+      <c r="AM202" s="65"/>
+      <c r="AN202" s="65"/>
+      <c r="AO202" s="65"/>
+      <c r="AP202" s="65"/>
+      <c r="AQ202" s="65"/>
+      <c r="AR202" s="65"/>
+      <c r="AS202" s="65"/>
+      <c r="AT202" s="65"/>
+      <c r="AU202" s="65"/>
+      <c r="AV202" s="65"/>
+      <c r="AW202" s="65"/>
+      <c r="AX202" s="65"/>
+    </row>
+    <row r="203" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="66"/>
+      <c r="B203" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C203" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D203" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E203" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F203" s="75">
+        <v>239302</v>
+      </c>
+      <c r="G203" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H203" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I203" s="70">
+        <v>33965.33</v>
+      </c>
+      <c r="J203" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K203" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L203" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M203" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N203" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O203" s="69"/>
+      <c r="P203" s="71"/>
+      <c r="Q203" s="71"/>
+      <c r="R203" s="64"/>
+      <c r="S203" s="64"/>
+      <c r="T203" s="64"/>
+      <c r="U203" s="64"/>
+      <c r="V203" s="64"/>
+      <c r="W203" s="64"/>
+      <c r="X203" s="64"/>
+      <c r="Y203" s="64"/>
+      <c r="Z203" s="65"/>
+      <c r="AA203" s="65"/>
+      <c r="AB203" s="65"/>
+      <c r="AC203" s="65"/>
+      <c r="AD203" s="65"/>
+      <c r="AE203" s="65"/>
+      <c r="AF203" s="65"/>
+      <c r="AG203" s="65"/>
+      <c r="AH203" s="65"/>
+      <c r="AI203" s="65"/>
+      <c r="AJ203" s="65"/>
+      <c r="AK203" s="65"/>
+      <c r="AL203" s="65"/>
+      <c r="AM203" s="65"/>
+      <c r="AN203" s="65"/>
+      <c r="AO203" s="65"/>
+      <c r="AP203" s="65"/>
+      <c r="AQ203" s="65"/>
+      <c r="AR203" s="65"/>
+      <c r="AS203" s="65"/>
+      <c r="AT203" s="65"/>
+      <c r="AU203" s="65"/>
+      <c r="AV203" s="65"/>
+      <c r="AW203" s="65"/>
+      <c r="AX203" s="65"/>
+    </row>
+    <row r="204" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="66"/>
+      <c r="B204" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C204" s="67">
+        <v>46102</v>
+      </c>
+      <c r="D204" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E204" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F204" s="75">
+        <v>239358</v>
+      </c>
+      <c r="G204" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H204" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I204" s="70">
+        <v>20513.09</v>
+      </c>
+      <c r="J204" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K204" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L204" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M204" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N204" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O204" s="69"/>
+      <c r="P204" s="71"/>
+      <c r="Q204" s="71"/>
+      <c r="R204" s="64"/>
+      <c r="S204" s="64"/>
+      <c r="T204" s="64"/>
+      <c r="U204" s="64"/>
+      <c r="V204" s="64"/>
+      <c r="W204" s="64"/>
+      <c r="X204" s="64"/>
+      <c r="Y204" s="64"/>
+      <c r="Z204" s="65"/>
+      <c r="AA204" s="65"/>
+      <c r="AB204" s="65"/>
+      <c r="AC204" s="65"/>
+      <c r="AD204" s="65"/>
+      <c r="AE204" s="65"/>
+      <c r="AF204" s="65"/>
+      <c r="AG204" s="65"/>
+      <c r="AH204" s="65"/>
+      <c r="AI204" s="65"/>
+      <c r="AJ204" s="65"/>
+      <c r="AK204" s="65"/>
+      <c r="AL204" s="65"/>
+      <c r="AM204" s="65"/>
+      <c r="AN204" s="65"/>
+      <c r="AO204" s="65"/>
+      <c r="AP204" s="65"/>
+      <c r="AQ204" s="65"/>
+      <c r="AR204" s="65"/>
+      <c r="AS204" s="65"/>
+      <c r="AT204" s="65"/>
+      <c r="AU204" s="65"/>
+      <c r="AV204" s="65"/>
+      <c r="AW204" s="65"/>
+      <c r="AX204" s="65"/>
+    </row>
+    <row r="205" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="66"/>
+      <c r="B205" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C205" s="67">
+        <v>46102</v>
+      </c>
+      <c r="D205" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E205" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F205" s="75">
+        <v>239337</v>
+      </c>
+      <c r="G205" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H205" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I205" s="70">
+        <v>46772.25</v>
+      </c>
+      <c r="J205" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K205" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L205" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M205" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N205" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O205" s="69"/>
+      <c r="P205" s="71"/>
+      <c r="Q205" s="71"/>
+      <c r="R205" s="64"/>
+      <c r="S205" s="64"/>
+      <c r="T205" s="64"/>
+      <c r="U205" s="64"/>
+      <c r="V205" s="64"/>
+      <c r="W205" s="64"/>
+      <c r="X205" s="64"/>
+      <c r="Y205" s="64"/>
+      <c r="Z205" s="65"/>
+      <c r="AA205" s="65"/>
+      <c r="AB205" s="65"/>
+      <c r="AC205" s="65"/>
+      <c r="AD205" s="65"/>
+      <c r="AE205" s="65"/>
+      <c r="AF205" s="65"/>
+      <c r="AG205" s="65"/>
+      <c r="AH205" s="65"/>
+      <c r="AI205" s="65"/>
+      <c r="AJ205" s="65"/>
+      <c r="AK205" s="65"/>
+      <c r="AL205" s="65"/>
+      <c r="AM205" s="65"/>
+      <c r="AN205" s="65"/>
+      <c r="AO205" s="65"/>
+      <c r="AP205" s="65"/>
+      <c r="AQ205" s="65"/>
+      <c r="AR205" s="65"/>
+      <c r="AS205" s="65"/>
+      <c r="AT205" s="65"/>
+      <c r="AU205" s="65"/>
+      <c r="AV205" s="65"/>
+      <c r="AW205" s="65"/>
+      <c r="AX205" s="65"/>
+    </row>
+    <row r="206" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="66"/>
+      <c r="B206" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C206" s="67">
+        <v>46103</v>
+      </c>
+      <c r="D206" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E206" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F206" s="75">
+        <v>239402</v>
+      </c>
+      <c r="G206" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H206" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I206" s="70">
+        <v>40605.379999999997</v>
+      </c>
+      <c r="J206" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K206" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L206" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M206" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N206" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O206" s="69"/>
+      <c r="P206" s="71"/>
+      <c r="Q206" s="71"/>
+      <c r="R206" s="64"/>
+      <c r="S206" s="64"/>
+      <c r="T206" s="64"/>
+      <c r="U206" s="64"/>
+      <c r="V206" s="64"/>
+      <c r="W206" s="64"/>
+      <c r="X206" s="64"/>
+      <c r="Y206" s="64"/>
+      <c r="Z206" s="65"/>
+      <c r="AA206" s="65"/>
+      <c r="AB206" s="65"/>
+      <c r="AC206" s="65"/>
+      <c r="AD206" s="65"/>
+      <c r="AE206" s="65"/>
+      <c r="AF206" s="65"/>
+      <c r="AG206" s="65"/>
+      <c r="AH206" s="65"/>
+      <c r="AI206" s="65"/>
+      <c r="AJ206" s="65"/>
+      <c r="AK206" s="65"/>
+      <c r="AL206" s="65"/>
+      <c r="AM206" s="65"/>
+      <c r="AN206" s="65"/>
+      <c r="AO206" s="65"/>
+      <c r="AP206" s="65"/>
+      <c r="AQ206" s="65"/>
+      <c r="AR206" s="65"/>
+      <c r="AS206" s="65"/>
+      <c r="AT206" s="65"/>
+      <c r="AU206" s="65"/>
+      <c r="AV206" s="65"/>
+      <c r="AW206" s="65"/>
+      <c r="AX206" s="65"/>
+    </row>
+    <row r="207" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="66"/>
+      <c r="B207" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C207" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D207" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E207" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F207" s="75">
+        <v>239304</v>
+      </c>
+      <c r="G207" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H207" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I207" s="70">
+        <v>50348.42</v>
+      </c>
+      <c r="J207" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K207" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L207" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M207" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N207" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O207" s="69"/>
+      <c r="P207" s="71"/>
+      <c r="Q207" s="71"/>
+      <c r="R207" s="64"/>
+      <c r="S207" s="64"/>
+      <c r="T207" s="64"/>
+      <c r="U207" s="64"/>
+      <c r="V207" s="64"/>
+      <c r="W207" s="64"/>
+      <c r="X207" s="64"/>
+      <c r="Y207" s="64"/>
+      <c r="Z207" s="65"/>
+      <c r="AA207" s="65"/>
+      <c r="AB207" s="65"/>
+      <c r="AC207" s="65"/>
+      <c r="AD207" s="65"/>
+      <c r="AE207" s="65"/>
+      <c r="AF207" s="65"/>
+      <c r="AG207" s="65"/>
+      <c r="AH207" s="65"/>
+      <c r="AI207" s="65"/>
+      <c r="AJ207" s="65"/>
+      <c r="AK207" s="65"/>
+      <c r="AL207" s="65"/>
+      <c r="AM207" s="65"/>
+      <c r="AN207" s="65"/>
+      <c r="AO207" s="65"/>
+      <c r="AP207" s="65"/>
+      <c r="AQ207" s="65"/>
+      <c r="AR207" s="65"/>
+      <c r="AS207" s="65"/>
+      <c r="AT207" s="65"/>
+      <c r="AU207" s="65"/>
+      <c r="AV207" s="65"/>
+      <c r="AW207" s="65"/>
+      <c r="AX207" s="65"/>
+    </row>
+    <row r="208" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="66"/>
+      <c r="B208" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C208" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D208" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E208" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F208" s="75">
+        <v>455202</v>
+      </c>
+      <c r="G208" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H208" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I208" s="70">
+        <v>8400</v>
+      </c>
+      <c r="J208" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K208" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L208" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M208" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N208" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O208" s="69"/>
+      <c r="P208" s="71"/>
+      <c r="Q208" s="71"/>
+      <c r="R208" s="64"/>
+      <c r="S208" s="64"/>
+      <c r="T208" s="64"/>
+      <c r="U208" s="64"/>
+      <c r="V208" s="64"/>
+      <c r="W208" s="64"/>
+      <c r="X208" s="64"/>
+      <c r="Y208" s="64"/>
+      <c r="Z208" s="65"/>
+      <c r="AA208" s="65"/>
+      <c r="AB208" s="65"/>
+      <c r="AC208" s="65"/>
+      <c r="AD208" s="65"/>
+      <c r="AE208" s="65"/>
+      <c r="AF208" s="65"/>
+      <c r="AG208" s="65"/>
+      <c r="AH208" s="65"/>
+      <c r="AI208" s="65"/>
+      <c r="AJ208" s="65"/>
+      <c r="AK208" s="65"/>
+      <c r="AL208" s="65"/>
+      <c r="AM208" s="65"/>
+      <c r="AN208" s="65"/>
+      <c r="AO208" s="65"/>
+      <c r="AP208" s="65"/>
+      <c r="AQ208" s="65"/>
+      <c r="AR208" s="65"/>
+      <c r="AS208" s="65"/>
+      <c r="AT208" s="65"/>
+      <c r="AU208" s="65"/>
+      <c r="AV208" s="65"/>
+      <c r="AW208" s="65"/>
+      <c r="AX208" s="65"/>
+    </row>
+    <row r="209" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="66"/>
+      <c r="B209" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C209" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D209" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E209" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="F209" s="75">
+        <v>132239</v>
+      </c>
+      <c r="G209" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H209" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="I190" s="95">
-        <v>20304.95</v>
-      </c>
-      <c r="J190" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K190" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L190" s="93" t="s">
+      <c r="I209" s="70">
+        <v>4556</v>
+      </c>
+      <c r="J209" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K209" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L209" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M209" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N209" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O209" s="69"/>
+      <c r="P209" s="71"/>
+      <c r="Q209" s="71"/>
+      <c r="R209" s="64"/>
+      <c r="S209" s="64"/>
+      <c r="T209" s="64"/>
+      <c r="U209" s="64"/>
+      <c r="V209" s="64"/>
+      <c r="W209" s="64"/>
+      <c r="X209" s="64"/>
+      <c r="Y209" s="64"/>
+      <c r="Z209" s="65"/>
+      <c r="AA209" s="65"/>
+      <c r="AB209" s="65"/>
+      <c r="AC209" s="65"/>
+      <c r="AD209" s="65"/>
+      <c r="AE209" s="65"/>
+      <c r="AF209" s="65"/>
+      <c r="AG209" s="65"/>
+      <c r="AH209" s="65"/>
+      <c r="AI209" s="65"/>
+      <c r="AJ209" s="65"/>
+      <c r="AK209" s="65"/>
+      <c r="AL209" s="65"/>
+      <c r="AM209" s="65"/>
+      <c r="AN209" s="65"/>
+      <c r="AO209" s="65"/>
+      <c r="AP209" s="65"/>
+      <c r="AQ209" s="65"/>
+      <c r="AR209" s="65"/>
+      <c r="AS209" s="65"/>
+      <c r="AT209" s="65"/>
+      <c r="AU209" s="65"/>
+      <c r="AV209" s="65"/>
+      <c r="AW209" s="65"/>
+      <c r="AX209" s="65"/>
+    </row>
+    <row r="210" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="66"/>
+      <c r="B210" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C210" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D210" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E210" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F210" s="75">
+        <v>264292</v>
+      </c>
+      <c r="G210" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H210" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I210" s="70">
+        <v>208.77</v>
+      </c>
+      <c r="J210" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K210" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L210" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M210" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N210" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O210" s="69"/>
+      <c r="P210" s="71"/>
+      <c r="Q210" s="71"/>
+      <c r="R210" s="64"/>
+      <c r="S210" s="64"/>
+      <c r="T210" s="64"/>
+      <c r="U210" s="64"/>
+      <c r="V210" s="64"/>
+      <c r="W210" s="64"/>
+      <c r="X210" s="64"/>
+      <c r="Y210" s="64"/>
+      <c r="Z210" s="65"/>
+      <c r="AA210" s="65"/>
+      <c r="AB210" s="65"/>
+      <c r="AC210" s="65"/>
+      <c r="AD210" s="65"/>
+      <c r="AE210" s="65"/>
+      <c r="AF210" s="65"/>
+      <c r="AG210" s="65"/>
+      <c r="AH210" s="65"/>
+      <c r="AI210" s="65"/>
+      <c r="AJ210" s="65"/>
+      <c r="AK210" s="65"/>
+      <c r="AL210" s="65"/>
+      <c r="AM210" s="65"/>
+      <c r="AN210" s="65"/>
+      <c r="AO210" s="65"/>
+      <c r="AP210" s="65"/>
+      <c r="AQ210" s="65"/>
+      <c r="AR210" s="65"/>
+      <c r="AS210" s="65"/>
+      <c r="AT210" s="65"/>
+      <c r="AU210" s="65"/>
+      <c r="AV210" s="65"/>
+      <c r="AW210" s="65"/>
+      <c r="AX210" s="65"/>
+    </row>
+    <row r="211" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="66"/>
+      <c r="B211" s="67">
+        <v>46093</v>
+      </c>
+      <c r="C211" s="67">
+        <v>46099</v>
+      </c>
+      <c r="D211" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E211" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F211" s="75">
+        <v>239250</v>
+      </c>
+      <c r="G211" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H211" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I211" s="70">
+        <v>2714.34</v>
+      </c>
+      <c r="J211" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K211" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L211" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="M190" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N190" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O190" s="92"/>
-      <c r="P190" s="96" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q190" s="97"/>
-      <c r="R190" s="98"/>
-      <c r="S190" s="98"/>
-      <c r="T190" s="98"/>
-      <c r="U190" s="98"/>
-      <c r="V190" s="98"/>
-      <c r="W190" s="98"/>
-      <c r="X190" s="98"/>
-      <c r="Y190" s="98"/>
-      <c r="Z190" s="99"/>
-      <c r="AA190" s="99"/>
-      <c r="AB190" s="99"/>
-      <c r="AC190" s="99"/>
-      <c r="AD190" s="99"/>
-      <c r="AE190" s="99"/>
-      <c r="AF190" s="99"/>
-      <c r="AG190" s="99"/>
-      <c r="AH190" s="99"/>
-      <c r="AI190" s="99"/>
-      <c r="AJ190" s="99"/>
-      <c r="AK190" s="99"/>
-      <c r="AL190" s="99"/>
-      <c r="AM190" s="99"/>
-      <c r="AN190" s="99"/>
-      <c r="AO190" s="99"/>
-      <c r="AP190" s="99"/>
-      <c r="AQ190" s="99"/>
-      <c r="AR190" s="99"/>
-      <c r="AS190" s="99"/>
-      <c r="AT190" s="99"/>
-      <c r="AU190" s="99"/>
-      <c r="AV190" s="99"/>
-      <c r="AW190" s="99"/>
-      <c r="AX190" s="99"/>
-    </row>
-    <row r="191" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="90"/>
-      <c r="B191" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C191" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D191" s="92"/>
-      <c r="E191" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F191" s="94">
-        <v>123008</v>
-      </c>
-      <c r="G191" s="93" t="s">
+      <c r="M211" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N211" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O211" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="P211" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q211" s="71"/>
+      <c r="R211" s="64"/>
+      <c r="S211" s="64"/>
+      <c r="T211" s="64"/>
+      <c r="U211" s="64"/>
+      <c r="V211" s="64"/>
+      <c r="W211" s="64"/>
+      <c r="X211" s="64"/>
+      <c r="Y211" s="64"/>
+      <c r="Z211" s="65"/>
+      <c r="AA211" s="65"/>
+      <c r="AB211" s="65"/>
+      <c r="AC211" s="65"/>
+      <c r="AD211" s="65"/>
+      <c r="AE211" s="65"/>
+      <c r="AF211" s="65"/>
+      <c r="AG211" s="65"/>
+      <c r="AH211" s="65"/>
+      <c r="AI211" s="65"/>
+      <c r="AJ211" s="65"/>
+      <c r="AK211" s="65"/>
+      <c r="AL211" s="65"/>
+      <c r="AM211" s="65"/>
+      <c r="AN211" s="65"/>
+      <c r="AO211" s="65"/>
+      <c r="AP211" s="65"/>
+      <c r="AQ211" s="65"/>
+      <c r="AR211" s="65"/>
+      <c r="AS211" s="65"/>
+      <c r="AT211" s="65"/>
+      <c r="AU211" s="65"/>
+      <c r="AV211" s="65"/>
+      <c r="AW211" s="65"/>
+      <c r="AX211" s="65"/>
+    </row>
+    <row r="212" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="66"/>
+      <c r="B212" s="67">
+        <v>46093</v>
+      </c>
+      <c r="C212" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D212" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E212" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F212" s="75">
+        <v>239278</v>
+      </c>
+      <c r="G212" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="H191" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I191" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J191" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K191" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L191" s="93" t="s">
+      <c r="H212" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I212" s="70">
+        <v>1784.35</v>
+      </c>
+      <c r="J212" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K212" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L212" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="M191" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N191" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O191" s="92"/>
-      <c r="P191" s="97"/>
-      <c r="Q191" s="97"/>
-      <c r="R191" s="98"/>
-      <c r="S191" s="98"/>
-      <c r="T191" s="98"/>
-      <c r="U191" s="98"/>
-      <c r="V191" s="98"/>
-      <c r="W191" s="98"/>
-      <c r="X191" s="98"/>
-      <c r="Y191" s="98"/>
-      <c r="Z191" s="99"/>
-      <c r="AA191" s="99"/>
-      <c r="AB191" s="99"/>
-      <c r="AC191" s="99"/>
-      <c r="AD191" s="99"/>
-      <c r="AE191" s="99"/>
-      <c r="AF191" s="99"/>
-      <c r="AG191" s="99"/>
-      <c r="AH191" s="99"/>
-      <c r="AI191" s="99"/>
-      <c r="AJ191" s="99"/>
-      <c r="AK191" s="99"/>
-      <c r="AL191" s="99"/>
-      <c r="AM191" s="99"/>
-      <c r="AN191" s="99"/>
-      <c r="AO191" s="99"/>
-      <c r="AP191" s="99"/>
-      <c r="AQ191" s="99"/>
-      <c r="AR191" s="99"/>
-      <c r="AS191" s="99"/>
-      <c r="AT191" s="99"/>
-      <c r="AU191" s="99"/>
-      <c r="AV191" s="99"/>
-      <c r="AW191" s="99"/>
-      <c r="AX191" s="99"/>
-    </row>
-    <row r="192" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="90"/>
-      <c r="B192" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C192" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D192" s="92"/>
-      <c r="E192" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F192" s="94">
-        <v>123009</v>
-      </c>
-      <c r="G192" s="93" t="s">
+      <c r="M212" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N212" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O212" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="P212" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q212" s="71"/>
+      <c r="R212" s="64"/>
+      <c r="S212" s="64"/>
+      <c r="T212" s="64"/>
+      <c r="U212" s="64"/>
+      <c r="V212" s="64"/>
+      <c r="W212" s="64"/>
+      <c r="X212" s="64"/>
+      <c r="Y212" s="64"/>
+      <c r="Z212" s="65"/>
+      <c r="AA212" s="65"/>
+      <c r="AB212" s="65"/>
+      <c r="AC212" s="65"/>
+      <c r="AD212" s="65"/>
+      <c r="AE212" s="65"/>
+      <c r="AF212" s="65"/>
+      <c r="AG212" s="65"/>
+      <c r="AH212" s="65"/>
+      <c r="AI212" s="65"/>
+      <c r="AJ212" s="65"/>
+      <c r="AK212" s="65"/>
+      <c r="AL212" s="65"/>
+      <c r="AM212" s="65"/>
+      <c r="AN212" s="65"/>
+      <c r="AO212" s="65"/>
+      <c r="AP212" s="65"/>
+      <c r="AQ212" s="65"/>
+      <c r="AR212" s="65"/>
+      <c r="AS212" s="65"/>
+      <c r="AT212" s="65"/>
+      <c r="AU212" s="65"/>
+      <c r="AV212" s="65"/>
+      <c r="AW212" s="65"/>
+      <c r="AX212" s="65"/>
+    </row>
+    <row r="213" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="66"/>
+      <c r="B213" s="67">
+        <v>46097</v>
+      </c>
+      <c r="C213" s="67">
+        <v>46102</v>
+      </c>
+      <c r="D213" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E213" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F213" s="75">
+        <v>239305</v>
+      </c>
+      <c r="G213" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="H192" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I192" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J192" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K192" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L192" s="93" t="s">
+      <c r="H213" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I213" s="70">
+        <v>1961.23</v>
+      </c>
+      <c r="J213" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K213" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L213" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="M192" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N192" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O192" s="92"/>
-      <c r="P192" s="97"/>
-      <c r="Q192" s="97"/>
-      <c r="R192" s="98"/>
-      <c r="S192" s="98"/>
-      <c r="T192" s="98"/>
-      <c r="U192" s="98"/>
-      <c r="V192" s="98"/>
-      <c r="W192" s="98"/>
-      <c r="X192" s="98"/>
-      <c r="Y192" s="98"/>
-      <c r="Z192" s="99"/>
-      <c r="AA192" s="99"/>
-      <c r="AB192" s="99"/>
-      <c r="AC192" s="99"/>
-      <c r="AD192" s="99"/>
-      <c r="AE192" s="99"/>
-      <c r="AF192" s="99"/>
-      <c r="AG192" s="99"/>
-      <c r="AH192" s="99"/>
-      <c r="AI192" s="99"/>
-      <c r="AJ192" s="99"/>
-      <c r="AK192" s="99"/>
-      <c r="AL192" s="99"/>
-      <c r="AM192" s="99"/>
-      <c r="AN192" s="99"/>
-      <c r="AO192" s="99"/>
-      <c r="AP192" s="99"/>
-      <c r="AQ192" s="99"/>
-      <c r="AR192" s="99"/>
-      <c r="AS192" s="99"/>
-      <c r="AT192" s="99"/>
-      <c r="AU192" s="99"/>
-      <c r="AV192" s="99"/>
-      <c r="AW192" s="99"/>
-      <c r="AX192" s="99"/>
-    </row>
-    <row r="193" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="90"/>
-      <c r="B193" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C193" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D193" s="92"/>
-      <c r="E193" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F193" s="94">
-        <v>123010</v>
-      </c>
-      <c r="G193" s="93" t="s">
+      <c r="M213" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N213" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O213" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="P213" s="73" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q213" s="71"/>
+      <c r="R213" s="64"/>
+      <c r="S213" s="64"/>
+      <c r="T213" s="64"/>
+      <c r="U213" s="64"/>
+      <c r="V213" s="64"/>
+      <c r="W213" s="64"/>
+      <c r="X213" s="64"/>
+      <c r="Y213" s="64"/>
+      <c r="Z213" s="65"/>
+      <c r="AA213" s="65"/>
+      <c r="AB213" s="65"/>
+      <c r="AC213" s="65"/>
+      <c r="AD213" s="65"/>
+      <c r="AE213" s="65"/>
+      <c r="AF213" s="65"/>
+      <c r="AG213" s="65"/>
+      <c r="AH213" s="65"/>
+      <c r="AI213" s="65"/>
+      <c r="AJ213" s="65"/>
+      <c r="AK213" s="65"/>
+      <c r="AL213" s="65"/>
+      <c r="AM213" s="65"/>
+      <c r="AN213" s="65"/>
+      <c r="AO213" s="65"/>
+      <c r="AP213" s="65"/>
+      <c r="AQ213" s="65"/>
+      <c r="AR213" s="65"/>
+      <c r="AS213" s="65"/>
+      <c r="AT213" s="65"/>
+      <c r="AU213" s="65"/>
+      <c r="AV213" s="65"/>
+      <c r="AW213" s="65"/>
+      <c r="AX213" s="65"/>
+    </row>
+    <row r="214" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="66"/>
+      <c r="B214" s="67">
+        <v>46097</v>
+      </c>
+      <c r="C214" s="67">
+        <v>46102</v>
+      </c>
+      <c r="D214" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E214" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F214" s="75">
+        <v>239299</v>
+      </c>
+      <c r="G214" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="H193" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I193" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J193" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K193" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L193" s="93" t="s">
+      <c r="H214" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I214" s="70">
+        <v>1103.23</v>
+      </c>
+      <c r="J214" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K214" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L214" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="M193" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N193" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O193" s="92"/>
-      <c r="P193" s="97"/>
-      <c r="Q193" s="97"/>
-      <c r="R193" s="98"/>
-      <c r="S193" s="98"/>
-      <c r="T193" s="98"/>
-      <c r="U193" s="98"/>
-      <c r="V193" s="98"/>
-      <c r="W193" s="98"/>
-      <c r="X193" s="98"/>
-      <c r="Y193" s="98"/>
-      <c r="Z193" s="99"/>
-      <c r="AA193" s="99"/>
-      <c r="AB193" s="99"/>
-      <c r="AC193" s="99"/>
-      <c r="AD193" s="99"/>
-      <c r="AE193" s="99"/>
-      <c r="AF193" s="99"/>
-      <c r="AG193" s="99"/>
-      <c r="AH193" s="99"/>
-      <c r="AI193" s="99"/>
-      <c r="AJ193" s="99"/>
-      <c r="AK193" s="99"/>
-      <c r="AL193" s="99"/>
-      <c r="AM193" s="99"/>
-      <c r="AN193" s="99"/>
-      <c r="AO193" s="99"/>
-      <c r="AP193" s="99"/>
-      <c r="AQ193" s="99"/>
-      <c r="AR193" s="99"/>
-      <c r="AS193" s="99"/>
-      <c r="AT193" s="99"/>
-      <c r="AU193" s="99"/>
-      <c r="AV193" s="99"/>
-      <c r="AW193" s="99"/>
-      <c r="AX193" s="99"/>
-    </row>
-    <row r="194" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="90"/>
-      <c r="B194" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C194" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D194" s="92"/>
-      <c r="E194" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F194" s="94">
-        <v>123011</v>
-      </c>
-      <c r="G194" s="93" t="s">
+      <c r="M214" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N214" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O214" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="P214" s="73" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q214" s="71"/>
+      <c r="R214" s="64"/>
+      <c r="S214" s="64"/>
+      <c r="T214" s="64"/>
+      <c r="U214" s="64"/>
+      <c r="V214" s="64"/>
+      <c r="W214" s="64"/>
+      <c r="X214" s="64"/>
+      <c r="Y214" s="64"/>
+      <c r="Z214" s="65"/>
+      <c r="AA214" s="65"/>
+      <c r="AB214" s="65"/>
+      <c r="AC214" s="65"/>
+      <c r="AD214" s="65"/>
+      <c r="AE214" s="65"/>
+      <c r="AF214" s="65"/>
+      <c r="AG214" s="65"/>
+      <c r="AH214" s="65"/>
+      <c r="AI214" s="65"/>
+      <c r="AJ214" s="65"/>
+      <c r="AK214" s="65"/>
+      <c r="AL214" s="65"/>
+      <c r="AM214" s="65"/>
+      <c r="AN214" s="65"/>
+      <c r="AO214" s="65"/>
+      <c r="AP214" s="65"/>
+      <c r="AQ214" s="65"/>
+      <c r="AR214" s="65"/>
+      <c r="AS214" s="65"/>
+      <c r="AT214" s="65"/>
+      <c r="AU214" s="65"/>
+      <c r="AV214" s="65"/>
+      <c r="AW214" s="65"/>
+      <c r="AX214" s="65"/>
+    </row>
+    <row r="215" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="66"/>
+      <c r="B215" s="67">
+        <v>46097</v>
+      </c>
+      <c r="C215" s="67">
+        <v>46102</v>
+      </c>
+      <c r="D215" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E215" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F215" s="75">
+        <v>239303</v>
+      </c>
+      <c r="G215" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="H194" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I194" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J194" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K194" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L194" s="93" t="s">
+      <c r="H215" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I215" s="70">
+        <v>2363.39</v>
+      </c>
+      <c r="J215" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K215" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L215" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="M194" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N194" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O194" s="92"/>
-      <c r="P194" s="97"/>
-      <c r="Q194" s="97"/>
-      <c r="R194" s="98"/>
-      <c r="S194" s="98"/>
-      <c r="T194" s="98"/>
-      <c r="U194" s="98"/>
-      <c r="V194" s="98"/>
-      <c r="W194" s="98"/>
-      <c r="X194" s="98"/>
-      <c r="Y194" s="98"/>
-      <c r="Z194" s="99"/>
-      <c r="AA194" s="99"/>
-      <c r="AB194" s="99"/>
-      <c r="AC194" s="99"/>
-      <c r="AD194" s="99"/>
-      <c r="AE194" s="99"/>
-      <c r="AF194" s="99"/>
-      <c r="AG194" s="99"/>
-      <c r="AH194" s="99"/>
-      <c r="AI194" s="99"/>
-      <c r="AJ194" s="99"/>
-      <c r="AK194" s="99"/>
-      <c r="AL194" s="99"/>
-      <c r="AM194" s="99"/>
-      <c r="AN194" s="99"/>
-      <c r="AO194" s="99"/>
-      <c r="AP194" s="99"/>
-      <c r="AQ194" s="99"/>
-      <c r="AR194" s="99"/>
-      <c r="AS194" s="99"/>
-      <c r="AT194" s="99"/>
-      <c r="AU194" s="99"/>
-      <c r="AV194" s="99"/>
-      <c r="AW194" s="99"/>
-      <c r="AX194" s="99"/>
-    </row>
-    <row r="195" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="90"/>
-      <c r="B195" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C195" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D195" s="92"/>
-      <c r="E195" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F195" s="94">
-        <v>123012</v>
-      </c>
-      <c r="G195" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H195" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I195" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J195" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K195" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L195" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M195" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N195" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O195" s="92"/>
-      <c r="P195" s="97"/>
-      <c r="Q195" s="97"/>
-      <c r="R195" s="98"/>
-      <c r="S195" s="98"/>
-      <c r="T195" s="98"/>
-      <c r="U195" s="98"/>
-      <c r="V195" s="98"/>
-      <c r="W195" s="98"/>
-      <c r="X195" s="98"/>
-      <c r="Y195" s="98"/>
-      <c r="Z195" s="99"/>
-      <c r="AA195" s="99"/>
-      <c r="AB195" s="99"/>
-      <c r="AC195" s="99"/>
-      <c r="AD195" s="99"/>
-      <c r="AE195" s="99"/>
-      <c r="AF195" s="99"/>
-      <c r="AG195" s="99"/>
-      <c r="AH195" s="99"/>
-      <c r="AI195" s="99"/>
-      <c r="AJ195" s="99"/>
-      <c r="AK195" s="99"/>
-      <c r="AL195" s="99"/>
-      <c r="AM195" s="99"/>
-      <c r="AN195" s="99"/>
-      <c r="AO195" s="99"/>
-      <c r="AP195" s="99"/>
-      <c r="AQ195" s="99"/>
-      <c r="AR195" s="99"/>
-      <c r="AS195" s="99"/>
-      <c r="AT195" s="99"/>
-      <c r="AU195" s="99"/>
-      <c r="AV195" s="99"/>
-      <c r="AW195" s="99"/>
-      <c r="AX195" s="99"/>
-    </row>
-    <row r="196" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="90"/>
-      <c r="B196" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C196" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D196" s="92"/>
-      <c r="E196" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F196" s="94">
-        <v>123013</v>
-      </c>
-      <c r="G196" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H196" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I196" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J196" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K196" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L196" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M196" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N196" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O196" s="92"/>
-      <c r="P196" s="97"/>
-      <c r="Q196" s="97"/>
-      <c r="R196" s="98"/>
-      <c r="S196" s="98"/>
-      <c r="T196" s="98"/>
-      <c r="U196" s="98"/>
-      <c r="V196" s="98"/>
-      <c r="W196" s="98"/>
-      <c r="X196" s="98"/>
-      <c r="Y196" s="98"/>
-      <c r="Z196" s="99"/>
-      <c r="AA196" s="99"/>
-      <c r="AB196" s="99"/>
-      <c r="AC196" s="99"/>
-      <c r="AD196" s="99"/>
-      <c r="AE196" s="99"/>
-      <c r="AF196" s="99"/>
-      <c r="AG196" s="99"/>
-      <c r="AH196" s="99"/>
-      <c r="AI196" s="99"/>
-      <c r="AJ196" s="99"/>
-      <c r="AK196" s="99"/>
-      <c r="AL196" s="99"/>
-      <c r="AM196" s="99"/>
-      <c r="AN196" s="99"/>
-      <c r="AO196" s="99"/>
-      <c r="AP196" s="99"/>
-      <c r="AQ196" s="99"/>
-      <c r="AR196" s="99"/>
-      <c r="AS196" s="99"/>
-      <c r="AT196" s="99"/>
-      <c r="AU196" s="99"/>
-      <c r="AV196" s="99"/>
-      <c r="AW196" s="99"/>
-      <c r="AX196" s="99"/>
-    </row>
-    <row r="197" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="90"/>
-      <c r="B197" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C197" s="91">
-        <v>46094</v>
-      </c>
-      <c r="D197" s="92"/>
-      <c r="E197" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F197" s="94">
-        <v>123014</v>
-      </c>
-      <c r="G197" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H197" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I197" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J197" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K197" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L197" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M197" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N197" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O197" s="92"/>
-      <c r="P197" s="97"/>
-      <c r="Q197" s="97"/>
-      <c r="R197" s="98"/>
-      <c r="S197" s="98"/>
-      <c r="T197" s="98"/>
-      <c r="U197" s="98"/>
-      <c r="V197" s="98"/>
-      <c r="W197" s="98"/>
-      <c r="X197" s="98"/>
-      <c r="Y197" s="98"/>
-      <c r="Z197" s="99"/>
-      <c r="AA197" s="99"/>
-      <c r="AB197" s="99"/>
-      <c r="AC197" s="99"/>
-      <c r="AD197" s="99"/>
-      <c r="AE197" s="99"/>
-      <c r="AF197" s="99"/>
-      <c r="AG197" s="99"/>
-      <c r="AH197" s="99"/>
-      <c r="AI197" s="99"/>
-      <c r="AJ197" s="99"/>
-      <c r="AK197" s="99"/>
-      <c r="AL197" s="99"/>
-      <c r="AM197" s="99"/>
-      <c r="AN197" s="99"/>
-      <c r="AO197" s="99"/>
-      <c r="AP197" s="99"/>
-      <c r="AQ197" s="99"/>
-      <c r="AR197" s="99"/>
-      <c r="AS197" s="99"/>
-      <c r="AT197" s="99"/>
-      <c r="AU197" s="99"/>
-      <c r="AV197" s="99"/>
-      <c r="AW197" s="99"/>
-      <c r="AX197" s="99"/>
-    </row>
-    <row r="198" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="90"/>
-      <c r="B198" s="91">
-        <v>46093</v>
-      </c>
-      <c r="C198" s="91">
-        <v>46095</v>
-      </c>
-      <c r="D198" s="92"/>
-      <c r="E198" s="93" t="s">
-        <v>30</v>
-      </c>
-      <c r="F198" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="G198" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H198" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="I198" s="95">
-        <v>69186.05</v>
-      </c>
-      <c r="J198" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K198" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="L198" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M198" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N198" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O198" s="92"/>
-      <c r="P198" s="96" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q198" s="97"/>
-      <c r="R198" s="98"/>
-      <c r="S198" s="98"/>
-      <c r="T198" s="98"/>
-      <c r="U198" s="98"/>
-      <c r="V198" s="98"/>
-      <c r="W198" s="98"/>
-      <c r="X198" s="98"/>
-      <c r="Y198" s="98"/>
-      <c r="Z198" s="99"/>
-      <c r="AA198" s="99"/>
-      <c r="AB198" s="99"/>
-      <c r="AC198" s="99"/>
-      <c r="AD198" s="99"/>
-      <c r="AE198" s="99"/>
-      <c r="AF198" s="99"/>
-      <c r="AG198" s="99"/>
-      <c r="AH198" s="99"/>
-      <c r="AI198" s="99"/>
-      <c r="AJ198" s="99"/>
-      <c r="AK198" s="99"/>
-      <c r="AL198" s="99"/>
-      <c r="AM198" s="99"/>
-      <c r="AN198" s="99"/>
-      <c r="AO198" s="99"/>
-      <c r="AP198" s="99"/>
-      <c r="AQ198" s="99"/>
-      <c r="AR198" s="99"/>
-      <c r="AS198" s="99"/>
-      <c r="AT198" s="99"/>
-      <c r="AU198" s="99"/>
-      <c r="AV198" s="99"/>
-      <c r="AW198" s="99"/>
-      <c r="AX198" s="99"/>
-    </row>
-    <row r="199" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="90"/>
-      <c r="B199" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C199" s="91">
-        <v>46096</v>
-      </c>
-      <c r="D199" s="92"/>
-      <c r="E199" s="93" t="s">
-        <v>35</v>
-      </c>
-      <c r="F199" s="92"/>
-      <c r="G199" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="H199" s="93" t="s">
-        <v>37</v>
-      </c>
-      <c r="I199" s="95">
-        <v>91850</v>
-      </c>
-      <c r="J199" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K199" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="L199" s="93" t="s">
-        <v>21</v>
-      </c>
-      <c r="M199" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N199" s="93" t="s">
-        <v>23</v>
-      </c>
-      <c r="O199" s="92"/>
-      <c r="P199" s="97"/>
-      <c r="Q199" s="96" t="s">
-        <v>39</v>
-      </c>
-      <c r="R199" s="98"/>
-      <c r="S199" s="98"/>
-      <c r="T199" s="98"/>
-      <c r="U199" s="98"/>
-      <c r="V199" s="98"/>
-      <c r="W199" s="98"/>
-      <c r="X199" s="98"/>
-      <c r="Y199" s="98"/>
-      <c r="Z199" s="99"/>
-      <c r="AA199" s="99"/>
-      <c r="AB199" s="99"/>
-      <c r="AC199" s="99"/>
-      <c r="AD199" s="99"/>
-      <c r="AE199" s="99"/>
-      <c r="AF199" s="99"/>
-      <c r="AG199" s="99"/>
-      <c r="AH199" s="99"/>
-      <c r="AI199" s="99"/>
-      <c r="AJ199" s="99"/>
-      <c r="AK199" s="99"/>
-      <c r="AL199" s="99"/>
-      <c r="AM199" s="99"/>
-      <c r="AN199" s="99"/>
-      <c r="AO199" s="99"/>
-      <c r="AP199" s="99"/>
-      <c r="AQ199" s="99"/>
-      <c r="AR199" s="99"/>
-      <c r="AS199" s="99"/>
-      <c r="AT199" s="99"/>
-      <c r="AU199" s="99"/>
-      <c r="AV199" s="99"/>
-      <c r="AW199" s="99"/>
-      <c r="AX199" s="99"/>
-    </row>
-    <row r="200" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="90"/>
-      <c r="B200" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C200" s="91">
-        <v>46096</v>
-      </c>
-      <c r="D200" s="92"/>
-      <c r="E200" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="F200" s="92"/>
-      <c r="G200" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="H200" s="93" t="s">
-        <v>186</v>
-      </c>
-      <c r="I200" s="95">
-        <v>87000</v>
-      </c>
-      <c r="J200" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K200" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="L200" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M200" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N200" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O200" s="92"/>
-      <c r="P200" s="97"/>
-      <c r="Q200" s="97"/>
-      <c r="R200" s="99"/>
-      <c r="S200" s="99"/>
-      <c r="T200" s="99"/>
-      <c r="U200" s="99"/>
-      <c r="V200" s="99"/>
-      <c r="W200" s="99"/>
-      <c r="X200" s="99"/>
-      <c r="Y200" s="99"/>
-      <c r="Z200" s="99"/>
-      <c r="AA200" s="99"/>
-      <c r="AB200" s="99"/>
-      <c r="AC200" s="99"/>
-      <c r="AD200" s="99"/>
-      <c r="AE200" s="99"/>
-      <c r="AF200" s="99"/>
-      <c r="AG200" s="99"/>
-      <c r="AH200" s="99"/>
-      <c r="AI200" s="99"/>
-      <c r="AJ200" s="99"/>
-      <c r="AK200" s="99"/>
-      <c r="AL200" s="99"/>
-      <c r="AM200" s="99"/>
-      <c r="AN200" s="99"/>
-      <c r="AO200" s="99"/>
-      <c r="AP200" s="99"/>
-      <c r="AQ200" s="99"/>
-      <c r="AR200" s="99"/>
-      <c r="AS200" s="99"/>
-      <c r="AT200" s="99"/>
-      <c r="AU200" s="99"/>
-      <c r="AV200" s="99"/>
-      <c r="AW200" s="99"/>
-      <c r="AX200" s="99"/>
-    </row>
-    <row r="201" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="90"/>
-      <c r="B201" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C201" s="91">
-        <v>46097</v>
-      </c>
-      <c r="D201" s="92"/>
-      <c r="E201" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F201" s="94">
-        <v>123036</v>
-      </c>
-      <c r="G201" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H201" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I201" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J201" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K201" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L201" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M201" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N201" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O201" s="92"/>
-      <c r="P201" s="97"/>
-      <c r="Q201" s="97"/>
-      <c r="R201" s="98"/>
-      <c r="S201" s="98"/>
-      <c r="T201" s="98"/>
-      <c r="U201" s="98"/>
-      <c r="V201" s="98"/>
-      <c r="W201" s="98"/>
-      <c r="X201" s="98"/>
-      <c r="Y201" s="98"/>
-      <c r="Z201" s="99"/>
-      <c r="AA201" s="99"/>
-      <c r="AB201" s="99"/>
-      <c r="AC201" s="99"/>
-      <c r="AD201" s="99"/>
-      <c r="AE201" s="99"/>
-      <c r="AF201" s="99"/>
-      <c r="AG201" s="99"/>
-      <c r="AH201" s="99"/>
-      <c r="AI201" s="99"/>
-      <c r="AJ201" s="99"/>
-      <c r="AK201" s="99"/>
-      <c r="AL201" s="99"/>
-      <c r="AM201" s="99"/>
-      <c r="AN201" s="99"/>
-      <c r="AO201" s="99"/>
-      <c r="AP201" s="99"/>
-      <c r="AQ201" s="99"/>
-      <c r="AR201" s="99"/>
-      <c r="AS201" s="99"/>
-      <c r="AT201" s="99"/>
-      <c r="AU201" s="99"/>
-      <c r="AV201" s="99"/>
-      <c r="AW201" s="99"/>
-      <c r="AX201" s="99"/>
-    </row>
-    <row r="202" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="90"/>
-      <c r="B202" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C202" s="91">
-        <v>46097</v>
-      </c>
-      <c r="D202" s="92"/>
-      <c r="E202" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F202" s="94">
-        <v>123037</v>
-      </c>
-      <c r="G202" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H202" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I202" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J202" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K202" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L202" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M202" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N202" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O202" s="92"/>
-      <c r="P202" s="97"/>
-      <c r="Q202" s="97"/>
-      <c r="R202" s="98"/>
-      <c r="S202" s="98"/>
-      <c r="T202" s="98"/>
-      <c r="U202" s="98"/>
-      <c r="V202" s="98"/>
-      <c r="W202" s="98"/>
-      <c r="X202" s="98"/>
-      <c r="Y202" s="98"/>
-      <c r="Z202" s="99"/>
-      <c r="AA202" s="99"/>
-      <c r="AB202" s="99"/>
-      <c r="AC202" s="99"/>
-      <c r="AD202" s="99"/>
-      <c r="AE202" s="99"/>
-      <c r="AF202" s="99"/>
-      <c r="AG202" s="99"/>
-      <c r="AH202" s="99"/>
-      <c r="AI202" s="99"/>
-      <c r="AJ202" s="99"/>
-      <c r="AK202" s="99"/>
-      <c r="AL202" s="99"/>
-      <c r="AM202" s="99"/>
-      <c r="AN202" s="99"/>
-      <c r="AO202" s="99"/>
-      <c r="AP202" s="99"/>
-      <c r="AQ202" s="99"/>
-      <c r="AR202" s="99"/>
-      <c r="AS202" s="99"/>
-      <c r="AT202" s="99"/>
-      <c r="AU202" s="99"/>
-      <c r="AV202" s="99"/>
-      <c r="AW202" s="99"/>
-      <c r="AX202" s="99"/>
-    </row>
-    <row r="203" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="90"/>
-      <c r="B203" s="91">
-        <v>46079</v>
-      </c>
-      <c r="C203" s="91">
-        <v>46097</v>
-      </c>
-      <c r="D203" s="92"/>
-      <c r="E203" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="F203" s="94">
-        <v>123038</v>
-      </c>
-      <c r="G203" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H203" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="I203" s="95">
-        <v>27943.03</v>
-      </c>
-      <c r="J203" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K203" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="L203" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M203" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N203" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O203" s="92"/>
-      <c r="P203" s="97"/>
-      <c r="Q203" s="97"/>
-      <c r="R203" s="98"/>
-      <c r="S203" s="98"/>
-      <c r="T203" s="98"/>
-      <c r="U203" s="98"/>
-      <c r="V203" s="98"/>
-      <c r="W203" s="98"/>
-      <c r="X203" s="98"/>
-      <c r="Y203" s="98"/>
-      <c r="Z203" s="99"/>
-      <c r="AA203" s="99"/>
-      <c r="AB203" s="99"/>
-      <c r="AC203" s="99"/>
-      <c r="AD203" s="99"/>
-      <c r="AE203" s="99"/>
-      <c r="AF203" s="99"/>
-      <c r="AG203" s="99"/>
-      <c r="AH203" s="99"/>
-      <c r="AI203" s="99"/>
-      <c r="AJ203" s="99"/>
-      <c r="AK203" s="99"/>
-      <c r="AL203" s="99"/>
-      <c r="AM203" s="99"/>
-      <c r="AN203" s="99"/>
-      <c r="AO203" s="99"/>
-      <c r="AP203" s="99"/>
-      <c r="AQ203" s="99"/>
-      <c r="AR203" s="99"/>
-      <c r="AS203" s="99"/>
-      <c r="AT203" s="99"/>
-      <c r="AU203" s="99"/>
-      <c r="AV203" s="99"/>
-      <c r="AW203" s="99"/>
-      <c r="AX203" s="99"/>
-    </row>
-    <row r="204" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="90"/>
-      <c r="B204" s="91">
-        <v>46093</v>
-      </c>
-      <c r="C204" s="91">
-        <v>46099</v>
-      </c>
-      <c r="D204" s="92"/>
-      <c r="E204" s="93" t="s">
-        <v>17</v>
-      </c>
-      <c r="F204" s="94">
-        <v>239234</v>
-      </c>
-      <c r="G204" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H204" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="I204" s="95">
-        <v>1993.24</v>
-      </c>
-      <c r="J204" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K204" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="L204" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M204" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N204" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O204" s="93" t="s">
+      <c r="M215" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N215" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O215" s="68" t="s">
         <v>246</v>
       </c>
-      <c r="P204" s="96" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q204" s="97"/>
-      <c r="R204" s="98"/>
-      <c r="S204" s="98"/>
-      <c r="T204" s="98"/>
-      <c r="U204" s="98"/>
-      <c r="V204" s="98"/>
-      <c r="W204" s="98"/>
-      <c r="X204" s="98"/>
-      <c r="Y204" s="98"/>
-      <c r="Z204" s="99"/>
-      <c r="AA204" s="99"/>
-      <c r="AB204" s="99"/>
-      <c r="AC204" s="99"/>
-      <c r="AD204" s="99"/>
-      <c r="AE204" s="99"/>
-      <c r="AF204" s="99"/>
-      <c r="AG204" s="99"/>
-      <c r="AH204" s="99"/>
-      <c r="AI204" s="99"/>
-      <c r="AJ204" s="99"/>
-      <c r="AK204" s="99"/>
-      <c r="AL204" s="99"/>
-      <c r="AM204" s="99"/>
-      <c r="AN204" s="99"/>
-      <c r="AO204" s="99"/>
-      <c r="AP204" s="99"/>
-      <c r="AQ204" s="99"/>
-      <c r="AR204" s="99"/>
-      <c r="AS204" s="99"/>
-      <c r="AT204" s="99"/>
-      <c r="AU204" s="99"/>
-      <c r="AV204" s="99"/>
-      <c r="AW204" s="99"/>
-      <c r="AX204" s="99"/>
-    </row>
-    <row r="205" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="90"/>
-      <c r="B205" s="91">
-        <v>46093</v>
-      </c>
-      <c r="C205" s="91">
-        <v>46099</v>
-      </c>
-      <c r="D205" s="92"/>
-      <c r="E205" s="93" t="s">
-        <v>17</v>
-      </c>
-      <c r="F205" s="94">
-        <v>239250</v>
-      </c>
-      <c r="G205" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H205" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="I205" s="95">
-        <v>2714.34</v>
-      </c>
-      <c r="J205" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K205" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="L205" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M205" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N205" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O205" s="93" t="s">
-        <v>246</v>
-      </c>
-      <c r="P205" s="96" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q205" s="97"/>
-      <c r="R205" s="98"/>
-      <c r="S205" s="98"/>
-      <c r="T205" s="98"/>
-      <c r="U205" s="98"/>
-      <c r="V205" s="98"/>
-      <c r="W205" s="98"/>
-      <c r="X205" s="98"/>
-      <c r="Y205" s="98"/>
-      <c r="Z205" s="99"/>
-      <c r="AA205" s="99"/>
-      <c r="AB205" s="99"/>
-      <c r="AC205" s="99"/>
-      <c r="AD205" s="99"/>
-      <c r="AE205" s="99"/>
-      <c r="AF205" s="99"/>
-      <c r="AG205" s="99"/>
-      <c r="AH205" s="99"/>
-      <c r="AI205" s="99"/>
-      <c r="AJ205" s="99"/>
-      <c r="AK205" s="99"/>
-      <c r="AL205" s="99"/>
-      <c r="AM205" s="99"/>
-      <c r="AN205" s="99"/>
-      <c r="AO205" s="99"/>
-      <c r="AP205" s="99"/>
-      <c r="AQ205" s="99"/>
-      <c r="AR205" s="99"/>
-      <c r="AS205" s="99"/>
-      <c r="AT205" s="99"/>
-      <c r="AU205" s="99"/>
-      <c r="AV205" s="99"/>
-      <c r="AW205" s="99"/>
-      <c r="AX205" s="99"/>
-    </row>
-    <row r="206" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="90"/>
-      <c r="B206" s="91">
-        <v>46093</v>
-      </c>
-      <c r="C206" s="91">
-        <v>46099</v>
-      </c>
-      <c r="D206" s="92"/>
-      <c r="E206" s="93" t="s">
-        <v>30</v>
-      </c>
-      <c r="F206" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="G206" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H206" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="I206" s="95">
-        <v>41034</v>
-      </c>
-      <c r="J206" s="93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K206" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="L206" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M206" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="N206" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="O206" s="93" t="s">
-        <v>257</v>
-      </c>
-      <c r="P206" s="96" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q206" s="97"/>
-      <c r="R206" s="98"/>
-      <c r="S206" s="98"/>
-      <c r="T206" s="98"/>
-      <c r="U206" s="98"/>
-      <c r="V206" s="98"/>
-      <c r="W206" s="98"/>
-      <c r="X206" s="98"/>
-      <c r="Y206" s="98"/>
-      <c r="Z206" s="99"/>
-      <c r="AA206" s="99"/>
-      <c r="AB206" s="99"/>
-      <c r="AC206" s="99"/>
-      <c r="AD206" s="99"/>
-      <c r="AE206" s="99"/>
-      <c r="AF206" s="99"/>
-      <c r="AG206" s="99"/>
-      <c r="AH206" s="99"/>
-      <c r="AI206" s="99"/>
-      <c r="AJ206" s="99"/>
-      <c r="AK206" s="99"/>
-      <c r="AL206" s="99"/>
-      <c r="AM206" s="99"/>
-      <c r="AN206" s="99"/>
-      <c r="AO206" s="99"/>
-      <c r="AP206" s="99"/>
-      <c r="AQ206" s="99"/>
-      <c r="AR206" s="99"/>
-      <c r="AS206" s="99"/>
-      <c r="AT206" s="99"/>
-      <c r="AU206" s="99"/>
-      <c r="AV206" s="99"/>
-      <c r="AW206" s="99"/>
-      <c r="AX206" s="99"/>
-    </row>
-    <row r="207" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="76"/>
-      <c r="B207" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C207" s="77">
-        <v>46098</v>
-      </c>
-      <c r="D207" s="81"/>
-      <c r="E207" s="78" t="s">
-        <v>96</v>
-      </c>
-      <c r="F207" s="81"/>
-      <c r="G207" s="78" t="s">
-        <v>36</v>
-      </c>
-      <c r="H207" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="I207" s="80">
-        <v>357721.76</v>
-      </c>
-      <c r="J207" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K207" s="78" t="s">
-        <v>97</v>
-      </c>
-      <c r="L207" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M207" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N207" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O207" s="81"/>
-      <c r="P207" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q207" s="85" t="s">
-        <v>39</v>
-      </c>
-      <c r="R207" s="83"/>
-      <c r="S207" s="83"/>
-      <c r="T207" s="83"/>
-      <c r="U207" s="83"/>
-      <c r="V207" s="83"/>
-      <c r="W207" s="83"/>
-      <c r="X207" s="83"/>
-      <c r="Y207" s="83"/>
-      <c r="Z207" s="84"/>
-      <c r="AA207" s="84"/>
-      <c r="AB207" s="84"/>
-      <c r="AC207" s="84"/>
-      <c r="AD207" s="84"/>
-      <c r="AE207" s="84"/>
-      <c r="AF207" s="84"/>
-      <c r="AG207" s="84"/>
-      <c r="AH207" s="84"/>
-      <c r="AI207" s="84"/>
-      <c r="AJ207" s="84"/>
-      <c r="AK207" s="84"/>
-      <c r="AL207" s="84"/>
-      <c r="AM207" s="84"/>
-      <c r="AN207" s="84"/>
-      <c r="AO207" s="84"/>
-      <c r="AP207" s="84"/>
-      <c r="AQ207" s="84"/>
-      <c r="AR207" s="84"/>
-      <c r="AS207" s="84"/>
-      <c r="AT207" s="84"/>
-      <c r="AU207" s="84"/>
-      <c r="AV207" s="84"/>
-      <c r="AW207" s="84"/>
-      <c r="AX207" s="84"/>
-    </row>
-    <row r="208" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="76"/>
-      <c r="B208" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C208" s="77">
-        <v>46100</v>
-      </c>
-      <c r="D208" s="81"/>
-      <c r="E208" s="78" t="s">
-        <v>150</v>
-      </c>
-      <c r="F208" s="79" t="s">
-        <v>151</v>
-      </c>
-      <c r="G208" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H208" s="78" t="s">
-        <v>152</v>
-      </c>
-      <c r="I208" s="80">
-        <v>163.96</v>
-      </c>
-      <c r="J208" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K208" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L208" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M208" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N208" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O208" s="81"/>
-      <c r="P208" s="82"/>
-      <c r="Q208" s="82"/>
-      <c r="R208" s="83"/>
-      <c r="S208" s="83"/>
-      <c r="T208" s="83"/>
-      <c r="U208" s="83"/>
-      <c r="V208" s="83"/>
-      <c r="W208" s="83"/>
-      <c r="X208" s="83"/>
-      <c r="Y208" s="83"/>
-      <c r="Z208" s="84"/>
-      <c r="AA208" s="84"/>
-      <c r="AB208" s="84"/>
-      <c r="AC208" s="84"/>
-      <c r="AD208" s="84"/>
-      <c r="AE208" s="84"/>
-      <c r="AF208" s="84"/>
-      <c r="AG208" s="84"/>
-      <c r="AH208" s="84"/>
-      <c r="AI208" s="84"/>
-      <c r="AJ208" s="84"/>
-      <c r="AK208" s="84"/>
-      <c r="AL208" s="84"/>
-      <c r="AM208" s="84"/>
-      <c r="AN208" s="84"/>
-      <c r="AO208" s="84"/>
-      <c r="AP208" s="84"/>
-      <c r="AQ208" s="84"/>
-      <c r="AR208" s="84"/>
-      <c r="AS208" s="84"/>
-      <c r="AT208" s="84"/>
-      <c r="AU208" s="84"/>
-      <c r="AV208" s="84"/>
-      <c r="AW208" s="84"/>
-      <c r="AX208" s="84"/>
-    </row>
-    <row r="209" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="76"/>
-      <c r="B209" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C209" s="77">
-        <v>46100</v>
-      </c>
-      <c r="D209" s="81"/>
-      <c r="E209" s="78" t="s">
-        <v>66</v>
-      </c>
-      <c r="F209" s="79">
-        <v>453494</v>
-      </c>
-      <c r="G209" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H209" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I209" s="80">
-        <v>10079.950000000001</v>
-      </c>
-      <c r="J209" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K209" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L209" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M209" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N209" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O209" s="81"/>
-      <c r="P209" s="82"/>
-      <c r="Q209" s="82"/>
-      <c r="R209" s="83"/>
-      <c r="S209" s="83"/>
-      <c r="T209" s="83"/>
-      <c r="U209" s="83"/>
-      <c r="V209" s="83"/>
-      <c r="W209" s="83"/>
-      <c r="X209" s="83"/>
-      <c r="Y209" s="83"/>
-      <c r="Z209" s="84"/>
-      <c r="AA209" s="84"/>
-      <c r="AB209" s="84"/>
-      <c r="AC209" s="84"/>
-      <c r="AD209" s="84"/>
-      <c r="AE209" s="84"/>
-      <c r="AF209" s="84"/>
-      <c r="AG209" s="84"/>
-      <c r="AH209" s="84"/>
-      <c r="AI209" s="84"/>
-      <c r="AJ209" s="84"/>
-      <c r="AK209" s="84"/>
-      <c r="AL209" s="84"/>
-      <c r="AM209" s="84"/>
-      <c r="AN209" s="84"/>
-      <c r="AO209" s="84"/>
-      <c r="AP209" s="84"/>
-      <c r="AQ209" s="84"/>
-      <c r="AR209" s="84"/>
-      <c r="AS209" s="84"/>
-      <c r="AT209" s="84"/>
-      <c r="AU209" s="84"/>
-      <c r="AV209" s="84"/>
-      <c r="AW209" s="84"/>
-      <c r="AX209" s="84"/>
-    </row>
-    <row r="210" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="76"/>
-      <c r="B210" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C210" s="77">
-        <v>46100</v>
-      </c>
-      <c r="D210" s="81"/>
-      <c r="E210" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="F210" s="79">
-        <v>264272</v>
-      </c>
-      <c r="G210" s="78" t="s">
-        <v>52</v>
-      </c>
-      <c r="H210" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="I210" s="80">
-        <v>3452.46</v>
-      </c>
-      <c r="J210" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K210" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L210" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M210" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N210" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O210" s="81"/>
-      <c r="P210" s="82"/>
-      <c r="Q210" s="82"/>
-      <c r="R210" s="83"/>
-      <c r="S210" s="83"/>
-      <c r="T210" s="83"/>
-      <c r="U210" s="83"/>
-      <c r="V210" s="83"/>
-      <c r="W210" s="83"/>
-      <c r="X210" s="83"/>
-      <c r="Y210" s="83"/>
-      <c r="Z210" s="84"/>
-      <c r="AA210" s="84"/>
-      <c r="AB210" s="84"/>
-      <c r="AC210" s="84"/>
-      <c r="AD210" s="84"/>
-      <c r="AE210" s="84"/>
-      <c r="AF210" s="84"/>
-      <c r="AG210" s="84"/>
-      <c r="AH210" s="84"/>
-      <c r="AI210" s="84"/>
-      <c r="AJ210" s="84"/>
-      <c r="AK210" s="84"/>
-      <c r="AL210" s="84"/>
-      <c r="AM210" s="84"/>
-      <c r="AN210" s="84"/>
-      <c r="AO210" s="84"/>
-      <c r="AP210" s="84"/>
-      <c r="AQ210" s="84"/>
-      <c r="AR210" s="84"/>
-      <c r="AS210" s="84"/>
-      <c r="AT210" s="84"/>
-      <c r="AU210" s="84"/>
-      <c r="AV210" s="84"/>
-      <c r="AW210" s="84"/>
-      <c r="AX210" s="84"/>
-    </row>
-    <row r="211" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="76"/>
-      <c r="B211" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C211" s="77">
-        <v>46100</v>
-      </c>
-      <c r="D211" s="81"/>
-      <c r="E211" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="F211" s="79">
-        <v>268025</v>
-      </c>
-      <c r="G211" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H211" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="I211" s="80">
-        <v>17864.88</v>
-      </c>
-      <c r="J211" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K211" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L211" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M211" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N211" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O211" s="81"/>
-      <c r="P211" s="82"/>
-      <c r="Q211" s="82"/>
-      <c r="R211" s="83"/>
-      <c r="S211" s="83"/>
-      <c r="T211" s="83"/>
-      <c r="U211" s="83"/>
-      <c r="V211" s="83"/>
-      <c r="W211" s="83"/>
-      <c r="X211" s="83"/>
-      <c r="Y211" s="83"/>
-      <c r="Z211" s="84"/>
-      <c r="AA211" s="84"/>
-      <c r="AB211" s="84"/>
-      <c r="AC211" s="84"/>
-      <c r="AD211" s="84"/>
-      <c r="AE211" s="84"/>
-      <c r="AF211" s="84"/>
-      <c r="AG211" s="84"/>
-      <c r="AH211" s="84"/>
-      <c r="AI211" s="84"/>
-      <c r="AJ211" s="84"/>
-      <c r="AK211" s="84"/>
-      <c r="AL211" s="84"/>
-      <c r="AM211" s="84"/>
-      <c r="AN211" s="84"/>
-      <c r="AO211" s="84"/>
-      <c r="AP211" s="84"/>
-      <c r="AQ211" s="84"/>
-      <c r="AR211" s="84"/>
-      <c r="AS211" s="84"/>
-      <c r="AT211" s="84"/>
-      <c r="AU211" s="84"/>
-      <c r="AV211" s="84"/>
-      <c r="AW211" s="84"/>
-      <c r="AX211" s="84"/>
-    </row>
-    <row r="212" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="76"/>
-      <c r="B212" s="77">
-        <v>46093</v>
-      </c>
-      <c r="C212" s="77">
-        <v>46100</v>
-      </c>
-      <c r="D212" s="81"/>
-      <c r="E212" s="78" t="s">
-        <v>154</v>
-      </c>
-      <c r="F212" s="79">
-        <v>924426</v>
-      </c>
-      <c r="G212" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H212" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="I212" s="80">
-        <v>7298.44</v>
-      </c>
-      <c r="J212" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K212" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L212" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M212" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N212" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O212" s="81"/>
-      <c r="P212" s="82"/>
-      <c r="Q212" s="82"/>
-      <c r="R212" s="83"/>
-      <c r="S212" s="83"/>
-      <c r="T212" s="83"/>
-      <c r="U212" s="83"/>
-      <c r="V212" s="83"/>
-      <c r="W212" s="83"/>
-      <c r="X212" s="83"/>
-      <c r="Y212" s="83"/>
-      <c r="Z212" s="84"/>
-      <c r="AA212" s="84"/>
-      <c r="AB212" s="84"/>
-      <c r="AC212" s="84"/>
-      <c r="AD212" s="84"/>
-      <c r="AE212" s="84"/>
-      <c r="AF212" s="84"/>
-      <c r="AG212" s="84"/>
-      <c r="AH212" s="84"/>
-      <c r="AI212" s="84"/>
-      <c r="AJ212" s="84"/>
-      <c r="AK212" s="84"/>
-      <c r="AL212" s="84"/>
-      <c r="AM212" s="84"/>
-      <c r="AN212" s="84"/>
-      <c r="AO212" s="84"/>
-      <c r="AP212" s="84"/>
-      <c r="AQ212" s="84"/>
-      <c r="AR212" s="84"/>
-      <c r="AS212" s="84"/>
-      <c r="AT212" s="84"/>
-      <c r="AU212" s="84"/>
-      <c r="AV212" s="84"/>
-      <c r="AW212" s="84"/>
-      <c r="AX212" s="84"/>
-    </row>
-    <row r="213" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="76"/>
-      <c r="B213" s="77">
-        <v>46093</v>
-      </c>
-      <c r="C213" s="77">
-        <v>46100</v>
-      </c>
-      <c r="D213" s="81"/>
-      <c r="E213" s="78" t="s">
-        <v>155</v>
-      </c>
-      <c r="F213" s="79">
-        <v>2295</v>
-      </c>
-      <c r="G213" s="78" t="s">
-        <v>52</v>
-      </c>
-      <c r="H213" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="I213" s="80">
-        <v>909.15</v>
-      </c>
-      <c r="J213" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K213" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L213" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M213" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N213" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O213" s="81"/>
-      <c r="P213" s="82"/>
-      <c r="Q213" s="82"/>
-      <c r="R213" s="83"/>
-      <c r="S213" s="83"/>
-      <c r="T213" s="83"/>
-      <c r="U213" s="83"/>
-      <c r="V213" s="83"/>
-      <c r="W213" s="83"/>
-      <c r="X213" s="83"/>
-      <c r="Y213" s="83"/>
-      <c r="Z213" s="84"/>
-      <c r="AA213" s="84"/>
-      <c r="AB213" s="84"/>
-      <c r="AC213" s="84"/>
-      <c r="AD213" s="84"/>
-      <c r="AE213" s="84"/>
-      <c r="AF213" s="84"/>
-      <c r="AG213" s="84"/>
-      <c r="AH213" s="84"/>
-      <c r="AI213" s="84"/>
-      <c r="AJ213" s="84"/>
-      <c r="AK213" s="84"/>
-      <c r="AL213" s="84"/>
-      <c r="AM213" s="84"/>
-      <c r="AN213" s="84"/>
-      <c r="AO213" s="84"/>
-      <c r="AP213" s="84"/>
-      <c r="AQ213" s="84"/>
-      <c r="AR213" s="84"/>
-      <c r="AS213" s="84"/>
-      <c r="AT213" s="84"/>
-      <c r="AU213" s="84"/>
-      <c r="AV213" s="84"/>
-      <c r="AW213" s="84"/>
-      <c r="AX213" s="84"/>
-    </row>
-    <row r="214" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="76"/>
-      <c r="B214" s="77">
-        <v>46093</v>
-      </c>
-      <c r="C214" s="77">
-        <v>46100</v>
-      </c>
-      <c r="D214" s="81"/>
-      <c r="E214" s="78" t="s">
-        <v>99</v>
-      </c>
-      <c r="F214" s="79">
-        <v>9755</v>
-      </c>
-      <c r="G214" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H214" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="I214" s="80">
-        <v>1700</v>
-      </c>
-      <c r="J214" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K214" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L214" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M214" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N214" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O214" s="81"/>
-      <c r="P214" s="82"/>
-      <c r="Q214" s="82"/>
-      <c r="R214" s="83"/>
-      <c r="S214" s="83"/>
-      <c r="T214" s="83"/>
-      <c r="U214" s="83"/>
-      <c r="V214" s="83"/>
-      <c r="W214" s="83"/>
-      <c r="X214" s="83"/>
-      <c r="Y214" s="83"/>
-      <c r="Z214" s="84"/>
-      <c r="AA214" s="84"/>
-      <c r="AB214" s="84"/>
-      <c r="AC214" s="84"/>
-      <c r="AD214" s="84"/>
-      <c r="AE214" s="84"/>
-      <c r="AF214" s="84"/>
-      <c r="AG214" s="84"/>
-      <c r="AH214" s="84"/>
-      <c r="AI214" s="84"/>
-      <c r="AJ214" s="84"/>
-      <c r="AK214" s="84"/>
-      <c r="AL214" s="84"/>
-      <c r="AM214" s="84"/>
-      <c r="AN214" s="84"/>
-      <c r="AO214" s="84"/>
-      <c r="AP214" s="84"/>
-      <c r="AQ214" s="84"/>
-      <c r="AR214" s="84"/>
-      <c r="AS214" s="84"/>
-      <c r="AT214" s="84"/>
-      <c r="AU214" s="84"/>
-      <c r="AV214" s="84"/>
-      <c r="AW214" s="84"/>
-      <c r="AX214" s="84"/>
-    </row>
-    <row r="215" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="76"/>
-      <c r="B215" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C215" s="77">
-        <v>46101</v>
-      </c>
-      <c r="D215" s="81"/>
-      <c r="E215" s="78" t="s">
-        <v>172</v>
-      </c>
-      <c r="F215" s="81"/>
-      <c r="G215" s="78" t="s">
-        <v>36</v>
-      </c>
-      <c r="H215" s="78" t="s">
-        <v>37</v>
-      </c>
-      <c r="I215" s="80">
-        <v>96500</v>
-      </c>
-      <c r="J215" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K215" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="L215" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M215" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N215" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O215" s="81"/>
-      <c r="P215" s="82"/>
-      <c r="Q215" s="85" t="s">
-        <v>39</v>
-      </c>
-      <c r="R215" s="83"/>
-      <c r="S215" s="83"/>
-      <c r="T215" s="83"/>
-      <c r="U215" s="83"/>
-      <c r="V215" s="83"/>
-      <c r="W215" s="83"/>
-      <c r="X215" s="83"/>
-      <c r="Y215" s="83"/>
-      <c r="Z215" s="84"/>
-      <c r="AA215" s="84"/>
-      <c r="AB215" s="84"/>
-      <c r="AC215" s="84"/>
-      <c r="AD215" s="84"/>
-      <c r="AE215" s="84"/>
-      <c r="AF215" s="84"/>
-      <c r="AG215" s="84"/>
-      <c r="AH215" s="84"/>
-      <c r="AI215" s="84"/>
-      <c r="AJ215" s="84"/>
-      <c r="AK215" s="84"/>
-      <c r="AL215" s="84"/>
-      <c r="AM215" s="84"/>
-      <c r="AN215" s="84"/>
-      <c r="AO215" s="84"/>
-      <c r="AP215" s="84"/>
-      <c r="AQ215" s="84"/>
-      <c r="AR215" s="84"/>
-      <c r="AS215" s="84"/>
-      <c r="AT215" s="84"/>
-      <c r="AU215" s="84"/>
-      <c r="AV215" s="84"/>
-      <c r="AW215" s="84"/>
-      <c r="AX215" s="84"/>
-    </row>
-    <row r="216" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P215" s="73" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q215" s="71"/>
+      <c r="R215" s="64"/>
+      <c r="S215" s="64"/>
+      <c r="T215" s="64"/>
+      <c r="U215" s="64"/>
+      <c r="V215" s="64"/>
+      <c r="W215" s="64"/>
+      <c r="X215" s="64"/>
+      <c r="Y215" s="64"/>
+      <c r="Z215" s="65"/>
+      <c r="AA215" s="65"/>
+      <c r="AB215" s="65"/>
+      <c r="AC215" s="65"/>
+      <c r="AD215" s="65"/>
+      <c r="AE215" s="65"/>
+      <c r="AF215" s="65"/>
+      <c r="AG215" s="65"/>
+      <c r="AH215" s="65"/>
+      <c r="AI215" s="65"/>
+      <c r="AJ215" s="65"/>
+      <c r="AK215" s="65"/>
+      <c r="AL215" s="65"/>
+      <c r="AM215" s="65"/>
+      <c r="AN215" s="65"/>
+      <c r="AO215" s="65"/>
+      <c r="AP215" s="65"/>
+      <c r="AQ215" s="65"/>
+      <c r="AR215" s="65"/>
+      <c r="AS215" s="65"/>
+      <c r="AT215" s="65"/>
+      <c r="AU215" s="65"/>
+      <c r="AV215" s="65"/>
+      <c r="AW215" s="65"/>
+      <c r="AX215" s="65"/>
+    </row>
+    <row r="216" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="66"/>
       <c r="B216" s="67">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="C216" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D216" s="69"/>
+        <v>46103</v>
+      </c>
+      <c r="D216" s="67">
+        <v>46101</v>
+      </c>
       <c r="E216" s="68" t="s">
-        <v>207</v>
-      </c>
-      <c r="F216" s="69"/>
+        <v>17</v>
+      </c>
+      <c r="F216" s="75">
+        <v>239338</v>
+      </c>
       <c r="G216" s="68" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H216" s="68" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="I216" s="70">
-        <v>405.34</v>
+        <v>1875.02</v>
       </c>
       <c r="J216" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K216" s="68" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L216" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M216" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N216" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O216" s="68">
-        <v>11981370647</v>
+        <v>216</v>
+      </c>
+      <c r="O216" s="68" t="s">
+        <v>246</v>
       </c>
       <c r="P216" s="73" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="Q216" s="71"/>
-      <c r="R216" s="65"/>
-      <c r="S216" s="65"/>
-      <c r="T216" s="65"/>
-      <c r="U216" s="65"/>
-      <c r="V216" s="65"/>
-      <c r="W216" s="65"/>
-      <c r="X216" s="65"/>
-      <c r="Y216" s="65"/>
+      <c r="R216" s="64"/>
+      <c r="S216" s="64"/>
+      <c r="T216" s="64"/>
+      <c r="U216" s="64"/>
+      <c r="V216" s="64"/>
+      <c r="W216" s="64"/>
+      <c r="X216" s="64"/>
+      <c r="Y216" s="64"/>
       <c r="Z216" s="65"/>
       <c r="AA216" s="65"/>
       <c r="AB216" s="65"/>
@@ -31872,48 +32290,52 @@
       <c r="AW216" s="65"/>
       <c r="AX216" s="65"/>
     </row>
-    <row r="217" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="66"/>
       <c r="B217" s="67">
-        <v>46076</v>
+        <v>46097</v>
       </c>
       <c r="C217" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D217" s="69"/>
+        <v>46103</v>
+      </c>
+      <c r="D217" s="67">
+        <v>46101</v>
+      </c>
       <c r="E217" s="68" t="s">
-        <v>378</v>
-      </c>
-      <c r="F217" s="69"/>
+        <v>17</v>
+      </c>
+      <c r="F217" s="75">
+        <v>239359</v>
+      </c>
       <c r="G217" s="68" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="H217" s="68" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="I217" s="70">
-        <v>20000</v>
+        <v>4527.51</v>
       </c>
       <c r="J217" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K217" s="68" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L217" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M217" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N217" s="68" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="O217" s="68" t="s">
-        <v>379</v>
+        <v>246</v>
       </c>
       <c r="P217" s="73" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="Q217" s="71"/>
       <c r="R217" s="64"/>
@@ -31950,56 +32372,62 @@
       <c r="AW217" s="65"/>
       <c r="AX217" s="65"/>
     </row>
-    <row r="218" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="66"/>
       <c r="B218" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C218" s="67">
         <v>46094</v>
       </c>
-      <c r="C218" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D218" s="69"/>
+      <c r="D218" s="67">
+        <v>46101</v>
+      </c>
       <c r="E218" s="68" t="s">
-        <v>129</v>
-      </c>
-      <c r="F218" s="69"/>
+        <v>86</v>
+      </c>
+      <c r="F218" s="75">
+        <v>123007</v>
+      </c>
       <c r="G218" s="68" t="s">
         <v>18</v>
       </c>
       <c r="H218" s="68" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I218" s="70">
-        <v>11650</v>
+        <v>3900</v>
       </c>
       <c r="J218" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K218" s="68" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L218" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M218" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N218" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O218" s="69"/>
+        <v>216</v>
+      </c>
+      <c r="O218" s="68" t="s">
+        <v>397</v>
+      </c>
       <c r="P218" s="73" t="s">
-        <v>210</v>
+        <v>301</v>
       </c>
       <c r="Q218" s="71"/>
-      <c r="R218" s="65"/>
-      <c r="S218" s="65"/>
-      <c r="T218" s="65"/>
-      <c r="U218" s="65"/>
-      <c r="V218" s="65"/>
-      <c r="W218" s="65"/>
-      <c r="X218" s="65"/>
-      <c r="Y218" s="65"/>
+      <c r="R218" s="64"/>
+      <c r="S218" s="64"/>
+      <c r="T218" s="64"/>
+      <c r="U218" s="64"/>
+      <c r="V218" s="64"/>
+      <c r="W218" s="64"/>
+      <c r="X218" s="64"/>
+      <c r="Y218" s="64"/>
       <c r="Z218" s="65"/>
       <c r="AA218" s="65"/>
       <c r="AB218" s="65"/>
@@ -32026,50 +32454,54 @@
       <c r="AW218" s="65"/>
       <c r="AX218" s="65"/>
     </row>
-    <row r="219" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="66"/>
+    <row r="219" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="69"/>
       <c r="B219" s="67">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="C219" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D219" s="69"/>
+        <v>46106</v>
+      </c>
+      <c r="D219" s="67">
+        <v>46101</v>
+      </c>
       <c r="E219" s="68" t="s">
-        <v>381</v>
-      </c>
-      <c r="F219" s="69"/>
+        <v>17</v>
+      </c>
+      <c r="F219" s="75">
+        <v>239441</v>
+      </c>
       <c r="G219" s="68" t="s">
         <v>18</v>
       </c>
       <c r="H219" s="68" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="I219" s="70">
-        <v>6500</v>
+        <v>1508.48</v>
       </c>
       <c r="J219" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K219" s="68" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="L219" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M219" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N219" s="68" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="O219" s="68" t="s">
-        <v>382</v>
+        <v>246</v>
       </c>
       <c r="P219" s="73" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q219" s="71"/>
+        <v>78</v>
+      </c>
+      <c r="Q219" s="89"/>
       <c r="R219" s="64"/>
       <c r="S219" s="64"/>
       <c r="T219" s="64"/>
@@ -32104,50 +32536,54 @@
       <c r="AW219" s="65"/>
       <c r="AX219" s="65"/>
     </row>
-    <row r="220" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="66"/>
+    <row r="220" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="69"/>
       <c r="B220" s="67">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C220" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D220" s="69"/>
+        <v>46106</v>
+      </c>
+      <c r="D220" s="67">
+        <v>46101</v>
+      </c>
       <c r="E220" s="68" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="F220" s="75">
-        <v>3185</v>
+        <v>239403</v>
       </c>
       <c r="G220" s="68" t="s">
         <v>18</v>
       </c>
       <c r="H220" s="68" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I220" s="70">
-        <v>96166.44</v>
+        <v>1723.24</v>
       </c>
       <c r="J220" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K220" s="68" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L220" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M220" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N220" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O220" s="69"/>
+        <v>216</v>
+      </c>
+      <c r="O220" s="68" t="s">
+        <v>246</v>
+      </c>
       <c r="P220" s="73" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q220" s="71"/>
+        <v>78</v>
+      </c>
+      <c r="Q220" s="89"/>
       <c r="R220" s="64"/>
       <c r="S220" s="64"/>
       <c r="T220" s="64"/>
@@ -32182,46 +32618,52 @@
       <c r="AW220" s="65"/>
       <c r="AX220" s="65"/>
     </row>
-    <row r="221" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="66"/>
       <c r="B221" s="67">
-        <v>46079</v>
+        <v>46100</v>
       </c>
       <c r="C221" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D221" s="69"/>
+        <v>46101</v>
+      </c>
+      <c r="D221" s="67">
+        <v>46101</v>
+      </c>
       <c r="E221" s="68" t="s">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="F221" s="69"/>
       <c r="G221" s="68" t="s">
         <v>52</v>
       </c>
       <c r="H221" s="68" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="I221" s="70">
-        <v>540</v>
+        <v>3845.04</v>
       </c>
       <c r="J221" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K221" s="68" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="L221" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M221" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N221" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O221" s="69"/>
-      <c r="P221" s="71"/>
-      <c r="Q221" s="71"/>
+        <v>216</v>
+      </c>
+      <c r="O221" s="69">
+        <v>3.7690001040010501E+46</v>
+      </c>
+      <c r="P221" s="86" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q221" s="69"/>
       <c r="R221" s="64"/>
       <c r="S221" s="64"/>
       <c r="T221" s="64"/>
@@ -32256,48 +32698,52 @@
       <c r="AW221" s="65"/>
       <c r="AX221" s="65"/>
     </row>
-    <row r="222" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="66"/>
       <c r="B222" s="67">
-        <v>46091</v>
+        <v>46100</v>
       </c>
       <c r="C222" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D222" s="69"/>
+        <v>46101</v>
+      </c>
+      <c r="D222" s="67">
+        <v>46101</v>
+      </c>
       <c r="E222" s="68" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F222" s="69"/>
       <c r="G222" s="68" t="s">
         <v>52</v>
       </c>
       <c r="H222" s="68" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="I222" s="70">
-        <v>448.55</v>
+        <v>921.9</v>
       </c>
       <c r="J222" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K222" s="68" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="L222" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M222" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N222" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O222" s="68" t="s">
-        <v>160</v>
-      </c>
-      <c r="P222" s="71"/>
-      <c r="Q222" s="71"/>
+        <v>216</v>
+      </c>
+      <c r="O222" s="69">
+        <v>3.7690001040010501E+46</v>
+      </c>
+      <c r="P222" s="86" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q222" s="69"/>
       <c r="R222" s="64"/>
       <c r="S222" s="64"/>
       <c r="T222" s="64"/>
@@ -32332,50 +32778,50 @@
       <c r="AW222" s="65"/>
       <c r="AX222" s="65"/>
     </row>
-    <row r="223" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="66"/>
       <c r="B223" s="67">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="C223" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D223" s="69"/>
+        <v>46101</v>
+      </c>
+      <c r="D223" s="67">
+        <v>46101</v>
+      </c>
       <c r="E223" s="68" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="F223" s="69"/>
       <c r="G223" s="68" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H223" s="68" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I223" s="70">
-        <v>9975</v>
+        <v>1242.3</v>
       </c>
       <c r="J223" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K223" s="68" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L223" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M223" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N223" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O223" s="68" t="s">
-        <v>76</v>
-      </c>
-      <c r="P223" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q223" s="71"/>
+        <v>216</v>
+      </c>
+      <c r="O223" s="69">
+        <v>8.2660000012742297E+47</v>
+      </c>
+      <c r="P223" s="69"/>
+      <c r="Q223" s="69"/>
       <c r="R223" s="64"/>
       <c r="S223" s="64"/>
       <c r="T223" s="64"/>
@@ -32410,49 +32856,49 @@
       <c r="AW223" s="65"/>
       <c r="AX223" s="65"/>
     </row>
-    <row r="224" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="66"/>
       <c r="B224" s="67">
-        <v>46059</v>
+        <v>46092</v>
       </c>
       <c r="C224" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D224" s="69"/>
+        <v>46101</v>
+      </c>
+      <c r="D224" s="67">
+        <v>46101</v>
+      </c>
       <c r="E224" s="68" t="s">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="F224" s="69"/>
       <c r="G224" s="68" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H224" s="68" t="s">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="I224" s="70">
-        <v>10000</v>
+        <v>146.75</v>
       </c>
       <c r="J224" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K224" s="68" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L224" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M224" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N224" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O224" s="68" t="s">
-        <v>76</v>
-      </c>
-      <c r="P224" s="73" t="s">
-        <v>162</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O224" s="68">
+        <v>8.4620000001246707E+47</v>
+      </c>
+      <c r="P224" s="71"/>
       <c r="Q224" s="71"/>
       <c r="R224" s="64"/>
       <c r="S224" s="64"/>
@@ -32488,17 +32934,19 @@
       <c r="AW224" s="65"/>
       <c r="AX224" s="65"/>
     </row>
-    <row r="225" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="66"/>
       <c r="B225" s="67">
         <v>46079</v>
       </c>
       <c r="C225" s="67">
-        <v>46100</v>
-      </c>
-      <c r="D225" s="69"/>
+        <v>46101</v>
+      </c>
+      <c r="D225" s="67">
+        <v>46101</v>
+      </c>
       <c r="E225" s="68" t="s">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="F225" s="69"/>
       <c r="G225" s="68" t="s">
@@ -32508,34 +32956,36 @@
         <v>33</v>
       </c>
       <c r="I225" s="70">
-        <v>20000</v>
+        <v>7851.77</v>
       </c>
       <c r="J225" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K225" s="68" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="L225" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M225" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N225" s="68" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="O225" s="69"/>
-      <c r="P225" s="71"/>
-      <c r="Q225" s="71"/>
-      <c r="R225" s="65"/>
-      <c r="S225" s="65"/>
-      <c r="T225" s="65"/>
-      <c r="U225" s="65"/>
-      <c r="V225" s="65"/>
-      <c r="W225" s="65"/>
-      <c r="X225" s="65"/>
-      <c r="Y225" s="65"/>
+      <c r="P225" s="86" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q225" s="69"/>
+      <c r="R225" s="64"/>
+      <c r="S225" s="64"/>
+      <c r="T225" s="64"/>
+      <c r="U225" s="64"/>
+      <c r="V225" s="64"/>
+      <c r="W225" s="64"/>
+      <c r="X225" s="64"/>
+      <c r="Y225" s="64"/>
       <c r="Z225" s="65"/>
       <c r="AA225" s="65"/>
       <c r="AB225" s="65"/>
@@ -32563,83 +33013,131 @@
       <c r="AX225" s="65"/>
     </row>
     <row r="226" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="100"/>
-      <c r="B226" s="101"/>
-      <c r="C226" s="101"/>
-      <c r="D226" s="101"/>
-      <c r="E226" s="101"/>
-      <c r="F226" s="101"/>
-      <c r="G226" s="101"/>
-      <c r="H226" s="101"/>
-      <c r="I226" s="102"/>
-      <c r="J226" s="101"/>
-      <c r="K226" s="101"/>
-      <c r="L226" s="101"/>
-      <c r="M226" s="101"/>
-      <c r="N226" s="101"/>
-      <c r="O226" s="101"/>
-      <c r="P226" s="102"/>
-      <c r="Q226" s="102"/>
-      <c r="R226" s="103"/>
-      <c r="S226" s="103"/>
-      <c r="T226" s="103"/>
-      <c r="U226" s="103"/>
-      <c r="V226" s="103"/>
-      <c r="W226" s="103"/>
-      <c r="X226" s="103"/>
-      <c r="Y226" s="103"/>
-      <c r="Z226" s="103"/>
-      <c r="AA226" s="103"/>
-      <c r="AB226" s="103"/>
-      <c r="AC226" s="103"/>
-      <c r="AD226" s="103"/>
-      <c r="AE226" s="103"/>
-      <c r="AF226" s="103"/>
-      <c r="AG226" s="103"/>
-      <c r="AH226" s="103"/>
-      <c r="AI226" s="103"/>
-      <c r="AJ226" s="103"/>
-      <c r="AK226" s="103"/>
-      <c r="AL226" s="103"/>
-      <c r="AM226" s="103"/>
-      <c r="AN226" s="103"/>
-      <c r="AO226" s="103"/>
-      <c r="AP226" s="103"/>
-      <c r="AQ226" s="103"/>
-      <c r="AR226" s="103"/>
-      <c r="AS226" s="103"/>
-      <c r="AT226" s="103"/>
-      <c r="AU226" s="103"/>
-      <c r="AV226" s="103"/>
-      <c r="AW226" s="103"/>
-      <c r="AX226" s="103"/>
+      <c r="A226" s="66"/>
+      <c r="B226" s="67">
+        <v>46094</v>
+      </c>
+      <c r="C226" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D226" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E226" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="F226" s="69"/>
+      <c r="G226" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H226" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="I226" s="70">
+        <v>84.24</v>
+      </c>
+      <c r="J226" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K226" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L226" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M226" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N226" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O226" s="69"/>
+      <c r="P226" s="69"/>
+      <c r="Q226" s="69"/>
+      <c r="R226" s="64"/>
+      <c r="S226" s="64"/>
+      <c r="T226" s="64"/>
+      <c r="U226" s="64"/>
+      <c r="V226" s="64"/>
+      <c r="W226" s="64"/>
+      <c r="X226" s="64"/>
+      <c r="Y226" s="64"/>
+      <c r="Z226" s="65"/>
+      <c r="AA226" s="65"/>
+      <c r="AB226" s="65"/>
+      <c r="AC226" s="65"/>
+      <c r="AD226" s="65"/>
+      <c r="AE226" s="65"/>
+      <c r="AF226" s="65"/>
+      <c r="AG226" s="65"/>
+      <c r="AH226" s="65"/>
+      <c r="AI226" s="65"/>
+      <c r="AJ226" s="65"/>
+      <c r="AK226" s="65"/>
+      <c r="AL226" s="65"/>
+      <c r="AM226" s="65"/>
+      <c r="AN226" s="65"/>
+      <c r="AO226" s="65"/>
+      <c r="AP226" s="65"/>
+      <c r="AQ226" s="65"/>
+      <c r="AR226" s="65"/>
+      <c r="AS226" s="65"/>
+      <c r="AT226" s="65"/>
+      <c r="AU226" s="65"/>
+      <c r="AV226" s="65"/>
+      <c r="AW226" s="65"/>
+      <c r="AX226" s="65"/>
     </row>
     <row r="227" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="66"/>
-      <c r="B227" s="69"/>
-      <c r="C227" s="69"/>
-      <c r="D227" s="69"/>
-      <c r="E227" s="69"/>
+      <c r="B227" s="67">
+        <v>46094</v>
+      </c>
+      <c r="C227" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D227" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E227" s="68" t="s">
+        <v>197</v>
+      </c>
       <c r="F227" s="69"/>
-      <c r="G227" s="69"/>
-      <c r="H227" s="69"/>
-      <c r="I227" s="71"/>
-      <c r="J227" s="69"/>
-      <c r="K227" s="69"/>
-      <c r="L227" s="69"/>
-      <c r="M227" s="69"/>
-      <c r="N227" s="69"/>
+      <c r="G227" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H227" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="I227" s="70">
+        <v>688.88</v>
+      </c>
+      <c r="J227" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K227" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L227" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M227" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N227" s="68" t="s">
+        <v>216</v>
+      </c>
       <c r="O227" s="69"/>
-      <c r="P227" s="71"/>
-      <c r="Q227" s="71"/>
-      <c r="R227" s="65"/>
-      <c r="S227" s="65"/>
-      <c r="T227" s="65"/>
-      <c r="U227" s="65"/>
-      <c r="V227" s="65"/>
-      <c r="W227" s="65"/>
-      <c r="X227" s="65"/>
-      <c r="Y227" s="65"/>
+      <c r="P227" s="69"/>
+      <c r="Q227" s="69"/>
+      <c r="R227" s="64"/>
+      <c r="S227" s="64"/>
+      <c r="T227" s="64"/>
+      <c r="U227" s="64"/>
+      <c r="V227" s="64"/>
+      <c r="W227" s="64"/>
+      <c r="X227" s="64"/>
+      <c r="Y227" s="64"/>
       <c r="Z227" s="65"/>
       <c r="AA227" s="65"/>
       <c r="AB227" s="65"/>
@@ -32666,32 +33164,62 @@
       <c r="AW227" s="65"/>
       <c r="AX227" s="65"/>
     </row>
-    <row r="228" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="66"/>
-      <c r="B228" s="69"/>
-      <c r="C228" s="69"/>
-      <c r="D228" s="69"/>
-      <c r="E228" s="69"/>
+      <c r="B228" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C228" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D228" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E228" s="68" t="s">
+        <v>165</v>
+      </c>
       <c r="F228" s="69"/>
-      <c r="G228" s="69"/>
-      <c r="H228" s="69"/>
-      <c r="I228" s="71"/>
-      <c r="J228" s="69"/>
-      <c r="K228" s="69"/>
-      <c r="L228" s="69"/>
-      <c r="M228" s="69"/>
-      <c r="N228" s="69"/>
-      <c r="O228" s="69"/>
-      <c r="P228" s="71"/>
-      <c r="Q228" s="71"/>
-      <c r="R228" s="65"/>
-      <c r="S228" s="65"/>
-      <c r="T228" s="65"/>
-      <c r="U228" s="65"/>
-      <c r="V228" s="65"/>
-      <c r="W228" s="65"/>
-      <c r="X228" s="65"/>
-      <c r="Y228" s="65"/>
+      <c r="G228" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H228" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="I228" s="70">
+        <v>700</v>
+      </c>
+      <c r="J228" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K228" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L228" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M228" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N228" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O228" s="68">
+        <v>11959274226</v>
+      </c>
+      <c r="P228" s="73" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q228" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="R228" s="64"/>
+      <c r="S228" s="64"/>
+      <c r="T228" s="64"/>
+      <c r="U228" s="64"/>
+      <c r="V228" s="64"/>
+      <c r="W228" s="64"/>
+      <c r="X228" s="64"/>
+      <c r="Y228" s="64"/>
       <c r="Z228" s="65"/>
       <c r="AA228" s="65"/>
       <c r="AB228" s="65"/>
@@ -32718,32 +33246,60 @@
       <c r="AW228" s="65"/>
       <c r="AX228" s="65"/>
     </row>
-    <row r="229" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="66"/>
-      <c r="B229" s="69"/>
-      <c r="C229" s="69"/>
-      <c r="D229" s="69"/>
-      <c r="E229" s="69"/>
+      <c r="B229" s="67">
+        <v>46101</v>
+      </c>
+      <c r="C229" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D229" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E229" s="68" t="s">
+        <v>400</v>
+      </c>
       <c r="F229" s="69"/>
-      <c r="G229" s="69"/>
-      <c r="H229" s="69"/>
-      <c r="I229" s="71"/>
-      <c r="J229" s="69"/>
-      <c r="K229" s="69"/>
-      <c r="L229" s="69"/>
-      <c r="M229" s="69"/>
-      <c r="N229" s="69"/>
-      <c r="O229" s="69"/>
-      <c r="P229" s="71"/>
+      <c r="G229" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H229" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I229" s="70">
+        <v>1580</v>
+      </c>
+      <c r="J229" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K229" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L229" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M229" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N229" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O229" s="68" t="s">
+        <v>401</v>
+      </c>
+      <c r="P229" s="9" t="s">
+        <v>402</v>
+      </c>
       <c r="Q229" s="71"/>
-      <c r="R229" s="65"/>
-      <c r="S229" s="65"/>
-      <c r="T229" s="65"/>
-      <c r="U229" s="65"/>
-      <c r="V229" s="65"/>
-      <c r="W229" s="65"/>
-      <c r="X229" s="65"/>
-      <c r="Y229" s="65"/>
+      <c r="R229" s="64"/>
+      <c r="S229" s="64"/>
+      <c r="T229" s="64"/>
+      <c r="U229" s="64"/>
+      <c r="V229" s="64"/>
+      <c r="W229" s="64"/>
+      <c r="X229" s="64"/>
+      <c r="Y229" s="64"/>
       <c r="Z229" s="65"/>
       <c r="AA229" s="65"/>
       <c r="AB229" s="65"/>
@@ -32770,32 +33326,60 @@
       <c r="AW229" s="65"/>
       <c r="AX229" s="65"/>
     </row>
-    <row r="230" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="66"/>
-      <c r="B230" s="69"/>
-      <c r="C230" s="69"/>
-      <c r="D230" s="69"/>
-      <c r="E230" s="69"/>
+      <c r="B230" s="67">
+        <v>46079</v>
+      </c>
+      <c r="C230" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D230" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E230" s="68" t="s">
+        <v>167</v>
+      </c>
       <c r="F230" s="69"/>
-      <c r="G230" s="69"/>
-      <c r="H230" s="69"/>
-      <c r="I230" s="71"/>
-      <c r="J230" s="69"/>
-      <c r="K230" s="69"/>
-      <c r="L230" s="69"/>
-      <c r="M230" s="69"/>
-      <c r="N230" s="69"/>
-      <c r="O230" s="69"/>
-      <c r="P230" s="71"/>
+      <c r="G230" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H230" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="I230" s="70">
+        <v>5000</v>
+      </c>
+      <c r="J230" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K230" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="L230" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M230" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N230" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O230" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="P230" s="73" t="s">
+        <v>169</v>
+      </c>
       <c r="Q230" s="71"/>
-      <c r="R230" s="65"/>
-      <c r="S230" s="65"/>
-      <c r="T230" s="65"/>
-      <c r="U230" s="65"/>
-      <c r="V230" s="65"/>
-      <c r="W230" s="65"/>
-      <c r="X230" s="65"/>
-      <c r="Y230" s="65"/>
+      <c r="R230" s="64"/>
+      <c r="S230" s="64"/>
+      <c r="T230" s="64"/>
+      <c r="U230" s="64"/>
+      <c r="V230" s="64"/>
+      <c r="W230" s="64"/>
+      <c r="X230" s="64"/>
+      <c r="Y230" s="64"/>
       <c r="Z230" s="65"/>
       <c r="AA230" s="65"/>
       <c r="AB230" s="65"/>
@@ -32823,58 +33407,82 @@
       <c r="AX230" s="65"/>
     </row>
     <row r="231" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="100"/>
-      <c r="B231" s="101"/>
-      <c r="C231" s="101"/>
-      <c r="D231" s="101"/>
-      <c r="E231" s="101"/>
-      <c r="F231" s="101"/>
-      <c r="G231" s="101"/>
-      <c r="H231" s="101"/>
-      <c r="I231" s="102"/>
-      <c r="J231" s="101"/>
-      <c r="K231" s="101"/>
-      <c r="L231" s="101"/>
-      <c r="M231" s="101"/>
-      <c r="N231" s="101"/>
-      <c r="O231" s="101"/>
-      <c r="P231" s="102"/>
-      <c r="Q231" s="102"/>
-      <c r="R231" s="103"/>
-      <c r="S231" s="103"/>
-      <c r="T231" s="103"/>
-      <c r="U231" s="103"/>
-      <c r="V231" s="103"/>
-      <c r="W231" s="103"/>
-      <c r="X231" s="103"/>
-      <c r="Y231" s="103"/>
-      <c r="Z231" s="103"/>
-      <c r="AA231" s="103"/>
-      <c r="AB231" s="103"/>
-      <c r="AC231" s="103"/>
-      <c r="AD231" s="103"/>
-      <c r="AE231" s="103"/>
-      <c r="AF231" s="103"/>
-      <c r="AG231" s="103"/>
-      <c r="AH231" s="103"/>
-      <c r="AI231" s="103"/>
-      <c r="AJ231" s="103"/>
-      <c r="AK231" s="103"/>
-      <c r="AL231" s="103"/>
-      <c r="AM231" s="103"/>
-      <c r="AN231" s="103"/>
-      <c r="AO231" s="103"/>
-      <c r="AP231" s="103"/>
-      <c r="AQ231" s="103"/>
-      <c r="AR231" s="103"/>
-      <c r="AS231" s="103"/>
-      <c r="AT231" s="103"/>
-      <c r="AU231" s="103"/>
-      <c r="AV231" s="103"/>
-      <c r="AW231" s="103"/>
-      <c r="AX231" s="103"/>
-    </row>
-    <row r="232" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="66"/>
+      <c r="B231" s="67">
+        <v>46101</v>
+      </c>
+      <c r="C231" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D231" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E231" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="F231" s="69"/>
+      <c r="G231" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H231" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="I231" s="70">
+        <v>14000</v>
+      </c>
+      <c r="J231" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K231" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L231" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M231" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N231" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O231" s="69"/>
+      <c r="P231" s="71"/>
+      <c r="Q231" s="71"/>
+      <c r="R231" s="64"/>
+      <c r="S231" s="64"/>
+      <c r="T231" s="64"/>
+      <c r="U231" s="64"/>
+      <c r="V231" s="64"/>
+      <c r="W231" s="64"/>
+      <c r="X231" s="64"/>
+      <c r="Y231" s="64"/>
+      <c r="Z231" s="65"/>
+      <c r="AA231" s="65"/>
+      <c r="AB231" s="65"/>
+      <c r="AC231" s="65"/>
+      <c r="AD231" s="65"/>
+      <c r="AE231" s="65"/>
+      <c r="AF231" s="65"/>
+      <c r="AG231" s="65"/>
+      <c r="AH231" s="65"/>
+      <c r="AI231" s="65"/>
+      <c r="AJ231" s="65"/>
+      <c r="AK231" s="65"/>
+      <c r="AL231" s="65"/>
+      <c r="AM231" s="65"/>
+      <c r="AN231" s="65"/>
+      <c r="AO231" s="65"/>
+      <c r="AP231" s="65"/>
+      <c r="AQ231" s="65"/>
+      <c r="AR231" s="65"/>
+      <c r="AS231" s="65"/>
+      <c r="AT231" s="65"/>
+      <c r="AU231" s="65"/>
+      <c r="AV231" s="65"/>
+      <c r="AW231" s="65"/>
+      <c r="AX231" s="65"/>
+    </row>
+    <row r="232" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="66"/>
       <c r="B232" s="67">
         <v>46097</v>
@@ -32882,9 +33490,11 @@
       <c r="C232" s="67">
         <v>46101</v>
       </c>
-      <c r="D232" s="69"/>
+      <c r="D232" s="67">
+        <v>46101</v>
+      </c>
       <c r="E232" s="68" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F232" s="69"/>
       <c r="G232" s="68" t="s">
@@ -32906,16 +33516,16 @@
         <v>27</v>
       </c>
       <c r="M232" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N232" s="68" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="O232" s="68" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="P232" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q232" s="71"/>
       <c r="R232" s="65"/>
@@ -32952,7 +33562,7 @@
       <c r="AW232" s="65"/>
       <c r="AX232" s="65"/>
     </row>
-    <row r="233" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="66"/>
       <c r="B233" s="67">
         <v>46097</v>
@@ -32960,9 +33570,11 @@
       <c r="C233" s="67">
         <v>46101</v>
       </c>
-      <c r="D233" s="69"/>
+      <c r="D233" s="67">
+        <v>46101</v>
+      </c>
       <c r="E233" s="68" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F233" s="69"/>
       <c r="G233" s="68" t="s">
@@ -32984,16 +33596,16 @@
         <v>27</v>
       </c>
       <c r="M233" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N233" s="68" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="O233" s="68" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="P233" s="73" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q233" s="71"/>
       <c r="R233" s="65"/>
@@ -33030,7 +33642,7 @@
       <c r="AW233" s="65"/>
       <c r="AX233" s="65"/>
     </row>
-    <row r="234" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="66"/>
       <c r="B234" s="67">
         <v>46079</v>
@@ -33038,48 +33650,50 @@
       <c r="C234" s="67">
         <v>46101</v>
       </c>
-      <c r="D234" s="69"/>
+      <c r="D234" s="67">
+        <v>46101</v>
+      </c>
       <c r="E234" s="68" t="s">
-        <v>123</v>
-      </c>
-      <c r="F234" s="69"/>
+        <v>17</v>
+      </c>
+      <c r="F234" s="75">
+        <v>239277</v>
+      </c>
       <c r="G234" s="68" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="H234" s="68" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="I234" s="70">
-        <v>110000</v>
+        <v>59591.360000000001</v>
       </c>
       <c r="J234" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K234" s="68" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="L234" s="68" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M234" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N234" s="68" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O234" s="69"/>
       <c r="P234" s="71"/>
-      <c r="Q234" s="73" t="s">
-        <v>39</v>
-      </c>
-      <c r="R234" s="65"/>
-      <c r="S234" s="65"/>
-      <c r="T234" s="65"/>
-      <c r="U234" s="65"/>
-      <c r="V234" s="65"/>
-      <c r="W234" s="65"/>
-      <c r="X234" s="65"/>
-      <c r="Y234" s="65"/>
+      <c r="Q234" s="71"/>
+      <c r="R234" s="64"/>
+      <c r="S234" s="64"/>
+      <c r="T234" s="64"/>
+      <c r="U234" s="64"/>
+      <c r="V234" s="64"/>
+      <c r="W234" s="64"/>
+      <c r="X234" s="64"/>
+      <c r="Y234" s="64"/>
       <c r="Z234" s="65"/>
       <c r="AA234" s="65"/>
       <c r="AB234" s="65"/>
@@ -33106,48 +33720,50 @@
       <c r="AW234" s="65"/>
       <c r="AX234" s="65"/>
     </row>
-    <row r="235" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="66"/>
       <c r="B235" s="67">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="C235" s="67">
         <v>46101</v>
       </c>
-      <c r="D235" s="69"/>
+      <c r="D235" s="67">
+        <v>46101</v>
+      </c>
       <c r="E235" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="F235" s="69"/>
+        <v>17</v>
+      </c>
+      <c r="F235" s="75">
+        <v>239298</v>
+      </c>
       <c r="G235" s="68" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H235" s="68" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I235" s="70">
-        <v>1242.3</v>
+        <v>68272.17</v>
       </c>
       <c r="J235" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K235" s="68" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L235" s="68" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M235" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N235" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O235" s="69" t="s">
-        <v>191</v>
-      </c>
-      <c r="P235" s="69"/>
-      <c r="Q235" s="69"/>
+        <v>23</v>
+      </c>
+      <c r="O235" s="69"/>
+      <c r="P235" s="71"/>
+      <c r="Q235" s="71"/>
       <c r="R235" s="64"/>
       <c r="S235" s="64"/>
       <c r="T235" s="64"/>
@@ -33182,27 +33798,29 @@
       <c r="AW235" s="65"/>
       <c r="AX235" s="65"/>
     </row>
-    <row r="236" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="66"/>
       <c r="B236" s="67">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="C236" s="67">
         <v>46101</v>
       </c>
-      <c r="D236" s="69"/>
+      <c r="D236" s="67">
+        <v>46101</v>
+      </c>
       <c r="E236" s="68" t="s">
-        <v>196</v>
+        <v>405</v>
       </c>
       <c r="F236" s="69"/>
       <c r="G236" s="68" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H236" s="68" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="I236" s="70">
-        <v>84.24</v>
+        <v>5514</v>
       </c>
       <c r="J236" s="68" t="b">
         <v>1</v>
@@ -33214,14 +33832,16 @@
         <v>27</v>
       </c>
       <c r="M236" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N236" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O236" s="69"/>
-      <c r="P236" s="69"/>
-      <c r="Q236" s="69"/>
+        <v>216</v>
+      </c>
+      <c r="O236" s="68" t="s">
+        <v>406</v>
+      </c>
+      <c r="P236" s="71"/>
+      <c r="Q236" s="71"/>
       <c r="R236" s="64"/>
       <c r="S236" s="64"/>
       <c r="T236" s="64"/>
@@ -33259,24 +33879,26 @@
     <row r="237" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="66"/>
       <c r="B237" s="67">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="C237" s="67">
         <v>46101</v>
       </c>
-      <c r="D237" s="69"/>
+      <c r="D237" s="67">
+        <v>46101</v>
+      </c>
       <c r="E237" s="68" t="s">
-        <v>197</v>
+        <v>407</v>
       </c>
       <c r="F237" s="69"/>
       <c r="G237" s="68" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H237" s="68" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="I237" s="70">
-        <v>688.88</v>
+        <v>4240</v>
       </c>
       <c r="J237" s="68" t="b">
         <v>1</v>
@@ -33288,14 +33910,16 @@
         <v>27</v>
       </c>
       <c r="M237" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N237" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O237" s="69"/>
-      <c r="P237" s="69"/>
-      <c r="Q237" s="69"/>
+        <v>216</v>
+      </c>
+      <c r="O237" s="68" t="s">
+        <v>408</v>
+      </c>
+      <c r="P237" s="71"/>
+      <c r="Q237" s="71"/>
       <c r="R237" s="64"/>
       <c r="S237" s="64"/>
       <c r="T237" s="64"/>
@@ -33330,48 +33954,50 @@
       <c r="AW237" s="65"/>
       <c r="AX237" s="65"/>
     </row>
-    <row r="238" spans="1:50" ht="31.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="66"/>
       <c r="B238" s="67">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C238" s="67">
         <v>46101</v>
       </c>
-      <c r="D238" s="69"/>
+      <c r="D238" s="67">
+        <v>46101</v>
+      </c>
       <c r="E238" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="F238" s="69"/>
+        <v>72</v>
+      </c>
+      <c r="F238" s="75">
+        <v>123589</v>
+      </c>
       <c r="G238" s="68" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H238" s="68" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I238" s="70">
-        <v>7851.77</v>
+        <v>26875.16</v>
       </c>
       <c r="J238" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K238" s="68" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L238" s="68" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M238" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N238" s="68" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O238" s="69"/>
-      <c r="P238" s="86" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q238" s="69"/>
+      <c r="P238" s="71"/>
+      <c r="Q238" s="71"/>
       <c r="R238" s="64"/>
       <c r="S238" s="64"/>
       <c r="T238" s="64"/>
@@ -33406,50 +34032,50 @@
       <c r="AW238" s="65"/>
       <c r="AX238" s="65"/>
     </row>
-    <row r="239" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="66"/>
       <c r="B239" s="67">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C239" s="67">
         <v>46101</v>
       </c>
-      <c r="D239" s="69"/>
+      <c r="D239" s="67">
+        <v>46101</v>
+      </c>
       <c r="E239" s="68" t="s">
-        <v>165</v>
-      </c>
-      <c r="F239" s="69"/>
+        <v>72</v>
+      </c>
+      <c r="F239" s="75">
+        <v>123587</v>
+      </c>
       <c r="G239" s="68" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H239" s="68" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="I239" s="70">
-        <v>700</v>
+        <v>26875.16</v>
       </c>
       <c r="J239" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K239" s="68" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L239" s="68" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M239" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N239" s="68" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O239" s="69"/>
-      <c r="P239" s="73" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q239" s="73" t="s">
-        <v>39</v>
-      </c>
+      <c r="P239" s="71"/>
+      <c r="Q239" s="71"/>
       <c r="R239" s="64"/>
       <c r="S239" s="64"/>
       <c r="T239" s="64"/>
@@ -33484,49 +34110,49 @@
       <c r="AW239" s="65"/>
       <c r="AX239" s="65"/>
     </row>
-    <row r="240" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="66"/>
       <c r="B240" s="67">
         <v>46079</v>
       </c>
       <c r="C240" s="67">
+        <v>46103</v>
+      </c>
+      <c r="D240" s="67">
         <v>46101</v>
       </c>
-      <c r="D240" s="69"/>
       <c r="E240" s="68" t="s">
-        <v>167</v>
-      </c>
-      <c r="F240" s="69"/>
+        <v>17</v>
+      </c>
+      <c r="F240" s="75">
+        <v>239440</v>
+      </c>
       <c r="G240" s="68" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H240" s="68" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="I240" s="70">
-        <v>5000</v>
+        <v>58208.11</v>
       </c>
       <c r="J240" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K240" s="68" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="L240" s="68" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M240" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N240" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O240" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="P240" s="73" t="s">
-        <v>169</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O240" s="69"/>
+      <c r="P240" s="71"/>
       <c r="Q240" s="71"/>
       <c r="R240" s="64"/>
       <c r="S240" s="64"/>
@@ -33562,45 +34188,49 @@
       <c r="AW240" s="65"/>
       <c r="AX240" s="65"/>
     </row>
-    <row r="241" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="66"/>
       <c r="B241" s="67">
         <v>46079</v>
       </c>
       <c r="C241" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D241" s="67">
         <v>46101</v>
       </c>
-      <c r="D241" s="69"/>
       <c r="E241" s="68" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="F241" s="69"/>
       <c r="G241" s="68" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="H241" s="68" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="I241" s="70">
-        <v>10000</v>
+        <v>42548.67</v>
       </c>
       <c r="J241" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K241" s="68" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="L241" s="68" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M241" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N241" s="68" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O241" s="69"/>
-      <c r="P241" s="71"/>
+      <c r="P241" s="73" t="s">
+        <v>149</v>
+      </c>
       <c r="Q241" s="73" t="s">
         <v>39</v>
       </c>
@@ -33638,50 +34268,54 @@
       <c r="AW241" s="65"/>
       <c r="AX241" s="65"/>
     </row>
-    <row r="242" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="66"/>
       <c r="B242" s="67">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="C242" s="67">
         <v>46101</v>
       </c>
-      <c r="D242" s="69"/>
+      <c r="D242" s="67">
+        <v>46101</v>
+      </c>
       <c r="E242" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="F242" s="69"/>
+        <v>87</v>
+      </c>
+      <c r="F242" s="75">
+        <v>308438</v>
+      </c>
       <c r="G242" s="68" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H242" s="68" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="I242" s="70">
-        <v>25000</v>
+        <v>79233.899999999994</v>
       </c>
       <c r="J242" s="68" t="b">
         <v>1</v>
       </c>
       <c r="K242" s="68" t="s">
-        <v>60</v>
+        <v>211</v>
       </c>
       <c r="L242" s="68" t="s">
         <v>27</v>
       </c>
       <c r="M242" s="68" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="N242" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O242" s="69"/>
+        <v>216</v>
+      </c>
+      <c r="O242" s="68">
+        <v>3.4191121278143298E+46</v>
+      </c>
       <c r="P242" s="73" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q242" s="73" t="s">
-        <v>39</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="Q242" s="71"/>
       <c r="R242" s="64"/>
       <c r="S242" s="64"/>
       <c r="T242" s="64"/>
@@ -33716,503 +34350,493 @@
       <c r="AW242" s="65"/>
       <c r="AX242" s="65"/>
     </row>
-    <row r="243" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="76"/>
-      <c r="B243" s="77">
+    <row r="243" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="66"/>
+      <c r="B243" s="67">
         <v>46079</v>
       </c>
-      <c r="C243" s="77">
+      <c r="C243" s="67">
         <v>46100</v>
       </c>
-      <c r="D243" s="81"/>
-      <c r="E243" s="78" t="s">
-        <v>146</v>
-      </c>
-      <c r="F243" s="81"/>
-      <c r="G243" s="78" t="s">
-        <v>57</v>
-      </c>
-      <c r="H243" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="I243" s="80">
-        <v>42548.67</v>
-      </c>
-      <c r="J243" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K243" s="78" t="s">
-        <v>148</v>
-      </c>
-      <c r="L243" s="78" t="s">
+      <c r="D243" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E243" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="F243" s="69"/>
+      <c r="G243" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H243" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="I243" s="70">
+        <v>23000</v>
+      </c>
+      <c r="J243" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K243" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="L243" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="M243" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N243" s="78" t="s">
+      <c r="M243" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N243" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="O243" s="81"/>
-      <c r="P243" s="85" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q243" s="85" t="s">
+      <c r="O243" s="69"/>
+      <c r="P243" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q243" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="R243" s="83"/>
-      <c r="S243" s="83"/>
-      <c r="T243" s="83"/>
-      <c r="U243" s="83"/>
-      <c r="V243" s="83"/>
-      <c r="W243" s="83"/>
-      <c r="X243" s="83"/>
-      <c r="Y243" s="83"/>
-      <c r="Z243" s="84"/>
-      <c r="AA243" s="84"/>
-      <c r="AB243" s="84"/>
-      <c r="AC243" s="84"/>
-      <c r="AD243" s="84"/>
-      <c r="AE243" s="84"/>
-      <c r="AF243" s="84"/>
-      <c r="AG243" s="84"/>
-      <c r="AH243" s="84"/>
-      <c r="AI243" s="84"/>
-      <c r="AJ243" s="84"/>
-      <c r="AK243" s="84"/>
-      <c r="AL243" s="84"/>
-      <c r="AM243" s="84"/>
-      <c r="AN243" s="84"/>
-      <c r="AO243" s="84"/>
-      <c r="AP243" s="84"/>
-      <c r="AQ243" s="84"/>
-      <c r="AR243" s="84"/>
-      <c r="AS243" s="84"/>
-      <c r="AT243" s="84"/>
-      <c r="AU243" s="84"/>
-      <c r="AV243" s="84"/>
-      <c r="AW243" s="84"/>
-      <c r="AX243" s="84"/>
-    </row>
-    <row r="244" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="76"/>
-      <c r="B244" s="77">
+      <c r="R243" s="64"/>
+      <c r="S243" s="64"/>
+      <c r="T243" s="64"/>
+      <c r="U243" s="64"/>
+      <c r="V243" s="64"/>
+      <c r="W243" s="64"/>
+      <c r="X243" s="64"/>
+      <c r="Y243" s="64"/>
+      <c r="Z243" s="65"/>
+      <c r="AA243" s="65"/>
+      <c r="AB243" s="65"/>
+      <c r="AC243" s="65"/>
+      <c r="AD243" s="65"/>
+      <c r="AE243" s="65"/>
+      <c r="AF243" s="65"/>
+      <c r="AG243" s="65"/>
+      <c r="AH243" s="65"/>
+      <c r="AI243" s="65"/>
+      <c r="AJ243" s="65"/>
+      <c r="AK243" s="65"/>
+      <c r="AL243" s="65"/>
+      <c r="AM243" s="65"/>
+      <c r="AN243" s="65"/>
+      <c r="AO243" s="65"/>
+      <c r="AP243" s="65"/>
+      <c r="AQ243" s="65"/>
+      <c r="AR243" s="65"/>
+      <c r="AS243" s="65"/>
+      <c r="AT243" s="65"/>
+      <c r="AU243" s="65"/>
+      <c r="AV243" s="65"/>
+      <c r="AW243" s="65"/>
+      <c r="AX243" s="65"/>
+    </row>
+    <row r="244" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="66"/>
+      <c r="B244" s="67">
+        <v>46100</v>
+      </c>
+      <c r="C244" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D244" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E244" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F244" s="69"/>
+      <c r="G244" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H244" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I244" s="70">
+        <v>3250</v>
+      </c>
+      <c r="J244" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K244" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L244" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M244" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N244" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O244" s="68">
+        <v>11981370647</v>
+      </c>
+      <c r="P244" s="71"/>
+      <c r="Q244" s="71"/>
+      <c r="R244" s="65"/>
+      <c r="S244" s="65"/>
+      <c r="T244" s="65"/>
+      <c r="U244" s="65"/>
+      <c r="V244" s="65"/>
+      <c r="W244" s="65"/>
+      <c r="X244" s="65"/>
+      <c r="Y244" s="65"/>
+      <c r="Z244" s="65"/>
+      <c r="AA244" s="65"/>
+      <c r="AB244" s="65"/>
+      <c r="AC244" s="65"/>
+      <c r="AD244" s="65"/>
+      <c r="AE244" s="65"/>
+      <c r="AF244" s="65"/>
+      <c r="AG244" s="65"/>
+      <c r="AH244" s="65"/>
+      <c r="AI244" s="65"/>
+      <c r="AJ244" s="65"/>
+      <c r="AK244" s="65"/>
+      <c r="AL244" s="65"/>
+      <c r="AM244" s="65"/>
+      <c r="AN244" s="65"/>
+      <c r="AO244" s="65"/>
+      <c r="AP244" s="65"/>
+      <c r="AQ244" s="65"/>
+      <c r="AR244" s="65"/>
+      <c r="AS244" s="65"/>
+      <c r="AT244" s="65"/>
+      <c r="AU244" s="65"/>
+      <c r="AV244" s="65"/>
+      <c r="AW244" s="65"/>
+      <c r="AX244" s="65"/>
+    </row>
+    <row r="245" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="66"/>
+      <c r="B245" s="67">
+        <v>46101</v>
+      </c>
+      <c r="C245" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D245" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E245" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F245" s="69"/>
+      <c r="G245" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H245" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="I245" s="70">
+        <v>545.5</v>
+      </c>
+      <c r="J245" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K245" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L245" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M245" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N245" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O245" s="68">
+        <v>11981370647</v>
+      </c>
+      <c r="P245" s="71"/>
+      <c r="Q245" s="71"/>
+      <c r="R245" s="65"/>
+      <c r="S245" s="65"/>
+      <c r="T245" s="65"/>
+      <c r="U245" s="65"/>
+      <c r="V245" s="65"/>
+      <c r="W245" s="65"/>
+      <c r="X245" s="65"/>
+      <c r="Y245" s="65"/>
+      <c r="Z245" s="65"/>
+      <c r="AA245" s="65"/>
+      <c r="AB245" s="65"/>
+      <c r="AC245" s="65"/>
+      <c r="AD245" s="65"/>
+      <c r="AE245" s="65"/>
+      <c r="AF245" s="65"/>
+      <c r="AG245" s="65"/>
+      <c r="AH245" s="65"/>
+      <c r="AI245" s="65"/>
+      <c r="AJ245" s="65"/>
+      <c r="AK245" s="65"/>
+      <c r="AL245" s="65"/>
+      <c r="AM245" s="65"/>
+      <c r="AN245" s="65"/>
+      <c r="AO245" s="65"/>
+      <c r="AP245" s="65"/>
+      <c r="AQ245" s="65"/>
+      <c r="AR245" s="65"/>
+      <c r="AS245" s="65"/>
+      <c r="AT245" s="65"/>
+      <c r="AU245" s="65"/>
+      <c r="AV245" s="65"/>
+      <c r="AW245" s="65"/>
+      <c r="AX245" s="65"/>
+    </row>
+    <row r="246" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="66"/>
+      <c r="B246" s="67">
+        <v>46100</v>
+      </c>
+      <c r="C246" s="67">
+        <v>46101</v>
+      </c>
+      <c r="D246" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E246" s="68" t="s">
+        <v>409</v>
+      </c>
+      <c r="F246" s="69"/>
+      <c r="G246" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H246" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="I246" s="70">
+        <v>224.59</v>
+      </c>
+      <c r="J246" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K246" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="L246" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M246" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N246" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O246" s="68" t="s">
+        <v>410</v>
+      </c>
+      <c r="P246" s="71"/>
+      <c r="Q246" s="71"/>
+      <c r="R246" s="64"/>
+      <c r="S246" s="64"/>
+      <c r="T246" s="64"/>
+      <c r="U246" s="64"/>
+      <c r="V246" s="64"/>
+      <c r="W246" s="64"/>
+      <c r="X246" s="64"/>
+      <c r="Y246" s="64"/>
+      <c r="Z246" s="65"/>
+      <c r="AA246" s="65"/>
+      <c r="AB246" s="65"/>
+      <c r="AC246" s="65"/>
+      <c r="AD246" s="65"/>
+      <c r="AE246" s="65"/>
+      <c r="AF246" s="65"/>
+      <c r="AG246" s="65"/>
+      <c r="AH246" s="65"/>
+      <c r="AI246" s="65"/>
+      <c r="AJ246" s="65"/>
+      <c r="AK246" s="65"/>
+      <c r="AL246" s="65"/>
+      <c r="AM246" s="65"/>
+      <c r="AN246" s="65"/>
+      <c r="AO246" s="65"/>
+      <c r="AP246" s="65"/>
+      <c r="AQ246" s="65"/>
+      <c r="AR246" s="65"/>
+      <c r="AS246" s="65"/>
+      <c r="AT246" s="65"/>
+      <c r="AU246" s="65"/>
+      <c r="AV246" s="65"/>
+      <c r="AW246" s="65"/>
+      <c r="AX246" s="65"/>
+    </row>
+    <row r="247" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="66"/>
+      <c r="B247" s="67">
+        <v>46100</v>
+      </c>
+      <c r="C247" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D247" s="67">
+        <v>46101</v>
+      </c>
+      <c r="E247" s="68" t="s">
+        <v>411</v>
+      </c>
+      <c r="F247" s="69"/>
+      <c r="G247" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H247" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="I247" s="70">
+        <v>165.36</v>
+      </c>
+      <c r="J247" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K247" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="L247" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="M247" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N247" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="O247" s="68" t="s">
+        <v>412</v>
+      </c>
+      <c r="P247" s="71"/>
+      <c r="Q247" s="71"/>
+      <c r="R247" s="64"/>
+      <c r="S247" s="64"/>
+      <c r="T247" s="64"/>
+      <c r="U247" s="64"/>
+      <c r="V247" s="64"/>
+      <c r="W247" s="64"/>
+      <c r="X247" s="64"/>
+      <c r="Y247" s="64"/>
+      <c r="Z247" s="65"/>
+      <c r="AA247" s="65"/>
+      <c r="AB247" s="65"/>
+      <c r="AC247" s="65"/>
+      <c r="AD247" s="65"/>
+      <c r="AE247" s="65"/>
+      <c r="AF247" s="65"/>
+      <c r="AG247" s="65"/>
+      <c r="AH247" s="65"/>
+      <c r="AI247" s="65"/>
+      <c r="AJ247" s="65"/>
+      <c r="AK247" s="65"/>
+      <c r="AL247" s="65"/>
+      <c r="AM247" s="65"/>
+      <c r="AN247" s="65"/>
+      <c r="AO247" s="65"/>
+      <c r="AP247" s="65"/>
+      <c r="AQ247" s="65"/>
+      <c r="AR247" s="65"/>
+      <c r="AS247" s="65"/>
+      <c r="AT247" s="65"/>
+      <c r="AU247" s="65"/>
+      <c r="AV247" s="65"/>
+      <c r="AW247" s="65"/>
+      <c r="AX247" s="65"/>
+    </row>
+    <row r="248" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="66"/>
+      <c r="B248" s="67">
         <v>46079</v>
       </c>
-      <c r="C244" s="77">
+      <c r="C248" s="67">
+        <v>46100</v>
+      </c>
+      <c r="D248" s="67">
         <v>46101</v>
       </c>
-      <c r="D244" s="81"/>
-      <c r="E244" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F244" s="79">
-        <v>239304</v>
-      </c>
-      <c r="G244" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H244" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I244" s="80">
-        <v>50348.42</v>
-      </c>
-      <c r="J244" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K244" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L244" s="78" t="s">
+      <c r="E248" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="F248" s="69"/>
+      <c r="G248" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H248" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="I248" s="70">
+        <v>18000</v>
+      </c>
+      <c r="J248" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K248" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="L248" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="M244" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N244" s="78" t="s">
+      <c r="M248" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="N248" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="O244" s="81"/>
-      <c r="P244" s="82"/>
-      <c r="Q244" s="82"/>
-      <c r="R244" s="83"/>
-      <c r="S244" s="83"/>
-      <c r="T244" s="83"/>
-      <c r="U244" s="83"/>
-      <c r="V244" s="83"/>
-      <c r="W244" s="83"/>
-      <c r="X244" s="83"/>
-      <c r="Y244" s="83"/>
-      <c r="Z244" s="84"/>
-      <c r="AA244" s="84"/>
-      <c r="AB244" s="84"/>
-      <c r="AC244" s="84"/>
-      <c r="AD244" s="84"/>
-      <c r="AE244" s="84"/>
-      <c r="AF244" s="84"/>
-      <c r="AG244" s="84"/>
-      <c r="AH244" s="84"/>
-      <c r="AI244" s="84"/>
-      <c r="AJ244" s="84"/>
-      <c r="AK244" s="84"/>
-      <c r="AL244" s="84"/>
-      <c r="AM244" s="84"/>
-      <c r="AN244" s="84"/>
-      <c r="AO244" s="84"/>
-      <c r="AP244" s="84"/>
-      <c r="AQ244" s="84"/>
-      <c r="AR244" s="84"/>
-      <c r="AS244" s="84"/>
-      <c r="AT244" s="84"/>
-      <c r="AU244" s="84"/>
-      <c r="AV244" s="84"/>
-      <c r="AW244" s="84"/>
-      <c r="AX244" s="84"/>
-    </row>
-    <row r="245" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="76"/>
-      <c r="B245" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C245" s="77">
-        <v>46101</v>
-      </c>
-      <c r="D245" s="81"/>
-      <c r="E245" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F245" s="79">
-        <v>239298</v>
-      </c>
-      <c r="G245" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H245" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I245" s="80">
-        <v>68272.17</v>
-      </c>
-      <c r="J245" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K245" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L245" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M245" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N245" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O245" s="81"/>
-      <c r="P245" s="82"/>
-      <c r="Q245" s="82"/>
-      <c r="R245" s="83"/>
-      <c r="S245" s="83"/>
-      <c r="T245" s="83"/>
-      <c r="U245" s="83"/>
-      <c r="V245" s="83"/>
-      <c r="W245" s="83"/>
-      <c r="X245" s="83"/>
-      <c r="Y245" s="83"/>
-      <c r="Z245" s="84"/>
-      <c r="AA245" s="84"/>
-      <c r="AB245" s="84"/>
-      <c r="AC245" s="84"/>
-      <c r="AD245" s="84"/>
-      <c r="AE245" s="84"/>
-      <c r="AF245" s="84"/>
-      <c r="AG245" s="84"/>
-      <c r="AH245" s="84"/>
-      <c r="AI245" s="84"/>
-      <c r="AJ245" s="84"/>
-      <c r="AK245" s="84"/>
-      <c r="AL245" s="84"/>
-      <c r="AM245" s="84"/>
-      <c r="AN245" s="84"/>
-      <c r="AO245" s="84"/>
-      <c r="AP245" s="84"/>
-      <c r="AQ245" s="84"/>
-      <c r="AR245" s="84"/>
-      <c r="AS245" s="84"/>
-      <c r="AT245" s="84"/>
-      <c r="AU245" s="84"/>
-      <c r="AV245" s="84"/>
-      <c r="AW245" s="84"/>
-      <c r="AX245" s="84"/>
-    </row>
-    <row r="246" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="76"/>
-      <c r="B246" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C246" s="77">
-        <v>46101</v>
-      </c>
-      <c r="D246" s="81"/>
-      <c r="E246" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F246" s="79">
-        <v>239302</v>
-      </c>
-      <c r="G246" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H246" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I246" s="80">
-        <v>33965.33</v>
-      </c>
-      <c r="J246" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K246" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L246" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M246" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N246" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O246" s="81"/>
-      <c r="P246" s="82"/>
-      <c r="Q246" s="82"/>
-      <c r="R246" s="83"/>
-      <c r="S246" s="83"/>
-      <c r="T246" s="83"/>
-      <c r="U246" s="83"/>
-      <c r="V246" s="83"/>
-      <c r="W246" s="83"/>
-      <c r="X246" s="83"/>
-      <c r="Y246" s="83"/>
-      <c r="Z246" s="84"/>
-      <c r="AA246" s="84"/>
-      <c r="AB246" s="84"/>
-      <c r="AC246" s="84"/>
-      <c r="AD246" s="84"/>
-      <c r="AE246" s="84"/>
-      <c r="AF246" s="84"/>
-      <c r="AG246" s="84"/>
-      <c r="AH246" s="84"/>
-      <c r="AI246" s="84"/>
-      <c r="AJ246" s="84"/>
-      <c r="AK246" s="84"/>
-      <c r="AL246" s="84"/>
-      <c r="AM246" s="84"/>
-      <c r="AN246" s="84"/>
-      <c r="AO246" s="84"/>
-      <c r="AP246" s="84"/>
-      <c r="AQ246" s="84"/>
-      <c r="AR246" s="84"/>
-      <c r="AS246" s="84"/>
-      <c r="AT246" s="84"/>
-      <c r="AU246" s="84"/>
-      <c r="AV246" s="84"/>
-      <c r="AW246" s="84"/>
-      <c r="AX246" s="84"/>
-    </row>
-    <row r="247" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="76"/>
-      <c r="B247" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C247" s="77">
-        <v>46101</v>
-      </c>
-      <c r="D247" s="81"/>
-      <c r="E247" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F247" s="79">
-        <v>239277</v>
-      </c>
-      <c r="G247" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H247" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I247" s="80">
-        <v>59591.360000000001</v>
-      </c>
-      <c r="J247" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K247" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L247" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M247" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N247" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O247" s="81"/>
-      <c r="P247" s="82"/>
-      <c r="Q247" s="82"/>
-      <c r="R247" s="83"/>
-      <c r="S247" s="83"/>
-      <c r="T247" s="83"/>
-      <c r="U247" s="83"/>
-      <c r="V247" s="83"/>
-      <c r="W247" s="83"/>
-      <c r="X247" s="83"/>
-      <c r="Y247" s="83"/>
-      <c r="Z247" s="84"/>
-      <c r="AA247" s="84"/>
-      <c r="AB247" s="84"/>
-      <c r="AC247" s="84"/>
-      <c r="AD247" s="84"/>
-      <c r="AE247" s="84"/>
-      <c r="AF247" s="84"/>
-      <c r="AG247" s="84"/>
-      <c r="AH247" s="84"/>
-      <c r="AI247" s="84"/>
-      <c r="AJ247" s="84"/>
-      <c r="AK247" s="84"/>
-      <c r="AL247" s="84"/>
-      <c r="AM247" s="84"/>
-      <c r="AN247" s="84"/>
-      <c r="AO247" s="84"/>
-      <c r="AP247" s="84"/>
-      <c r="AQ247" s="84"/>
-      <c r="AR247" s="84"/>
-      <c r="AS247" s="84"/>
-      <c r="AT247" s="84"/>
-      <c r="AU247" s="84"/>
-      <c r="AV247" s="84"/>
-      <c r="AW247" s="84"/>
-      <c r="AX247" s="84"/>
-    </row>
-    <row r="248" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="76"/>
-      <c r="B248" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C248" s="77">
-        <v>46101</v>
-      </c>
-      <c r="D248" s="81"/>
-      <c r="E248" s="78" t="s">
-        <v>66</v>
-      </c>
-      <c r="F248" s="79">
-        <v>455202</v>
-      </c>
-      <c r="G248" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H248" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I248" s="80">
-        <v>8400</v>
-      </c>
-      <c r="J248" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K248" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L248" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M248" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N248" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O248" s="81"/>
-      <c r="P248" s="82"/>
-      <c r="Q248" s="82"/>
-      <c r="R248" s="83"/>
-      <c r="S248" s="83"/>
-      <c r="T248" s="83"/>
-      <c r="U248" s="83"/>
-      <c r="V248" s="83"/>
-      <c r="W248" s="83"/>
-      <c r="X248" s="83"/>
-      <c r="Y248" s="83"/>
-      <c r="Z248" s="84"/>
-      <c r="AA248" s="84"/>
-      <c r="AB248" s="84"/>
-      <c r="AC248" s="84"/>
-      <c r="AD248" s="84"/>
-      <c r="AE248" s="84"/>
-      <c r="AF248" s="84"/>
-      <c r="AG248" s="84"/>
-      <c r="AH248" s="84"/>
-      <c r="AI248" s="84"/>
-      <c r="AJ248" s="84"/>
-      <c r="AK248" s="84"/>
-      <c r="AL248" s="84"/>
-      <c r="AM248" s="84"/>
-      <c r="AN248" s="84"/>
-      <c r="AO248" s="84"/>
-      <c r="AP248" s="84"/>
-      <c r="AQ248" s="84"/>
-      <c r="AR248" s="84"/>
-      <c r="AS248" s="84"/>
-      <c r="AT248" s="84"/>
-      <c r="AU248" s="84"/>
-      <c r="AV248" s="84"/>
-      <c r="AW248" s="84"/>
-      <c r="AX248" s="84"/>
-    </row>
-    <row r="249" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O248" s="69"/>
+      <c r="P248" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q248" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="R248" s="64"/>
+      <c r="S248" s="64"/>
+      <c r="T248" s="64"/>
+      <c r="U248" s="64"/>
+      <c r="V248" s="64"/>
+      <c r="W248" s="64"/>
+      <c r="X248" s="64"/>
+      <c r="Y248" s="64"/>
+      <c r="Z248" s="65"/>
+      <c r="AA248" s="65"/>
+      <c r="AB248" s="65"/>
+      <c r="AC248" s="65"/>
+      <c r="AD248" s="65"/>
+      <c r="AE248" s="65"/>
+      <c r="AF248" s="65"/>
+      <c r="AG248" s="65"/>
+      <c r="AH248" s="65"/>
+      <c r="AI248" s="65"/>
+      <c r="AJ248" s="65"/>
+      <c r="AK248" s="65"/>
+      <c r="AL248" s="65"/>
+      <c r="AM248" s="65"/>
+      <c r="AN248" s="65"/>
+      <c r="AO248" s="65"/>
+      <c r="AP248" s="65"/>
+      <c r="AQ248" s="65"/>
+      <c r="AR248" s="65"/>
+      <c r="AS248" s="65"/>
+      <c r="AT248" s="65"/>
+      <c r="AU248" s="65"/>
+      <c r="AV248" s="65"/>
+      <c r="AW248" s="65"/>
+      <c r="AX248" s="65"/>
+    </row>
+    <row r="249" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="76"/>
-      <c r="B249" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C249" s="77">
-        <v>46101</v>
-      </c>
+      <c r="B249" s="77"/>
+      <c r="C249" s="77"/>
       <c r="D249" s="81"/>
-      <c r="E249" s="78" t="s">
-        <v>173</v>
-      </c>
-      <c r="F249" s="79">
-        <v>132239</v>
-      </c>
-      <c r="G249" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H249" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="I249" s="80">
-        <v>4556</v>
-      </c>
-      <c r="J249" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K249" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L249" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M249" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N249" s="78" t="s">
-        <v>23</v>
-      </c>
+      <c r="E249" s="78"/>
+      <c r="F249" s="79"/>
+      <c r="G249" s="78"/>
+      <c r="H249" s="78"/>
+      <c r="I249" s="80"/>
+      <c r="J249" s="78"/>
+      <c r="K249" s="78"/>
+      <c r="L249" s="78"/>
+      <c r="M249" s="78"/>
+      <c r="N249" s="78"/>
       <c r="O249" s="81"/>
       <c r="P249" s="82"/>
       <c r="Q249" s="82"/>
@@ -34250,45 +34874,21 @@
       <c r="AW249" s="84"/>
       <c r="AX249" s="84"/>
     </row>
-    <row r="250" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="76"/>
-      <c r="B250" s="77">
-        <v>46079</v>
-      </c>
-      <c r="C250" s="77">
-        <v>46101</v>
-      </c>
+      <c r="B250" s="77"/>
+      <c r="C250" s="77"/>
       <c r="D250" s="81"/>
-      <c r="E250" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="F250" s="79">
-        <v>264292</v>
-      </c>
-      <c r="G250" s="78" t="s">
-        <v>52</v>
-      </c>
-      <c r="H250" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="I250" s="80">
-        <v>208.77</v>
-      </c>
-      <c r="J250" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K250" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L250" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M250" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N250" s="78" t="s">
-        <v>23</v>
-      </c>
+      <c r="E250" s="78"/>
+      <c r="F250" s="79"/>
+      <c r="G250" s="78"/>
+      <c r="H250" s="78"/>
+      <c r="I250" s="80"/>
+      <c r="J250" s="78"/>
+      <c r="K250" s="78"/>
+      <c r="L250" s="78"/>
+      <c r="M250" s="78"/>
+      <c r="N250" s="78"/>
       <c r="O250" s="81"/>
       <c r="P250" s="82"/>
       <c r="Q250" s="82"/>
@@ -34326,45 +34926,21 @@
       <c r="AW250" s="84"/>
       <c r="AX250" s="84"/>
     </row>
-    <row r="251" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="76"/>
-      <c r="B251" s="77">
-        <v>46093</v>
-      </c>
-      <c r="C251" s="77">
-        <v>46101</v>
-      </c>
+      <c r="B251" s="77"/>
+      <c r="C251" s="77"/>
       <c r="D251" s="81"/>
-      <c r="E251" s="78" t="s">
-        <v>174</v>
-      </c>
-      <c r="F251" s="79">
-        <v>10550</v>
-      </c>
-      <c r="G251" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H251" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="I251" s="80">
-        <v>15396</v>
-      </c>
-      <c r="J251" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K251" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L251" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M251" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N251" s="78" t="s">
-        <v>23</v>
-      </c>
+      <c r="E251" s="78"/>
+      <c r="F251" s="79"/>
+      <c r="G251" s="78"/>
+      <c r="H251" s="78"/>
+      <c r="I251" s="80"/>
+      <c r="J251" s="78"/>
+      <c r="K251" s="78"/>
+      <c r="L251" s="78"/>
+      <c r="M251" s="78"/>
+      <c r="N251" s="78"/>
       <c r="O251" s="81"/>
       <c r="P251" s="82"/>
       <c r="Q251" s="82"/>
@@ -34402,45 +34978,21 @@
       <c r="AW251" s="84"/>
       <c r="AX251" s="84"/>
     </row>
-    <row r="252" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="76"/>
-      <c r="B252" s="77">
-        <v>46093</v>
-      </c>
-      <c r="C252" s="77">
-        <v>46101</v>
-      </c>
+      <c r="B252" s="77"/>
+      <c r="C252" s="77"/>
       <c r="D252" s="81"/>
-      <c r="E252" s="78" t="s">
-        <v>101</v>
-      </c>
-      <c r="F252" s="79">
-        <v>8060</v>
-      </c>
-      <c r="G252" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H252" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I252" s="80">
-        <v>53488.32</v>
-      </c>
-      <c r="J252" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K252" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L252" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M252" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N252" s="78" t="s">
-        <v>23</v>
-      </c>
+      <c r="E252" s="78"/>
+      <c r="F252" s="79"/>
+      <c r="G252" s="78"/>
+      <c r="H252" s="78"/>
+      <c r="I252" s="80"/>
+      <c r="J252" s="78"/>
+      <c r="K252" s="78"/>
+      <c r="L252" s="78"/>
+      <c r="M252" s="78"/>
+      <c r="N252" s="78"/>
       <c r="O252" s="81"/>
       <c r="P252" s="82"/>
       <c r="Q252" s="82"/>
@@ -34478,45 +35030,21 @@
       <c r="AW252" s="84"/>
       <c r="AX252" s="84"/>
     </row>
-    <row r="253" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="76"/>
-      <c r="B253" s="77">
-        <v>46093</v>
-      </c>
-      <c r="C253" s="77">
-        <v>46101</v>
-      </c>
+      <c r="B253" s="77"/>
+      <c r="C253" s="77"/>
       <c r="D253" s="81"/>
-      <c r="E253" s="78" t="s">
-        <v>72</v>
-      </c>
-      <c r="F253" s="79">
-        <v>123589</v>
-      </c>
-      <c r="G253" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H253" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="I253" s="80">
-        <v>26875.16</v>
-      </c>
-      <c r="J253" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K253" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L253" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M253" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N253" s="78" t="s">
-        <v>23</v>
-      </c>
+      <c r="E253" s="78"/>
+      <c r="F253" s="79"/>
+      <c r="G253" s="78"/>
+      <c r="H253" s="78"/>
+      <c r="I253" s="80"/>
+      <c r="J253" s="78"/>
+      <c r="K253" s="78"/>
+      <c r="L253" s="78"/>
+      <c r="M253" s="78"/>
+      <c r="N253" s="78"/>
       <c r="O253" s="81"/>
       <c r="P253" s="82"/>
       <c r="Q253" s="82"/>
@@ -34554,45 +35082,21 @@
       <c r="AW253" s="84"/>
       <c r="AX253" s="84"/>
     </row>
-    <row r="254" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="76"/>
-      <c r="B254" s="77">
-        <v>46093</v>
-      </c>
-      <c r="C254" s="77">
-        <v>46101</v>
-      </c>
+      <c r="B254" s="77"/>
+      <c r="C254" s="77"/>
       <c r="D254" s="81"/>
-      <c r="E254" s="78" t="s">
-        <v>72</v>
-      </c>
-      <c r="F254" s="79">
-        <v>123587</v>
-      </c>
-      <c r="G254" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="H254" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="I254" s="80">
-        <v>26875.16</v>
-      </c>
-      <c r="J254" s="78" t="b">
-        <v>1</v>
-      </c>
-      <c r="K254" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="L254" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M254" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="N254" s="78" t="s">
-        <v>23</v>
-      </c>
+      <c r="E254" s="78"/>
+      <c r="F254" s="79"/>
+      <c r="G254" s="78"/>
+      <c r="H254" s="78"/>
+      <c r="I254" s="80"/>
+      <c r="J254" s="78"/>
+      <c r="K254" s="78"/>
+      <c r="L254" s="78"/>
+      <c r="M254" s="78"/>
+      <c r="N254" s="78"/>
       <c r="O254" s="81"/>
       <c r="P254" s="82"/>
       <c r="Q254" s="82"/>
@@ -34630,49 +35134,23 @@
       <c r="AW254" s="84"/>
       <c r="AX254" s="84"/>
     </row>
-    <row r="255" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="66"/>
-      <c r="B255" s="67">
-        <v>46093</v>
-      </c>
-      <c r="C255" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B255" s="67"/>
+      <c r="C255" s="67"/>
       <c r="D255" s="69"/>
-      <c r="E255" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="F255" s="75">
-        <v>239278</v>
-      </c>
-      <c r="G255" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="H255" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="I255" s="70">
-        <v>1784.35</v>
-      </c>
-      <c r="J255" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K255" s="68" t="s">
-        <v>26</v>
-      </c>
-      <c r="L255" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M255" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N255" s="68" t="s">
-        <v>28</v>
-      </c>
+      <c r="E255" s="68"/>
+      <c r="F255" s="75"/>
+      <c r="G255" s="68"/>
+      <c r="H255" s="68"/>
+      <c r="I255" s="70"/>
+      <c r="J255" s="68"/>
+      <c r="K255" s="68"/>
+      <c r="L255" s="68"/>
+      <c r="M255" s="68"/>
+      <c r="N255" s="68"/>
       <c r="O255" s="69"/>
-      <c r="P255" s="73" t="s">
-        <v>175</v>
-      </c>
+      <c r="P255" s="73"/>
       <c r="Q255" s="71"/>
       <c r="R255" s="64"/>
       <c r="S255" s="64"/>
@@ -34708,49 +35186,23 @@
       <c r="AW255" s="65"/>
       <c r="AX255" s="65"/>
     </row>
-    <row r="256" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="66"/>
-      <c r="B256" s="67">
-        <v>46093</v>
-      </c>
-      <c r="C256" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B256" s="67"/>
+      <c r="C256" s="67"/>
       <c r="D256" s="69"/>
-      <c r="E256" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="F256" s="75" t="s">
-        <v>176</v>
-      </c>
-      <c r="G256" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="H256" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="I256" s="70">
-        <v>15549.89</v>
-      </c>
-      <c r="J256" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K256" s="68" t="s">
-        <v>26</v>
-      </c>
-      <c r="L256" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M256" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N256" s="68" t="s">
-        <v>28</v>
-      </c>
+      <c r="E256" s="68"/>
+      <c r="F256" s="75"/>
+      <c r="G256" s="68"/>
+      <c r="H256" s="68"/>
+      <c r="I256" s="70"/>
+      <c r="J256" s="68"/>
+      <c r="K256" s="68"/>
+      <c r="L256" s="68"/>
+      <c r="M256" s="68"/>
+      <c r="N256" s="68"/>
       <c r="O256" s="69"/>
-      <c r="P256" s="73" t="s">
-        <v>175</v>
-      </c>
+      <c r="P256" s="73"/>
       <c r="Q256" s="71"/>
       <c r="R256" s="64"/>
       <c r="S256" s="64"/>
@@ -34786,49 +35238,23 @@
       <c r="AW256" s="65"/>
       <c r="AX256" s="65"/>
     </row>
-    <row r="257" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="66"/>
-      <c r="B257" s="67">
-        <v>46094</v>
-      </c>
-      <c r="C257" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B257" s="67"/>
+      <c r="C257" s="67"/>
       <c r="D257" s="69"/>
-      <c r="E257" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="F257" s="75">
-        <v>308438</v>
-      </c>
-      <c r="G257" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="H257" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="I257" s="70">
-        <v>79233.899999999994</v>
-      </c>
-      <c r="J257" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K257" s="68" t="s">
-        <v>211</v>
-      </c>
-      <c r="L257" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M257" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N257" s="68" t="s">
-        <v>28</v>
-      </c>
+      <c r="E257" s="68"/>
+      <c r="F257" s="75"/>
+      <c r="G257" s="68"/>
+      <c r="H257" s="68"/>
+      <c r="I257" s="70"/>
+      <c r="J257" s="68"/>
+      <c r="K257" s="68"/>
+      <c r="L257" s="68"/>
+      <c r="M257" s="68"/>
+      <c r="N257" s="68"/>
       <c r="O257" s="69"/>
-      <c r="P257" s="73" t="s">
-        <v>389</v>
-      </c>
+      <c r="P257" s="73"/>
       <c r="Q257" s="71"/>
       <c r="R257" s="64"/>
       <c r="S257" s="64"/>
@@ -34864,48 +35290,24 @@
       <c r="AW257" s="65"/>
       <c r="AX257" s="65"/>
     </row>
-    <row r="258" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="66"/>
-      <c r="B258" s="67">
-        <v>46079</v>
-      </c>
-      <c r="C258" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B258" s="67"/>
+      <c r="C258" s="67"/>
       <c r="D258" s="69"/>
-      <c r="E258" s="68" t="s">
-        <v>177</v>
-      </c>
+      <c r="E258" s="68"/>
       <c r="F258" s="69"/>
-      <c r="G258" s="68" t="s">
-        <v>36</v>
-      </c>
-      <c r="H258" s="68" t="s">
-        <v>49</v>
-      </c>
-      <c r="I258" s="70">
-        <v>5000</v>
-      </c>
-      <c r="J258" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K258" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="L258" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M258" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N258" s="68" t="s">
-        <v>28</v>
-      </c>
+      <c r="G258" s="68"/>
+      <c r="H258" s="68"/>
+      <c r="I258" s="70"/>
+      <c r="J258" s="68"/>
+      <c r="K258" s="68"/>
+      <c r="L258" s="68"/>
+      <c r="M258" s="68"/>
+      <c r="N258" s="68"/>
       <c r="O258" s="69"/>
       <c r="P258" s="71"/>
-      <c r="Q258" s="73" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q258" s="73"/>
       <c r="R258" s="64"/>
       <c r="S258" s="64"/>
       <c r="T258" s="64"/>
@@ -34940,50 +35342,24 @@
       <c r="AW258" s="65"/>
       <c r="AX258" s="65"/>
     </row>
-    <row r="259" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="66"/>
-      <c r="B259" s="67">
-        <v>46079</v>
-      </c>
-      <c r="C259" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B259" s="67"/>
+      <c r="C259" s="67"/>
       <c r="D259" s="69"/>
-      <c r="E259" s="68" t="s">
-        <v>73</v>
-      </c>
+      <c r="E259" s="68"/>
       <c r="F259" s="69"/>
-      <c r="G259" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="H259" s="68" t="s">
-        <v>53</v>
-      </c>
-      <c r="I259" s="70">
-        <v>8000</v>
-      </c>
-      <c r="J259" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K259" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="L259" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M259" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N259" s="68" t="s">
-        <v>28</v>
-      </c>
+      <c r="G259" s="68"/>
+      <c r="H259" s="68"/>
+      <c r="I259" s="70"/>
+      <c r="J259" s="68"/>
+      <c r="K259" s="68"/>
+      <c r="L259" s="68"/>
+      <c r="M259" s="68"/>
+      <c r="N259" s="68"/>
       <c r="O259" s="69"/>
-      <c r="P259" s="73" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q259" s="73" t="s">
-        <v>39</v>
-      </c>
+      <c r="P259" s="73"/>
+      <c r="Q259" s="73"/>
       <c r="R259" s="64"/>
       <c r="S259" s="64"/>
       <c r="T259" s="64"/>
@@ -35018,46 +35394,22 @@
       <c r="AW259" s="65"/>
       <c r="AX259" s="65"/>
     </row>
-    <row r="260" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="66"/>
-      <c r="B260" s="67">
-        <v>46092</v>
-      </c>
-      <c r="C260" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B260" s="67"/>
+      <c r="C260" s="67"/>
       <c r="D260" s="69"/>
-      <c r="E260" s="68" t="s">
-        <v>179</v>
-      </c>
+      <c r="E260" s="68"/>
       <c r="F260" s="69"/>
-      <c r="G260" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="H260" s="68" t="s">
-        <v>180</v>
-      </c>
-      <c r="I260" s="70">
-        <v>146.75</v>
-      </c>
-      <c r="J260" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K260" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="L260" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M260" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N260" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O260" s="68" t="s">
-        <v>181</v>
-      </c>
+      <c r="G260" s="68"/>
+      <c r="H260" s="68"/>
+      <c r="I260" s="70"/>
+      <c r="J260" s="68"/>
+      <c r="K260" s="68"/>
+      <c r="L260" s="68"/>
+      <c r="M260" s="68"/>
+      <c r="N260" s="68"/>
+      <c r="O260" s="68"/>
       <c r="P260" s="71"/>
       <c r="Q260" s="71"/>
       <c r="R260" s="64"/>
@@ -35094,49 +35446,23 @@
       <c r="AW260" s="65"/>
       <c r="AX260" s="65"/>
     </row>
-    <row r="261" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="66"/>
-      <c r="B261" s="67">
-        <v>46084</v>
-      </c>
-      <c r="C261" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B261" s="67"/>
+      <c r="C261" s="67"/>
       <c r="D261" s="69"/>
-      <c r="E261" s="68" t="s">
-        <v>182</v>
-      </c>
+      <c r="E261" s="68"/>
       <c r="F261" s="69"/>
-      <c r="G261" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="H261" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="I261" s="70">
-        <v>22800</v>
-      </c>
-      <c r="J261" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K261" s="68" t="s">
-        <v>26</v>
-      </c>
-      <c r="L261" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M261" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N261" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O261" s="68" t="s">
-        <v>94</v>
-      </c>
-      <c r="P261" s="73" t="s">
-        <v>183</v>
-      </c>
+      <c r="G261" s="68"/>
+      <c r="H261" s="68"/>
+      <c r="I261" s="70"/>
+      <c r="J261" s="68"/>
+      <c r="K261" s="68"/>
+      <c r="L261" s="68"/>
+      <c r="M261" s="68"/>
+      <c r="N261" s="68"/>
+      <c r="O261" s="68"/>
+      <c r="P261" s="73"/>
       <c r="Q261" s="71"/>
       <c r="R261" s="64"/>
       <c r="S261" s="64"/>
@@ -35172,49 +35498,23 @@
       <c r="AW261" s="65"/>
       <c r="AX261" s="65"/>
     </row>
-    <row r="262" spans="1:50" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:50" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="66"/>
-      <c r="B262" s="67">
-        <v>46071</v>
-      </c>
-      <c r="C262" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B262" s="67"/>
+      <c r="C262" s="67"/>
       <c r="D262" s="69"/>
-      <c r="E262" s="68" t="s">
-        <v>184</v>
-      </c>
+      <c r="E262" s="68"/>
       <c r="F262" s="69"/>
-      <c r="G262" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="H262" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="I262" s="70">
-        <v>88344</v>
-      </c>
-      <c r="J262" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K262" s="68" t="s">
-        <v>26</v>
-      </c>
-      <c r="L262" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M262" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N262" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O262" s="68" t="s">
-        <v>185</v>
-      </c>
-      <c r="P262" s="73" t="s">
-        <v>175</v>
-      </c>
+      <c r="G262" s="68"/>
+      <c r="H262" s="68"/>
+      <c r="I262" s="70"/>
+      <c r="J262" s="68"/>
+      <c r="K262" s="68"/>
+      <c r="L262" s="68"/>
+      <c r="M262" s="68"/>
+      <c r="N262" s="68"/>
+      <c r="O262" s="68"/>
+      <c r="P262" s="73"/>
       <c r="Q262" s="71"/>
       <c r="R262" s="64"/>
       <c r="S262" s="64"/>
@@ -35250,43 +35550,21 @@
       <c r="AW262" s="65"/>
       <c r="AX262" s="65"/>
     </row>
-    <row r="263" spans="1:50" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="66"/>
-      <c r="B263" s="67">
-        <v>46079</v>
-      </c>
-      <c r="C263" s="67">
-        <v>46101</v>
-      </c>
+      <c r="B263" s="67"/>
+      <c r="C263" s="67"/>
       <c r="D263" s="69"/>
-      <c r="E263" s="68" t="s">
-        <v>94</v>
-      </c>
+      <c r="E263" s="68"/>
       <c r="F263" s="69"/>
-      <c r="G263" s="68" t="s">
-        <v>33</v>
-      </c>
-      <c r="H263" s="68" t="s">
-        <v>33</v>
-      </c>
-      <c r="I263" s="70">
-        <v>20000</v>
-      </c>
-      <c r="J263" s="68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K263" s="68" t="s">
-        <v>95</v>
-      </c>
-      <c r="L263" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="M263" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N263" s="68" t="s">
-        <v>28</v>
-      </c>
+      <c r="G263" s="68"/>
+      <c r="H263" s="68"/>
+      <c r="I263" s="70"/>
+      <c r="J263" s="68"/>
+      <c r="K263" s="68"/>
+      <c r="L263" s="68"/>
+      <c r="M263" s="68"/>
+      <c r="N263" s="68"/>
       <c r="O263" s="69"/>
       <c r="P263" s="71"/>
       <c r="Q263" s="71"/>
@@ -35326,9 +35604,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="O12" r:id="rId1" display="mailto:tiagodanielrx@hotmail.com" xr:uid="{95A20793-BC46-4B42-B3C7-758F00BF2F17}"/>
-    <hyperlink ref="O95" r:id="rId2" display="mailto:eulergrs@gmail.com" xr:uid="{74CFD429-94C3-47BA-AFA6-37568994B4B3}"/>
+    <hyperlink ref="O12" r:id="rId1" display="mailto:tiagodanielrx@hotmail.com" xr:uid="{D01F70E5-20CC-4DEE-A35B-3D49062CE853}"/>
+    <hyperlink ref="O95" r:id="rId2" display="mailto:eulergrs@gmail.com" xr:uid="{E37379CD-09F2-46A2-A54F-BE16E1BD7763}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>